--- a/data/hachioji_kousei_yakkyoku.xlsx
+++ b/data/hachioji_kousei_yakkyoku.xlsx
@@ -16,8 +16,15 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="1">
-    <numFmt numFmtId="164" formatCode="yyyy-mm-dd h:mm:ss"/>
+  <numFmts count="8">
+    <numFmt numFmtId="164" formatCode="0000000"/>
+    <numFmt numFmtId="165" formatCode="[$-411]ggge&quot;年&quot;m&quot;月&quot;d&quot;日&quot;;@"/>
+    <numFmt numFmtId="166" formatCode="0;[Red]0"/>
+    <numFmt numFmtId="167" formatCode="yyyy-mm-dd h:mm:ss"/>
+    <numFmt numFmtId="168" formatCode="[&lt;=999]000;000\-0000"/>
+    <numFmt numFmtId="169" formatCode="0_);[Red]\(0\)"/>
+    <numFmt numFmtId="170" formatCode="[&lt;=999]000;[&lt;=9999]000\-00;000\-0000"/>
+    <numFmt numFmtId="171" formatCode="[$]ggge&quot;年&quot;m&quot;月&quot;d&quot;日&quot;;@"/>
   </numFmts>
   <fonts count="1">
     <font>
@@ -48,9 +55,16 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="9">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="166" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="168" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="169" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="170" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="171" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -420,16 +434,25 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>指定自立支援医療機関（育成・更生医療）指定一覧【薬局】（令和8年6月1日現在）</t>
         </is>
       </c>
+      <c r="D1" s="2" t="n"/>
+      <c r="E1" s="2" t="n"/>
+      <c r="F1" s="2" t="n"/>
+      <c r="G1" s="2" t="n"/>
       <c r="Q1" t="inlineStr">
         <is>
           <t>変更届（　、～平成年月日）</t>
         </is>
       </c>
+      <c r="R1" s="3" t="n"/>
+      <c r="S1" s="3" t="n"/>
+      <c r="X1" s="1" t="n"/>
+      <c r="AA1" s="1" t="n"/>
+      <c r="AB1" s="1" t="n"/>
       <c r="AC1" t="inlineStr">
         <is>
           <t>【R5.7.1分まで】
@@ -450,7 +473,7 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" t="inlineStr">
+      <c r="A2" s="1" t="inlineStr">
         <is>
           <t>61</t>
         </is>
@@ -478,17 +501,17 @@
           <t>薬剤師</t>
         </is>
       </c>
-      <c r="Q2" t="inlineStr">
+      <c r="Q2" s="1" t="inlineStr">
         <is>
           <t>薬剤師の変更（直近）</t>
         </is>
       </c>
-      <c r="R2" t="inlineStr">
+      <c r="R2" s="3" t="inlineStr">
         <is>
           <t>申請年月日</t>
         </is>
       </c>
-      <c r="S2" t="inlineStr">
+      <c r="S2" s="3" t="inlineStr">
         <is>
           <t>指定年月日</t>
         </is>
@@ -513,7 +536,7 @@
           <t>文書番号</t>
         </is>
       </c>
-      <c r="X2" t="inlineStr">
+      <c r="X2" s="1" t="inlineStr">
         <is>
           <t>医療種別</t>
         </is>
@@ -528,12 +551,12 @@
           <t>更生医療</t>
         </is>
       </c>
-      <c r="AA2" t="inlineStr">
+      <c r="AA2" s="1" t="inlineStr">
         <is>
           <t>指定年月</t>
         </is>
       </c>
-      <c r="AB2" t="inlineStr">
+      <c r="AB2" s="1" t="inlineStr">
         <is>
           <t xml:space="preserve">廃止・
 辞退・
@@ -588,22 +611,22 @@
       </c>
     </row>
     <row r="3">
-      <c r="D3" t="inlineStr">
+      <c r="D3" s="2" t="inlineStr">
         <is>
           <t>コード</t>
         </is>
       </c>
-      <c r="E3" t="inlineStr">
+      <c r="E3" s="2" t="inlineStr">
         <is>
           <t>コード桁数</t>
         </is>
       </c>
-      <c r="F3" t="inlineStr">
+      <c r="F3" s="2" t="inlineStr">
         <is>
           <t>都13/薬局4</t>
         </is>
       </c>
-      <c r="G3" t="inlineStr">
+      <c r="G3" s="2" t="inlineStr">
         <is>
           <t>重複</t>
         </is>
@@ -618,7 +641,7 @@
           <t>郵便番号</t>
         </is>
       </c>
-      <c r="J3" t="inlineStr">
+      <c r="J3" s="1" t="inlineStr">
         <is>
           <t>区市町村名</t>
         </is>
@@ -648,30 +671,31 @@
           <t>所　在　地</t>
         </is>
       </c>
-      <c r="S3" t="inlineStr">
+      <c r="S3" s="3" t="inlineStr">
         <is>
           <t>（みなし指定）</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" t="inlineStr">
+      <c r="A4" s="1" t="inlineStr">
         <is>
           <t>2-1</t>
         </is>
       </c>
-      <c r="D4" t="n">
+      <c r="C4" s="1" t="n"/>
+      <c r="D4" s="2" t="n">
         <v>2955607</v>
       </c>
       <c r="E4" t="n">
         <v>7</v>
       </c>
-      <c r="F4" t="inlineStr">
+      <c r="F4" s="4" t="inlineStr">
         <is>
           <t>1342955607</t>
         </is>
       </c>
-      <c r="G4" t="inlineStr">
+      <c r="G4" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">　</t>
         </is>
@@ -686,12 +710,12 @@
           <t>193-0835</t>
         </is>
       </c>
-      <c r="J4" t="inlineStr">
+      <c r="J4" s="1" t="inlineStr">
         <is>
           <t>24八王子市</t>
         </is>
       </c>
-      <c r="K4" t="inlineStr">
+      <c r="K4" s="1" t="inlineStr">
         <is>
           <t>八王子市千人町２－１９－１９</t>
         </is>
@@ -711,7 +735,7 @@
           <t>174-0043</t>
         </is>
       </c>
-      <c r="O4" t="inlineStr">
+      <c r="O4" s="1" t="inlineStr">
         <is>
           <t>東京都板橋区坂下２－３２－２３</t>
         </is>
@@ -726,16 +750,16 @@
           <t>変更届（茂木　毅　～令和4年6月30日）</t>
         </is>
       </c>
-      <c r="R4" s="1" t="n">
+      <c r="R4" s="3" t="n">
         <v>39160</v>
       </c>
       <c r="S4" t="n">
         <v>39234</v>
       </c>
-      <c r="T4" s="1" t="n">
+      <c r="T4" s="3" t="n">
         <v>39234</v>
       </c>
-      <c r="U4" t="inlineStr">
+      <c r="U4" s="1" t="inlineStr">
         <is>
           <t>19福保障計第209号</t>
         </is>
@@ -748,7 +772,7 @@
           <t>6八福障第6793号</t>
         </is>
       </c>
-      <c r="X4" t="inlineStr">
+      <c r="X4" s="1" t="inlineStr">
         <is>
           <t>育成医療・更生医療</t>
         </is>
@@ -774,7 +798,7 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" t="inlineStr">
+      <c r="A5" s="1" t="inlineStr">
         <is>
           <t>2-2</t>
         </is>
@@ -784,18 +808,18 @@
           <t>○</t>
         </is>
       </c>
-      <c r="D5" t="n">
+      <c r="D5" s="2" t="n">
         <v>2951184</v>
       </c>
       <c r="E5" t="n">
         <v>7</v>
       </c>
-      <c r="F5" t="inlineStr">
+      <c r="F5" s="4" t="inlineStr">
         <is>
           <t>1342951184</t>
         </is>
       </c>
-      <c r="G5" t="inlineStr">
+      <c r="G5" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">　</t>
         </is>
@@ -810,7 +834,7 @@
           <t>193-0844</t>
         </is>
       </c>
-      <c r="J5" t="inlineStr">
+      <c r="J5" s="1" t="inlineStr">
         <is>
           <t>24八王子市</t>
         </is>
@@ -835,7 +859,8 @@
           <t>藤村　誠一郎</t>
         </is>
       </c>
-      <c r="R5" s="1" t="n">
+      <c r="Q5" s="1" t="n"/>
+      <c r="R5" s="3" t="n">
         <v>39107</v>
       </c>
       <c r="S5" t="n">
@@ -849,7 +874,7 @@
           <t>18福保障計第1343号</t>
         </is>
       </c>
-      <c r="X5" t="inlineStr">
+      <c r="X5" s="1" t="inlineStr">
         <is>
           <t>育成医療・更生医療</t>
         </is>
@@ -873,23 +898,24 @@
       </c>
     </row>
     <row r="6">
-      <c r="A6" t="inlineStr">
+      <c r="A6" s="1" t="inlineStr">
         <is>
           <t>2-3</t>
         </is>
       </c>
-      <c r="D6" t="n">
+      <c r="C6" s="1" t="n"/>
+      <c r="D6" s="2" t="n">
         <v>2951200</v>
       </c>
       <c r="E6" t="n">
         <v>7</v>
       </c>
-      <c r="F6" t="inlineStr">
+      <c r="F6" s="4" t="inlineStr">
         <is>
           <t>1342951200</t>
         </is>
       </c>
-      <c r="G6" t="inlineStr">
+      <c r="G6" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">　</t>
         </is>
@@ -904,7 +930,7 @@
           <t>193-0943</t>
         </is>
       </c>
-      <c r="J6" t="inlineStr">
+      <c r="J6" s="1" t="inlineStr">
         <is>
           <t>24八王子市</t>
         </is>
@@ -939,12 +965,12 @@
           <t>森本　達也</t>
         </is>
       </c>
-      <c r="Q6" t="inlineStr">
+      <c r="Q6" s="1" t="inlineStr">
         <is>
           <t>変更届(神山　吉平、～令和3年9月30日）</t>
         </is>
       </c>
-      <c r="R6" s="1" t="n">
+      <c r="R6" s="3" t="n">
         <v>39022</v>
       </c>
       <c r="S6" t="n">
@@ -953,7 +979,7 @@
       <c r="T6" t="n">
         <v>39114</v>
       </c>
-      <c r="U6" t="inlineStr">
+      <c r="U6" s="1" t="inlineStr">
         <is>
           <t>18福保障計第1319号</t>
         </is>
@@ -966,7 +992,7 @@
           <t>6八福障第5363号</t>
         </is>
       </c>
-      <c r="X6" t="inlineStr">
+      <c r="X6" s="1" t="inlineStr">
         <is>
           <t>育成医療・更生医療</t>
         </is>
@@ -982,7 +1008,7 @@
       </c>
     </row>
     <row r="7">
-      <c r="A7" t="inlineStr">
+      <c r="A7" s="1" t="inlineStr">
         <is>
           <t>2-4</t>
         </is>
@@ -992,18 +1018,18 @@
           <t>○</t>
         </is>
       </c>
-      <c r="D7" t="n">
+      <c r="D7" s="2" t="n">
         <v>2951283</v>
       </c>
       <c r="E7" t="n">
         <v>7</v>
       </c>
-      <c r="F7" t="inlineStr">
+      <c r="F7" s="4" t="inlineStr">
         <is>
           <t>1342951283</t>
         </is>
       </c>
-      <c r="G7" t="inlineStr">
+      <c r="G7" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">　</t>
         </is>
@@ -1018,7 +1044,7 @@
           <t>193-0832</t>
         </is>
       </c>
-      <c r="J7" t="inlineStr">
+      <c r="J7" s="1" t="inlineStr">
         <is>
           <t>24八王子市</t>
         </is>
@@ -1043,7 +1069,8 @@
           <t>井上　優子</t>
         </is>
       </c>
-      <c r="R7" s="1" t="n">
+      <c r="Q7" s="1" t="n"/>
+      <c r="R7" s="3" t="n">
         <v>39059</v>
       </c>
       <c r="S7" t="n">
@@ -1057,7 +1084,7 @@
           <t>18福保障計第1221号</t>
         </is>
       </c>
-      <c r="X7" t="inlineStr">
+      <c r="X7" s="1" t="inlineStr">
         <is>
           <t>育成医療・更生医療</t>
         </is>
@@ -1081,23 +1108,24 @@
       </c>
     </row>
     <row r="8">
-      <c r="A8" t="inlineStr">
+      <c r="A8" s="1" t="inlineStr">
         <is>
           <t>2-5</t>
         </is>
       </c>
-      <c r="D8" t="n">
+      <c r="C8" s="1" t="n"/>
+      <c r="D8" s="2" t="n">
         <v>2951333</v>
       </c>
       <c r="E8" t="n">
         <v>7</v>
       </c>
-      <c r="F8" t="inlineStr">
+      <c r="F8" s="4" t="inlineStr">
         <is>
           <t>1342951333</t>
         </is>
       </c>
-      <c r="G8" t="inlineStr">
+      <c r="G8" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">　</t>
         </is>
@@ -1112,7 +1140,7 @@
           <t>192-0066</t>
         </is>
       </c>
-      <c r="J8" t="inlineStr">
+      <c r="J8" s="1" t="inlineStr">
         <is>
           <t>24八王子市</t>
         </is>
@@ -1147,7 +1175,8 @@
           <t>根岸　徹</t>
         </is>
       </c>
-      <c r="R8" s="1" t="n">
+      <c r="Q8" s="1" t="n"/>
+      <c r="R8" s="3" t="n">
         <v>39022</v>
       </c>
       <c r="S8" t="n">
@@ -1156,7 +1185,7 @@
       <c r="T8" t="n">
         <v>39114</v>
       </c>
-      <c r="U8" t="inlineStr">
+      <c r="U8" s="1" t="inlineStr">
         <is>
           <t>18福保障計第1319号</t>
         </is>
@@ -1169,7 +1198,7 @@
           <t>6八福障第5134号</t>
         </is>
       </c>
-      <c r="X8" t="inlineStr">
+      <c r="X8" s="1" t="inlineStr">
         <is>
           <t>育成医療・更生医療</t>
         </is>
@@ -1185,23 +1214,24 @@
       </c>
     </row>
     <row r="9">
-      <c r="A9" t="inlineStr">
+      <c r="A9" s="1" t="inlineStr">
         <is>
           <t>2-6</t>
         </is>
       </c>
-      <c r="D9" t="n">
+      <c r="C9" s="1" t="n"/>
+      <c r="D9" s="2" t="n">
         <v>2955334</v>
       </c>
       <c r="E9" t="n">
         <v>7</v>
       </c>
-      <c r="F9" t="inlineStr">
+      <c r="F9" s="4" t="inlineStr">
         <is>
           <t>1342955334</t>
         </is>
       </c>
-      <c r="G9" t="inlineStr">
+      <c r="G9" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">　</t>
         </is>
@@ -1216,7 +1246,7 @@
           <t>192-0046</t>
         </is>
       </c>
-      <c r="J9" t="inlineStr">
+      <c r="J9" s="1" t="inlineStr">
         <is>
           <t>24八王子市</t>
         </is>
@@ -1256,7 +1286,7 @@
           <t>変更届（原　義浩、～令和6年9月10日）</t>
         </is>
       </c>
-      <c r="R9" s="1" t="n">
+      <c r="R9" s="3" t="n">
         <v>39045</v>
       </c>
       <c r="S9" t="n">
@@ -1265,7 +1295,7 @@
       <c r="T9" t="n">
         <v>39114</v>
       </c>
-      <c r="U9" t="inlineStr">
+      <c r="U9" s="1" t="inlineStr">
         <is>
           <t>18福保障計第1319号</t>
         </is>
@@ -1278,7 +1308,7 @@
           <t>6八福障第5095号</t>
         </is>
       </c>
-      <c r="X9" t="inlineStr">
+      <c r="X9" s="1" t="inlineStr">
         <is>
           <t>育成医療・更生医療</t>
         </is>
@@ -1314,23 +1344,23 @@
       </c>
     </row>
     <row r="10">
-      <c r="A10" t="inlineStr">
+      <c r="A10" s="1" t="inlineStr">
         <is>
           <t>2-7</t>
         </is>
       </c>
-      <c r="D10" t="n">
+      <c r="D10" s="2" t="n">
         <v>2951622</v>
       </c>
       <c r="E10" t="n">
         <v>7</v>
       </c>
-      <c r="F10" t="inlineStr">
+      <c r="F10" s="4" t="inlineStr">
         <is>
           <t>1342951622</t>
         </is>
       </c>
-      <c r="G10" t="inlineStr">
+      <c r="G10" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">　</t>
         </is>
@@ -1345,7 +1375,7 @@
           <t>193-0944</t>
         </is>
       </c>
-      <c r="J10" t="inlineStr">
+      <c r="J10" s="1" t="inlineStr">
         <is>
           <t>24八王子市</t>
         </is>
@@ -1385,7 +1415,7 @@
           <t>変更届(添石　遼平、～令和7年6月30日）</t>
         </is>
       </c>
-      <c r="R10" s="1" t="n">
+      <c r="R10" s="3" t="n">
         <v>39039</v>
       </c>
       <c r="S10" t="n">
@@ -1407,7 +1437,7 @@
           <t>6八福障第5202号</t>
         </is>
       </c>
-      <c r="X10" t="inlineStr">
+      <c r="X10" s="1" t="inlineStr">
         <is>
           <t>育成医療・更生医療</t>
         </is>
@@ -1428,23 +1458,24 @@
       </c>
     </row>
     <row r="11">
-      <c r="A11" t="inlineStr">
+      <c r="A11" s="1" t="inlineStr">
         <is>
           <t>2-8</t>
         </is>
       </c>
-      <c r="D11" t="n">
+      <c r="C11" s="1" t="n"/>
+      <c r="D11" s="2" t="n">
         <v>2951630</v>
       </c>
       <c r="E11" t="n">
         <v>7</v>
       </c>
-      <c r="F11" t="inlineStr">
+      <c r="F11" s="4" t="inlineStr">
         <is>
           <t>1342951630</t>
         </is>
       </c>
-      <c r="G11" t="inlineStr">
+      <c r="G11" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">　</t>
         </is>
@@ -1459,12 +1490,12 @@
           <t>193-0816</t>
         </is>
       </c>
-      <c r="J11" t="inlineStr">
+      <c r="J11" s="1" t="inlineStr">
         <is>
           <t>24八王子市</t>
         </is>
       </c>
-      <c r="K11" t="inlineStr">
+      <c r="K11" s="1" t="inlineStr">
         <is>
           <t>八王子市大楽寺町１３６－５</t>
         </is>
@@ -1484,7 +1515,7 @@
           <t>193-0816</t>
         </is>
       </c>
-      <c r="O11" t="inlineStr">
+      <c r="O11" s="1" t="inlineStr">
         <is>
           <t>東京都八王子市大楽寺町１３６－５</t>
         </is>
@@ -1494,7 +1525,8 @@
           <t>荒井　英冶</t>
         </is>
       </c>
-      <c r="R11" s="1" t="n">
+      <c r="Q11" s="1" t="n"/>
+      <c r="R11" s="3" t="n">
         <v>39163</v>
       </c>
       <c r="S11" t="n">
@@ -1503,7 +1535,7 @@
       <c r="T11" t="n">
         <v>39234</v>
       </c>
-      <c r="U11" t="inlineStr">
+      <c r="U11" s="1" t="inlineStr">
         <is>
           <t>19福保障計第209号</t>
         </is>
@@ -1516,7 +1548,7 @@
           <t>6八福障第6991号</t>
         </is>
       </c>
-      <c r="X11" t="inlineStr">
+      <c r="X11" s="1" t="inlineStr">
         <is>
           <t>育成医療・更生医療</t>
         </is>
@@ -1532,23 +1564,23 @@
       </c>
     </row>
     <row r="12">
-      <c r="A12" t="inlineStr">
+      <c r="A12" s="1" t="inlineStr">
         <is>
           <t>2-9</t>
         </is>
       </c>
-      <c r="D12" t="n">
+      <c r="D12" s="2" t="n">
         <v>2955342</v>
       </c>
       <c r="E12" t="n">
         <v>7</v>
       </c>
-      <c r="F12" t="inlineStr">
+      <c r="F12" s="4" t="inlineStr">
         <is>
           <t>1342955342</t>
         </is>
       </c>
-      <c r="G12" t="inlineStr">
+      <c r="G12" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">　</t>
         </is>
@@ -1563,7 +1595,7 @@
           <t>193-0832</t>
         </is>
       </c>
-      <c r="J12" t="inlineStr">
+      <c r="J12" s="1" t="inlineStr">
         <is>
           <t>24八王子市</t>
         </is>
@@ -1603,7 +1635,7 @@
           <t>変更届（曽我部　ひな、～令和6年9月10日）</t>
         </is>
       </c>
-      <c r="R12" s="1" t="n">
+      <c r="R12" s="3" t="n">
         <v>39080</v>
       </c>
       <c r="S12" t="n">
@@ -1625,7 +1657,7 @@
           <t>6八福障第6622号</t>
         </is>
       </c>
-      <c r="X12" t="inlineStr">
+      <c r="X12" s="1" t="inlineStr">
         <is>
           <t>育成医療・更生医療</t>
         </is>
@@ -1661,23 +1693,23 @@
       </c>
     </row>
     <row r="13">
-      <c r="A13" t="inlineStr">
+      <c r="A13" s="1" t="inlineStr">
         <is>
           <t>2-10</t>
         </is>
       </c>
-      <c r="D13" t="n">
+      <c r="D13" s="2" t="n">
         <v>2951796</v>
       </c>
       <c r="E13" t="n">
         <v>7</v>
       </c>
-      <c r="F13" t="inlineStr">
+      <c r="F13" s="4" t="inlineStr">
         <is>
           <t>1342951796</t>
         </is>
       </c>
-      <c r="G13" t="inlineStr">
+      <c r="G13" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">　</t>
         </is>
@@ -1687,12 +1719,12 @@
           <t>ミネ薬局　南大沢店</t>
         </is>
       </c>
-      <c r="I13" t="inlineStr">
+      <c r="I13" s="2" t="inlineStr">
         <is>
           <t>192-0364</t>
         </is>
       </c>
-      <c r="J13" t="inlineStr">
+      <c r="J13" s="1" t="inlineStr">
         <is>
           <t>24八王子市</t>
         </is>
@@ -1732,7 +1764,7 @@
           <t>変更届（鎌田　鈴子、～令和5年8月31日）</t>
         </is>
       </c>
-      <c r="R13" s="1" t="n">
+      <c r="R13" s="3" t="n">
         <v>39423</v>
       </c>
       <c r="S13" t="n">
@@ -1754,7 +1786,7 @@
           <t>7八福障第6127号</t>
         </is>
       </c>
-      <c r="X13" t="inlineStr">
+      <c r="X13" s="1" t="inlineStr">
         <is>
           <t>育成医療・更生医療</t>
         </is>
@@ -1770,23 +1802,24 @@
       </c>
     </row>
     <row r="14">
-      <c r="A14" t="inlineStr">
+      <c r="A14" s="1" t="inlineStr">
         <is>
           <t>2-11</t>
         </is>
       </c>
-      <c r="D14" t="n">
+      <c r="C14" s="1" t="n"/>
+      <c r="D14" s="2" t="n">
         <v>2952083</v>
       </c>
       <c r="E14" t="n">
         <v>7</v>
       </c>
-      <c r="F14" t="inlineStr">
+      <c r="F14" s="4" t="inlineStr">
         <is>
           <t>1342952083</t>
         </is>
       </c>
-      <c r="G14" t="inlineStr">
+      <c r="G14" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">　</t>
         </is>
@@ -1801,7 +1834,7 @@
           <t>193-0832</t>
         </is>
       </c>
-      <c r="J14" t="inlineStr">
+      <c r="J14" s="1" t="inlineStr">
         <is>
           <t>24八王子市</t>
         </is>
@@ -1841,7 +1874,7 @@
           <t>変更届（指田　幸、～平成27年12月31日）</t>
         </is>
       </c>
-      <c r="R14" s="1" t="n">
+      <c r="R14" s="3" t="n">
         <v>39022</v>
       </c>
       <c r="S14" t="n">
@@ -1850,7 +1883,7 @@
       <c r="T14" t="n">
         <v>39114</v>
       </c>
-      <c r="U14" t="inlineStr">
+      <c r="U14" s="1" t="inlineStr">
         <is>
           <t>18福保障計第1319号</t>
         </is>
@@ -1863,7 +1896,7 @@
           <t>6八福障第5664号</t>
         </is>
       </c>
-      <c r="X14" t="inlineStr">
+      <c r="X14" s="1" t="inlineStr">
         <is>
           <t>育成医療・更生医療</t>
         </is>
@@ -1879,7 +1912,7 @@
       </c>
     </row>
     <row r="15">
-      <c r="A15" t="inlineStr">
+      <c r="A15" s="1" t="inlineStr">
         <is>
           <t>2-12</t>
         </is>
@@ -1889,18 +1922,18 @@
           <t>○</t>
         </is>
       </c>
-      <c r="D15" t="n">
+      <c r="D15" s="2" t="n">
         <v>2952133</v>
       </c>
       <c r="E15" t="n">
         <v>7</v>
       </c>
-      <c r="F15" t="inlineStr">
+      <c r="F15" s="4" t="inlineStr">
         <is>
           <t>1342952133</t>
         </is>
       </c>
-      <c r="G15" t="inlineStr">
+      <c r="G15" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">　</t>
         </is>
@@ -1915,7 +1948,7 @@
           <t>192-0904</t>
         </is>
       </c>
-      <c r="J15" t="inlineStr">
+      <c r="J15" s="1" t="inlineStr">
         <is>
           <t>24八王子市</t>
         </is>
@@ -1950,10 +1983,11 @@
           <t>村松　知英子</t>
         </is>
       </c>
-      <c r="R15" s="1" t="n">
+      <c r="Q15" s="1" t="n"/>
+      <c r="R15" s="3" t="n">
         <v>38993</v>
       </c>
-      <c r="S15" s="1" t="n">
+      <c r="S15" s="3" t="n">
         <v>39052</v>
       </c>
       <c r="T15" t="n">
@@ -1972,7 +2006,7 @@
           <t>24福保障計第1132号</t>
         </is>
       </c>
-      <c r="X15" t="inlineStr">
+      <c r="X15" s="1" t="inlineStr">
         <is>
           <t>育成医療・更生医療</t>
         </is>
@@ -1996,23 +2030,23 @@
       </c>
     </row>
     <row r="16">
-      <c r="A16" t="inlineStr">
+      <c r="A16" s="1" t="inlineStr">
         <is>
           <t>2-13</t>
         </is>
       </c>
-      <c r="D16" t="n">
+      <c r="D16" s="2" t="n">
         <v>2956373</v>
       </c>
       <c r="E16" t="n">
         <v>7</v>
       </c>
-      <c r="F16" t="inlineStr">
+      <c r="F16" s="4" t="inlineStr">
         <is>
           <t>1342956373</t>
         </is>
       </c>
-      <c r="G16" t="inlineStr">
+      <c r="G16" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">　</t>
         </is>
@@ -2027,7 +2061,7 @@
           <t>193-0832</t>
         </is>
       </c>
-      <c r="J16" t="inlineStr">
+      <c r="J16" s="1" t="inlineStr">
         <is>
           <t>24八王子市</t>
         </is>
@@ -2067,7 +2101,7 @@
           <t>変更届（福谷　桂　～令和4年6月30日）</t>
         </is>
       </c>
-      <c r="R16" s="1" t="n">
+      <c r="R16" s="3" t="n">
         <v>39036</v>
       </c>
       <c r="S16" t="n">
@@ -2089,7 +2123,7 @@
           <t>6八福障第5241号</t>
         </is>
       </c>
-      <c r="X16" t="inlineStr">
+      <c r="X16" s="1" t="inlineStr">
         <is>
           <t>育成医療・更生医療</t>
         </is>
@@ -2120,23 +2154,23 @@
       </c>
     </row>
     <row r="17">
-      <c r="A17" t="inlineStr">
+      <c r="A17" s="1" t="inlineStr">
         <is>
           <t>2-14</t>
         </is>
       </c>
-      <c r="D17" t="n">
+      <c r="D17" s="2" t="n">
         <v>2952182</v>
       </c>
       <c r="E17" t="n">
         <v>7</v>
       </c>
-      <c r="F17" t="inlineStr">
+      <c r="F17" s="4" t="inlineStr">
         <is>
           <t>1342952182</t>
         </is>
       </c>
-      <c r="G17" t="inlineStr">
+      <c r="G17" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">　</t>
         </is>
@@ -2151,7 +2185,7 @@
           <t>192-0904</t>
         </is>
       </c>
-      <c r="J17" t="inlineStr">
+      <c r="J17" s="1" t="inlineStr">
         <is>
           <t>24八王子市</t>
         </is>
@@ -2186,10 +2220,11 @@
           <t>橘　隆二</t>
         </is>
       </c>
-      <c r="R17" s="1" t="n">
+      <c r="Q17" s="1" t="n"/>
+      <c r="R17" s="3" t="n">
         <v>39025</v>
       </c>
-      <c r="S17" s="1" t="n">
+      <c r="S17" s="3" t="n">
         <v>38808</v>
       </c>
       <c r="T17" t="n">
@@ -2208,7 +2243,7 @@
           <t>6八福障第5175号</t>
         </is>
       </c>
-      <c r="X17" t="inlineStr">
+      <c r="X17" s="1" t="inlineStr">
         <is>
           <t>育成医療・更生医療</t>
         </is>
@@ -2224,23 +2259,23 @@
       </c>
     </row>
     <row r="18">
-      <c r="A18" t="inlineStr">
+      <c r="A18" s="1" t="inlineStr">
         <is>
           <t>2-15</t>
         </is>
       </c>
-      <c r="D18" t="n">
+      <c r="D18" s="2" t="n">
         <v>2955599</v>
       </c>
       <c r="E18" t="n">
         <v>7</v>
       </c>
-      <c r="F18" t="inlineStr">
+      <c r="F18" s="4" t="inlineStr">
         <is>
           <t>1342955599</t>
         </is>
       </c>
-      <c r="G18" t="inlineStr">
+      <c r="G18" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">　</t>
         </is>
@@ -2255,7 +2290,7 @@
           <t>192-0083</t>
         </is>
       </c>
-      <c r="J18" t="inlineStr">
+      <c r="J18" s="1" t="inlineStr">
         <is>
           <t>24八王子市</t>
         </is>
@@ -2291,10 +2326,11 @@
           <t>三橋　由美</t>
         </is>
       </c>
-      <c r="R18" s="1" t="n">
+      <c r="Q18" s="1" t="n"/>
+      <c r="R18" s="3" t="n">
         <v>38972</v>
       </c>
-      <c r="S18" s="1" t="n">
+      <c r="S18" s="3" t="n">
         <v>39052</v>
       </c>
       <c r="T18" t="n">
@@ -2313,7 +2349,7 @@
           <t>30八福障収第703号</t>
         </is>
       </c>
-      <c r="X18" t="inlineStr">
+      <c r="X18" s="1" t="inlineStr">
         <is>
           <t>育成医療・更生医療</t>
         </is>
@@ -2371,23 +2407,24 @@
       </c>
     </row>
     <row r="19">
-      <c r="A19" t="inlineStr">
+      <c r="A19" s="1" t="inlineStr">
         <is>
           <t>2-16</t>
         </is>
       </c>
-      <c r="D19" t="n">
+      <c r="C19" s="1" t="n"/>
+      <c r="D19" s="2" t="n">
         <v>2952232</v>
       </c>
       <c r="E19" t="n">
         <v>7</v>
       </c>
-      <c r="F19" t="inlineStr">
+      <c r="F19" s="4" t="inlineStr">
         <is>
           <t>1342952232</t>
         </is>
       </c>
-      <c r="G19" t="inlineStr">
+      <c r="G19" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">　</t>
         </is>
@@ -2402,7 +2439,7 @@
           <t>192-0911</t>
         </is>
       </c>
-      <c r="J19" t="inlineStr">
+      <c r="J19" s="1" t="inlineStr">
         <is>
           <t>24八王子市</t>
         </is>
@@ -2442,7 +2479,7 @@
           <t>変更届(大牛　悠介、～令和7年8月31日）</t>
         </is>
       </c>
-      <c r="R19" s="1" t="n">
+      <c r="R19" s="3" t="n">
         <v>39022</v>
       </c>
       <c r="S19" t="n">
@@ -2451,7 +2488,7 @@
       <c r="T19" t="n">
         <v>39114</v>
       </c>
-      <c r="U19" t="inlineStr">
+      <c r="U19" s="1" t="inlineStr">
         <is>
           <t>18福保障計第1319号</t>
         </is>
@@ -2464,7 +2501,7 @@
           <t>6八福障第5665号</t>
         </is>
       </c>
-      <c r="X19" t="inlineStr">
+      <c r="X19" s="1" t="inlineStr">
         <is>
           <t>育成医療・更生医療</t>
         </is>
@@ -2480,23 +2517,24 @@
       </c>
     </row>
     <row r="20">
-      <c r="A20" t="inlineStr">
+      <c r="A20" s="1" t="inlineStr">
         <is>
           <t>2-17</t>
         </is>
       </c>
-      <c r="D20" t="n">
+      <c r="C20" s="1" t="n"/>
+      <c r="D20" s="2" t="n">
         <v>2952299</v>
       </c>
       <c r="E20" t="n">
         <v>7</v>
       </c>
-      <c r="F20" t="inlineStr">
+      <c r="F20" s="4" t="inlineStr">
         <is>
           <t>1342952299</t>
         </is>
       </c>
-      <c r="G20" t="inlineStr">
+      <c r="G20" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">　</t>
         </is>
@@ -2511,12 +2549,12 @@
           <t>192-0364</t>
         </is>
       </c>
-      <c r="J20" t="inlineStr">
+      <c r="J20" s="1" t="inlineStr">
         <is>
           <t>24八王子市</t>
         </is>
       </c>
-      <c r="K20" t="inlineStr">
+      <c r="K20" s="1" t="inlineStr">
         <is>
           <t>八王子市南大沢２－２７　フレスコ南大沢</t>
         </is>
@@ -2536,7 +2574,7 @@
           <t>192-0364</t>
         </is>
       </c>
-      <c r="O20" t="inlineStr">
+      <c r="O20" s="1" t="inlineStr">
         <is>
           <t>東京都八王子市南大沢２－２７　フレスコ南大沢</t>
         </is>
@@ -2546,6 +2584,7 @@
           <t>溝口　由喜和</t>
         </is>
       </c>
+      <c r="Q20" s="1" t="n"/>
       <c r="R20" t="n">
         <v>39173</v>
       </c>
@@ -2555,7 +2594,7 @@
       <c r="T20" t="n">
         <v>39234</v>
       </c>
-      <c r="U20" t="inlineStr">
+      <c r="U20" s="1" t="inlineStr">
         <is>
           <t>19福保障計第209号</t>
         </is>
@@ -2568,7 +2607,7 @@
           <t>6八福障第6850号</t>
         </is>
       </c>
-      <c r="X20" t="inlineStr">
+      <c r="X20" s="1" t="inlineStr">
         <is>
           <t>育成医療・更生医療</t>
         </is>
@@ -2589,23 +2628,24 @@
       </c>
     </row>
     <row r="21">
-      <c r="A21" t="inlineStr">
+      <c r="A21" s="1" t="inlineStr">
         <is>
           <t>2-18</t>
         </is>
       </c>
-      <c r="D21" t="n">
+      <c r="C21" s="1" t="n"/>
+      <c r="D21" s="2" t="n">
         <v>2952406</v>
       </c>
       <c r="E21" t="n">
         <v>7</v>
       </c>
-      <c r="F21" t="inlineStr">
+      <c r="F21" s="4" t="inlineStr">
         <is>
           <t>1342952406</t>
         </is>
       </c>
-      <c r="G21" t="inlineStr">
+      <c r="G21" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">　</t>
         </is>
@@ -2620,12 +2660,12 @@
           <t>193-0931</t>
         </is>
       </c>
-      <c r="J21" t="inlineStr">
+      <c r="J21" s="1" t="inlineStr">
         <is>
           <t>24八王子市</t>
         </is>
       </c>
-      <c r="K21" t="inlineStr">
+      <c r="K21" s="1" t="inlineStr">
         <is>
           <t>八王子市台町３－１６－１６</t>
         </is>
@@ -2660,7 +2700,7 @@
           <t>変更届（早川　ひろ美、～令和5年9月20日）</t>
         </is>
       </c>
-      <c r="R21" s="1" t="n">
+      <c r="R21" s="3" t="n">
         <v>39155</v>
       </c>
       <c r="S21" t="n">
@@ -2669,7 +2709,7 @@
       <c r="T21" t="n">
         <v>39234</v>
       </c>
-      <c r="U21" t="inlineStr">
+      <c r="U21" s="1" t="inlineStr">
         <is>
           <t>19福保障計第209号</t>
         </is>
@@ -2682,7 +2722,7 @@
           <t>6八福障第6739号</t>
         </is>
       </c>
-      <c r="X21" t="inlineStr">
+      <c r="X21" s="1" t="inlineStr">
         <is>
           <t>育成医療・更生医療</t>
         </is>
@@ -2698,7 +2738,7 @@
       </c>
     </row>
     <row r="22">
-      <c r="A22" t="inlineStr">
+      <c r="A22" s="1" t="inlineStr">
         <is>
           <t>2-19</t>
         </is>
@@ -2708,18 +2748,18 @@
           <t>○</t>
         </is>
       </c>
-      <c r="D22" t="n">
+      <c r="D22" s="2" t="n">
         <v>2952430</v>
       </c>
       <c r="E22" t="n">
         <v>7</v>
       </c>
-      <c r="F22" t="inlineStr">
+      <c r="F22" s="4" t="inlineStr">
         <is>
           <t>1342952430</t>
         </is>
       </c>
-      <c r="G22" t="inlineStr">
+      <c r="G22" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">　</t>
         </is>
@@ -2734,7 +2774,7 @@
           <t>192-0082</t>
         </is>
       </c>
-      <c r="J22" t="inlineStr">
+      <c r="J22" s="1" t="inlineStr">
         <is>
           <t>24八王子市</t>
         </is>
@@ -2769,15 +2809,15 @@
           <t>松本　瑞恵</t>
         </is>
       </c>
-      <c r="Q22" t="inlineStr">
+      <c r="Q22" s="1" t="inlineStr">
         <is>
           <t>変更届(小野　孝子、～平成21年２月28日）</t>
         </is>
       </c>
-      <c r="R22" s="1" t="n">
+      <c r="R22" s="3" t="n">
         <v>38972</v>
       </c>
-      <c r="S22" s="1" t="n">
+      <c r="S22" s="3" t="n">
         <v>39052</v>
       </c>
       <c r="T22" t="n">
@@ -2796,7 +2836,7 @@
           <t>24福保障計第1132号</t>
         </is>
       </c>
-      <c r="X22" t="inlineStr">
+      <c r="X22" s="1" t="inlineStr">
         <is>
           <t>育成医療・更生医療</t>
         </is>
@@ -2820,7 +2860,7 @@
       </c>
     </row>
     <row r="23">
-      <c r="A23" t="inlineStr">
+      <c r="A23" s="1" t="inlineStr">
         <is>
           <t>2-20</t>
         </is>
@@ -2830,18 +2870,18 @@
           <t>○</t>
         </is>
       </c>
-      <c r="D23" t="n">
+      <c r="D23" s="2" t="n">
         <v>2952455</v>
       </c>
       <c r="E23" t="n">
         <v>7</v>
       </c>
-      <c r="F23" t="inlineStr">
+      <c r="F23" s="4" t="inlineStr">
         <is>
           <t>1342952455</t>
         </is>
       </c>
-      <c r="G23" t="inlineStr">
+      <c r="G23" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">　</t>
         </is>
@@ -2856,7 +2896,7 @@
           <t>193-0824</t>
         </is>
       </c>
-      <c r="J23" t="inlineStr">
+      <c r="J23" s="1" t="inlineStr">
         <is>
           <t>24八王子市</t>
         </is>
@@ -2881,7 +2921,8 @@
           <t>鈴木　敏之</t>
         </is>
       </c>
-      <c r="R23" s="1" t="n">
+      <c r="Q23" s="1" t="n"/>
+      <c r="R23" s="3" t="n">
         <v>39025</v>
       </c>
       <c r="S23" t="n">
@@ -2895,7 +2936,7 @@
           <t>18福保障計第940号</t>
         </is>
       </c>
-      <c r="X23" t="inlineStr">
+      <c r="X23" s="1" t="inlineStr">
         <is>
           <t>育成医療・更生医療</t>
         </is>
@@ -2912,30 +2953,30 @@
       <c r="AB23" t="n">
         <v>42306</v>
       </c>
-      <c r="AC23" t="inlineStr">
+      <c r="AC23" s="1" t="inlineStr">
         <is>
           <t>廃止届（平成23年６月30日廃止、薬局廃業）</t>
         </is>
       </c>
     </row>
     <row r="24">
-      <c r="A24" t="inlineStr">
+      <c r="A24" s="1" t="inlineStr">
         <is>
           <t>2-21</t>
         </is>
       </c>
-      <c r="D24" t="n">
+      <c r="D24" s="2" t="n">
         <v>2955870</v>
       </c>
       <c r="E24" t="n">
         <v>7</v>
       </c>
-      <c r="F24" t="inlineStr">
+      <c r="F24" s="4" t="inlineStr">
         <is>
           <t>1342955870</t>
         </is>
       </c>
-      <c r="G24" t="inlineStr">
+      <c r="G24" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">　</t>
         </is>
@@ -2950,7 +2991,7 @@
           <t>192-0002</t>
         </is>
       </c>
-      <c r="J24" t="inlineStr">
+      <c r="J24" s="1" t="inlineStr">
         <is>
           <t>24八王子市</t>
         </is>
@@ -2990,7 +3031,7 @@
           <t>変更届（栗原　章、～平成31年2月28日）</t>
         </is>
       </c>
-      <c r="R24" s="1" t="n">
+      <c r="R24" s="3" t="n">
         <v>39025</v>
       </c>
       <c r="S24" t="n">
@@ -3012,7 +3053,7 @@
           <t>6八福障第5243号</t>
         </is>
       </c>
-      <c r="X24" t="inlineStr">
+      <c r="X24" s="1" t="inlineStr">
         <is>
           <t>育成医療・更生医療</t>
         </is>
@@ -3043,23 +3084,24 @@
       </c>
     </row>
     <row r="25">
-      <c r="A25" t="inlineStr">
+      <c r="A25" s="1" t="inlineStr">
         <is>
           <t>2-22</t>
         </is>
       </c>
-      <c r="D25" t="n">
+      <c r="C25" s="1" t="n"/>
+      <c r="D25" s="2" t="n">
         <v>2952513</v>
       </c>
       <c r="E25" t="n">
         <v>7</v>
       </c>
-      <c r="F25" t="inlineStr">
+      <c r="F25" s="4" t="inlineStr">
         <is>
           <t>1342952513</t>
         </is>
       </c>
-      <c r="G25" t="inlineStr">
+      <c r="G25" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">　</t>
         </is>
@@ -3074,7 +3116,7 @@
           <t>192-0042</t>
         </is>
       </c>
-      <c r="J25" t="inlineStr">
+      <c r="J25" s="1" t="inlineStr">
         <is>
           <t>24八王子市</t>
         </is>
@@ -3114,7 +3156,7 @@
           <t>変更届（土屋　良夫、～令和7年10月31日）</t>
         </is>
       </c>
-      <c r="R25" s="1" t="n">
+      <c r="R25" s="3" t="n">
         <v>39030</v>
       </c>
       <c r="S25" t="n">
@@ -3123,7 +3165,7 @@
       <c r="T25" t="n">
         <v>39114</v>
       </c>
-      <c r="U25" t="inlineStr">
+      <c r="U25" s="1" t="inlineStr">
         <is>
           <t>18福保障計第1319号</t>
         </is>
@@ -3136,7 +3178,7 @@
           <t>6八福障第5268号</t>
         </is>
       </c>
-      <c r="X25" t="inlineStr">
+      <c r="X25" s="1" t="inlineStr">
         <is>
           <t>育成医療・更生医療</t>
         </is>
@@ -3152,7 +3194,7 @@
       </c>
     </row>
     <row r="26">
-      <c r="A26" t="inlineStr">
+      <c r="A26" s="1" t="inlineStr">
         <is>
           <t>2-23</t>
         </is>
@@ -3162,18 +3204,18 @@
           <t>○</t>
         </is>
       </c>
-      <c r="D26" t="n">
+      <c r="D26" s="2" t="n">
         <v>2952547</v>
       </c>
       <c r="E26" t="n">
         <v>7</v>
       </c>
-      <c r="F26" t="inlineStr">
+      <c r="F26" s="4" t="inlineStr">
         <is>
           <t>1342952547</t>
         </is>
       </c>
-      <c r="G26" t="inlineStr">
+      <c r="G26" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">　</t>
         </is>
@@ -3188,12 +3230,12 @@
           <t>193-0942</t>
         </is>
       </c>
-      <c r="J26" t="inlineStr">
+      <c r="J26" s="1" t="inlineStr">
         <is>
           <t>24八王子市</t>
         </is>
       </c>
-      <c r="K26" t="inlineStr">
+      <c r="K26" s="1" t="inlineStr">
         <is>
           <t>八王子市椚田町２４１　第２藤ビル１０２</t>
         </is>
@@ -3208,7 +3250,7 @@
           <t>株式会社ムラタ</t>
         </is>
       </c>
-      <c r="N26" t="inlineStr">
+      <c r="N26" s="1" t="inlineStr">
         <is>
           <t>192-0916</t>
         </is>
@@ -3228,7 +3270,7 @@
           <t>変更届（梅原　昌宏、～平成23年２月16日）</t>
         </is>
       </c>
-      <c r="R26" s="1" t="n">
+      <c r="R26" s="3" t="n">
         <v>39171</v>
       </c>
       <c r="S26" t="n">
@@ -3237,7 +3279,7 @@
       <c r="T26" t="n">
         <v>39234</v>
       </c>
-      <c r="U26" t="inlineStr">
+      <c r="U26" s="1" t="inlineStr">
         <is>
           <t>19福保障計第209号</t>
         </is>
@@ -3250,7 +3292,7 @@
           <t>25福保障計第274号</t>
         </is>
       </c>
-      <c r="X26" t="inlineStr">
+      <c r="X26" s="1" t="inlineStr">
         <is>
           <t>育成医療・更生医療</t>
         </is>
@@ -3279,23 +3321,23 @@
       </c>
     </row>
     <row r="27">
-      <c r="A27" t="inlineStr">
+      <c r="A27" s="1" t="inlineStr">
         <is>
           <t>2-24</t>
         </is>
       </c>
-      <c r="D27" t="n">
+      <c r="D27" s="2" t="n">
         <v>2952562</v>
       </c>
       <c r="E27" t="n">
         <v>7</v>
       </c>
-      <c r="F27" t="inlineStr">
+      <c r="F27" s="4" t="inlineStr">
         <is>
           <t>1342952562</t>
         </is>
       </c>
-      <c r="G27" t="inlineStr">
+      <c r="G27" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">　</t>
         </is>
@@ -3310,7 +3352,7 @@
           <t>193-0823</t>
         </is>
       </c>
-      <c r="J27" t="inlineStr">
+      <c r="J27" s="1" t="inlineStr">
         <is>
           <t>24八王子市</t>
         </is>
@@ -3345,15 +3387,15 @@
           <t>横溝　智章</t>
         </is>
       </c>
-      <c r="Q27" t="inlineStr">
+      <c r="Q27" s="1" t="inlineStr">
         <is>
           <t>変更届(島崎　啓、～平成29年7月1日)</t>
         </is>
       </c>
-      <c r="R27" s="1" t="n">
+      <c r="R27" s="3" t="n">
         <v>38947</v>
       </c>
-      <c r="S27" s="1" t="n">
+      <c r="S27" s="3" t="n">
         <v>39052</v>
       </c>
       <c r="T27" t="n">
@@ -3372,7 +3414,7 @@
           <t>30八福障収第745号</t>
         </is>
       </c>
-      <c r="X27" t="inlineStr">
+      <c r="X27" s="1" t="inlineStr">
         <is>
           <t>育成医療・更生医療</t>
         </is>
@@ -3393,23 +3435,23 @@
       </c>
     </row>
     <row r="28">
-      <c r="A28" t="inlineStr">
+      <c r="A28" s="1" t="inlineStr">
         <is>
           <t>2-25</t>
         </is>
       </c>
-      <c r="D28" t="n">
+      <c r="D28" s="2" t="n">
         <v>2955268</v>
       </c>
       <c r="E28" t="n">
         <v>7</v>
       </c>
-      <c r="F28" t="inlineStr">
+      <c r="F28" s="4" t="inlineStr">
         <is>
           <t>1342955268</t>
         </is>
       </c>
-      <c r="G28" t="inlineStr">
+      <c r="G28" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">　</t>
         </is>
@@ -3419,12 +3461,12 @@
           <t>アイセイ薬局　子安町店</t>
         </is>
       </c>
-      <c r="I28" t="inlineStr">
+      <c r="I28" s="2" t="inlineStr">
         <is>
           <t>192-0904</t>
         </is>
       </c>
-      <c r="J28" t="inlineStr">
+      <c r="J28" s="1" t="inlineStr">
         <is>
           <t>24八王子市</t>
         </is>
@@ -3459,12 +3501,12 @@
           <t>日野　郁子</t>
         </is>
       </c>
-      <c r="Q28" t="inlineStr">
+      <c r="Q28" s="1" t="inlineStr">
         <is>
           <t>変更届(小林　良樹、～令和3年4月1日)</t>
         </is>
       </c>
-      <c r="R28" s="1" t="n">
+      <c r="R28" s="3" t="n">
         <v>39478</v>
       </c>
       <c r="S28" t="n">
@@ -3478,7 +3520,7 @@
           <t>19福保障計第1462号</t>
         </is>
       </c>
-      <c r="V28" s="1" t="n">
+      <c r="V28" s="3" t="n">
         <v>46113</v>
       </c>
       <c r="W28" t="inlineStr">
@@ -3486,7 +3528,7 @@
           <t>7八福障第8160号</t>
         </is>
       </c>
-      <c r="X28" t="inlineStr">
+      <c r="X28" s="1" t="inlineStr">
         <is>
           <t>育成医療・更生医療</t>
         </is>
@@ -3512,23 +3554,23 @@
       </c>
     </row>
     <row r="29">
-      <c r="A29" t="inlineStr">
+      <c r="A29" s="1" t="inlineStr">
         <is>
           <t>2-26</t>
         </is>
       </c>
-      <c r="D29" t="n">
+      <c r="D29" s="2" t="n">
         <v>2952687</v>
       </c>
       <c r="E29" t="n">
         <v>7</v>
       </c>
-      <c r="F29" t="inlineStr">
+      <c r="F29" s="4" t="inlineStr">
         <is>
           <t>1342952687</t>
         </is>
       </c>
-      <c r="G29" t="inlineStr">
+      <c r="G29" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">　</t>
         </is>
@@ -3543,7 +3585,7 @@
           <t>192-0082</t>
         </is>
       </c>
-      <c r="J29" t="inlineStr">
+      <c r="J29" s="1" t="inlineStr">
         <is>
           <t>24八王子市</t>
         </is>
@@ -3578,7 +3620,8 @@
           <t>下原　町子</t>
         </is>
       </c>
-      <c r="R29" s="1" t="n">
+      <c r="Q29" s="1" t="n"/>
+      <c r="R29" s="3" t="n">
         <v>38961</v>
       </c>
       <c r="S29" t="n">
@@ -3600,7 +3643,7 @@
           <t>30八福障収第702号</t>
         </is>
       </c>
-      <c r="X29" t="inlineStr">
+      <c r="X29" s="1" t="inlineStr">
         <is>
           <t>育成医療・更生医療</t>
         </is>
@@ -3621,23 +3664,23 @@
       </c>
     </row>
     <row r="30">
-      <c r="A30" t="inlineStr">
+      <c r="A30" s="1" t="inlineStr">
         <is>
           <t>2-27</t>
         </is>
       </c>
-      <c r="D30" t="n">
+      <c r="D30" s="2" t="n">
         <v>2952752</v>
       </c>
       <c r="E30" t="n">
         <v>7</v>
       </c>
-      <c r="F30" t="inlineStr">
+      <c r="F30" s="4" t="inlineStr">
         <is>
           <t>1342952752</t>
         </is>
       </c>
-      <c r="G30" t="inlineStr">
+      <c r="G30" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">　</t>
         </is>
@@ -3652,7 +3695,7 @@
           <t>192-0053</t>
         </is>
       </c>
-      <c r="J30" t="inlineStr">
+      <c r="J30" s="1" t="inlineStr">
         <is>
           <t>24八王子市</t>
         </is>
@@ -3692,10 +3735,10 @@
           <t>変更届（神田　静子、～平成25年７月11日）</t>
         </is>
       </c>
-      <c r="R30" s="1" t="n">
+      <c r="R30" s="3" t="n">
         <v>38992</v>
       </c>
-      <c r="S30" s="1" t="n">
+      <c r="S30" s="3" t="n">
         <v>39052</v>
       </c>
       <c r="T30" t="n">
@@ -3714,7 +3757,7 @@
           <t>30八福障収第559号</t>
         </is>
       </c>
-      <c r="X30" t="inlineStr">
+      <c r="X30" s="1" t="inlineStr">
         <is>
           <t>育成医療・更生医療</t>
         </is>
@@ -3730,23 +3773,23 @@
       </c>
     </row>
     <row r="31">
-      <c r="A31" t="inlineStr">
+      <c r="A31" s="1" t="inlineStr">
         <is>
           <t>2-28</t>
         </is>
       </c>
-      <c r="D31" t="n">
+      <c r="D31" s="2" t="n">
         <v>2952760</v>
       </c>
       <c r="E31" t="n">
         <v>7</v>
       </c>
-      <c r="F31" t="inlineStr">
+      <c r="F31" s="4" t="inlineStr">
         <is>
           <t>1342952760</t>
         </is>
       </c>
-      <c r="G31" t="inlineStr">
+      <c r="G31" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">　</t>
         </is>
@@ -3761,7 +3804,7 @@
           <t>192-0914</t>
         </is>
       </c>
-      <c r="J31" t="inlineStr">
+      <c r="J31" s="1" t="inlineStr">
         <is>
           <t>24八王子市</t>
         </is>
@@ -3796,7 +3839,8 @@
           <t>橘　京子</t>
         </is>
       </c>
-      <c r="R31" s="1" t="n">
+      <c r="Q31" s="1" t="n"/>
+      <c r="R31" s="3" t="n">
         <v>39025</v>
       </c>
       <c r="S31" t="n">
@@ -3818,7 +3862,7 @@
           <t>6八福障第5176号</t>
         </is>
       </c>
-      <c r="X31" t="inlineStr">
+      <c r="X31" s="1" t="inlineStr">
         <is>
           <t>育成医療・更生医療</t>
         </is>
@@ -3834,23 +3878,24 @@
       </c>
     </row>
     <row r="32">
-      <c r="A32" t="inlineStr">
+      <c r="A32" s="1" t="inlineStr">
         <is>
           <t>2-29</t>
         </is>
       </c>
-      <c r="D32" t="n">
+      <c r="C32" s="1" t="n"/>
+      <c r="D32" s="2" t="n">
         <v>2952828</v>
       </c>
       <c r="E32" t="n">
         <v>7</v>
       </c>
-      <c r="F32" t="inlineStr">
+      <c r="F32" s="4" t="inlineStr">
         <is>
           <t>1342952828</t>
         </is>
       </c>
-      <c r="G32" t="inlineStr">
+      <c r="G32" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">　</t>
         </is>
@@ -3865,12 +3910,12 @@
           <t>192-0906</t>
         </is>
       </c>
-      <c r="J32" t="inlineStr">
+      <c r="J32" s="1" t="inlineStr">
         <is>
           <t>24八王子市</t>
         </is>
       </c>
-      <c r="K32" t="inlineStr">
+      <c r="K32" s="1" t="inlineStr">
         <is>
           <t>八王子市北野町５６０－２３</t>
         </is>
@@ -3900,6 +3945,7 @@
           <t>新井　幸子</t>
         </is>
       </c>
+      <c r="Q32" s="1" t="n"/>
       <c r="R32" t="n">
         <v>39227</v>
       </c>
@@ -3909,7 +3955,7 @@
       <c r="T32" t="n">
         <v>39295</v>
       </c>
-      <c r="U32" t="inlineStr">
+      <c r="U32" s="1" t="inlineStr">
         <is>
           <t>19福保障計第430号</t>
         </is>
@@ -3922,7 +3968,7 @@
           <t>7八福障第1714号</t>
         </is>
       </c>
-      <c r="X32" t="inlineStr">
+      <c r="X32" s="1" t="inlineStr">
         <is>
           <t>育成医療・更生医療</t>
         </is>
@@ -3938,7 +3984,7 @@
       </c>
     </row>
     <row r="33">
-      <c r="A33" t="inlineStr">
+      <c r="A33" s="1" t="inlineStr">
         <is>
           <t>2-30</t>
         </is>
@@ -3948,18 +3994,18 @@
           <t>○</t>
         </is>
       </c>
-      <c r="D33" t="n">
+      <c r="D33" s="2" t="n">
         <v>2952893</v>
       </c>
       <c r="E33" t="n">
         <v>7</v>
       </c>
-      <c r="F33" t="inlineStr">
+      <c r="F33" s="4" t="inlineStr">
         <is>
           <t>1342952893</t>
         </is>
       </c>
-      <c r="G33" t="inlineStr">
+      <c r="G33" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">　</t>
         </is>
@@ -3974,12 +4020,12 @@
           <t>193-0931</t>
         </is>
       </c>
-      <c r="J33" t="inlineStr">
+      <c r="J33" s="1" t="inlineStr">
         <is>
           <t>24八王子市</t>
         </is>
       </c>
-      <c r="K33" t="inlineStr">
+      <c r="K33" s="1" t="inlineStr">
         <is>
           <t>八王子市台町４－４５－１０　台町ビル１階</t>
         </is>
@@ -4009,6 +4055,7 @@
           <t>沢田　英之</t>
         </is>
       </c>
+      <c r="Q33" s="1" t="n"/>
       <c r="R33" t="n">
         <v>39150</v>
       </c>
@@ -4018,12 +4065,12 @@
       <c r="T33" t="n">
         <v>39234</v>
       </c>
-      <c r="U33" t="inlineStr">
+      <c r="U33" s="1" t="inlineStr">
         <is>
           <t>19福保障計第209号</t>
         </is>
       </c>
-      <c r="X33" t="inlineStr">
+      <c r="X33" s="1" t="inlineStr">
         <is>
           <t>育成医療・更生医療</t>
         </is>
@@ -4047,23 +4094,24 @@
       </c>
     </row>
     <row r="34">
-      <c r="A34" t="inlineStr">
+      <c r="A34" s="1" t="inlineStr">
         <is>
           <t>2-31</t>
         </is>
       </c>
-      <c r="D34" t="n">
+      <c r="C34" s="1" t="n"/>
+      <c r="D34" s="2" t="n">
         <v>2952976</v>
       </c>
       <c r="E34" t="n">
         <v>7</v>
       </c>
-      <c r="F34" t="inlineStr">
+      <c r="F34" s="4" t="inlineStr">
         <is>
           <t>1342952976</t>
         </is>
       </c>
-      <c r="G34" t="inlineStr">
+      <c r="G34" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">　</t>
         </is>
@@ -4078,7 +4126,7 @@
           <t>192-0075</t>
         </is>
       </c>
-      <c r="J34" t="inlineStr">
+      <c r="J34" s="1" t="inlineStr">
         <is>
           <t>24八王子市</t>
         </is>
@@ -4118,7 +4166,7 @@
           <t>変更届（河合　大樹、～令和7年3月31日）</t>
         </is>
       </c>
-      <c r="R34" s="1" t="n">
+      <c r="R34" s="3" t="n">
         <v>39022</v>
       </c>
       <c r="S34" t="n">
@@ -4127,7 +4175,7 @@
       <c r="T34" t="n">
         <v>39114</v>
       </c>
-      <c r="U34" t="inlineStr">
+      <c r="U34" s="1" t="inlineStr">
         <is>
           <t>18福保障計第1319号</t>
         </is>
@@ -4140,7 +4188,7 @@
           <t>6八福障第5666号</t>
         </is>
       </c>
-      <c r="X34" t="inlineStr">
+      <c r="X34" s="1" t="inlineStr">
         <is>
           <t>育成医療・更生医療</t>
         </is>
@@ -4156,23 +4204,24 @@
       </c>
     </row>
     <row r="35">
-      <c r="A35" t="inlineStr">
+      <c r="A35" s="1" t="inlineStr">
         <is>
           <t>2-32</t>
         </is>
       </c>
-      <c r="D35" t="n">
+      <c r="C35" s="1" t="n"/>
+      <c r="D35" s="2" t="n">
         <v>2953057</v>
       </c>
       <c r="E35" t="n">
         <v>7</v>
       </c>
-      <c r="F35" t="inlineStr">
+      <c r="F35" s="4" t="inlineStr">
         <is>
           <t>1342953057</t>
         </is>
       </c>
-      <c r="G35" t="inlineStr">
+      <c r="G35" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">　</t>
         </is>
@@ -4182,12 +4231,12 @@
           <t>ウェルパーク薬局　八王子北口店</t>
         </is>
       </c>
-      <c r="I35" t="inlineStr">
+      <c r="I35" s="5" t="inlineStr">
         <is>
           <t>192-0083</t>
         </is>
       </c>
-      <c r="J35" t="inlineStr">
+      <c r="J35" s="1" t="inlineStr">
         <is>
           <t>24八王子市</t>
         </is>
@@ -4227,7 +4276,7 @@
           <t>変更届（粉川　茅奈美、～令和7年12月31日）</t>
         </is>
       </c>
-      <c r="R35" s="1" t="n">
+      <c r="R35" s="3" t="n">
         <v>40387</v>
       </c>
       <c r="S35" t="n">
@@ -4275,23 +4324,24 @@
       </c>
     </row>
     <row r="36">
-      <c r="A36" t="inlineStr">
+      <c r="A36" s="1" t="inlineStr">
         <is>
           <t>2-33</t>
         </is>
       </c>
-      <c r="D36" t="n">
+      <c r="C36" s="1" t="n"/>
+      <c r="D36" s="2" t="n">
         <v>2953073</v>
       </c>
       <c r="E36" t="n">
         <v>7</v>
       </c>
-      <c r="F36" t="inlineStr">
+      <c r="F36" s="4" t="inlineStr">
         <is>
           <t>1342953073</t>
         </is>
       </c>
-      <c r="G36" t="inlineStr">
+      <c r="G36" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">　</t>
         </is>
@@ -4306,12 +4356,12 @@
           <t>193-0832</t>
         </is>
       </c>
-      <c r="J36" t="inlineStr">
+      <c r="J36" s="1" t="inlineStr">
         <is>
           <t>24八王子市</t>
         </is>
       </c>
-      <c r="K36" t="inlineStr">
+      <c r="K36" s="1" t="inlineStr">
         <is>
           <t>八王子市散田町４－１１－１５</t>
         </is>
@@ -4346,7 +4396,7 @@
           <t>変更届（佐藤　宏子、～平成28年９月11日）</t>
         </is>
       </c>
-      <c r="R36" s="1" t="n">
+      <c r="R36" s="3" t="n">
         <v>39157</v>
       </c>
       <c r="S36" t="n">
@@ -4355,7 +4405,7 @@
       <c r="T36" t="n">
         <v>39234</v>
       </c>
-      <c r="U36" t="inlineStr">
+      <c r="U36" s="1" t="inlineStr">
         <is>
           <t>19福保障計第209号</t>
         </is>
@@ -4368,7 +4418,7 @@
           <t>6八福障第7016号</t>
         </is>
       </c>
-      <c r="X36" t="inlineStr">
+      <c r="X36" s="1" t="inlineStr">
         <is>
           <t>育成医療・更生医療</t>
         </is>
@@ -4384,23 +4434,23 @@
       </c>
     </row>
     <row r="37">
-      <c r="A37" t="inlineStr">
+      <c r="A37" s="1" t="inlineStr">
         <is>
           <t>2-34</t>
         </is>
       </c>
-      <c r="D37" t="n">
+      <c r="D37" s="2" t="n">
         <v>2953172</v>
       </c>
       <c r="E37" t="n">
         <v>7</v>
       </c>
-      <c r="F37" t="inlineStr">
+      <c r="F37" s="4" t="inlineStr">
         <is>
           <t>1342953172</t>
         </is>
       </c>
-      <c r="G37" t="inlineStr">
+      <c r="G37" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">　</t>
         </is>
@@ -4415,7 +4465,7 @@
           <t>192-0914</t>
         </is>
       </c>
-      <c r="J37" t="inlineStr">
+      <c r="J37" s="1" t="inlineStr">
         <is>
           <t>24八王子市</t>
         </is>
@@ -4455,7 +4505,7 @@
           <t>変更届（原田　靖裕、～平成26年5月31日）</t>
         </is>
       </c>
-      <c r="R37" s="1" t="n">
+      <c r="R37" s="3" t="n">
         <v>39025</v>
       </c>
       <c r="S37" t="n">
@@ -4477,7 +4527,7 @@
           <t>6八福障第5177号</t>
         </is>
       </c>
-      <c r="X37" t="inlineStr">
+      <c r="X37" s="1" t="inlineStr">
         <is>
           <t>育成医療・更生医療</t>
         </is>
@@ -4493,23 +4543,24 @@
       </c>
     </row>
     <row r="38">
-      <c r="A38" t="inlineStr">
+      <c r="A38" s="1" t="inlineStr">
         <is>
           <t>2-35</t>
         </is>
       </c>
-      <c r="D38" t="n">
+      <c r="C38" s="1" t="n"/>
+      <c r="D38" s="2" t="n">
         <v>2955276</v>
       </c>
       <c r="E38" t="n">
         <v>7</v>
       </c>
-      <c r="F38" t="inlineStr">
+      <c r="F38" s="4" t="inlineStr">
         <is>
           <t>1342955276</t>
         </is>
       </c>
-      <c r="G38" t="inlineStr">
+      <c r="G38" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">　</t>
         </is>
@@ -4524,7 +4575,7 @@
           <t>192-0903</t>
         </is>
       </c>
-      <c r="J38" t="inlineStr">
+      <c r="J38" s="1" t="inlineStr">
         <is>
           <t>24八王子市</t>
         </is>
@@ -4564,7 +4615,7 @@
           <t>変更届（梅原　大、～平成29年1月31日）</t>
         </is>
       </c>
-      <c r="R38" s="1" t="n">
+      <c r="R38" s="3" t="n">
         <v>39020</v>
       </c>
       <c r="S38" t="n">
@@ -4573,7 +4624,7 @@
       <c r="T38" t="n">
         <v>39114</v>
       </c>
-      <c r="U38" t="inlineStr">
+      <c r="U38" s="1" t="inlineStr">
         <is>
           <t>18福保障計第1319号</t>
         </is>
@@ -4586,7 +4637,7 @@
           <t>6八福障第5270号</t>
         </is>
       </c>
-      <c r="X38" t="inlineStr">
+      <c r="X38" s="1" t="inlineStr">
         <is>
           <t>育成医療・更生医療</t>
         </is>
@@ -4612,23 +4663,23 @@
       </c>
     </row>
     <row r="39">
-      <c r="A39" t="inlineStr">
+      <c r="A39" s="1" t="inlineStr">
         <is>
           <t>2-36</t>
         </is>
       </c>
-      <c r="D39" t="n">
+      <c r="D39" s="2" t="n">
         <v>2953289</v>
       </c>
       <c r="E39" t="n">
         <v>7</v>
       </c>
-      <c r="F39" t="inlineStr">
+      <c r="F39" s="4" t="inlineStr">
         <is>
           <t>1342953289</t>
         </is>
       </c>
-      <c r="G39" t="inlineStr">
+      <c r="G39" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">　</t>
         </is>
@@ -4643,7 +4694,7 @@
           <t>192-0083</t>
         </is>
       </c>
-      <c r="J39" t="inlineStr">
+      <c r="J39" s="1" t="inlineStr">
         <is>
           <t>24八王子市</t>
         </is>
@@ -4678,7 +4729,8 @@
           <t>山田　弘志</t>
         </is>
       </c>
-      <c r="R39" s="1" t="n">
+      <c r="Q39" s="1" t="n"/>
+      <c r="R39" s="3" t="n">
         <v>39058</v>
       </c>
       <c r="S39" t="n">
@@ -4700,7 +4752,7 @@
           <t>6八福障第7190号</t>
         </is>
       </c>
-      <c r="X39" t="inlineStr">
+      <c r="X39" s="1" t="inlineStr">
         <is>
           <t>育成医療・更生医療</t>
         </is>
@@ -4721,23 +4773,23 @@
       </c>
     </row>
     <row r="40">
-      <c r="A40" t="inlineStr">
+      <c r="A40" s="1" t="inlineStr">
         <is>
           <t>2-37</t>
         </is>
       </c>
-      <c r="D40" t="n">
+      <c r="D40" s="2" t="n">
         <v>2953354</v>
       </c>
       <c r="E40" t="n">
         <v>7</v>
       </c>
-      <c r="F40" t="inlineStr">
+      <c r="F40" s="4" t="inlineStr">
         <is>
           <t>1342953354</t>
         </is>
       </c>
-      <c r="G40" t="inlineStr">
+      <c r="G40" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">　</t>
         </is>
@@ -4752,7 +4804,7 @@
           <t>192-0042</t>
         </is>
       </c>
-      <c r="J40" t="inlineStr">
+      <c r="J40" s="1" t="inlineStr">
         <is>
           <t>24八王子市</t>
         </is>
@@ -4787,7 +4839,8 @@
           <t>大井　志朗</t>
         </is>
       </c>
-      <c r="R40" s="1" t="n">
+      <c r="Q40" s="1" t="n"/>
+      <c r="R40" s="3" t="n">
         <v>39042</v>
       </c>
       <c r="S40" t="n">
@@ -4809,7 +4862,7 @@
           <t>6八福障第5203号</t>
         </is>
       </c>
-      <c r="X40" t="inlineStr">
+      <c r="X40" s="1" t="inlineStr">
         <is>
           <t>育成医療・更生医療</t>
         </is>
@@ -4825,23 +4878,23 @@
       </c>
     </row>
     <row r="41">
-      <c r="A41" t="inlineStr">
+      <c r="A41" s="1" t="inlineStr">
         <is>
           <t>2-38</t>
         </is>
       </c>
-      <c r="D41" t="n">
+      <c r="D41" s="2" t="n">
         <v>2953412</v>
       </c>
       <c r="E41" t="n">
         <v>7</v>
       </c>
-      <c r="F41" t="inlineStr">
+      <c r="F41" s="4" t="inlineStr">
         <is>
           <t>1342953412</t>
         </is>
       </c>
-      <c r="G41" t="inlineStr">
+      <c r="G41" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">　</t>
         </is>
@@ -4851,12 +4904,12 @@
           <t>ふじ薬局　めじろ台店</t>
         </is>
       </c>
-      <c r="I41" t="inlineStr">
+      <c r="I41" s="2" t="inlineStr">
         <is>
           <t>193-0833</t>
         </is>
       </c>
-      <c r="J41" t="inlineStr">
+      <c r="J41" s="1" t="inlineStr">
         <is>
           <t>24八王子市</t>
         </is>
@@ -4891,12 +4944,12 @@
           <t>後藤　明彦</t>
         </is>
       </c>
-      <c r="Q41" t="inlineStr">
+      <c r="Q41" s="1" t="inlineStr">
         <is>
           <t>変更届（藤本　美智子～令和2年4月26日）</t>
         </is>
       </c>
-      <c r="R41" s="1" t="n">
+      <c r="R41" s="3" t="n">
         <v>39423</v>
       </c>
       <c r="S41" t="n">
@@ -4918,7 +4971,7 @@
           <t>7八福障第6127号</t>
         </is>
       </c>
-      <c r="X41" t="inlineStr">
+      <c r="X41" s="1" t="inlineStr">
         <is>
           <t>育成医療・更生医療</t>
         </is>
@@ -4934,7 +4987,7 @@
       </c>
     </row>
     <row r="42">
-      <c r="A42" t="inlineStr">
+      <c r="A42" s="1" t="inlineStr">
         <is>
           <t>2-39</t>
         </is>
@@ -4944,18 +4997,18 @@
           <t>○</t>
         </is>
       </c>
-      <c r="D42" t="n">
+      <c r="D42" s="2" t="n">
         <v>2953503</v>
       </c>
       <c r="E42" t="n">
         <v>7</v>
       </c>
-      <c r="F42" t="inlineStr">
+      <c r="F42" s="4" t="inlineStr">
         <is>
           <t>1342953503</t>
         </is>
       </c>
-      <c r="G42" t="inlineStr">
+      <c r="G42" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">　</t>
         </is>
@@ -4970,7 +5023,7 @@
           <t>192-0916</t>
         </is>
       </c>
-      <c r="J42" t="inlineStr">
+      <c r="J42" s="1" t="inlineStr">
         <is>
           <t>24八王子市</t>
         </is>
@@ -5010,7 +5063,7 @@
           <t>変更届（藤野　操子、～平成30年10月31日）</t>
         </is>
       </c>
-      <c r="R42" s="1" t="n">
+      <c r="R42" s="3" t="n">
         <v>39051</v>
       </c>
       <c r="S42" t="n">
@@ -5019,7 +5072,7 @@
       <c r="T42" t="n">
         <v>39114</v>
       </c>
-      <c r="U42" t="inlineStr">
+      <c r="U42" s="1" t="inlineStr">
         <is>
           <t>18福保障計第1319号</t>
         </is>
@@ -5032,7 +5085,7 @@
           <t>30八福障収第1058号</t>
         </is>
       </c>
-      <c r="X42" t="inlineStr">
+      <c r="X42" s="1" t="inlineStr">
         <is>
           <t>育成医療・更生医療</t>
         </is>
@@ -5061,23 +5114,23 @@
       </c>
     </row>
     <row r="43">
-      <c r="A43" t="inlineStr">
+      <c r="A43" s="1" t="inlineStr">
         <is>
           <t>2-40</t>
         </is>
       </c>
-      <c r="D43" t="n">
+      <c r="D43" s="2" t="n">
         <v>2953511</v>
       </c>
       <c r="E43" t="n">
         <v>7</v>
       </c>
-      <c r="F43" t="inlineStr">
+      <c r="F43" s="4" t="inlineStr">
         <is>
           <t>1342953511</t>
         </is>
       </c>
-      <c r="G43" t="inlineStr">
+      <c r="G43" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">　</t>
         </is>
@@ -5092,7 +5145,7 @@
           <t>192-0046</t>
         </is>
       </c>
-      <c r="J43" t="inlineStr">
+      <c r="J43" s="1" t="inlineStr">
         <is>
           <t>24八王子市</t>
         </is>
@@ -5127,12 +5180,12 @@
           <t>野嶋　亜紀子</t>
         </is>
       </c>
-      <c r="Q43" t="inlineStr">
+      <c r="Q43" s="1" t="inlineStr">
         <is>
           <t>変更届(熊崎　洋子、～令和6年3月31日)</t>
         </is>
       </c>
-      <c r="R43" s="1" t="n">
+      <c r="R43" s="3" t="n">
         <v>41460</v>
       </c>
       <c r="S43" t="n">
@@ -5154,7 +5207,7 @@
           <t>7八福障第4047号</t>
         </is>
       </c>
-      <c r="X43" t="inlineStr">
+      <c r="X43" s="1" t="inlineStr">
         <is>
           <t>育成医療・更生医療</t>
         </is>
@@ -5168,14 +5221,14 @@
       <c r="AA43" t="n">
         <v>42510</v>
       </c>
-      <c r="AC43" t="inlineStr">
+      <c r="AC43" s="1" t="inlineStr">
         <is>
           <t>変更届(古屋希枝、～令和2年11月16日)</t>
         </is>
       </c>
     </row>
     <row r="44">
-      <c r="A44" t="inlineStr">
+      <c r="A44" s="1" t="inlineStr">
         <is>
           <t>2-41</t>
         </is>
@@ -5185,18 +5238,18 @@
           <t>○</t>
         </is>
       </c>
-      <c r="D44" t="n">
+      <c r="D44" s="2" t="n">
         <v>2953552</v>
       </c>
       <c r="E44" t="n">
         <v>7</v>
       </c>
-      <c r="F44" t="inlineStr">
+      <c r="F44" s="4" t="inlineStr">
         <is>
           <t>1342953552</t>
         </is>
       </c>
-      <c r="G44" t="inlineStr">
+      <c r="G44" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">　</t>
         </is>
@@ -5206,12 +5259,12 @@
           <t>グリーン薬局</t>
         </is>
       </c>
-      <c r="I44" t="inlineStr">
+      <c r="I44" s="1" t="inlineStr">
         <is>
           <t>192-0916</t>
         </is>
       </c>
-      <c r="J44" t="inlineStr">
+      <c r="J44" s="1" t="inlineStr">
         <is>
           <t>24八王子市</t>
         </is>
@@ -5246,7 +5299,8 @@
           <t>近藤　みどり</t>
         </is>
       </c>
-      <c r="R44" s="1" t="n">
+      <c r="Q44" s="1" t="n"/>
+      <c r="R44" s="3" t="n">
         <v>40889</v>
       </c>
       <c r="S44" t="n">
@@ -5268,7 +5322,7 @@
           <t>29八福障収第863号</t>
         </is>
       </c>
-      <c r="X44" t="inlineStr">
+      <c r="X44" s="1" t="inlineStr">
         <is>
           <t>育成医療・更生医療</t>
         </is>
@@ -5297,23 +5351,24 @@
       </c>
     </row>
     <row r="45">
-      <c r="A45" t="inlineStr">
+      <c r="A45" s="1" t="inlineStr">
         <is>
           <t>2-42</t>
         </is>
       </c>
-      <c r="D45" t="n">
+      <c r="C45" s="1" t="n"/>
+      <c r="D45" s="2" t="n">
         <v>2953560</v>
       </c>
       <c r="E45" t="n">
         <v>7</v>
       </c>
-      <c r="F45" t="inlineStr">
+      <c r="F45" s="4" t="inlineStr">
         <is>
           <t>1342953560</t>
         </is>
       </c>
-      <c r="G45" t="inlineStr">
+      <c r="G45" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">　</t>
         </is>
@@ -5328,12 +5383,12 @@
           <t>193-0813</t>
         </is>
       </c>
-      <c r="J45" t="inlineStr">
+      <c r="J45" s="1" t="inlineStr">
         <is>
           <t>24八王子市</t>
         </is>
       </c>
-      <c r="K45" t="inlineStr">
+      <c r="K45" s="1" t="inlineStr">
         <is>
           <t>八王子市四谷町７２０－１</t>
         </is>
@@ -5363,7 +5418,7 @@
           <t>曽根原　かい</t>
         </is>
       </c>
-      <c r="Q45" t="inlineStr">
+      <c r="Q45" s="1" t="inlineStr">
         <is>
           <t>変更届（杉山　哲久　、～平成24年11月14日）</t>
         </is>
@@ -5377,7 +5432,7 @@
       <c r="T45" t="n">
         <v>39234</v>
       </c>
-      <c r="U45" t="inlineStr">
+      <c r="U45" s="1" t="inlineStr">
         <is>
           <t>19福保障計第209号</t>
         </is>
@@ -5390,7 +5445,7 @@
           <t>6八福障第6828号</t>
         </is>
       </c>
-      <c r="X45" t="inlineStr">
+      <c r="X45" s="1" t="inlineStr">
         <is>
           <t>育成医療・更生医療</t>
         </is>
@@ -5406,23 +5461,23 @@
       </c>
     </row>
     <row r="46">
-      <c r="A46" t="inlineStr">
+      <c r="A46" s="1" t="inlineStr">
         <is>
           <t>2-43</t>
         </is>
       </c>
-      <c r="D46" t="n">
+      <c r="D46" s="2" t="n">
         <v>2956159</v>
       </c>
       <c r="E46" t="n">
         <v>7</v>
       </c>
-      <c r="F46" t="inlineStr">
+      <c r="F46" s="4" t="inlineStr">
         <is>
           <t>1342956159</t>
         </is>
       </c>
-      <c r="G46" t="inlineStr">
+      <c r="G46" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">　</t>
         </is>
@@ -5437,7 +5492,7 @@
           <t>193-0833</t>
         </is>
       </c>
-      <c r="J46" t="inlineStr">
+      <c r="J46" s="1" t="inlineStr">
         <is>
           <t>24八王子市</t>
         </is>
@@ -5477,10 +5532,10 @@
           <t>変更届(小野　宏、～令和7年2月28日）</t>
         </is>
       </c>
-      <c r="R46" s="1" t="n">
+      <c r="R46" s="3" t="n">
         <v>38933</v>
       </c>
-      <c r="S46" s="1" t="n">
+      <c r="S46" s="3" t="n">
         <v>38991</v>
       </c>
       <c r="T46" t="n">
@@ -5499,7 +5554,7 @@
           <t>30八福障収第716号</t>
         </is>
       </c>
-      <c r="X46" t="inlineStr">
+      <c r="X46" s="1" t="inlineStr">
         <is>
           <t>育成医療・更生医療</t>
         </is>
@@ -5535,23 +5590,23 @@
       </c>
     </row>
     <row r="47">
-      <c r="A47" t="inlineStr">
+      <c r="A47" s="1" t="inlineStr">
         <is>
           <t>2-44</t>
         </is>
       </c>
-      <c r="D47" t="n">
+      <c r="D47" s="2" t="n">
         <v>2953867</v>
       </c>
       <c r="E47" t="n">
         <v>7</v>
       </c>
-      <c r="F47" t="inlineStr">
+      <c r="F47" s="4" t="inlineStr">
         <is>
           <t>1342953867</t>
         </is>
       </c>
-      <c r="G47" t="inlineStr">
+      <c r="G47" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">　</t>
         </is>
@@ -5566,7 +5621,7 @@
           <t>192-0045</t>
         </is>
       </c>
-      <c r="J47" t="inlineStr">
+      <c r="J47" s="1" t="inlineStr">
         <is>
           <t>24八王子市</t>
         </is>
@@ -5606,7 +5661,7 @@
           <t>変更届(宇田川　悟史～令和元年8月1日)</t>
         </is>
       </c>
-      <c r="R47" s="1" t="n">
+      <c r="R47" s="3" t="n">
         <v>41727</v>
       </c>
       <c r="S47" t="n">
@@ -5621,7 +5676,7 @@
 第362号</t>
         </is>
       </c>
-      <c r="V47" s="1" t="n">
+      <c r="V47" s="3" t="n">
         <v>46113</v>
       </c>
       <c r="W47" t="inlineStr">
@@ -5629,7 +5684,7 @@
           <t>7八福障第8160号</t>
         </is>
       </c>
-      <c r="X47" t="inlineStr">
+      <c r="X47" s="1" t="inlineStr">
         <is>
           <t>育成医療・更生医療</t>
         </is>
@@ -5643,30 +5698,33 @@
       <c r="AA47" t="n">
         <v>42606</v>
       </c>
-      <c r="AC47" t="inlineStr">
+      <c r="AC47" s="1" t="inlineStr">
         <is>
           <t>変更届（代表取締役：長尾　愛→長尾　健、変更日：令和７年１月１１日）</t>
         </is>
       </c>
+      <c r="AD47" s="1" t="n"/>
+      <c r="AE47" s="1" t="n"/>
     </row>
     <row r="48">
-      <c r="A48" t="inlineStr">
+      <c r="A48" s="1" t="inlineStr">
         <is>
           <t>2-45</t>
         </is>
       </c>
-      <c r="D48" t="n">
+      <c r="C48" s="1" t="n"/>
+      <c r="D48" s="2" t="n">
         <v>2953891</v>
       </c>
       <c r="E48" t="n">
         <v>7</v>
       </c>
-      <c r="F48" t="inlineStr">
+      <c r="F48" s="4" t="inlineStr">
         <is>
           <t>1342953891</t>
         </is>
       </c>
-      <c r="G48" t="inlineStr">
+      <c r="G48" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">　</t>
         </is>
@@ -5681,12 +5739,12 @@
           <t>192-0154</t>
         </is>
       </c>
-      <c r="J48" t="inlineStr">
+      <c r="J48" s="1" t="inlineStr">
         <is>
           <t>24八王子市</t>
         </is>
       </c>
-      <c r="K48" t="inlineStr">
+      <c r="K48" s="1" t="inlineStr">
         <is>
           <t>八王子市下恩方１１４５－１</t>
         </is>
@@ -5721,7 +5779,7 @@
           <t>変更届(松寺　義貴、～令和6年8月27日）</t>
         </is>
       </c>
-      <c r="R48" s="1" t="n">
+      <c r="R48" s="3" t="n">
         <v>39155</v>
       </c>
       <c r="S48" t="n">
@@ -5730,7 +5788,7 @@
       <c r="T48" t="n">
         <v>39234</v>
       </c>
-      <c r="U48" t="inlineStr">
+      <c r="U48" s="1" t="inlineStr">
         <is>
           <t>19福保障計第209号</t>
         </is>
@@ -5743,7 +5801,7 @@
           <t>6八福障第6795号</t>
         </is>
       </c>
-      <c r="X48" t="inlineStr">
+      <c r="X48" s="1" t="inlineStr">
         <is>
           <t>育成医療・更生医療</t>
         </is>
@@ -5759,7 +5817,7 @@
       </c>
     </row>
     <row r="49">
-      <c r="A49" t="inlineStr">
+      <c r="A49" s="1" t="inlineStr">
         <is>
           <t>2-46</t>
         </is>
@@ -5769,18 +5827,18 @@
           <t>○</t>
         </is>
       </c>
-      <c r="D49" t="n">
+      <c r="D49" s="2" t="n">
         <v>2953941</v>
       </c>
       <c r="E49" t="n">
         <v>7</v>
       </c>
-      <c r="F49" t="inlineStr">
+      <c r="F49" s="4" t="inlineStr">
         <is>
           <t>1342953941</t>
         </is>
       </c>
-      <c r="G49" t="inlineStr">
+      <c r="G49" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">　</t>
         </is>
@@ -5795,7 +5853,7 @@
           <t>192-0073</t>
         </is>
       </c>
-      <c r="J49" t="inlineStr">
+      <c r="J49" s="1" t="inlineStr">
         <is>
           <t>24八王子市</t>
         </is>
@@ -5835,7 +5893,7 @@
           <t>変更届(田村　剛、～平成27年9月16日）</t>
         </is>
       </c>
-      <c r="R49" s="1" t="n">
+      <c r="R49" s="3" t="n">
         <v>39132</v>
       </c>
       <c r="S49" t="n">
@@ -5857,7 +5915,7 @@
           <t>24福保障計第1738号</t>
         </is>
       </c>
-      <c r="X49" t="inlineStr">
+      <c r="X49" s="1" t="inlineStr">
         <is>
           <t>育成医療・更生医療</t>
         </is>
@@ -5891,7 +5949,7 @@
       </c>
     </row>
     <row r="50">
-      <c r="A50" t="inlineStr">
+      <c r="A50" s="1" t="inlineStr">
         <is>
           <t>2-47</t>
         </is>
@@ -5901,18 +5959,18 @@
           <t>○</t>
         </is>
       </c>
-      <c r="D50" t="n">
+      <c r="D50" s="2" t="n">
         <v>2953958</v>
       </c>
       <c r="E50" t="n">
         <v>7</v>
       </c>
-      <c r="F50" t="inlineStr">
+      <c r="F50" s="4" t="inlineStr">
         <is>
           <t>1342953958</t>
         </is>
       </c>
-      <c r="G50" t="inlineStr">
+      <c r="G50" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">　</t>
         </is>
@@ -5922,12 +5980,12 @@
           <t>あさひ薬局</t>
         </is>
       </c>
-      <c r="I50" t="inlineStr">
+      <c r="I50" s="2" t="inlineStr">
         <is>
           <t>192-0024</t>
         </is>
       </c>
-      <c r="J50" t="inlineStr">
+      <c r="J50" s="1" t="inlineStr">
         <is>
           <t>24八王子市</t>
         </is>
@@ -5952,12 +6010,12 @@
           <t>千葉　聖</t>
         </is>
       </c>
-      <c r="Q50" t="inlineStr">
+      <c r="Q50" s="1" t="inlineStr">
         <is>
           <t>変更届(田辺　道夫、～平成21年７月31日）</t>
         </is>
       </c>
-      <c r="R50" s="1" t="n">
+      <c r="R50" s="3" t="n">
         <v>39416</v>
       </c>
       <c r="S50" t="n">
@@ -5979,7 +6037,7 @@
           <t>25福保障計第1523号</t>
         </is>
       </c>
-      <c r="X50" t="inlineStr">
+      <c r="X50" s="1" t="inlineStr">
         <is>
           <t>育成医療・更生医療</t>
         </is>
@@ -6003,23 +6061,23 @@
       </c>
     </row>
     <row r="51">
-      <c r="A51" t="inlineStr">
+      <c r="A51" s="1" t="inlineStr">
         <is>
           <t>2-48</t>
         </is>
       </c>
-      <c r="D51" t="n">
+      <c r="D51" s="2" t="n">
         <v>2953982</v>
       </c>
       <c r="E51" t="n">
         <v>7</v>
       </c>
-      <c r="F51" t="inlineStr">
+      <c r="F51" s="4" t="inlineStr">
         <is>
           <t>1342953982</t>
         </is>
       </c>
-      <c r="G51" t="inlineStr">
+      <c r="G51" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">　</t>
         </is>
@@ -6029,12 +6087,12 @@
           <t>クリエイトエス・ディー八王子元本郷店薬局</t>
         </is>
       </c>
-      <c r="I51" t="inlineStr">
+      <c r="I51" s="2" t="inlineStr">
         <is>
           <t>192-0051</t>
         </is>
       </c>
-      <c r="J51" t="inlineStr">
+      <c r="J51" s="1" t="inlineStr">
         <is>
           <t>24八王子市</t>
         </is>
@@ -6069,12 +6127,12 @@
           <t>鳥谷　いづみ</t>
         </is>
       </c>
-      <c r="Q51" t="inlineStr">
+      <c r="Q51" s="1" t="inlineStr">
         <is>
           <t>変更届(関川　裕也、～令和6年9月10日）</t>
         </is>
       </c>
-      <c r="R51" s="1" t="n">
+      <c r="R51" s="3" t="n">
         <v>39479</v>
       </c>
       <c r="S51" t="n">
@@ -6088,7 +6146,7 @@
           <t>19福保障計第1462号</t>
         </is>
       </c>
-      <c r="V51" s="1" t="n">
+      <c r="V51" s="3" t="n">
         <v>46113</v>
       </c>
       <c r="W51" t="inlineStr">
@@ -6096,7 +6154,7 @@
           <t>7八福障第8160号</t>
         </is>
       </c>
-      <c r="X51" t="inlineStr">
+      <c r="X51" s="1" t="inlineStr">
         <is>
           <t>育成医療・更生医療</t>
         </is>
@@ -6117,23 +6175,23 @@
       </c>
     </row>
     <row r="52">
-      <c r="A52" t="inlineStr">
+      <c r="A52" s="1" t="inlineStr">
         <is>
           <t>2-49</t>
         </is>
       </c>
-      <c r="D52" t="n">
+      <c r="D52" s="2" t="n">
         <v>2954030</v>
       </c>
       <c r="E52" t="n">
         <v>7</v>
       </c>
-      <c r="F52" t="inlineStr">
+      <c r="F52" s="4" t="inlineStr">
         <is>
           <t>1342954030</t>
         </is>
       </c>
-      <c r="G52" t="inlineStr">
+      <c r="G52" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">　</t>
         </is>
@@ -6148,12 +6206,12 @@
           <t>192-0914</t>
         </is>
       </c>
-      <c r="J52" t="inlineStr">
+      <c r="J52" s="1" t="inlineStr">
         <is>
           <t>24八王子市</t>
         </is>
       </c>
-      <c r="K52" t="inlineStr">
+      <c r="K52" s="2" t="inlineStr">
         <is>
           <t>八王子市片倉町３４２－３　Ｋ’ｓ片倉ビル１階</t>
         </is>
@@ -6183,7 +6241,7 @@
           <t>小林　貴美</t>
         </is>
       </c>
-      <c r="R52" s="1" t="n">
+      <c r="R52" s="3" t="n">
         <v>39738</v>
       </c>
       <c r="S52" t="n">
@@ -6205,7 +6263,7 @@
           <t>26福保障計第1657号</t>
         </is>
       </c>
-      <c r="X52" t="inlineStr">
+      <c r="X52" s="1" t="inlineStr">
         <is>
           <t>育成医療・更生医療</t>
         </is>
@@ -6226,23 +6284,23 @@
       </c>
     </row>
     <row r="53">
-      <c r="A53" t="inlineStr">
+      <c r="A53" s="1" t="inlineStr">
         <is>
           <t>2-50</t>
         </is>
       </c>
-      <c r="D53" t="n">
+      <c r="D53" s="2" t="n">
         <v>2954055</v>
       </c>
       <c r="E53" t="n">
         <v>7</v>
       </c>
-      <c r="F53" t="inlineStr">
+      <c r="F53" s="4" t="inlineStr">
         <is>
           <t>1342954055</t>
         </is>
       </c>
-      <c r="G53" t="inlineStr">
+      <c r="G53" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">　</t>
         </is>
@@ -6257,7 +6315,7 @@
           <t>193-0931</t>
         </is>
       </c>
-      <c r="J53" t="inlineStr">
+      <c r="J53" s="1" t="inlineStr">
         <is>
           <t>24八王子市</t>
         </is>
@@ -6292,15 +6350,15 @@
           <t>井上　慶大</t>
         </is>
       </c>
-      <c r="Q53" t="inlineStr">
+      <c r="Q53" s="1" t="inlineStr">
         <is>
           <t>変更届(齋藤　紋也子、～令和2年7月31日）</t>
         </is>
       </c>
-      <c r="R53" s="1" t="n">
+      <c r="R53" s="3" t="n">
         <v>39036</v>
       </c>
-      <c r="S53" s="1" t="n">
+      <c r="S53" s="3" t="n">
         <v>38808</v>
       </c>
       <c r="T53" t="n">
@@ -6319,7 +6377,7 @@
           <t>6八福障第5357号</t>
         </is>
       </c>
-      <c r="X53" t="inlineStr">
+      <c r="X53" s="1" t="inlineStr">
         <is>
           <t>育成医療・更生医療</t>
         </is>
@@ -6340,7 +6398,7 @@
       </c>
     </row>
     <row r="54">
-      <c r="A54" t="inlineStr">
+      <c r="A54" s="1" t="inlineStr">
         <is>
           <t>2-51</t>
         </is>
@@ -6350,18 +6408,18 @@
           <t>○</t>
         </is>
       </c>
-      <c r="D54" t="n">
+      <c r="D54" s="2" t="n">
         <v>2955300</v>
       </c>
       <c r="E54" t="n">
         <v>7</v>
       </c>
-      <c r="F54" t="inlineStr">
+      <c r="F54" s="4" t="inlineStr">
         <is>
           <t>1342955300</t>
         </is>
       </c>
-      <c r="G54" t="inlineStr">
+      <c r="G54" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">　</t>
         </is>
@@ -6376,7 +6434,7 @@
           <t>193-0832</t>
         </is>
       </c>
-      <c r="J54" t="inlineStr">
+      <c r="J54" s="1" t="inlineStr">
         <is>
           <t>24八王子市</t>
         </is>
@@ -6416,10 +6474,10 @@
           <t>変更届（有吉　麻理恵　、～平成24年６月15日）</t>
         </is>
       </c>
-      <c r="R54" s="1" t="n">
+      <c r="R54" s="3" t="n">
         <v>39108</v>
       </c>
-      <c r="S54" s="1" t="n">
+      <c r="S54" s="3" t="n">
         <v>38808</v>
       </c>
       <c r="T54" t="n">
@@ -6438,7 +6496,7 @@
           <t>24福保障計第1452号</t>
         </is>
       </c>
-      <c r="X54" t="inlineStr">
+      <c r="X54" s="1" t="inlineStr">
         <is>
           <t>育成医療・更生医療</t>
         </is>
@@ -6467,23 +6525,23 @@
       </c>
     </row>
     <row r="55">
-      <c r="A55" t="inlineStr">
+      <c r="A55" s="1" t="inlineStr">
         <is>
           <t>2-52</t>
         </is>
       </c>
-      <c r="D55" t="n">
+      <c r="D55" s="2" t="n">
         <v>2954147</v>
       </c>
       <c r="E55" t="n">
         <v>7</v>
       </c>
-      <c r="F55" t="inlineStr">
+      <c r="F55" s="4" t="inlineStr">
         <is>
           <t>1342954147</t>
         </is>
       </c>
-      <c r="G55" t="inlineStr">
+      <c r="G55" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">　</t>
         </is>
@@ -6498,7 +6556,7 @@
           <t>193-0845</t>
         </is>
       </c>
-      <c r="J55" t="inlineStr">
+      <c r="J55" s="1" t="inlineStr">
         <is>
           <t>24八王子市</t>
         </is>
@@ -6533,11 +6591,12 @@
           <t>金森　建夫</t>
         </is>
       </c>
-      <c r="Q55" t="inlineStr">
+      <c r="Q55" s="1" t="inlineStr">
         <is>
           <t>変更届(高部　雅、～令和6年7月25日）</t>
         </is>
       </c>
+      <c r="R55" s="3" t="n"/>
       <c r="S55" t="n">
         <v>38899</v>
       </c>
@@ -6557,7 +6616,7 @@
           <t>6八福障第1276号</t>
         </is>
       </c>
-      <c r="X55" t="inlineStr">
+      <c r="X55" s="1" t="inlineStr">
         <is>
           <t>育成医療・更生医療</t>
         </is>
@@ -6578,23 +6637,23 @@
       </c>
     </row>
     <row r="56">
-      <c r="A56" t="inlineStr">
+      <c r="A56" s="1" t="inlineStr">
         <is>
           <t>2-53</t>
         </is>
       </c>
-      <c r="D56" t="n">
+      <c r="D56" s="2" t="n">
         <v>2955946</v>
       </c>
       <c r="E56" t="n">
         <v>7</v>
       </c>
-      <c r="F56" t="inlineStr">
+      <c r="F56" s="4" t="inlineStr">
         <is>
           <t>1342955946</t>
         </is>
       </c>
-      <c r="G56" t="inlineStr">
+      <c r="G56" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">　</t>
         </is>
@@ -6604,12 +6663,12 @@
           <t>クオール薬局　八王子店</t>
         </is>
       </c>
-      <c r="I56" t="inlineStr">
+      <c r="I56" s="1" t="inlineStr">
         <is>
           <t>192-0904</t>
         </is>
       </c>
-      <c r="J56" t="inlineStr">
+      <c r="J56" s="1" t="inlineStr">
         <is>
           <t>24八王子市</t>
         </is>
@@ -6644,12 +6703,12 @@
           <t>秋間　愼介</t>
         </is>
       </c>
-      <c r="Q56" t="inlineStr">
+      <c r="Q56" s="1" t="inlineStr">
         <is>
           <t>変更届(松田　早苗、～令和4年9月4日）</t>
         </is>
       </c>
-      <c r="R56" s="1" t="n">
+      <c r="R56" s="3" t="n">
         <v>40148</v>
       </c>
       <c r="S56" t="n">
@@ -6702,23 +6761,23 @@
       </c>
     </row>
     <row r="57">
-      <c r="A57" t="inlineStr">
+      <c r="A57" s="1" t="inlineStr">
         <is>
           <t>2-54</t>
         </is>
       </c>
-      <c r="D57" t="n">
+      <c r="D57" s="2" t="n">
         <v>2955532</v>
       </c>
       <c r="E57" t="n">
         <v>7</v>
       </c>
-      <c r="F57" t="inlineStr">
+      <c r="F57" s="4" t="inlineStr">
         <is>
           <t>1342955532</t>
         </is>
       </c>
-      <c r="G57" t="inlineStr">
+      <c r="G57" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">　</t>
         </is>
@@ -6733,7 +6792,7 @@
           <t>192-0046</t>
         </is>
       </c>
-      <c r="J57" t="inlineStr">
+      <c r="J57" s="1" t="inlineStr">
         <is>
           <t>24八王子市</t>
         </is>
@@ -6768,11 +6827,12 @@
           <t>杉本　梨枝</t>
         </is>
       </c>
-      <c r="Q57" t="inlineStr">
+      <c r="Q57" s="1" t="inlineStr">
         <is>
           <t>変更届（中井　亮太、～令和7年12月31日）</t>
         </is>
       </c>
+      <c r="R57" s="3" t="n"/>
       <c r="S57" t="n">
         <v>38899</v>
       </c>
@@ -6792,7 +6852,7 @@
           <t>6八福障第1259号</t>
         </is>
       </c>
-      <c r="X57" t="inlineStr">
+      <c r="X57" s="1" t="inlineStr">
         <is>
           <t>育成医療・更生医療</t>
         </is>
@@ -6853,23 +6913,23 @@
       </c>
     </row>
     <row r="58">
-      <c r="A58" t="inlineStr">
+      <c r="A58" s="1" t="inlineStr">
         <is>
           <t>2-55</t>
         </is>
       </c>
-      <c r="D58" t="n">
+      <c r="D58" s="2" t="n">
         <v>2954246</v>
       </c>
       <c r="E58" t="n">
         <v>7</v>
       </c>
-      <c r="F58" t="inlineStr">
+      <c r="F58" s="4" t="inlineStr">
         <is>
           <t>1342954246</t>
         </is>
       </c>
-      <c r="G58" t="inlineStr">
+      <c r="G58" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">　</t>
         </is>
@@ -6884,7 +6944,7 @@
           <t>193-0833</t>
         </is>
       </c>
-      <c r="J58" t="inlineStr">
+      <c r="J58" s="1" t="inlineStr">
         <is>
           <t>24八王子市</t>
         </is>
@@ -6919,12 +6979,12 @@
           <t>有賀　直樹</t>
         </is>
       </c>
-      <c r="Q58" t="inlineStr">
+      <c r="Q58" s="1" t="inlineStr">
         <is>
           <t>変更届(千葉　聖、～令和5年5月15日）</t>
         </is>
       </c>
-      <c r="R58" s="1" t="n">
+      <c r="R58" s="3" t="n">
         <v>39020</v>
       </c>
       <c r="S58" t="n">
@@ -6946,7 +7006,7 @@
           <t>6八福障第5240号</t>
         </is>
       </c>
-      <c r="X58" t="inlineStr">
+      <c r="X58" s="1" t="inlineStr">
         <is>
           <t>育成医療・更生医療</t>
         </is>
@@ -6972,23 +7032,23 @@
       </c>
     </row>
     <row r="59">
-      <c r="A59" t="inlineStr">
+      <c r="A59" s="1" t="inlineStr">
         <is>
           <t>2-56</t>
         </is>
       </c>
-      <c r="D59" t="n">
+      <c r="D59" s="2" t="n">
         <v>2955326</v>
       </c>
       <c r="E59" t="n">
         <v>7</v>
       </c>
-      <c r="F59" t="inlineStr">
+      <c r="F59" s="4" t="inlineStr">
         <is>
           <t>1342955326</t>
         </is>
       </c>
-      <c r="G59" t="inlineStr">
+      <c r="G59" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">　</t>
         </is>
@@ -7003,7 +7063,7 @@
           <t>193-0832</t>
         </is>
       </c>
-      <c r="J59" t="inlineStr">
+      <c r="J59" s="1" t="inlineStr">
         <is>
           <t>24八王子市</t>
         </is>
@@ -7038,12 +7098,12 @@
           <t>菅沼　麻里奈</t>
         </is>
       </c>
-      <c r="Q59" t="inlineStr">
+      <c r="Q59" s="1" t="inlineStr">
         <is>
           <t>変更届（轟木　孝倫、～令和7年5月31日）</t>
         </is>
       </c>
-      <c r="R59" s="1" t="n">
+      <c r="R59" s="3" t="n">
         <v>39050</v>
       </c>
       <c r="S59" t="n">
@@ -7065,7 +7125,7 @@
           <t>6八福障第5096号</t>
         </is>
       </c>
-      <c r="X59" t="inlineStr">
+      <c r="X59" s="1" t="inlineStr">
         <is>
           <t>育成医療・更生医療</t>
         </is>
@@ -7106,23 +7166,23 @@
       </c>
     </row>
     <row r="60">
-      <c r="A60" t="inlineStr">
+      <c r="A60" s="1" t="inlineStr">
         <is>
           <t>2-57</t>
         </is>
       </c>
-      <c r="D60" t="n">
+      <c r="D60" s="2" t="n">
         <v>2954378</v>
       </c>
       <c r="E60" t="n">
         <v>7</v>
       </c>
-      <c r="F60" t="inlineStr">
+      <c r="F60" s="4" t="inlineStr">
         <is>
           <t>1342954378</t>
         </is>
       </c>
-      <c r="G60" t="inlineStr">
+      <c r="G60" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">　</t>
         </is>
@@ -7137,7 +7197,7 @@
           <t>193-0845</t>
         </is>
       </c>
-      <c r="J60" t="inlineStr">
+      <c r="J60" s="1" t="inlineStr">
         <is>
           <t>24八王子市</t>
         </is>
@@ -7172,12 +7232,12 @@
           <t>橋本　咲帆</t>
         </is>
       </c>
-      <c r="Q60" t="inlineStr">
+      <c r="Q60" s="1" t="inlineStr">
         <is>
           <t>変更届(吉田　善紀、～令和7年9月30日）</t>
         </is>
       </c>
-      <c r="R60" s="1" t="n">
+      <c r="R60" s="3" t="n">
         <v>38997</v>
       </c>
       <c r="S60" t="n">
@@ -7199,7 +7259,7 @@
           <t>6八福障第5356号</t>
         </is>
       </c>
-      <c r="X60" t="inlineStr">
+      <c r="X60" s="1" t="inlineStr">
         <is>
           <t>育成医療・更生医療</t>
         </is>
@@ -7225,7 +7285,7 @@
       </c>
     </row>
     <row r="61">
-      <c r="A61" t="inlineStr">
+      <c r="A61" s="1" t="inlineStr">
         <is>
           <t>2-58</t>
         </is>
@@ -7235,18 +7295,18 @@
           <t>○</t>
         </is>
       </c>
-      <c r="D61" t="n">
+      <c r="D61" s="2" t="n">
         <v>2954394</v>
       </c>
       <c r="E61" t="n">
         <v>7</v>
       </c>
-      <c r="F61" t="inlineStr">
+      <c r="F61" s="4" t="inlineStr">
         <is>
           <t>1342954394</t>
         </is>
       </c>
-      <c r="G61" t="inlineStr">
+      <c r="G61" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">　</t>
         </is>
@@ -7256,12 +7316,12 @@
           <t>日本調剤　八王子薬局</t>
         </is>
       </c>
-      <c r="I61" t="inlineStr">
+      <c r="I61" s="1" t="inlineStr">
         <is>
           <t>192-0046</t>
         </is>
       </c>
-      <c r="J61" t="inlineStr">
+      <c r="J61" s="1" t="inlineStr">
         <is>
           <t>24八王子市</t>
         </is>
@@ -7271,7 +7331,7 @@
           <t>八王子市明神町４－９－７　京王八王子西口ビル１階</t>
         </is>
       </c>
-      <c r="L61" t="inlineStr">
+      <c r="L61" s="6" t="inlineStr">
         <is>
           <t>042-643-5270</t>
         </is>
@@ -7296,7 +7356,8 @@
           <t>佐々木　純</t>
         </is>
       </c>
-      <c r="R61" s="1" t="n">
+      <c r="Q61" s="1" t="n"/>
+      <c r="R61" s="3" t="n">
         <v>40626</v>
       </c>
       <c r="S61" t="n">
@@ -7310,7 +7371,7 @@
           <t>23福保障計第197号</t>
         </is>
       </c>
-      <c r="X61" t="inlineStr">
+      <c r="X61" s="1" t="inlineStr">
         <is>
           <t>育成医療・更生医療</t>
         </is>
@@ -7334,23 +7395,23 @@
       </c>
     </row>
     <row r="62">
-      <c r="A62" t="inlineStr">
+      <c r="A62" s="1" t="inlineStr">
         <is>
           <t>2-58</t>
         </is>
       </c>
-      <c r="D62" t="n">
+      <c r="D62" s="2" t="n">
         <v>2954394</v>
       </c>
       <c r="E62" t="n">
         <v>7</v>
       </c>
-      <c r="F62" t="inlineStr">
+      <c r="F62" s="4" t="inlineStr">
         <is>
           <t>1342954394</t>
         </is>
       </c>
-      <c r="G62" t="inlineStr">
+      <c r="G62" s="2" t="inlineStr">
         <is>
           <t>二重</t>
         </is>
@@ -7360,12 +7421,12 @@
           <t>日本調剤八王子薬局</t>
         </is>
       </c>
-      <c r="I62" t="inlineStr">
+      <c r="I62" s="1" t="inlineStr">
         <is>
           <t>192-0046</t>
         </is>
       </c>
-      <c r="J62" t="inlineStr">
+      <c r="J62" s="1" t="inlineStr">
         <is>
           <t>24八王子市</t>
         </is>
@@ -7405,7 +7466,7 @@
           <t>変更届（山口　剛志、～令和5年7月31日</t>
         </is>
       </c>
-      <c r="R62" s="1" t="n">
+      <c r="R62" s="3" t="n">
         <v>40940</v>
       </c>
       <c r="S62" t="n">
@@ -7427,7 +7488,7 @@
           <t>5八福障第6667号</t>
         </is>
       </c>
-      <c r="X62" t="inlineStr">
+      <c r="X62" s="1" t="inlineStr">
         <is>
           <t>育成医療・更生医療</t>
         </is>
@@ -7441,7 +7502,7 @@
       <c r="AA62" t="n">
         <v>42404</v>
       </c>
-      <c r="AC62" t="inlineStr">
+      <c r="AC62" s="1" t="inlineStr">
         <is>
           <t>変更届（小峯　雪乃、～令和元年５月１日）</t>
         </is>
@@ -7463,23 +7524,23 @@
       </c>
     </row>
     <row r="63">
-      <c r="A63" t="inlineStr">
+      <c r="A63" s="1" t="inlineStr">
         <is>
           <t>2-59</t>
         </is>
       </c>
-      <c r="D63" t="n">
+      <c r="D63" s="2" t="n">
         <v>2954410</v>
       </c>
       <c r="E63" t="n">
         <v>7</v>
       </c>
-      <c r="F63" t="inlineStr">
+      <c r="F63" s="4" t="inlineStr">
         <is>
           <t>1342954410</t>
         </is>
       </c>
-      <c r="G63" t="inlineStr">
+      <c r="G63" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">　</t>
         </is>
@@ -7489,12 +7550,12 @@
           <t xml:space="preserve">クリーン薬局　</t>
         </is>
       </c>
-      <c r="I63" t="inlineStr">
+      <c r="I63" s="7" t="inlineStr">
         <is>
           <t>192-0083</t>
         </is>
       </c>
-      <c r="J63" t="inlineStr">
+      <c r="J63" s="1" t="inlineStr">
         <is>
           <t>24八王子市</t>
         </is>
@@ -7529,7 +7590,8 @@
           <t>永山　美保</t>
         </is>
       </c>
-      <c r="R63" s="1" t="n">
+      <c r="Q63" s="1" t="n"/>
+      <c r="R63" s="3" t="n">
         <v>40693</v>
       </c>
       <c r="S63" t="n">
@@ -7551,7 +7613,7 @@
           <t>5八福障収第3160号</t>
         </is>
       </c>
-      <c r="X63" t="inlineStr">
+      <c r="X63" s="1" t="inlineStr">
         <is>
           <t>育成医療・更生医療</t>
         </is>
@@ -7572,23 +7634,23 @@
       </c>
     </row>
     <row r="64">
-      <c r="A64" t="inlineStr">
+      <c r="A64" s="1" t="inlineStr">
         <is>
           <t>2-60</t>
         </is>
       </c>
-      <c r="D64" t="n">
+      <c r="D64" s="2" t="n">
         <v>2955086</v>
       </c>
       <c r="E64" t="n">
         <v>7</v>
       </c>
-      <c r="F64" t="inlineStr">
+      <c r="F64" s="4" t="inlineStr">
         <is>
           <t>1342955086</t>
         </is>
       </c>
-      <c r="G64" t="inlineStr">
+      <c r="G64" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">　</t>
         </is>
@@ -7598,12 +7660,12 @@
           <t>なの花薬局　八王子みなみ野店</t>
         </is>
       </c>
-      <c r="I64" t="inlineStr">
+      <c r="I64" s="7" t="inlineStr">
         <is>
           <t>192-0918</t>
         </is>
       </c>
-      <c r="J64" t="inlineStr">
+      <c r="J64" s="1" t="inlineStr">
         <is>
           <t>24八王子市</t>
         </is>
@@ -7638,12 +7700,12 @@
           <t>金子　紗永美</t>
         </is>
       </c>
-      <c r="Q64" t="inlineStr">
+      <c r="Q64" s="1" t="inlineStr">
         <is>
           <t>変更届（川代　奈美、～令和3年8月1日）</t>
         </is>
       </c>
-      <c r="R64" s="1" t="n">
+      <c r="R64" s="3" t="n">
         <v>40691</v>
       </c>
       <c r="S64" t="n">
@@ -7665,7 +7727,7 @@
           <t>5八福障第2026号</t>
         </is>
       </c>
-      <c r="X64" t="inlineStr">
+      <c r="X64" s="1" t="inlineStr">
         <is>
           <t>育成医療・更生医療</t>
         </is>
@@ -7701,23 +7763,23 @@
       </c>
     </row>
     <row r="65">
-      <c r="A65" t="inlineStr">
+      <c r="A65" s="1" t="inlineStr">
         <is>
           <t>2-61</t>
         </is>
       </c>
-      <c r="D65" t="n">
+      <c r="D65" s="2" t="n">
         <v>2955391</v>
       </c>
       <c r="E65" t="n">
         <v>7</v>
       </c>
-      <c r="F65" t="inlineStr">
+      <c r="F65" s="4" t="inlineStr">
         <is>
           <t>1342955391</t>
         </is>
       </c>
-      <c r="G65" t="inlineStr">
+      <c r="G65" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">　</t>
         </is>
@@ -7727,12 +7789,12 @@
           <t>QOLサポートクオール薬局　京王八王子店</t>
         </is>
       </c>
-      <c r="I65" t="inlineStr">
+      <c r="I65" s="1" t="inlineStr">
         <is>
           <t>192-0046</t>
         </is>
       </c>
-      <c r="J65" t="inlineStr">
+      <c r="J65" s="1" t="inlineStr">
         <is>
           <t>24八王子市</t>
         </is>
@@ -7767,12 +7829,12 @@
           <t>塙　真美子</t>
         </is>
       </c>
-      <c r="Q65" t="inlineStr">
+      <c r="Q65" s="1" t="inlineStr">
         <is>
           <t>変更届（髙橋　紀章、～令和4年2月2日）</t>
         </is>
       </c>
-      <c r="R65" s="1" t="n">
+      <c r="R65" s="3" t="n">
         <v>40759</v>
       </c>
       <c r="S65" t="n">
@@ -7794,7 +7856,7 @@
           <t>5八福障第2026号</t>
         </is>
       </c>
-      <c r="X65" t="inlineStr">
+      <c r="X65" s="1" t="inlineStr">
         <is>
           <t>育成医療・更生医療</t>
         </is>
@@ -7830,28 +7892,29 @@
       </c>
     </row>
     <row r="66">
-      <c r="A66" t="inlineStr">
+      <c r="A66" s="1" t="inlineStr">
         <is>
           <t>2-62</t>
         </is>
       </c>
+      <c r="B66" s="1" t="n"/>
       <c r="C66" t="inlineStr">
         <is>
           <t>○</t>
         </is>
       </c>
-      <c r="D66" t="n">
+      <c r="D66" s="2" t="n">
         <v>2954477</v>
       </c>
       <c r="E66" t="n">
         <v>7</v>
       </c>
-      <c r="F66" t="inlineStr">
+      <c r="F66" s="4" t="inlineStr">
         <is>
           <t>1342954477</t>
         </is>
       </c>
-      <c r="G66" t="inlineStr">
+      <c r="G66" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">　</t>
         </is>
@@ -7861,12 +7924,12 @@
           <t>セイジョー薬局　八王子北口店</t>
         </is>
       </c>
-      <c r="I66" t="inlineStr">
+      <c r="I66" s="1" t="inlineStr">
         <is>
           <t>192-0085</t>
         </is>
       </c>
-      <c r="J66" t="inlineStr">
+      <c r="J66" s="1" t="inlineStr">
         <is>
           <t>24八王子市</t>
         </is>
@@ -7891,10 +7954,11 @@
           <t>鈴木　大輔</t>
         </is>
       </c>
-      <c r="R66" s="1" t="n">
+      <c r="Q66" s="1" t="n"/>
+      <c r="R66" s="3" t="n">
         <v>40738</v>
       </c>
-      <c r="S66" s="1" t="n">
+      <c r="S66" s="3" t="n">
         <v>40817</v>
       </c>
       <c r="T66" t="n">
@@ -7905,7 +7969,7 @@
           <t>23福保障計第722号</t>
         </is>
       </c>
-      <c r="X66" t="inlineStr">
+      <c r="X66" s="1" t="inlineStr">
         <is>
           <t>育成医療・更生医療</t>
         </is>
@@ -7929,23 +7993,23 @@
       </c>
     </row>
     <row r="67">
-      <c r="A67" t="inlineStr">
+      <c r="A67" s="1" t="inlineStr">
         <is>
           <t>2-63</t>
         </is>
       </c>
-      <c r="D67" t="n">
+      <c r="D67" s="2" t="n">
         <v>2954535</v>
       </c>
       <c r="E67" t="n">
         <v>7</v>
       </c>
-      <c r="F67" t="inlineStr">
+      <c r="F67" s="4" t="inlineStr">
         <is>
           <t>1342954535</t>
         </is>
       </c>
-      <c r="G67" t="inlineStr">
+      <c r="G67" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">　</t>
         </is>
@@ -7955,12 +8019,12 @@
           <t>南山堂薬局　八王子店</t>
         </is>
       </c>
-      <c r="I67" t="inlineStr">
+      <c r="I67" s="1" t="inlineStr">
         <is>
           <t>192-0081</t>
         </is>
       </c>
-      <c r="J67" t="inlineStr">
+      <c r="J67" s="1" t="inlineStr">
         <is>
           <t>24八王子市</t>
         </is>
@@ -7995,12 +8059,12 @@
           <t>小山田　純子</t>
         </is>
       </c>
-      <c r="Q67" t="inlineStr">
+      <c r="Q67" s="1" t="inlineStr">
         <is>
           <t>変更届（中村　絵美、～令和3年9月1日）</t>
         </is>
       </c>
-      <c r="R67" s="1" t="n">
+      <c r="R67" s="3" t="n">
         <v>40833</v>
       </c>
       <c r="S67" t="n">
@@ -8022,7 +8086,7 @@
           <t>5八福障第6165号</t>
         </is>
       </c>
-      <c r="X67" t="inlineStr">
+      <c r="X67" s="1" t="inlineStr">
         <is>
           <t>育成医療・更生医療</t>
         </is>
@@ -8043,23 +8107,23 @@
       </c>
     </row>
     <row r="68">
-      <c r="A68" t="inlineStr">
+      <c r="A68" s="1" t="inlineStr">
         <is>
           <t>2-64</t>
         </is>
       </c>
-      <c r="D68" t="n">
+      <c r="D68" s="2" t="n">
         <v>2954576</v>
       </c>
       <c r="E68" t="n">
         <v>7</v>
       </c>
-      <c r="F68" t="inlineStr">
+      <c r="F68" s="4" t="inlineStr">
         <is>
           <t>1342954576</t>
         </is>
       </c>
-      <c r="G68" t="inlineStr">
+      <c r="G68" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">　</t>
         </is>
@@ -8069,12 +8133,12 @@
           <t>つとむ薬局</t>
         </is>
       </c>
-      <c r="I68" t="inlineStr">
+      <c r="I68" s="5" t="inlineStr">
         <is>
           <t>193-0844</t>
         </is>
       </c>
-      <c r="J68" t="inlineStr">
+      <c r="J68" s="1" t="inlineStr">
         <is>
           <t>24八王子市</t>
         </is>
@@ -8109,7 +8173,8 @@
           <t>樋口　勉</t>
         </is>
       </c>
-      <c r="R68" s="1" t="n">
+      <c r="Q68" s="1" t="n"/>
+      <c r="R68" s="3" t="n">
         <v>40309</v>
       </c>
       <c r="S68" t="n">
@@ -8152,25 +8217,26 @@
           <t>更新申請（育成医療→なし）、～令和4年6月30日）</t>
         </is>
       </c>
+      <c r="AE68" s="1" t="n"/>
     </row>
     <row r="69">
-      <c r="A69" t="inlineStr">
+      <c r="A69" s="1" t="inlineStr">
         <is>
           <t>2-65</t>
         </is>
       </c>
-      <c r="D69" t="n">
+      <c r="D69" s="2" t="n">
         <v>2955912</v>
       </c>
       <c r="E69" t="n">
         <v>7</v>
       </c>
-      <c r="F69" t="inlineStr">
+      <c r="F69" s="4" t="inlineStr">
         <is>
           <t>1342955912</t>
         </is>
       </c>
-      <c r="G69" t="inlineStr">
+      <c r="G69" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">　</t>
         </is>
@@ -8180,12 +8246,12 @@
           <t>マリン薬局　八王子別所店</t>
         </is>
       </c>
-      <c r="I69" t="inlineStr">
+      <c r="I69" s="1" t="inlineStr">
         <is>
           <t>192-0363</t>
         </is>
       </c>
-      <c r="J69" t="inlineStr">
+      <c r="J69" s="1" t="inlineStr">
         <is>
           <t>24八王子市</t>
         </is>
@@ -8218,12 +8284,12 @@
           <t>清水　知恵子</t>
         </is>
       </c>
-      <c r="Q69" t="inlineStr">
+      <c r="Q69" s="1" t="inlineStr">
         <is>
           <t>変更届（茨木　直子　～令和5年4月30日）</t>
         </is>
       </c>
-      <c r="R69" s="1" t="n">
+      <c r="R69" s="3" t="n">
         <v>40940</v>
       </c>
       <c r="S69" t="n">
@@ -8245,7 +8311,7 @@
           <t>5八福障第6668号</t>
         </is>
       </c>
-      <c r="X69" t="inlineStr">
+      <c r="X69" s="1" t="inlineStr">
         <is>
           <t>育成医療・更生医療</t>
         </is>
@@ -8281,23 +8347,23 @@
       </c>
     </row>
     <row r="70">
-      <c r="A70" t="inlineStr">
+      <c r="A70" s="1" t="inlineStr">
         <is>
           <t>2-66</t>
         </is>
       </c>
-      <c r="D70" t="n">
+      <c r="D70" s="2" t="n">
         <v>2954600</v>
       </c>
       <c r="E70" t="n">
         <v>7</v>
       </c>
-      <c r="F70" t="inlineStr">
+      <c r="F70" s="4" t="inlineStr">
         <is>
           <t>1342954600</t>
         </is>
       </c>
-      <c r="G70" t="inlineStr">
+      <c r="G70" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">　</t>
         </is>
@@ -8307,12 +8373,12 @@
           <t>みかん薬局　八王子店</t>
         </is>
       </c>
-      <c r="I70" t="inlineStr">
+      <c r="I70" s="1" t="inlineStr">
         <is>
           <t>192-0081</t>
         </is>
       </c>
-      <c r="J70" t="inlineStr">
+      <c r="J70" s="1" t="inlineStr">
         <is>
           <t>24八王子市</t>
         </is>
@@ -8348,12 +8414,12 @@
           <t>荻野　倫啓</t>
         </is>
       </c>
-      <c r="Q70" t="inlineStr">
+      <c r="Q70" s="1" t="inlineStr">
         <is>
           <t>変更届（古屋　恭子、～令和6年4月30日）</t>
         </is>
       </c>
-      <c r="R70" s="1" t="n">
+      <c r="R70" s="3" t="n">
         <v>40912</v>
       </c>
       <c r="S70" t="n">
@@ -8375,7 +8441,7 @@
           <t>5八福障第6687号</t>
         </is>
       </c>
-      <c r="X70" t="inlineStr">
+      <c r="X70" s="1" t="inlineStr">
         <is>
           <t>育成医療・更生医療</t>
         </is>
@@ -8396,23 +8462,24 @@
       </c>
     </row>
     <row r="71">
-      <c r="A71" t="inlineStr">
+      <c r="A71" s="1" t="inlineStr">
         <is>
           <t>2-67</t>
         </is>
       </c>
-      <c r="D71" t="n">
+      <c r="C71" s="1" t="n"/>
+      <c r="D71" s="2" t="n">
         <v>2954618</v>
       </c>
       <c r="E71" t="n">
         <v>7</v>
       </c>
-      <c r="F71" t="inlineStr">
+      <c r="F71" s="4" t="inlineStr">
         <is>
           <t>1342954618</t>
         </is>
       </c>
-      <c r="G71" t="inlineStr">
+      <c r="G71" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">　</t>
         </is>
@@ -8422,12 +8489,12 @@
           <t>オレンジ薬局　西寺方店</t>
         </is>
       </c>
-      <c r="I71" t="inlineStr">
+      <c r="I71" s="1" t="inlineStr">
         <is>
           <t>192-0153</t>
         </is>
       </c>
-      <c r="J71" t="inlineStr">
+      <c r="J71" s="1" t="inlineStr">
         <is>
           <t>24八王子市</t>
         </is>
@@ -8462,12 +8529,12 @@
           <t>篠原　菊子</t>
         </is>
       </c>
-      <c r="Q71" t="inlineStr">
+      <c r="Q71" s="1" t="inlineStr">
         <is>
           <t>変更届（志田　勝都夫、～平成28年８月28日）</t>
         </is>
       </c>
-      <c r="R71" s="1" t="n">
+      <c r="R71" s="3" t="n">
         <v>41004</v>
       </c>
       <c r="S71" t="n">
@@ -8489,7 +8556,7 @@
           <t>5八福障第6662号</t>
         </is>
       </c>
-      <c r="X71" t="inlineStr">
+      <c r="X71" s="1" t="inlineStr">
         <is>
           <t>育成医療・更生医療</t>
         </is>
@@ -8503,25 +8570,27 @@
       <c r="AA71" t="n">
         <v>42406</v>
       </c>
+      <c r="AC71" s="1" t="n"/>
+      <c r="AD71" s="1" t="n"/>
     </row>
     <row r="72">
-      <c r="A72" t="inlineStr">
+      <c r="A72" s="1" t="inlineStr">
         <is>
           <t>2-68</t>
         </is>
       </c>
-      <c r="D72" t="n">
+      <c r="D72" s="2" t="n">
         <v>2955490</v>
       </c>
       <c r="E72" t="n">
         <v>7</v>
       </c>
-      <c r="F72" t="inlineStr">
+      <c r="F72" s="4" t="inlineStr">
         <is>
           <t>1342955490</t>
         </is>
       </c>
-      <c r="G72" t="inlineStr">
+      <c r="G72" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">　</t>
         </is>
@@ -8531,12 +8600,12 @@
           <t>八王子メロン薬局</t>
         </is>
       </c>
-      <c r="I72" t="inlineStr">
+      <c r="I72" s="1" t="inlineStr">
         <is>
           <t>192-0082</t>
         </is>
       </c>
-      <c r="J72" t="inlineStr">
+      <c r="J72" s="1" t="inlineStr">
         <is>
           <t>24八王子市</t>
         </is>
@@ -8571,12 +8640,12 @@
           <t>坂本　隆之</t>
         </is>
       </c>
-      <c r="Q72" t="inlineStr">
+      <c r="Q72" s="1" t="inlineStr">
         <is>
           <t>変更届（豊田　陽祐、～平成31年4月30日）</t>
         </is>
       </c>
-      <c r="R72" s="1" t="n">
+      <c r="R72" s="3" t="n">
         <v>41060</v>
       </c>
       <c r="S72" t="n">
@@ -8598,7 +8667,7 @@
           <t>6八福障第1174号</t>
         </is>
       </c>
-      <c r="X72" t="inlineStr">
+      <c r="X72" s="1" t="inlineStr">
         <is>
           <t>育成医療・更生医療</t>
         </is>
@@ -8619,23 +8688,23 @@
       </c>
     </row>
     <row r="73">
-      <c r="A73" t="inlineStr">
+      <c r="A73" s="1" t="inlineStr">
         <is>
           <t>2-69</t>
         </is>
       </c>
-      <c r="D73" t="n">
+      <c r="D73" s="2" t="n">
         <v>2954667</v>
       </c>
       <c r="E73" t="n">
         <v>7</v>
       </c>
-      <c r="F73" t="inlineStr">
+      <c r="F73" s="4" t="inlineStr">
         <is>
           <t>1342954667</t>
         </is>
       </c>
-      <c r="G73" t="inlineStr">
+      <c r="G73" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">　</t>
         </is>
@@ -8645,12 +8714,12 @@
           <t>日本調剤大和田薬局</t>
         </is>
       </c>
-      <c r="I73" t="inlineStr">
+      <c r="I73" s="1" t="inlineStr">
         <is>
           <t>192-0045</t>
         </is>
       </c>
-      <c r="J73" t="inlineStr">
+      <c r="J73" s="1" t="inlineStr">
         <is>
           <t>24八王子市</t>
         </is>
@@ -8685,12 +8754,12 @@
           <t>廣瀬　直美</t>
         </is>
       </c>
-      <c r="Q73" t="inlineStr">
+      <c r="Q73" s="1" t="inlineStr">
         <is>
           <t>変更届（小池　洋輔　、～平成26年３月31日）</t>
         </is>
       </c>
-      <c r="R73" s="1" t="n">
+      <c r="R73" s="3" t="n">
         <v>41183</v>
       </c>
       <c r="S73" t="n">
@@ -8712,7 +8781,7 @@
           <t>30八福障収第724号</t>
         </is>
       </c>
-      <c r="X73" t="inlineStr">
+      <c r="X73" s="1" t="inlineStr">
         <is>
           <t>育成医療・更生医療</t>
         </is>
@@ -8743,7 +8812,7 @@
       </c>
     </row>
     <row r="74">
-      <c r="A74" t="inlineStr">
+      <c r="A74" s="1" t="inlineStr">
         <is>
           <t>2-70</t>
         </is>
@@ -8753,18 +8822,18 @@
           <t>○</t>
         </is>
       </c>
-      <c r="D74" t="n">
+      <c r="D74" s="2" t="n">
         <v>2954675</v>
       </c>
       <c r="E74" t="n">
         <v>7</v>
       </c>
-      <c r="F74" t="inlineStr">
+      <c r="F74" s="4" t="inlineStr">
         <is>
           <t>1342954675</t>
         </is>
       </c>
-      <c r="G74" t="inlineStr">
+      <c r="G74" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">　</t>
         </is>
@@ -8779,7 +8848,7 @@
           <t>193-0801</t>
         </is>
       </c>
-      <c r="J74" t="inlineStr">
+      <c r="J74" s="1" t="inlineStr">
         <is>
           <t>24八王子市</t>
         </is>
@@ -8809,12 +8878,12 @@
           <t>多々井　良成</t>
         </is>
       </c>
-      <c r="Q74" t="inlineStr">
+      <c r="Q74" s="1" t="inlineStr">
         <is>
           <t>変更届（藤井　瑛久、～平成25年８月21日）</t>
         </is>
       </c>
-      <c r="R74" s="1" t="n">
+      <c r="R74" s="3" t="n">
         <v>41325</v>
       </c>
       <c r="S74" t="n">
@@ -8823,12 +8892,12 @@
       <c r="T74" t="n">
         <v>41426</v>
       </c>
-      <c r="U74" t="inlineStr">
+      <c r="U74" s="1" t="inlineStr">
         <is>
           <t>25福保障計第249号</t>
         </is>
       </c>
-      <c r="X74" t="inlineStr">
+      <c r="X74" s="1" t="inlineStr">
         <is>
           <t>育成医療・更生医療</t>
         </is>
@@ -8852,7 +8921,7 @@
       </c>
     </row>
     <row r="75">
-      <c r="A75" t="inlineStr">
+      <c r="A75" s="1" t="inlineStr">
         <is>
           <t>2-71</t>
         </is>
@@ -8862,18 +8931,18 @@
           <t>○</t>
         </is>
       </c>
-      <c r="D75" t="n">
+      <c r="D75" s="2" t="n">
         <v>2955102</v>
       </c>
       <c r="E75" t="n">
         <v>7</v>
       </c>
-      <c r="F75" t="inlineStr">
+      <c r="F75" s="4" t="inlineStr">
         <is>
           <t>1342955102</t>
         </is>
       </c>
-      <c r="G75" t="inlineStr">
+      <c r="G75" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">　</t>
         </is>
@@ -8888,7 +8957,7 @@
           <t>192-0083</t>
         </is>
       </c>
-      <c r="J75" t="inlineStr">
+      <c r="J75" s="1" t="inlineStr">
         <is>
           <t>24八王子市</t>
         </is>
@@ -8908,7 +8977,7 @@
           <t>株式会社アインファーマシーズ</t>
         </is>
       </c>
-      <c r="N75" t="inlineStr">
+      <c r="N75" s="1" t="inlineStr">
         <is>
           <t>003-0005</t>
         </is>
@@ -8923,12 +8992,12 @@
           <t>秋間　知子</t>
         </is>
       </c>
-      <c r="Q75" t="inlineStr">
+      <c r="Q75" s="1" t="inlineStr">
         <is>
           <t>変更届(田中誠～平成28年3月31日)</t>
         </is>
       </c>
-      <c r="R75" s="1" t="n">
+      <c r="R75" s="3" t="n">
         <v>41366</v>
       </c>
       <c r="S75" t="n">
@@ -8937,12 +9006,12 @@
       <c r="T75" t="n">
         <v>41426</v>
       </c>
-      <c r="U75" t="inlineStr">
+      <c r="U75" s="1" t="inlineStr">
         <is>
           <t>25福保障計第249号</t>
         </is>
       </c>
-      <c r="X75" t="inlineStr">
+      <c r="X75" s="1" t="inlineStr">
         <is>
           <t>育成医療・更生医療</t>
         </is>
@@ -8976,23 +9045,23 @@
       </c>
     </row>
     <row r="76">
-      <c r="A76" t="inlineStr">
+      <c r="A76" s="1" t="inlineStr">
         <is>
           <t>2-72</t>
         </is>
       </c>
-      <c r="D76" t="n">
+      <c r="D76" s="2" t="n">
         <v>2954733</v>
       </c>
       <c r="E76" t="n">
         <v>7</v>
       </c>
-      <c r="F76" t="inlineStr">
+      <c r="F76" s="4" t="inlineStr">
         <is>
           <t>1342954733</t>
         </is>
       </c>
-      <c r="G76" t="inlineStr">
+      <c r="G76" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">　</t>
         </is>
@@ -9002,17 +9071,17 @@
           <t>ノムラ薬局　大和田５丁目店</t>
         </is>
       </c>
-      <c r="I76" t="inlineStr">
+      <c r="I76" s="1" t="inlineStr">
         <is>
           <t>192-0045</t>
         </is>
       </c>
-      <c r="J76" t="inlineStr">
+      <c r="J76" s="1" t="inlineStr">
         <is>
           <t>24八王子市</t>
         </is>
       </c>
-      <c r="K76" t="inlineStr">
+      <c r="K76" s="1" t="inlineStr">
         <is>
           <t>八王子市大和田町５－２６－１５　グランドールＭ＆Ｋ１階</t>
         </is>
@@ -9042,10 +9111,11 @@
           <t>橋本　喜一</t>
         </is>
       </c>
-      <c r="R76" s="1" t="n">
+      <c r="Q76" s="1" t="n"/>
+      <c r="R76" s="3" t="n">
         <v>41446</v>
       </c>
-      <c r="S76" s="1" t="n">
+      <c r="S76" s="3" t="n">
         <v>41548</v>
       </c>
       <c r="T76" t="n">
@@ -9064,7 +9134,7 @@
           <t>7八福障第4047号</t>
         </is>
       </c>
-      <c r="X76" t="inlineStr">
+      <c r="X76" s="1" t="inlineStr">
         <is>
           <t>育成医療・更生医療</t>
         </is>
@@ -9080,23 +9150,23 @@
       </c>
     </row>
     <row r="77">
-      <c r="A77" t="inlineStr">
+      <c r="A77" s="1" t="inlineStr">
         <is>
           <t>2-73</t>
         </is>
       </c>
-      <c r="D77" t="n">
+      <c r="D77" s="2" t="n">
         <v>2955110</v>
       </c>
       <c r="E77" t="n">
         <v>7</v>
       </c>
-      <c r="F77" t="inlineStr">
+      <c r="F77" s="4" t="inlineStr">
         <is>
           <t>1342955110</t>
         </is>
       </c>
-      <c r="G77" t="inlineStr">
+      <c r="G77" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">　</t>
         </is>
@@ -9111,7 +9181,7 @@
           <t>193-0816</t>
         </is>
       </c>
-      <c r="J77" t="inlineStr">
+      <c r="J77" s="1" t="inlineStr">
         <is>
           <t>24八王子市</t>
         </is>
@@ -9131,7 +9201,7 @@
           <t>株式会社アインファーマシーズ</t>
         </is>
       </c>
-      <c r="N77" t="inlineStr">
+      <c r="N77" s="1" t="inlineStr">
         <is>
           <t>003-0005</t>
         </is>
@@ -9146,15 +9216,15 @@
           <t>小俣　華子</t>
         </is>
       </c>
-      <c r="Q77" t="inlineStr">
+      <c r="Q77" s="1" t="inlineStr">
         <is>
           <t>変更届(有賀　直樹～令和４年２月１日)</t>
         </is>
       </c>
-      <c r="R77" s="1" t="n">
+      <c r="R77" s="3" t="n">
         <v>41453</v>
       </c>
-      <c r="S77" s="1" t="n">
+      <c r="S77" s="3" t="n">
         <v>41548</v>
       </c>
       <c r="T77" t="n">
@@ -9173,7 +9243,7 @@
           <t>7八福障第4047号</t>
         </is>
       </c>
-      <c r="X77" t="inlineStr">
+      <c r="X77" s="1" t="inlineStr">
         <is>
           <t>育成医療・更生医療</t>
         </is>
@@ -9209,23 +9279,24 @@
       </c>
     </row>
     <row r="78">
-      <c r="A78" t="inlineStr">
+      <c r="A78" s="1" t="inlineStr">
         <is>
           <t>2-74</t>
         </is>
       </c>
-      <c r="D78" t="n">
+      <c r="C78" s="1" t="n"/>
+      <c r="D78" s="2" t="n">
         <v>2954816</v>
       </c>
       <c r="E78" t="n">
         <v>7</v>
       </c>
-      <c r="F78" t="inlineStr">
+      <c r="F78" s="4" t="inlineStr">
         <is>
           <t>1342954816</t>
         </is>
       </c>
-      <c r="G78" t="inlineStr">
+      <c r="G78" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">　</t>
         </is>
@@ -9240,7 +9311,7 @@
           <t>192-0151</t>
         </is>
       </c>
-      <c r="J78" t="inlineStr">
+      <c r="J78" s="1" t="inlineStr">
         <is>
           <t>24八王子市</t>
         </is>
@@ -9275,12 +9346,12 @@
           <t>島﨑　優子</t>
         </is>
       </c>
-      <c r="Q78" t="inlineStr">
+      <c r="Q78" s="1" t="inlineStr">
         <is>
           <t>変更届(奥住　由美子、～平成25年10月31日）</t>
         </is>
       </c>
-      <c r="R78" s="1" t="n">
+      <c r="R78" s="3" t="n">
         <v>39000</v>
       </c>
       <c r="S78" t="n">
@@ -9289,7 +9360,7 @@
       <c r="T78" t="n">
         <v>39114</v>
       </c>
-      <c r="U78" t="inlineStr">
+      <c r="U78" s="1" t="inlineStr">
         <is>
           <t>18福保障計第1319号</t>
         </is>
@@ -9302,7 +9373,7 @@
           <t>6八福障第5449号</t>
         </is>
       </c>
-      <c r="X78" t="inlineStr">
+      <c r="X78" s="1" t="inlineStr">
         <is>
           <t>育成医療・更生医療</t>
         </is>
@@ -9323,23 +9394,23 @@
       </c>
     </row>
     <row r="79">
-      <c r="A79" t="inlineStr">
+      <c r="A79" s="1" t="inlineStr">
         <is>
           <t>2-75</t>
         </is>
       </c>
-      <c r="D79" t="n">
+      <c r="D79" s="2" t="n">
         <v>2955474</v>
       </c>
       <c r="E79" t="n">
         <v>7</v>
       </c>
-      <c r="F79" t="inlineStr">
+      <c r="F79" s="4" t="inlineStr">
         <is>
           <t>1342955474</t>
         </is>
       </c>
-      <c r="G79" t="inlineStr">
+      <c r="G79" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">　</t>
         </is>
@@ -9354,12 +9425,12 @@
           <t>193-0934</t>
         </is>
       </c>
-      <c r="J79" t="inlineStr">
+      <c r="J79" s="1" t="inlineStr">
         <is>
           <t>24八王子市</t>
         </is>
       </c>
-      <c r="K79" t="inlineStr">
+      <c r="K79" s="7" t="inlineStr">
         <is>
           <t>八王子市小比企町４８０－１　サニーヒルいそま１０１－２号</t>
         </is>
@@ -9390,12 +9461,12 @@
           <t>内多　知子</t>
         </is>
       </c>
-      <c r="Q79" t="inlineStr">
+      <c r="Q79" s="1" t="inlineStr">
         <is>
           <t>変更届(堀　尚輝、～令和7年11月30日）</t>
         </is>
       </c>
-      <c r="R79" s="1" t="n">
+      <c r="R79" s="3" t="n">
         <v>41757</v>
       </c>
       <c r="S79" t="n">
@@ -9413,7 +9484,7 @@
       <c r="V79" t="n">
         <v>44044</v>
       </c>
-      <c r="W79" t="inlineStr">
+      <c r="W79" s="1" t="inlineStr">
         <is>
           <t>2八福障収第234号</t>
         </is>
@@ -9437,25 +9508,26 @@
           <t>変更届（開設者名・住所（株式会社コミュニティメディカル　東京都府中市住吉町１－８４－１ステーザ府中中河原1階(ｺｰﾄﾞ2954857)→、～平成31年3月31日）</t>
         </is>
       </c>
+      <c r="AD79" s="1" t="n"/>
     </row>
     <row r="80">
-      <c r="A80" t="inlineStr">
+      <c r="A80" s="1" t="inlineStr">
         <is>
           <t>2-76</t>
         </is>
       </c>
-      <c r="D80" t="n">
+      <c r="D80" s="2" t="n">
         <v>2955649</v>
       </c>
       <c r="E80" t="n">
         <v>7</v>
       </c>
-      <c r="F80" t="inlineStr">
+      <c r="F80" s="4" t="inlineStr">
         <is>
           <t>1342955649</t>
         </is>
       </c>
-      <c r="G80" t="inlineStr">
+      <c r="G80" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">　</t>
         </is>
@@ -9465,17 +9537,17 @@
           <t>東京薬科大学附属薬局</t>
         </is>
       </c>
-      <c r="I80" t="inlineStr">
+      <c r="I80" s="1" t="inlineStr">
         <is>
           <t>192-0034</t>
         </is>
       </c>
-      <c r="J80" t="inlineStr">
+      <c r="J80" s="1" t="inlineStr">
         <is>
           <t>24八王子市</t>
         </is>
       </c>
-      <c r="K80" t="inlineStr">
+      <c r="K80" s="7" t="inlineStr">
         <is>
           <t>八王子市大谷町１７８－１１</t>
         </is>
@@ -9505,12 +9577,12 @@
           <t>藤田　茂起</t>
         </is>
       </c>
-      <c r="Q80" t="inlineStr">
+      <c r="Q80" s="1" t="inlineStr">
         <is>
           <t>変更届(藤﨑　玲子、～令和7年4月20日）</t>
         </is>
       </c>
-      <c r="R80" s="1" t="n">
+      <c r="R80" s="3" t="n">
         <v>41796</v>
       </c>
       <c r="S80" t="n">
@@ -9528,7 +9600,7 @@
       <c r="V80" t="n">
         <v>44044</v>
       </c>
-      <c r="W80" t="inlineStr">
+      <c r="W80" s="1" t="inlineStr">
         <is>
           <t>31八福障収第1797号</t>
         </is>
@@ -9552,30 +9624,30 @@
           <t>変更届（開設者住所（東京都八王子市堀之内１４３２－１→、～令和1年8月30日）</t>
         </is>
       </c>
-      <c r="AD80" t="inlineStr">
+      <c r="AD80" s="1" t="inlineStr">
         <is>
           <t>変更届（コード（2954873→）開設者（一般財団法人東京薬科大学附属社会医療研究所　八王子市大谷町１７８－１１→、～令和2年6月30日）</t>
         </is>
       </c>
     </row>
     <row r="81">
-      <c r="A81" t="inlineStr">
+      <c r="A81" s="1" t="inlineStr">
         <is>
           <t>2-77</t>
         </is>
       </c>
-      <c r="D81" t="n">
+      <c r="D81" s="2" t="n">
         <v>2955094</v>
       </c>
       <c r="E81" t="n">
         <v>7</v>
       </c>
-      <c r="F81" t="inlineStr">
+      <c r="F81" s="4" t="inlineStr">
         <is>
           <t>1342955094</t>
         </is>
       </c>
-      <c r="G81" t="inlineStr">
+      <c r="G81" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">　</t>
         </is>
@@ -9585,17 +9657,17 @@
           <t>アイン薬局　八王子店</t>
         </is>
       </c>
-      <c r="I81" t="inlineStr">
+      <c r="I81" s="1" t="inlineStr">
         <is>
           <t>192-0034</t>
         </is>
       </c>
-      <c r="J81" t="inlineStr">
+      <c r="J81" s="1" t="inlineStr">
         <is>
           <t>24八王子市</t>
         </is>
       </c>
-      <c r="K81" t="inlineStr">
+      <c r="K81" s="7" t="inlineStr">
         <is>
           <t>八王子市大谷町３０２</t>
         </is>
@@ -9625,12 +9697,12 @@
           <t>千葉　朋寛</t>
         </is>
       </c>
-      <c r="Q81" t="inlineStr">
+      <c r="Q81" s="1" t="inlineStr">
         <is>
           <t>変更届（嶋田　佳宏、～令和2年6月1日）</t>
         </is>
       </c>
-      <c r="R81" s="1" t="n">
+      <c r="R81" s="3" t="n">
         <v>41795</v>
       </c>
       <c r="S81" t="n">
@@ -9648,7 +9720,7 @@
       <c r="V81" t="n">
         <v>44044</v>
       </c>
-      <c r="W81" t="inlineStr">
+      <c r="W81" s="1" t="inlineStr">
         <is>
           <t>2八福障収第252号</t>
         </is>
@@ -9684,23 +9756,23 @@
       </c>
     </row>
     <row r="82">
-      <c r="A82" t="inlineStr">
+      <c r="A82" s="1" t="inlineStr">
         <is>
           <t>2-78</t>
         </is>
       </c>
-      <c r="D82" t="n">
+      <c r="D82" s="2" t="n">
         <v>2954915</v>
       </c>
       <c r="E82" t="n">
         <v>7</v>
       </c>
-      <c r="F82" t="inlineStr">
+      <c r="F82" s="4" t="inlineStr">
         <is>
           <t>1342954915</t>
         </is>
       </c>
-      <c r="G82" t="inlineStr">
+      <c r="G82" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">　</t>
         </is>
@@ -9715,12 +9787,12 @@
           <t>192-0071</t>
         </is>
       </c>
-      <c r="J82" t="inlineStr">
+      <c r="J82" s="1" t="inlineStr">
         <is>
           <t>24八王子市</t>
         </is>
       </c>
-      <c r="K82" t="inlineStr">
+      <c r="K82" s="7" t="inlineStr">
         <is>
           <t>八王子市八日町８－１　ビュータワー八王子１階</t>
         </is>
@@ -9750,12 +9822,12 @@
           <t>栗原　由希</t>
         </is>
       </c>
-      <c r="Q82" t="inlineStr">
+      <c r="Q82" s="1" t="inlineStr">
         <is>
           <t>変更届（河合　洋介、～平成29年11月30日）</t>
         </is>
       </c>
-      <c r="R82" s="1" t="n">
+      <c r="R82" s="3" t="n">
         <v>41794</v>
       </c>
       <c r="S82" t="n">
@@ -9773,7 +9845,7 @@
       <c r="V82" t="n">
         <v>44044</v>
       </c>
-      <c r="W82" t="inlineStr">
+      <c r="W82" s="1" t="inlineStr">
         <is>
           <t>2八福障収第271号</t>
         </is>
@@ -9797,25 +9869,26 @@
           <t>変更届(代表取締役変更：榊原　栄一→杉浦　伸哉、変更日：令和7年5月26日）</t>
         </is>
       </c>
+      <c r="AD82" s="1" t="n"/>
     </row>
     <row r="83">
-      <c r="A83" t="inlineStr">
+      <c r="A83" s="1" t="inlineStr">
         <is>
           <t>2-79</t>
         </is>
       </c>
-      <c r="D83" t="n">
+      <c r="D83" s="2" t="n">
         <v>2954964</v>
       </c>
       <c r="E83" t="n">
         <v>7</v>
       </c>
-      <c r="F83" t="inlineStr">
+      <c r="F83" s="4" t="inlineStr">
         <is>
           <t>1342954964</t>
         </is>
       </c>
-      <c r="G83" t="inlineStr">
+      <c r="G83" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">　</t>
         </is>
@@ -9825,12 +9898,12 @@
           <t>さつき薬局　椚田店</t>
         </is>
       </c>
-      <c r="I83" t="inlineStr">
+      <c r="I83" s="1" t="inlineStr">
         <is>
           <t>193-0942</t>
         </is>
       </c>
-      <c r="J83" t="inlineStr">
+      <c r="J83" s="1" t="inlineStr">
         <is>
           <t>24八王子市</t>
         </is>
@@ -9865,12 +9938,12 @@
           <t>八木　博文</t>
         </is>
       </c>
-      <c r="Q83" t="inlineStr">
+      <c r="Q83" s="1" t="inlineStr">
         <is>
           <t>変更届（青木　一平、～令和5年9月30日）</t>
         </is>
       </c>
-      <c r="R83" s="1" t="n">
+      <c r="R83" s="3" t="n">
         <v>39904</v>
       </c>
       <c r="S83" t="n">
@@ -9916,25 +9989,26 @@
           <t>変更届（開設者住所（八王子市北野台５－４７－５→）、～平成28年3月31日）</t>
         </is>
       </c>
+      <c r="AE83" s="1" t="n"/>
     </row>
     <row r="84">
-      <c r="A84" t="inlineStr">
+      <c r="A84" s="1" t="inlineStr">
         <is>
           <t>2-80</t>
         </is>
       </c>
-      <c r="D84" t="n">
+      <c r="D84" s="2" t="n">
         <v>2952349</v>
       </c>
       <c r="E84" t="n">
         <v>7</v>
       </c>
-      <c r="F84" t="inlineStr">
+      <c r="F84" s="4" t="inlineStr">
         <is>
           <t>1342952349</t>
         </is>
       </c>
-      <c r="G84" t="inlineStr">
+      <c r="G84" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">　</t>
         </is>
@@ -9944,12 +10018,12 @@
           <t>さつき薬局　楢原店</t>
         </is>
       </c>
-      <c r="I84" t="inlineStr">
+      <c r="I84" s="1" t="inlineStr">
         <is>
           <t>193-0803</t>
         </is>
       </c>
-      <c r="J84" t="inlineStr">
+      <c r="J84" s="1" t="inlineStr">
         <is>
           <t>24八王子市</t>
         </is>
@@ -9984,12 +10058,12 @@
           <t>河住　宏平</t>
         </is>
       </c>
-      <c r="Q84" t="inlineStr">
+      <c r="Q84" s="1" t="inlineStr">
         <is>
           <t>変更届（吉賀　智紀、～令和３年４月16日）</t>
         </is>
       </c>
-      <c r="R84" s="1" t="n">
+      <c r="R84" s="3" t="n">
         <v>42501</v>
       </c>
       <c r="S84" t="n">
@@ -10025,25 +10099,26 @@
       <c r="AA84" t="n">
         <v>42807</v>
       </c>
+      <c r="AE84" s="1" t="n"/>
     </row>
     <row r="85">
-      <c r="A85" t="inlineStr">
+      <c r="A85" s="1" t="inlineStr">
         <is>
           <t>2-81</t>
         </is>
       </c>
-      <c r="D85" t="n">
+      <c r="D85" s="2" t="n">
         <v>2955151</v>
       </c>
       <c r="E85" t="n">
         <v>7</v>
       </c>
-      <c r="F85" t="inlineStr">
+      <c r="F85" s="4" t="inlineStr">
         <is>
           <t>1342955151</t>
         </is>
       </c>
-      <c r="G85" t="inlineStr">
+      <c r="G85" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">　</t>
         </is>
@@ -10053,12 +10128,12 @@
           <t>アロエ調剤薬局</t>
         </is>
       </c>
-      <c r="I85" t="inlineStr">
+      <c r="I85" s="1" t="inlineStr">
         <is>
           <t>193-0845</t>
         </is>
       </c>
-      <c r="J85" t="inlineStr">
+      <c r="J85" s="1" t="inlineStr">
         <is>
           <t>24八王子市</t>
         </is>
@@ -10098,7 +10173,7 @@
           <t>変更届（小林　佑也　～平成30年10月31日）</t>
         </is>
       </c>
-      <c r="R85" s="1" t="n">
+      <c r="R85" s="3" t="n">
         <v>42580</v>
       </c>
       <c r="S85" t="n">
@@ -10112,7 +10187,7 @@
           <t>28八福障収第402号</t>
         </is>
       </c>
-      <c r="V85" s="1" t="n">
+      <c r="V85" s="3" t="n">
         <v>44835</v>
       </c>
       <c r="W85" t="inlineStr">
@@ -10139,25 +10214,26 @@
           <t>変更届（開設者住所（八王子市初沢町1231-6　ウイングタカオ1F→）～平成30年10月30日</t>
         </is>
       </c>
+      <c r="AE85" s="1" t="n"/>
     </row>
     <row r="86">
-      <c r="A86" t="inlineStr">
+      <c r="A86" s="1" t="inlineStr">
         <is>
           <t>2-82</t>
         </is>
       </c>
-      <c r="D86" t="n">
+      <c r="D86" s="2" t="n">
         <v>2955219</v>
       </c>
       <c r="E86" t="n">
         <v>7</v>
       </c>
-      <c r="F86" t="inlineStr">
+      <c r="F86" s="4" t="inlineStr">
         <is>
           <t>1342955219</t>
         </is>
       </c>
-      <c r="G86" t="inlineStr">
+      <c r="G86" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">　</t>
         </is>
@@ -10167,12 +10243,12 @@
           <t>クリエイト薬局　八王子台町店</t>
         </is>
       </c>
-      <c r="I86" t="inlineStr">
+      <c r="I86" s="1" t="inlineStr">
         <is>
           <t>193-0931</t>
         </is>
       </c>
-      <c r="J86" t="inlineStr">
+      <c r="J86" s="1" t="inlineStr">
         <is>
           <t>24八王子市</t>
         </is>
@@ -10207,7 +10283,8 @@
           <t>竹中　亮介</t>
         </is>
       </c>
-      <c r="R86" s="1" t="n">
+      <c r="Q86" s="1" t="n"/>
+      <c r="R86" s="3" t="n">
         <v>42769</v>
       </c>
       <c r="S86" t="n">
@@ -10248,25 +10325,26 @@
           <t>変更届(開設者（代表取締役）変更（廣瀨　泰三→瀧屋　幸彦)、変更日：令和5年9月1日</t>
         </is>
       </c>
+      <c r="AE86" s="1" t="n"/>
     </row>
     <row r="87">
-      <c r="A87" t="inlineStr">
+      <c r="A87" s="1" t="inlineStr">
         <is>
           <t>2-83</t>
         </is>
       </c>
-      <c r="D87" t="n">
+      <c r="D87" s="2" t="n">
         <v>2954931</v>
       </c>
       <c r="E87" t="n">
         <v>7</v>
       </c>
-      <c r="F87" t="inlineStr">
+      <c r="F87" s="4" t="inlineStr">
         <is>
           <t>1342954931</t>
         </is>
       </c>
-      <c r="G87" t="inlineStr">
+      <c r="G87" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">　</t>
         </is>
@@ -10276,17 +10354,17 @@
           <t>ウエルシア薬局　八王子みなみ野店</t>
         </is>
       </c>
-      <c r="I87" t="inlineStr">
+      <c r="I87" s="1" t="inlineStr">
         <is>
           <t>192-0916</t>
         </is>
       </c>
-      <c r="J87" t="inlineStr">
+      <c r="J87" s="1" t="inlineStr">
         <is>
           <t>24八王子市</t>
         </is>
       </c>
-      <c r="K87" t="inlineStr">
+      <c r="K87" s="7" t="inlineStr">
         <is>
           <t>八王子市みなみ野５－１５－５</t>
         </is>
@@ -10316,7 +10394,7 @@
           <t>小澤　藍加</t>
         </is>
       </c>
-      <c r="Q87" t="inlineStr">
+      <c r="Q87" s="1" t="inlineStr">
         <is>
           <t>変更届(田中　美智子、～令和６年2月10日）</t>
         </is>
@@ -10324,7 +10402,7 @@
       <c r="R87" t="n">
         <v>43147</v>
       </c>
-      <c r="S87" s="1" t="n">
+      <c r="S87" s="3" t="n">
         <v>43191</v>
       </c>
       <c r="T87" t="n">
@@ -10338,7 +10416,7 @@
       <c r="V87" t="n">
         <v>45383</v>
       </c>
-      <c r="W87" t="inlineStr">
+      <c r="W87" s="1" t="inlineStr">
         <is>
           <t>5八福障第6663号</t>
         </is>
@@ -10357,30 +10435,31 @@
       <c r="AA87" t="n">
         <v>43004</v>
       </c>
-      <c r="AC87" t="inlineStr">
+      <c r="AC87" s="1" t="inlineStr">
         <is>
           <t>変更届(代表取締役　松本忠久→田中純)、～令和５年３月１日）</t>
         </is>
       </c>
+      <c r="AD87" s="1" t="n"/>
     </row>
     <row r="88">
-      <c r="A88" t="inlineStr">
+      <c r="A88" s="1" t="inlineStr">
         <is>
           <t>2-84</t>
         </is>
       </c>
-      <c r="D88" t="n">
+      <c r="D88" s="2" t="n">
         <v>2955631</v>
       </c>
       <c r="E88" t="n">
         <v>7</v>
       </c>
-      <c r="F88" t="inlineStr">
+      <c r="F88" s="4" t="inlineStr">
         <is>
           <t>1342955631</t>
         </is>
       </c>
-      <c r="G88" t="inlineStr">
+      <c r="G88" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">　</t>
         </is>
@@ -10390,17 +10469,17 @@
           <t>フォレスト南大沢薬局</t>
         </is>
       </c>
-      <c r="I88" t="inlineStr">
+      <c r="I88" s="1" t="inlineStr">
         <is>
           <t>192-0364</t>
         </is>
       </c>
-      <c r="J88" t="inlineStr">
+      <c r="J88" s="1" t="inlineStr">
         <is>
           <t>24八王子市</t>
         </is>
       </c>
-      <c r="K88" t="inlineStr">
+      <c r="K88" s="7" t="inlineStr">
         <is>
           <t>八王子市南大沢２－２５－２Ｆ</t>
         </is>
@@ -10430,15 +10509,15 @@
           <t>片岡　実香</t>
         </is>
       </c>
-      <c r="Q88" t="inlineStr">
+      <c r="Q88" s="1" t="inlineStr">
         <is>
           <t>変更届（藤田　一成、～令和6年9月30日）</t>
         </is>
       </c>
-      <c r="R88" s="1" t="n">
+      <c r="R88" s="3" t="n">
         <v>43117</v>
       </c>
-      <c r="S88" s="1" t="n">
+      <c r="S88" s="3" t="n">
         <v>43191</v>
       </c>
       <c r="T88" t="n">
@@ -10452,7 +10531,7 @@
       <c r="V88" t="n">
         <v>45383</v>
       </c>
-      <c r="W88" t="inlineStr">
+      <c r="W88" s="1" t="inlineStr">
         <is>
           <t>5八福障第6661号</t>
         </is>
@@ -10478,23 +10557,23 @@
       </c>
     </row>
     <row r="89">
-      <c r="A89" t="inlineStr">
+      <c r="A89" s="1" t="inlineStr">
         <is>
           <t>2-85</t>
         </is>
       </c>
-      <c r="D89" t="n">
+      <c r="D89" s="2" t="n">
         <v>2955375</v>
       </c>
       <c r="E89" t="n">
         <v>7</v>
       </c>
-      <c r="F89" t="inlineStr">
+      <c r="F89" s="4" t="inlineStr">
         <is>
           <t>1342955375</t>
         </is>
       </c>
-      <c r="G89" t="inlineStr">
+      <c r="G89" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">　</t>
         </is>
@@ -10504,12 +10583,12 @@
           <t>薬局マツモトキヨシ　セレオ西八王子店</t>
         </is>
       </c>
-      <c r="I89" t="inlineStr">
+      <c r="I89" s="1" t="inlineStr">
         <is>
           <t>193-0835</t>
         </is>
       </c>
-      <c r="J89" t="inlineStr">
+      <c r="J89" s="1" t="inlineStr">
         <is>
           <t>24八王子市</t>
         </is>
@@ -10544,15 +10623,15 @@
           <t>道上　望</t>
         </is>
       </c>
-      <c r="Q89" t="inlineStr">
+      <c r="Q89" s="1" t="inlineStr">
         <is>
           <t>変更届（山田　雅音　～令和6年7月20日）</t>
         </is>
       </c>
-      <c r="R89" s="1" t="n">
+      <c r="R89" s="3" t="n">
         <v>43363</v>
       </c>
-      <c r="S89" s="1" t="n">
+      <c r="S89" s="3" t="n">
         <v>43466</v>
       </c>
       <c r="T89" t="n">
@@ -10585,25 +10664,26 @@
       <c r="AA89" t="n">
         <v>43101</v>
       </c>
+      <c r="AE89" s="1" t="n"/>
     </row>
     <row r="90">
-      <c r="A90" t="inlineStr">
+      <c r="A90" s="1" t="inlineStr">
         <is>
           <t>2-86</t>
         </is>
       </c>
-      <c r="D90" t="n">
+      <c r="D90" s="2" t="n">
         <v>2953099</v>
       </c>
       <c r="E90" t="n">
         <v>7</v>
       </c>
-      <c r="F90" t="inlineStr">
+      <c r="F90" s="4" t="inlineStr">
         <is>
           <t>1342953099</t>
         </is>
       </c>
-      <c r="G90" t="inlineStr">
+      <c r="G90" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">　</t>
         </is>
@@ -10613,17 +10693,17 @@
           <t>下島調剤薬局</t>
         </is>
       </c>
-      <c r="I90" t="inlineStr">
+      <c r="I90" s="1" t="inlineStr">
         <is>
           <t>192-0052</t>
         </is>
       </c>
-      <c r="J90" t="inlineStr">
+      <c r="J90" s="1" t="inlineStr">
         <is>
           <t>24八王子市</t>
         </is>
       </c>
-      <c r="K90" t="inlineStr">
+      <c r="K90" s="7" t="inlineStr">
         <is>
           <t>八王子市本郷町３－２０</t>
         </is>
@@ -10658,10 +10738,10 @@
           <t>変更届（下島　潤一　～令和6年10月6日）</t>
         </is>
       </c>
-      <c r="R90" s="1" t="n">
+      <c r="R90" s="3" t="n">
         <v>43388</v>
       </c>
-      <c r="S90" s="1" t="n">
+      <c r="S90" s="3" t="n">
         <v>43466</v>
       </c>
       <c r="T90" t="n">
@@ -10694,25 +10774,27 @@
       <c r="AA90" t="n">
         <v>43101</v>
       </c>
+      <c r="AC90" s="1" t="n"/>
+      <c r="AD90" s="1" t="n"/>
     </row>
     <row r="91">
-      <c r="A91" t="inlineStr">
+      <c r="A91" s="1" t="inlineStr">
         <is>
           <t>2-87</t>
         </is>
       </c>
-      <c r="D91" t="n">
+      <c r="D91" s="2" t="n">
         <v>2955888</v>
       </c>
       <c r="E91" t="n">
         <v>7</v>
       </c>
-      <c r="F91" t="inlineStr">
+      <c r="F91" s="4" t="inlineStr">
         <is>
           <t>1342955888</t>
         </is>
       </c>
-      <c r="G91" t="inlineStr">
+      <c r="G91" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">　</t>
         </is>
@@ -10722,17 +10804,17 @@
           <t>オレンジ薬局　鑓水店</t>
         </is>
       </c>
-      <c r="I91" t="inlineStr">
+      <c r="I91" s="1" t="inlineStr">
         <is>
           <t>192-0375</t>
         </is>
       </c>
-      <c r="J91" t="inlineStr">
+      <c r="J91" s="1" t="inlineStr">
         <is>
           <t>24八王子市</t>
         </is>
       </c>
-      <c r="K91" t="inlineStr">
+      <c r="K91" s="7" t="inlineStr">
         <is>
           <t>八王子市鑓水２－１７５－９</t>
         </is>
@@ -10762,10 +10844,11 @@
           <t>出射　健太</t>
         </is>
       </c>
-      <c r="R91" s="1" t="n">
+      <c r="Q91" s="1" t="n"/>
+      <c r="R91" s="3" t="n">
         <v>43374</v>
       </c>
-      <c r="S91" s="1" t="n">
+      <c r="S91" s="3" t="n">
         <v>43466</v>
       </c>
       <c r="T91" t="n">
@@ -10803,30 +10886,30 @@
           <t>変更届（開設者名（株式会社リバーサル、東京都中央区八重洲1-5-15（コード2955318)→、～令和4年4月1日）</t>
         </is>
       </c>
-      <c r="AD91" t="inlineStr">
+      <c r="AD91" s="1" t="inlineStr">
         <is>
           <t>変更届（代表取締役（田代　雅也→岡田なぎさ)→、～令和4年4月1日）</t>
         </is>
       </c>
     </row>
     <row r="92">
-      <c r="A92" t="inlineStr">
+      <c r="A92" s="1" t="inlineStr">
         <is>
           <t>2-88</t>
         </is>
       </c>
-      <c r="D92" t="n">
+      <c r="D92" s="2" t="n">
         <v>2955524</v>
       </c>
       <c r="E92" t="n">
         <v>7</v>
       </c>
-      <c r="F92" t="inlineStr">
+      <c r="F92" s="4" t="inlineStr">
         <is>
           <t>1342955524</t>
         </is>
       </c>
-      <c r="G92" t="inlineStr">
+      <c r="G92" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">　</t>
         </is>
@@ -10836,17 +10919,17 @@
           <t>薬のヒグチ薬局　北八王子店</t>
         </is>
       </c>
-      <c r="I92" t="inlineStr">
+      <c r="I92" s="1" t="inlineStr">
         <is>
           <t>192-0032</t>
         </is>
       </c>
-      <c r="J92" t="inlineStr">
+      <c r="J92" s="1" t="inlineStr">
         <is>
           <t>24八王子市</t>
         </is>
       </c>
-      <c r="K92" t="inlineStr">
+      <c r="K92" s="7" t="inlineStr">
         <is>
           <t>八王子市石川町２９６０－８</t>
         </is>
@@ -10876,15 +10959,15 @@
           <t>鈴木　洋一</t>
         </is>
       </c>
-      <c r="Q92" t="inlineStr">
+      <c r="Q92" s="1" t="inlineStr">
         <is>
           <t>変更届(廣瀨　誠、～令和6年8月31日）</t>
         </is>
       </c>
-      <c r="R92" s="1" t="n">
+      <c r="R92" s="3" t="n">
         <v>43444</v>
       </c>
-      <c r="S92" s="1" t="n">
+      <c r="S92" s="3" t="n">
         <v>43556</v>
       </c>
       <c r="T92" t="n">
@@ -10895,10 +10978,10 @@
           <t>30八福障収第2231号</t>
         </is>
       </c>
-      <c r="V92" s="1" t="n">
+      <c r="V92" s="8" t="n">
         <v>45748</v>
       </c>
-      <c r="W92" t="inlineStr">
+      <c r="W92" s="1" t="inlineStr">
         <is>
           <t>6八福障第6796号</t>
         </is>
@@ -10922,25 +11005,26 @@
           <t>変更届（開設者名（薬ヒグチ＆ファーマライズ株式会社（コード2955052)→、～令和元年5月31日）</t>
         </is>
       </c>
+      <c r="AD92" s="1" t="n"/>
     </row>
     <row r="93">
-      <c r="A93" t="inlineStr">
+      <c r="A93" s="1" t="inlineStr">
         <is>
           <t>2-89</t>
         </is>
       </c>
-      <c r="D93" t="n">
+      <c r="D93" s="2" t="n">
         <v>2955458</v>
       </c>
       <c r="E93" t="n">
         <v>7</v>
       </c>
-      <c r="F93" t="inlineStr">
+      <c r="F93" s="4" t="inlineStr">
         <is>
           <t>1342955458</t>
         </is>
       </c>
-      <c r="G93" t="inlineStr">
+      <c r="G93" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">　</t>
         </is>
@@ -10950,17 +11034,17 @@
           <t>クリエイト薬局　八王子万町店</t>
         </is>
       </c>
-      <c r="I93" t="inlineStr">
+      <c r="I93" s="1" t="inlineStr">
         <is>
           <t>192-0903</t>
         </is>
       </c>
-      <c r="J93" t="inlineStr">
+      <c r="J93" s="1" t="inlineStr">
         <is>
           <t>24八王子市</t>
         </is>
       </c>
-      <c r="K93" t="inlineStr">
+      <c r="K93" s="7" t="inlineStr">
         <is>
           <t>八王子市万町２０－１</t>
         </is>
@@ -10990,15 +11074,15 @@
           <t>小松　結</t>
         </is>
       </c>
-      <c r="Q93" t="inlineStr">
+      <c r="Q93" s="1" t="inlineStr">
         <is>
           <t>変更届（清水　翔太、～令和5年9月10日）</t>
         </is>
       </c>
-      <c r="R93" s="1" t="n">
+      <c r="R93" s="3" t="n">
         <v>43572</v>
       </c>
-      <c r="S93" t="inlineStr">
+      <c r="S93" s="3" t="inlineStr">
         <is>
           <t>令和元年7月1日</t>
         </is>
@@ -11013,10 +11097,10 @@
           <t>31八福障収第109号</t>
         </is>
       </c>
-      <c r="V93" s="1" t="n">
+      <c r="V93" s="8" t="n">
         <v>45839</v>
       </c>
-      <c r="W93" t="inlineStr">
+      <c r="W93" s="1" t="inlineStr">
         <is>
           <t>7八福障第1714号</t>
         </is>
@@ -11040,9 +11124,10 @@
           <t>変更届(開設者（代表取締役）変更（廣瀨　泰三→瀧屋　幸彦)、変更日：令和5年9月1日</t>
         </is>
       </c>
+      <c r="AD93" s="1" t="n"/>
     </row>
     <row r="94">
-      <c r="A94" t="inlineStr">
+      <c r="A94" s="1" t="inlineStr">
         <is>
           <t>2-90</t>
         </is>
@@ -11052,18 +11137,18 @@
           <t>○</t>
         </is>
       </c>
-      <c r="D94" t="n">
+      <c r="D94" s="2" t="n">
         <v>2955482</v>
       </c>
       <c r="E94" t="n">
         <v>7</v>
       </c>
-      <c r="F94" t="inlineStr">
+      <c r="F94" s="4" t="inlineStr">
         <is>
           <t>1342955482</t>
         </is>
       </c>
-      <c r="G94" t="inlineStr">
+      <c r="G94" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">　</t>
         </is>
@@ -11073,17 +11158,17 @@
           <t>日本調剤　八王子南口薬局</t>
         </is>
       </c>
-      <c r="I94" t="inlineStr">
+      <c r="I94" s="1" t="inlineStr">
         <is>
           <t>192-0904</t>
         </is>
       </c>
-      <c r="J94" t="inlineStr">
+      <c r="J94" s="1" t="inlineStr">
         <is>
           <t>24八王子市</t>
         </is>
       </c>
-      <c r="K94" t="inlineStr">
+      <c r="K94" s="7" t="inlineStr">
         <is>
           <t>八王子市子安町１－１－３　南口第二ビル１階</t>
         </is>
@@ -11113,15 +11198,15 @@
           <t>駒田　沙織</t>
         </is>
       </c>
-      <c r="Q94" t="inlineStr">
+      <c r="Q94" s="1" t="inlineStr">
         <is>
           <t>変更届（田島保利、～令和元年６月１日）</t>
         </is>
       </c>
-      <c r="R94" s="1" t="n">
+      <c r="R94" s="3" t="n">
         <v>43578</v>
       </c>
-      <c r="S94" t="inlineStr">
+      <c r="S94" s="3" t="inlineStr">
         <is>
           <t>令和元年7月1日</t>
         </is>
@@ -11136,6 +11221,8 @@
           <t>31八福障収第169号</t>
         </is>
       </c>
+      <c r="V94" s="1" t="n"/>
+      <c r="W94" s="1" t="n"/>
       <c r="X94" t="inlineStr">
         <is>
           <t>育成医療・更生医療</t>
@@ -11159,25 +11246,26 @@
 </t>
         </is>
       </c>
+      <c r="AD94" s="1" t="n"/>
     </row>
     <row r="95">
-      <c r="A95" t="inlineStr">
+      <c r="A95" s="1" t="inlineStr">
         <is>
           <t>2-90</t>
         </is>
       </c>
-      <c r="D95" t="n">
+      <c r="D95" s="2" t="n">
         <v>2955482</v>
       </c>
       <c r="E95" t="n">
         <v>7</v>
       </c>
-      <c r="F95" t="inlineStr">
+      <c r="F95" s="4" t="inlineStr">
         <is>
           <t>1342955482</t>
         </is>
       </c>
-      <c r="G95" t="inlineStr">
+      <c r="G95" s="2" t="inlineStr">
         <is>
           <t>二重</t>
         </is>
@@ -11187,17 +11275,17 @@
           <t>日本調剤　八王子南口薬局</t>
         </is>
       </c>
-      <c r="I95" t="inlineStr">
+      <c r="I95" s="1" t="inlineStr">
         <is>
           <t>192-0904</t>
         </is>
       </c>
-      <c r="J95" t="inlineStr">
+      <c r="J95" s="1" t="inlineStr">
         <is>
           <t>24八王子市</t>
         </is>
       </c>
-      <c r="K95" t="inlineStr">
+      <c r="K95" s="7" t="inlineStr">
         <is>
           <t>八王子市子安町１－１－３　南口第二ビル１階</t>
         </is>
@@ -11227,10 +11315,11 @@
           <t>播田　千歳</t>
         </is>
       </c>
-      <c r="R95" s="1" t="n">
+      <c r="Q95" s="1" t="n"/>
+      <c r="R95" s="3" t="n">
         <v>44267</v>
       </c>
-      <c r="S95" s="1" t="n">
+      <c r="S95" s="3" t="n">
         <v>44378</v>
       </c>
       <c r="T95" t="n">
@@ -11241,6 +11330,8 @@
           <t>２八福障収第1729号</t>
         </is>
       </c>
+      <c r="V95" s="1" t="n"/>
+      <c r="W95" s="1" t="n"/>
       <c r="X95" t="inlineStr">
         <is>
           <t>育成医療・更生医療</t>
@@ -11272,23 +11363,23 @@
       </c>
     </row>
     <row r="96">
-      <c r="A96" t="inlineStr">
+      <c r="A96" s="1" t="inlineStr">
         <is>
           <t>2-91</t>
         </is>
       </c>
-      <c r="D96" t="n">
+      <c r="D96" s="2" t="n">
         <v>2955573</v>
       </c>
       <c r="E96" t="n">
         <v>7</v>
       </c>
-      <c r="F96" t="inlineStr">
+      <c r="F96" s="4" t="inlineStr">
         <is>
           <t>1342955573</t>
         </is>
       </c>
-      <c r="G96" t="inlineStr">
+      <c r="G96" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">　</t>
         </is>
@@ -11298,17 +11389,17 @@
           <t>クリエイト薬局八王子散田町店</t>
         </is>
       </c>
-      <c r="I96" t="inlineStr">
+      <c r="I96" s="1" t="inlineStr">
         <is>
           <t>193-0832</t>
         </is>
       </c>
-      <c r="J96" t="inlineStr">
+      <c r="J96" s="1" t="inlineStr">
         <is>
           <t>24八王子市</t>
         </is>
       </c>
-      <c r="K96" t="inlineStr">
+      <c r="K96" s="7" t="inlineStr">
         <is>
           <t>八王子市散田町３－１４－２０</t>
         </is>
@@ -11343,10 +11434,10 @@
           <t>変更届（鳥谷　いづみ、～令和6年9月10日）</t>
         </is>
       </c>
-      <c r="R96" s="1" t="n">
+      <c r="R96" s="3" t="n">
         <v>43867</v>
       </c>
-      <c r="S96" s="1" t="n">
+      <c r="S96" s="3" t="n">
         <v>43922</v>
       </c>
       <c r="T96" t="n">
@@ -11357,7 +11448,7 @@
           <t>31八福障収第1484号</t>
         </is>
       </c>
-      <c r="V96" s="1" t="n">
+      <c r="V96" s="3" t="n">
         <v>46113</v>
       </c>
       <c r="W96" t="inlineStr">
@@ -11384,25 +11475,26 @@
           <t>変更届(開設者（代表取締役）変更（廣瀨　泰三→瀧屋　幸彦)、変更日：令和5年9月1日</t>
         </is>
       </c>
+      <c r="AD96" s="1" t="n"/>
     </row>
     <row r="97">
-      <c r="A97" t="inlineStr">
+      <c r="A97" s="1" t="inlineStr">
         <is>
           <t>2-92</t>
         </is>
       </c>
-      <c r="D97" t="n">
+      <c r="D97" s="2" t="n">
         <v>2955615</v>
       </c>
       <c r="E97" t="n">
         <v>7</v>
       </c>
-      <c r="F97" t="inlineStr">
+      <c r="F97" s="4" t="inlineStr">
         <is>
           <t>1342955615</t>
         </is>
       </c>
-      <c r="G97" t="inlineStr">
+      <c r="G97" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">　</t>
         </is>
@@ -11412,17 +11504,17 @@
           <t>スギ薬局　八王子別所店</t>
         </is>
       </c>
-      <c r="I97" t="inlineStr">
+      <c r="I97" s="1" t="inlineStr">
         <is>
           <t>192-0363</t>
         </is>
       </c>
-      <c r="J97" t="inlineStr">
+      <c r="J97" s="1" t="inlineStr">
         <is>
           <t>24八王子市</t>
         </is>
       </c>
-      <c r="K97" t="inlineStr">
+      <c r="K97" s="7" t="inlineStr">
         <is>
           <t>八王子市別所２－４１－１</t>
         </is>
@@ -11452,10 +11544,11 @@
           <t>竹内　惇</t>
         </is>
       </c>
-      <c r="R97" s="1" t="n">
+      <c r="Q97" s="1" t="n"/>
+      <c r="R97" s="3" t="n">
         <v>43949</v>
       </c>
-      <c r="S97" s="1" t="n">
+      <c r="S97" s="3" t="n">
         <v>44013</v>
       </c>
       <c r="T97" t="n">
@@ -11466,6 +11559,8 @@
           <t>２八福障収第187号</t>
         </is>
       </c>
+      <c r="V97" s="1" t="n"/>
+      <c r="W97" s="1" t="n"/>
       <c r="X97" t="inlineStr">
         <is>
           <t>育成医療・更生医療</t>
@@ -11485,9 +11580,10 @@
           <t>変更届(代表取締役変更：榊原　栄一→杉浦　伸哉、変更日：令和7年5月26日）</t>
         </is>
       </c>
+      <c r="AD97" s="1" t="n"/>
     </row>
     <row r="98">
-      <c r="A98" t="inlineStr">
+      <c r="A98" s="1" t="inlineStr">
         <is>
           <t>2-93</t>
         </is>
@@ -11498,12 +11594,12 @@
       <c r="E98" t="n">
         <v>7</v>
       </c>
-      <c r="F98" t="inlineStr">
+      <c r="F98" s="4" t="inlineStr">
         <is>
           <t>1342954188</t>
         </is>
       </c>
-      <c r="G98" t="inlineStr">
+      <c r="G98" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">　</t>
         </is>
@@ -11518,7 +11614,7 @@
           <t>192-0351</t>
         </is>
       </c>
-      <c r="J98" t="inlineStr">
+      <c r="J98" s="1" t="inlineStr">
         <is>
           <t>24八王子市</t>
         </is>
@@ -11553,7 +11649,7 @@
           <t>滝島　麻衣</t>
         </is>
       </c>
-      <c r="R98" s="1" t="n">
+      <c r="R98" s="3" t="n">
         <v>44064</v>
       </c>
       <c r="S98" t="n">
@@ -11583,7 +11679,7 @@
       </c>
     </row>
     <row r="99">
-      <c r="A99" t="inlineStr">
+      <c r="A99" s="1" t="inlineStr">
         <is>
           <t>2-94</t>
         </is>
@@ -11594,12 +11690,12 @@
       <c r="E99" t="n">
         <v>7</v>
       </c>
-      <c r="F99" t="inlineStr">
+      <c r="F99" s="4" t="inlineStr">
         <is>
           <t>1342954071</t>
         </is>
       </c>
-      <c r="G99" t="inlineStr">
+      <c r="G99" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">　</t>
         </is>
@@ -11614,7 +11710,7 @@
           <t>192-0918</t>
         </is>
       </c>
-      <c r="J99" t="inlineStr">
+      <c r="J99" s="1" t="inlineStr">
         <is>
           <t>24八王子市</t>
         </is>
@@ -11649,7 +11745,7 @@
           <t>中村　優子</t>
         </is>
       </c>
-      <c r="R99" s="1" t="n">
+      <c r="R99" s="3" t="n">
         <v>44057</v>
       </c>
       <c r="S99" t="n">
@@ -11679,7 +11775,7 @@
       </c>
     </row>
     <row r="100">
-      <c r="A100" t="inlineStr">
+      <c r="A100" s="1" t="inlineStr">
         <is>
           <t>2-95</t>
         </is>
@@ -11690,12 +11786,12 @@
       <c r="E100" t="n">
         <v>7</v>
       </c>
-      <c r="F100" t="inlineStr">
+      <c r="F100" s="4" t="inlineStr">
         <is>
           <t>1342955656</t>
         </is>
       </c>
-      <c r="G100" t="inlineStr">
+      <c r="G100" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">　</t>
         </is>
@@ -11710,7 +11806,7 @@
           <t>192-0046</t>
         </is>
       </c>
-      <c r="J100" t="inlineStr">
+      <c r="J100" s="1" t="inlineStr">
         <is>
           <t>24八王子市</t>
         </is>
@@ -11795,7 +11891,7 @@
       </c>
     </row>
     <row r="101">
-      <c r="A101" t="inlineStr">
+      <c r="A101" s="1" t="inlineStr">
         <is>
           <t>2-96</t>
         </is>
@@ -11806,12 +11902,12 @@
       <c r="E101" t="n">
         <v>7</v>
       </c>
-      <c r="F101" t="inlineStr">
+      <c r="F101" s="4" t="inlineStr">
         <is>
           <t>1342955722</t>
         </is>
       </c>
-      <c r="G101" t="inlineStr">
+      <c r="G101" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">　</t>
         </is>
@@ -11826,7 +11922,7 @@
           <t xml:space="preserve">192-0085 </t>
         </is>
       </c>
-      <c r="J101" t="inlineStr">
+      <c r="J101" s="1" t="inlineStr">
         <is>
           <t>24八王子市</t>
         </is>
@@ -11896,7 +11992,7 @@
       </c>
     </row>
     <row r="102">
-      <c r="A102" t="inlineStr">
+      <c r="A102" s="1" t="inlineStr">
         <is>
           <t>2-97</t>
         </is>
@@ -11907,12 +12003,12 @@
       <c r="E102" t="n">
         <v>7</v>
       </c>
-      <c r="F102" t="inlineStr">
+      <c r="F102" s="4" t="inlineStr">
         <is>
           <t>1342955755</t>
         </is>
       </c>
-      <c r="G102" t="inlineStr">
+      <c r="G102" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">　</t>
         </is>
@@ -11927,7 +12023,7 @@
           <t>192-0361</t>
         </is>
       </c>
-      <c r="J102" t="inlineStr">
+      <c r="J102" s="1" t="inlineStr">
         <is>
           <t>24八王子市</t>
         </is>
@@ -11997,7 +12093,7 @@
       </c>
     </row>
     <row r="103">
-      <c r="A103" t="inlineStr">
+      <c r="A103" s="1" t="inlineStr">
         <is>
           <t>2-98</t>
         </is>
@@ -12008,12 +12104,12 @@
       <c r="E103" t="n">
         <v>7</v>
       </c>
-      <c r="F103" t="inlineStr">
+      <c r="F103" s="4" t="inlineStr">
         <is>
           <t>1342955698</t>
         </is>
       </c>
-      <c r="G103" t="inlineStr">
+      <c r="G103" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">　</t>
         </is>
@@ -12028,7 +12124,7 @@
           <t>192-0364</t>
         </is>
       </c>
-      <c r="J103" t="inlineStr">
+      <c r="J103" s="1" t="inlineStr">
         <is>
           <t>24八王子市</t>
         </is>
@@ -12093,23 +12189,23 @@
       </c>
     </row>
     <row r="104">
-      <c r="A104" t="inlineStr">
+      <c r="A104" s="1" t="inlineStr">
         <is>
           <t>2-99</t>
         </is>
       </c>
-      <c r="D104" t="n">
+      <c r="D104" s="2" t="n">
         <v>2955730</v>
       </c>
       <c r="E104" t="n">
         <v>7</v>
       </c>
-      <c r="F104" t="inlineStr">
+      <c r="F104" s="4" t="inlineStr">
         <is>
           <t>1342955730</t>
         </is>
       </c>
-      <c r="G104" t="inlineStr">
+      <c r="G104" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">　</t>
         </is>
@@ -12124,7 +12220,7 @@
           <t>192-0031</t>
         </is>
       </c>
-      <c r="J104" t="inlineStr">
+      <c r="J104" s="1" t="inlineStr">
         <is>
           <t>24八王子市</t>
         </is>
@@ -12164,7 +12260,7 @@
           <t>変更届（亀井　晨佑、～令和7年8月24日）</t>
         </is>
       </c>
-      <c r="R104" s="1" t="n">
+      <c r="R104" s="3" t="n">
         <v>44403</v>
       </c>
       <c r="S104" t="n">
@@ -12178,7 +12274,8 @@
           <t>３八福障収第588号</t>
         </is>
       </c>
-      <c r="X104" t="inlineStr">
+      <c r="V104" s="1" t="n"/>
+      <c r="X104" s="1" t="inlineStr">
         <is>
           <t>育成医療・更生医療</t>
         </is>
@@ -12199,7 +12296,7 @@
       </c>
     </row>
     <row r="105">
-      <c r="A105" t="inlineStr">
+      <c r="A105" s="1" t="inlineStr">
         <is>
           <t>2-100</t>
         </is>
@@ -12215,12 +12312,12 @@
       <c r="E105" t="n">
         <v>7</v>
       </c>
-      <c r="F105" t="inlineStr">
+      <c r="F105" s="4" t="inlineStr">
         <is>
           <t>1342955797</t>
         </is>
       </c>
-      <c r="G105" t="inlineStr">
+      <c r="G105" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">　</t>
         </is>
@@ -12235,7 +12332,7 @@
           <t>193-0835</t>
         </is>
       </c>
-      <c r="J105" t="inlineStr">
+      <c r="J105" s="1" t="inlineStr">
         <is>
           <t>24八王子市</t>
         </is>
@@ -12289,7 +12386,7 @@
           <t>３八福障収第856号</t>
         </is>
       </c>
-      <c r="X105" t="inlineStr">
+      <c r="X105" s="1" t="inlineStr">
         <is>
           <t>育成医療・更生医療</t>
         </is>
@@ -12318,7 +12415,7 @@
       </c>
     </row>
     <row r="106">
-      <c r="A106" t="inlineStr">
+      <c r="A106" s="1" t="inlineStr">
         <is>
           <t>2-101</t>
         </is>
@@ -12329,12 +12426,12 @@
       <c r="E106" t="n">
         <v>7</v>
       </c>
-      <c r="F106" t="inlineStr">
+      <c r="F106" s="4" t="inlineStr">
         <is>
           <t>1342955813</t>
         </is>
       </c>
-      <c r="G106" t="inlineStr">
+      <c r="G106" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">　</t>
         </is>
@@ -12349,7 +12446,7 @@
           <t>193-0832</t>
         </is>
       </c>
-      <c r="J106" t="inlineStr">
+      <c r="J106" s="1" t="inlineStr">
         <is>
           <t>24八王子市</t>
         </is>
@@ -12403,7 +12500,7 @@
           <t>３八福障収第1070号</t>
         </is>
       </c>
-      <c r="X106" t="inlineStr">
+      <c r="X106" s="1" t="inlineStr">
         <is>
           <t>育成医療・更生医療</t>
         </is>
@@ -12424,7 +12521,7 @@
       </c>
     </row>
     <row r="107">
-      <c r="A107" t="inlineStr">
+      <c r="A107" s="1" t="inlineStr">
         <is>
           <t>2-102</t>
         </is>
@@ -12435,12 +12532,12 @@
       <c r="E107" t="n">
         <v>7</v>
       </c>
-      <c r="F107" t="inlineStr">
+      <c r="F107" s="4" t="inlineStr">
         <is>
           <t>1342955839</t>
         </is>
       </c>
-      <c r="G107" t="inlineStr">
+      <c r="G107" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">　</t>
         </is>
@@ -12455,7 +12552,7 @@
           <t>192-0913</t>
         </is>
       </c>
-      <c r="J107" t="inlineStr">
+      <c r="J107" s="1" t="inlineStr">
         <is>
           <t>24八王子市</t>
         </is>
@@ -12509,7 +12606,7 @@
           <t>３八福障収第1095号</t>
         </is>
       </c>
-      <c r="X107" t="inlineStr">
+      <c r="X107" s="1" t="inlineStr">
         <is>
           <t>育成医療・更生医療</t>
         </is>
@@ -12530,7 +12627,7 @@
       </c>
     </row>
     <row r="108">
-      <c r="A108" t="inlineStr">
+      <c r="A108" s="1" t="inlineStr">
         <is>
           <t>2-103</t>
         </is>
@@ -12541,12 +12638,12 @@
       <c r="E108" t="n">
         <v>7</v>
       </c>
-      <c r="F108" t="inlineStr">
+      <c r="F108" s="4" t="inlineStr">
         <is>
           <t>1342955862</t>
         </is>
       </c>
-      <c r="G108" t="inlineStr">
+      <c r="G108" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">　</t>
         </is>
@@ -12561,7 +12658,7 @@
           <t>192-0916</t>
         </is>
       </c>
-      <c r="J108" t="inlineStr">
+      <c r="J108" s="1" t="inlineStr">
         <is>
           <t>24八王子市</t>
         </is>
@@ -12615,7 +12712,7 @@
           <t>３八福障収第1529号</t>
         </is>
       </c>
-      <c r="X108" t="inlineStr">
+      <c r="X108" s="1" t="inlineStr">
         <is>
           <t>育成医療・更生医療</t>
         </is>
@@ -12631,7 +12728,7 @@
       </c>
     </row>
     <row r="109">
-      <c r="A109" t="inlineStr">
+      <c r="A109" s="1" t="inlineStr">
         <is>
           <t>2-104</t>
         </is>
@@ -12642,12 +12739,12 @@
       <c r="E109" t="n">
         <v>7</v>
       </c>
-      <c r="F109" t="inlineStr">
+      <c r="F109" s="4" t="inlineStr">
         <is>
           <t>1342956092</t>
         </is>
       </c>
-      <c r="G109" t="inlineStr">
+      <c r="G109" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">　</t>
         </is>
@@ -12662,7 +12759,7 @@
           <t>192-0033</t>
         </is>
       </c>
-      <c r="J109" t="inlineStr">
+      <c r="J109" s="1" t="inlineStr">
         <is>
           <t>24八王子市</t>
         </is>
@@ -12711,7 +12808,7 @@
           <t>３八福障収第1422号</t>
         </is>
       </c>
-      <c r="X109" t="inlineStr">
+      <c r="X109" s="1" t="inlineStr">
         <is>
           <t>育成医療・更生医療</t>
         </is>
@@ -12732,7 +12829,7 @@
       </c>
     </row>
     <row r="110">
-      <c r="A110" t="inlineStr">
+      <c r="A110" s="1" t="inlineStr">
         <is>
           <t>2-105</t>
         </is>
@@ -12743,12 +12840,12 @@
       <c r="E110" t="n">
         <v>7</v>
       </c>
-      <c r="F110" t="inlineStr">
+      <c r="F110" s="4" t="inlineStr">
         <is>
           <t>1342952059</t>
         </is>
       </c>
-      <c r="G110" t="inlineStr">
+      <c r="G110" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">　</t>
         </is>
@@ -12763,7 +12860,7 @@
           <t>193-0823</t>
         </is>
       </c>
-      <c r="J110" t="inlineStr">
+      <c r="J110" s="1" t="inlineStr">
         <is>
           <t>24八王子市</t>
         </is>
@@ -12817,7 +12914,7 @@
           <t>３八福障収第1405号</t>
         </is>
       </c>
-      <c r="X110" t="inlineStr">
+      <c r="X110" s="1" t="inlineStr">
         <is>
           <t>育成医療・更生医療</t>
         </is>
@@ -12838,7 +12935,7 @@
       </c>
     </row>
     <row r="111">
-      <c r="A111" t="inlineStr">
+      <c r="A111" s="1" t="inlineStr">
         <is>
           <t>2-106</t>
         </is>
@@ -12849,12 +12946,12 @@
       <c r="E111" t="n">
         <v>7</v>
       </c>
-      <c r="F111" t="inlineStr">
+      <c r="F111" s="4" t="inlineStr">
         <is>
           <t>1342955433</t>
         </is>
       </c>
-      <c r="G111" t="inlineStr">
+      <c r="G111" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">　</t>
         </is>
@@ -12869,7 +12966,7 @@
           <t>192-0082</t>
         </is>
       </c>
-      <c r="J111" t="inlineStr">
+      <c r="J111" s="1" t="inlineStr">
         <is>
           <t>24八王子市</t>
         </is>
@@ -12918,7 +13015,7 @@
           <t>３八福障収第1627号</t>
         </is>
       </c>
-      <c r="X111" t="inlineStr">
+      <c r="X111" s="1" t="inlineStr">
         <is>
           <t>育成医療・更生医療</t>
         </is>
@@ -12932,7 +13029,7 @@
       <c r="AA111" t="n">
         <v>50407</v>
       </c>
-      <c r="AC111" t="inlineStr">
+      <c r="AC111" s="1" t="inlineStr">
         <is>
           <t>変更届(代表取締役　松本忠久→田中純一)、～令和５年３月１日）</t>
         </is>
@@ -12944,7 +13041,7 @@
       </c>
     </row>
     <row r="112">
-      <c r="A112" t="inlineStr">
+      <c r="A112" s="1" t="inlineStr">
         <is>
           <t>2-107</t>
         </is>
@@ -12955,12 +13052,12 @@
       <c r="E112" t="n">
         <v>7</v>
       </c>
-      <c r="F112" t="inlineStr">
+      <c r="F112" s="4" t="inlineStr">
         <is>
           <t>1342955672</t>
         </is>
       </c>
-      <c r="G112" t="inlineStr">
+      <c r="G112" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">　</t>
         </is>
@@ -12975,7 +13072,7 @@
           <t>192-0363</t>
         </is>
       </c>
-      <c r="J112" t="inlineStr">
+      <c r="J112" s="1" t="inlineStr">
         <is>
           <t>24八王子市</t>
         </is>
@@ -13029,7 +13126,7 @@
           <t>４八福障収第218号</t>
         </is>
       </c>
-      <c r="X112" t="inlineStr">
+      <c r="X112" s="1" t="inlineStr">
         <is>
           <t>育成医療・更生医療</t>
         </is>
@@ -13056,12 +13153,12 @@
       <c r="E113" t="n">
         <v>7</v>
       </c>
-      <c r="F113" t="inlineStr">
+      <c r="F113" s="4" t="inlineStr">
         <is>
           <t>1342953925</t>
         </is>
       </c>
-      <c r="G113" t="inlineStr">
+      <c r="G113" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">　</t>
         </is>
@@ -13076,7 +13173,7 @@
           <t>193-0942</t>
         </is>
       </c>
-      <c r="J113" t="inlineStr">
+      <c r="J113" s="1" t="inlineStr">
         <is>
           <t>24八王子市</t>
         </is>
@@ -13130,7 +13227,7 @@
           <t>３八福障収第1589号</t>
         </is>
       </c>
-      <c r="X113" t="inlineStr">
+      <c r="X113" s="1" t="inlineStr">
         <is>
           <t>育成医療・更生医療</t>
         </is>
@@ -13144,7 +13241,7 @@
       <c r="AA113" t="n">
         <v>50407</v>
       </c>
-      <c r="AC113" t="inlineStr">
+      <c r="AC113" s="1" t="inlineStr">
         <is>
           <t>変更届(代表取締役　松本忠久→田中純一)、～令和５年３月１日）</t>
         </is>
@@ -13162,11 +13259,12 @@
       <c r="E114" t="n">
         <v>7</v>
       </c>
-      <c r="F114" t="inlineStr">
+      <c r="F114" s="4" t="inlineStr">
         <is>
           <t>1342955979</t>
         </is>
       </c>
+      <c r="G114" s="2" t="n"/>
       <c r="H114" t="inlineStr">
         <is>
           <t>スギ薬局　八王子片倉店</t>
@@ -13177,7 +13275,7 @@
           <t>192-0914</t>
         </is>
       </c>
-      <c r="J114" t="inlineStr">
+      <c r="J114" s="1" t="inlineStr">
         <is>
           <t>24八王子市</t>
         </is>
@@ -13231,7 +13329,7 @@
           <t>４八福障収第1013号</t>
         </is>
       </c>
-      <c r="X114" t="inlineStr">
+      <c r="X114" s="1" t="inlineStr">
         <is>
           <t>育成医療・更生医療</t>
         </is>
@@ -13263,11 +13361,12 @@
       <c r="E115" t="n">
         <v>7</v>
       </c>
-      <c r="F115" t="inlineStr">
+      <c r="F115" s="4" t="inlineStr">
         <is>
           <t>1342956001</t>
         </is>
       </c>
+      <c r="G115" s="2" t="n"/>
       <c r="H115" t="inlineStr">
         <is>
           <t>てぃーだ薬局</t>
@@ -13278,7 +13377,7 @@
           <t>111-0036</t>
         </is>
       </c>
-      <c r="J115" t="inlineStr">
+      <c r="J115" s="1" t="inlineStr">
         <is>
           <t>24八王子市</t>
         </is>
@@ -13327,7 +13426,7 @@
           <t>４八福障収第1034号</t>
         </is>
       </c>
-      <c r="X115" t="inlineStr">
+      <c r="X115" s="1" t="inlineStr">
         <is>
           <t>育成医療・更生医療</t>
         </is>
@@ -13341,6 +13440,7 @@
       <c r="AA115" t="n">
         <v>50501</v>
       </c>
+      <c r="AC115" s="1" t="n"/>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
@@ -13354,11 +13454,12 @@
       <c r="E116" t="n">
         <v>7</v>
       </c>
-      <c r="F116" t="inlineStr">
+      <c r="F116" s="4" t="inlineStr">
         <is>
           <t>1342955953</t>
         </is>
       </c>
+      <c r="G116" s="2" t="n"/>
       <c r="H116" t="inlineStr">
         <is>
           <t>ノムラ薬局　北野店</t>
@@ -13369,7 +13470,7 @@
           <t>192-0911</t>
         </is>
       </c>
-      <c r="J116" t="inlineStr">
+      <c r="J116" s="1" t="inlineStr">
         <is>
           <t>24八王子市</t>
         </is>
@@ -13418,7 +13519,7 @@
           <t>４八福障収第1041号</t>
         </is>
       </c>
-      <c r="X116" t="inlineStr">
+      <c r="X116" s="1" t="inlineStr">
         <is>
           <t>育成医療・更生医療</t>
         </is>
@@ -13432,6 +13533,7 @@
       <c r="AA116" t="n">
         <v>50501</v>
       </c>
+      <c r="AC116" s="1" t="n"/>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
@@ -13445,11 +13547,12 @@
       <c r="E117" t="n">
         <v>7</v>
       </c>
-      <c r="F117" t="inlineStr">
+      <c r="F117" s="4" t="inlineStr">
         <is>
           <t>1342955763</t>
         </is>
       </c>
+      <c r="G117" s="2" t="n"/>
       <c r="H117" t="inlineStr">
         <is>
           <t>とらお薬局</t>
@@ -13460,7 +13563,7 @@
           <t>193-0815</t>
         </is>
       </c>
-      <c r="J117" t="inlineStr">
+      <c r="J117" s="1" t="inlineStr">
         <is>
           <t>24八王子市</t>
         </is>
@@ -13509,7 +13612,7 @@
           <t>４八福障収第1033号</t>
         </is>
       </c>
-      <c r="X117" t="inlineStr">
+      <c r="X117" s="1" t="inlineStr">
         <is>
           <t>育成医療・更生医療</t>
         </is>
@@ -13523,6 +13626,7 @@
       <c r="AA117" t="n">
         <v>50501</v>
       </c>
+      <c r="AC117" s="1" t="n"/>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
@@ -13536,12 +13640,12 @@
       <c r="E118" t="n">
         <v>7</v>
       </c>
-      <c r="F118" t="inlineStr">
+      <c r="F118" s="4" t="inlineStr">
         <is>
           <t>1342955987</t>
         </is>
       </c>
-      <c r="G118" t="inlineStr">
+      <c r="G118" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">　</t>
         </is>
@@ -13556,7 +13660,7 @@
           <t>193-0834</t>
         </is>
       </c>
-      <c r="J118" t="inlineStr">
+      <c r="J118" s="1" t="inlineStr">
         <is>
           <t>24八王子市</t>
         </is>
@@ -13610,7 +13714,7 @@
           <t>４八福障収第1294</t>
         </is>
       </c>
-      <c r="X118" t="inlineStr">
+      <c r="X118" s="1" t="inlineStr">
         <is>
           <t>育成医療・更生医療</t>
         </is>
@@ -13637,12 +13741,12 @@
       <c r="E119" t="n">
         <v>7</v>
       </c>
-      <c r="F119" t="inlineStr">
+      <c r="F119" s="4" t="inlineStr">
         <is>
           <t>1342955995</t>
         </is>
       </c>
-      <c r="G119" t="inlineStr">
+      <c r="G119" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">　</t>
         </is>
@@ -13657,7 +13761,7 @@
           <t>192-0055</t>
         </is>
       </c>
-      <c r="J119" t="inlineStr">
+      <c r="J119" s="1" t="inlineStr">
         <is>
           <t>24八王子市</t>
         </is>
@@ -13711,7 +13815,7 @@
           <t>４八福障収第1373号</t>
         </is>
       </c>
-      <c r="X119" t="inlineStr">
+      <c r="X119" s="1" t="inlineStr">
         <is>
           <t>育成医療・更生医療</t>
         </is>
@@ -13743,7 +13847,7 @@
       <c r="E120" t="n">
         <v>7</v>
       </c>
-      <c r="F120" t="inlineStr">
+      <c r="F120" s="4" t="inlineStr">
         <is>
           <t>1342956019</t>
         </is>
@@ -13758,7 +13862,7 @@
           <t>193-0835</t>
         </is>
       </c>
-      <c r="J120" t="inlineStr">
+      <c r="J120" s="1" t="inlineStr">
         <is>
           <t>24八王子市</t>
         </is>
@@ -13807,7 +13911,7 @@
           <t>５八福障第1095号</t>
         </is>
       </c>
-      <c r="X120" t="inlineStr">
+      <c r="X120" s="1" t="inlineStr">
         <is>
           <t>育成医療・更生医療</t>
         </is>
@@ -13823,7 +13927,7 @@
       </c>
     </row>
     <row r="121">
-      <c r="A121" t="inlineStr">
+      <c r="A121" s="1" t="inlineStr">
         <is>
           <t>2-116</t>
         </is>
@@ -13834,12 +13938,12 @@
       <c r="E121" t="n">
         <v>7</v>
       </c>
-      <c r="F121" t="inlineStr">
+      <c r="F121" s="4" t="inlineStr">
         <is>
           <t>1342956027</t>
         </is>
       </c>
-      <c r="G121" t="inlineStr">
+      <c r="G121" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">　</t>
         </is>
@@ -13854,7 +13958,7 @@
           <t>193-0803</t>
         </is>
       </c>
-      <c r="J121" t="inlineStr">
+      <c r="J121" s="1" t="inlineStr">
         <is>
           <t>24八王子市</t>
         </is>
@@ -13919,7 +14023,7 @@
       </c>
     </row>
     <row r="122">
-      <c r="A122" t="inlineStr">
+      <c r="A122" s="1" t="inlineStr">
         <is>
           <t>2-117</t>
         </is>
@@ -13930,12 +14034,12 @@
       <c r="E122" t="n">
         <v>7</v>
       </c>
-      <c r="F122" t="inlineStr">
+      <c r="F122" s="4" t="inlineStr">
         <is>
           <t>1342956035</t>
         </is>
       </c>
-      <c r="G122" t="inlineStr">
+      <c r="G122" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">　</t>
         </is>
@@ -13950,7 +14054,7 @@
           <t>193-0832</t>
         </is>
       </c>
-      <c r="J122" t="inlineStr">
+      <c r="J122" s="1" t="inlineStr">
         <is>
           <t>24八王子市</t>
         </is>
@@ -13999,7 +14103,7 @@
           <t>５八福障第3758号</t>
         </is>
       </c>
-      <c r="X122" t="inlineStr">
+      <c r="X122" s="1" t="inlineStr">
         <is>
           <t>育成医療・更生医療</t>
         </is>
@@ -14046,7 +14150,7 @@
           <t>192-0074</t>
         </is>
       </c>
-      <c r="J123" t="inlineStr">
+      <c r="J123" s="1" t="inlineStr">
         <is>
           <t>24八王子市</t>
         </is>
@@ -14095,7 +14199,7 @@
           <t>５八福障第5425号</t>
         </is>
       </c>
-      <c r="X123" t="inlineStr">
+      <c r="X123" s="1" t="inlineStr">
         <is>
           <t>育成医療・更生医療</t>
         </is>
@@ -14137,7 +14241,7 @@
           <t>193-0824</t>
         </is>
       </c>
-      <c r="J124" t="inlineStr">
+      <c r="J124" s="1" t="inlineStr">
         <is>
           <t>24八王子市</t>
         </is>
@@ -14186,7 +14290,7 @@
           <t>５八福障第6445号</t>
         </is>
       </c>
-      <c r="X124" t="inlineStr">
+      <c r="X124" s="1" t="inlineStr">
         <is>
           <t>育成医療・更生医療</t>
         </is>
@@ -14233,7 +14337,7 @@
           <t>193-0811</t>
         </is>
       </c>
-      <c r="J125" t="inlineStr">
+      <c r="J125" s="1" t="inlineStr">
         <is>
           <t>24八王子市</t>
         </is>
@@ -14282,7 +14386,7 @@
           <t>６八福障第4142号</t>
         </is>
       </c>
-      <c r="X125" t="inlineStr">
+      <c r="X125" s="1" t="inlineStr">
         <is>
           <t>育成医療・更生医療</t>
         </is>
@@ -14324,7 +14428,7 @@
           <t>192-0916</t>
         </is>
       </c>
-      <c r="J126" t="inlineStr">
+      <c r="J126" s="1" t="inlineStr">
         <is>
           <t>24八王子市</t>
         </is>
@@ -14373,7 +14477,7 @@
           <t>６八福障第4142号</t>
         </is>
       </c>
-      <c r="X126" t="inlineStr">
+      <c r="X126" s="1" t="inlineStr">
         <is>
           <t>育成医療・更生医療</t>
         </is>
@@ -14420,7 +14524,7 @@
           <t>193-0803</t>
         </is>
       </c>
-      <c r="J127" t="inlineStr">
+      <c r="J127" s="1" t="inlineStr">
         <is>
           <t>24八王子市</t>
         </is>
@@ -14435,7 +14539,7 @@
           <t>042-686-0353</t>
         </is>
       </c>
-      <c r="M127" t="inlineStr">
+      <c r="M127" s="3" t="inlineStr">
         <is>
           <t>株式会社NeoLinks</t>
         </is>
@@ -14469,7 +14573,7 @@
           <t>６八福障第6221号</t>
         </is>
       </c>
-      <c r="X127" t="inlineStr">
+      <c r="X127" s="1" t="inlineStr">
         <is>
           <t>育成医療・更生医療</t>
         </is>
@@ -14511,7 +14615,7 @@
           <t>192-0355</t>
         </is>
       </c>
-      <c r="J128" t="inlineStr">
+      <c r="J128" s="1" t="inlineStr">
         <is>
           <t>24八王子市</t>
         </is>
@@ -14526,7 +14630,7 @@
           <t>042-670-2593</t>
         </is>
       </c>
-      <c r="M128" t="inlineStr">
+      <c r="M128" s="3" t="inlineStr">
         <is>
           <t>株式会社アイセイ薬局</t>
         </is>
@@ -14560,7 +14664,7 @@
           <t>６八福障第6221号</t>
         </is>
       </c>
-      <c r="X128" t="inlineStr">
+      <c r="X128" s="1" t="inlineStr">
         <is>
           <t>育成医療・更生医療</t>
         </is>
@@ -14602,7 +14706,7 @@
           <t>192-0045</t>
         </is>
       </c>
-      <c r="J129" t="inlineStr">
+      <c r="J129" s="1" t="inlineStr">
         <is>
           <t>24八王子市</t>
         </is>
@@ -14617,7 +14721,7 @@
           <t>042-631-8570</t>
         </is>
       </c>
-      <c r="M129" t="inlineStr">
+      <c r="M129" s="3" t="inlineStr">
         <is>
           <t>株式会社クリエイトエス・ディー</t>
         </is>
@@ -14627,7 +14731,7 @@
           <t>225-0014</t>
         </is>
       </c>
-      <c r="O129" t="inlineStr">
+      <c r="O129" s="3" t="inlineStr">
         <is>
           <t>神奈川県横浜市青葉区荏田西2-3-2</t>
         </is>
@@ -14656,7 +14760,7 @@
           <t>６八福障第6221号</t>
         </is>
       </c>
-      <c r="X129" t="inlineStr">
+      <c r="X129" s="1" t="inlineStr">
         <is>
           <t>育成医療・更生医療</t>
         </is>
@@ -14698,7 +14802,7 @@
           <t>192-0364</t>
         </is>
       </c>
-      <c r="J130" t="inlineStr">
+      <c r="J130" s="1" t="inlineStr">
         <is>
           <t>24八王子市</t>
         </is>
@@ -14713,7 +14817,7 @@
           <t>042-653-9341</t>
         </is>
       </c>
-      <c r="M130" t="inlineStr">
+      <c r="M130" s="3" t="inlineStr">
         <is>
           <t>株式会社プラックス</t>
         </is>
@@ -14747,7 +14851,7 @@
           <t>６八福障第8018号</t>
         </is>
       </c>
-      <c r="X130" t="inlineStr">
+      <c r="X130" s="1" t="inlineStr">
         <is>
           <t>育成医療・更生医療</t>
         </is>
@@ -14789,7 +14893,7 @@
           <t>193-0803</t>
         </is>
       </c>
-      <c r="J131" t="inlineStr">
+      <c r="J131" s="1" t="inlineStr">
         <is>
           <t>24八王子市</t>
         </is>
@@ -14804,7 +14908,7 @@
           <t>042-649-6969</t>
         </is>
       </c>
-      <c r="M131" t="inlineStr">
+      <c r="M131" s="3" t="inlineStr">
         <is>
           <t>株式会社寶輪会</t>
         </is>
@@ -14814,7 +14918,7 @@
           <t>259-0201</t>
         </is>
       </c>
-      <c r="O131" t="inlineStr">
+      <c r="O131" s="3" t="inlineStr">
         <is>
           <t>神奈川県足柄下郡真鶴町真鶴字入窪１３２２－１</t>
         </is>
@@ -14838,7 +14942,7 @@
           <t>６八福障第8018号</t>
         </is>
       </c>
-      <c r="X131" t="inlineStr">
+      <c r="X131" s="1" t="inlineStr">
         <is>
           <t>育成医療・更生医療</t>
         </is>
@@ -14880,7 +14984,7 @@
           <t>193-0835</t>
         </is>
       </c>
-      <c r="J132" t="inlineStr">
+      <c r="J132" s="1" t="inlineStr">
         <is>
           <t>24八王子市</t>
         </is>
@@ -14895,7 +14999,7 @@
           <t>042-665-7716</t>
         </is>
       </c>
-      <c r="M132" t="inlineStr">
+      <c r="M132" s="3" t="inlineStr">
         <is>
           <t>株式会社MEDIPORT</t>
         </is>
@@ -14905,7 +15009,7 @@
           <t>192-0046</t>
         </is>
       </c>
-      <c r="O132" t="inlineStr">
+      <c r="O132" s="3" t="inlineStr">
         <is>
           <t>八王子市明神町4-8-13</t>
         </is>
@@ -14929,7 +15033,7 @@
           <t>７八福障第1714号</t>
         </is>
       </c>
-      <c r="X132" t="inlineStr">
+      <c r="X132" s="1" t="inlineStr">
         <is>
           <t>育成医療・更生医療</t>
         </is>
@@ -14971,7 +15075,7 @@
           <t>193-0944</t>
         </is>
       </c>
-      <c r="J133" t="inlineStr">
+      <c r="J133" s="1" t="inlineStr">
         <is>
           <t>24八王子市</t>
         </is>
@@ -14986,7 +15090,7 @@
           <t>042-673-2468</t>
         </is>
       </c>
-      <c r="M133" t="inlineStr">
+      <c r="M133" s="3" t="inlineStr">
         <is>
           <t>株式会社フォルマン</t>
         </is>
@@ -14996,7 +15100,7 @@
           <t>327-0843</t>
         </is>
       </c>
-      <c r="O133" t="inlineStr">
+      <c r="O133" s="3" t="inlineStr">
         <is>
           <t>栃木県佐野市堀米町３９６６－１</t>
         </is>
@@ -15025,7 +15129,7 @@
           <t>７八福障第6127号</t>
         </is>
       </c>
-      <c r="X133" t="inlineStr">
+      <c r="X133" s="1" t="inlineStr">
         <is>
           <t>育成医療・更生医療</t>
         </is>
@@ -15067,7 +15171,7 @@
           <t>192-0033</t>
         </is>
       </c>
-      <c r="J134" t="inlineStr">
+      <c r="J134" s="1" t="inlineStr">
         <is>
           <t>24八王子市</t>
         </is>
@@ -15082,7 +15186,7 @@
           <t>042-649-5606</t>
         </is>
       </c>
-      <c r="M134" t="inlineStr">
+      <c r="M134" s="3" t="inlineStr">
         <is>
           <t>日本調剤株式会社</t>
         </is>
@@ -15092,7 +15196,7 @@
           <t>108-0014</t>
         </is>
       </c>
-      <c r="O134" t="inlineStr">
+      <c r="O134" s="3" t="inlineStr">
         <is>
           <t>東京都港区芝五丁目３３番１１号</t>
         </is>
@@ -15116,7 +15220,7 @@
           <t>7八福障第8178号</t>
         </is>
       </c>
-      <c r="X134" t="inlineStr">
+      <c r="X134" s="1" t="inlineStr">
         <is>
           <t>育成医療・更生医療</t>
         </is>
@@ -15158,7 +15262,7 @@
           <t>192-0046</t>
         </is>
       </c>
-      <c r="J135" t="inlineStr">
+      <c r="J135" s="1" t="inlineStr">
         <is>
           <t>24八王子市</t>
         </is>
@@ -15173,7 +15277,7 @@
           <t>042-649-2838</t>
         </is>
       </c>
-      <c r="M135" t="inlineStr">
+      <c r="M135" s="3" t="inlineStr">
         <is>
           <t>株式会社マツモトキヨシ</t>
         </is>
@@ -15183,7 +15287,7 @@
           <t>270-0034</t>
         </is>
       </c>
-      <c r="O135" t="inlineStr">
+      <c r="O135" s="3" t="inlineStr">
         <is>
           <t>千葉県松戸市新松戸東９番地１</t>
         </is>
@@ -15207,7 +15311,7 @@
           <t>7八福障第8178号</t>
         </is>
       </c>
-      <c r="X135" t="inlineStr">
+      <c r="X135" s="1" t="inlineStr">
         <is>
           <t>育成医療・更生医療</t>
         </is>
@@ -15249,7 +15353,7 @@
           <t>192-0083</t>
         </is>
       </c>
-      <c r="J136" t="inlineStr">
+      <c r="J136" s="1" t="inlineStr">
         <is>
           <t>24八王子市</t>
         </is>
@@ -15264,7 +15368,7 @@
           <t>042-649-9810</t>
         </is>
       </c>
-      <c r="M136" t="inlineStr">
+      <c r="M136" s="3" t="inlineStr">
         <is>
           <t>株式会社トラストファーマシー</t>
         </is>
@@ -15274,7 +15378,7 @@
           <t>171-0022</t>
         </is>
       </c>
-      <c r="O136" t="inlineStr">
+      <c r="O136" s="3" t="inlineStr">
         <is>
           <t>東京都豊島区南池袋２－２９－１２</t>
         </is>
@@ -15298,7 +15402,7 @@
           <t>7八福障第8178号</t>
         </is>
       </c>
-      <c r="X136" t="inlineStr">
+      <c r="X136" s="1" t="inlineStr">
         <is>
           <t>育成医療・更生医療</t>
         </is>
@@ -15340,7 +15444,7 @@
           <t>192-0916</t>
         </is>
       </c>
-      <c r="J137" t="inlineStr">
+      <c r="J137" s="1" t="inlineStr">
         <is>
           <t>24八王子市</t>
         </is>
@@ -15355,7 +15459,7 @@
           <t>042-632-7255</t>
         </is>
       </c>
-      <c r="M137" t="inlineStr">
+      <c r="M137" s="3" t="inlineStr">
         <is>
           <t>株式会社カインズ</t>
         </is>
@@ -15365,7 +15469,7 @@
           <t>151-0053</t>
         </is>
       </c>
-      <c r="O137" t="inlineStr">
+      <c r="O137" s="3" t="inlineStr">
         <is>
           <t>東京都渋谷区代々木２－５－５</t>
         </is>
@@ -15389,7 +15493,7 @@
           <t>7八福障第8178号</t>
         </is>
       </c>
-      <c r="X137" t="inlineStr">
+      <c r="X137" s="1" t="inlineStr">
         <is>
           <t>育成医療・更生医療</t>
         </is>
@@ -15406,9 +15510,15 @@
     </row>
     <row r="138"/>
     <row r="139"/>
-    <row r="140"/>
-    <row r="141"/>
-    <row r="142"/>
+    <row r="140">
+      <c r="I140" s="6" t="n"/>
+    </row>
+    <row r="141">
+      <c r="I141" s="6" t="n"/>
+    </row>
+    <row r="142">
+      <c r="I142" s="6" t="n"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/hachioji_kousei_yakkyoku.xlsx
+++ b/data/hachioji_kousei_yakkyoku.xlsx
@@ -1,24 +1,22 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="27932"/>
-  <workbookPr defaultThemeVersion="202300"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30131"/>
+  <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\H.H\Desktop\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\h_hyakutake\Desktop\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{1A1DF8AE-02D9-46A1-80E9-FA6423B14126}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{DCD0A6E2-DBD6-48C3-BC9E-7B5E4BEC55E4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="23260" windowHeight="13900" xr2:uid="{9BBBB9BE-A425-455E-8E82-0F637A225DB1}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11760" xr2:uid="{733131F7-ABF7-482D-B677-C4F12645DCAA}"/>
   </bookViews>
   <sheets>
     <sheet name="薬局" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">薬局!$A$3:$AK$137</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="0">薬局!$A$1:$AK$141</definedName>
-    <definedName name="_xlnm.Print_Titles" localSheetId="0">薬局!$2:$3</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -32,8 +30,6 @@
         <xcalcf:feature name="microsoft.com:FV"/>
         <xcalcf:feature name="microsoft.com:CNMTM"/>
         <xcalcf:feature name="microsoft.com:LET_WF"/>
-        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
-        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
       </xcalcf:calcFeatures>
     </ext>
   </extLst>
@@ -41,9 +37,9 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1990" uniqueCount="1406">
-  <si>
-    <t>指定自立支援医療機関（育成・更生医療）指定一覧【薬局】（令和8年6月1日現在）</t>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2008" uniqueCount="1414">
+  <si>
+    <t>指定自立支援医療機関（育成・更生医療）指定一覧【薬局】（令和8年7月1日現在）</t>
     <rPh sb="0" eb="2">
       <t>シテイ</t>
     </rPh>
@@ -159,7 +155,7 @@
     <phoneticPr fontId="6"/>
   </si>
   <si>
-    <t>61</t>
+    <t>No.</t>
     <phoneticPr fontId="6"/>
   </si>
   <si>
@@ -5836,6 +5832,10 @@
     <t>2-50</t>
   </si>
   <si>
+    <t>開設者氏名、医療機関コード変更</t>
+    <phoneticPr fontId="6"/>
+  </si>
+  <si>
     <t>開晴薬局</t>
   </si>
   <si>
@@ -5959,6 +5959,43 @@
     <phoneticPr fontId="5"/>
   </si>
   <si>
+    <t>変更届（開設者氏名：株式会社開晴　代表取締役　斉藤　晴子→株式会社ミカンネット　代表取締役　井上　菜津子、医療機関コード：2954055→後日連絡、変更日：令和8年8月1日）</t>
+    <rPh sb="14" eb="15">
+      <t>カイ</t>
+    </rPh>
+    <rPh sb="15" eb="16">
+      <t>セイ</t>
+    </rPh>
+    <rPh sb="23" eb="25">
+      <t>サイトウ</t>
+    </rPh>
+    <rPh sb="26" eb="27">
+      <t>ハレ</t>
+    </rPh>
+    <rPh sb="27" eb="28">
+      <t>コ</t>
+    </rPh>
+    <rPh sb="46" eb="48">
+      <t>イノウエ</t>
+    </rPh>
+    <rPh sb="49" eb="50">
+      <t>ナ</t>
+    </rPh>
+    <rPh sb="50" eb="51">
+      <t>ツ</t>
+    </rPh>
+    <rPh sb="51" eb="52">
+      <t>コ</t>
+    </rPh>
+    <rPh sb="69" eb="71">
+      <t>ゴジツ</t>
+    </rPh>
+    <rPh sb="71" eb="73">
+      <t>レンラク</t>
+    </rPh>
+    <phoneticPr fontId="6"/>
+  </si>
+  <si>
     <t>2-51</t>
   </si>
   <si>
@@ -7315,6 +7352,10 @@
     <phoneticPr fontId="5"/>
   </si>
   <si>
+    <t>変更（薬剤師の変更）</t>
+    <phoneticPr fontId="6"/>
+  </si>
+  <si>
     <t>日本調剤八王子薬局</t>
     <rPh sb="0" eb="2">
       <t>ニホン</t>
@@ -7347,31 +7388,25 @@
     <phoneticPr fontId="5"/>
   </si>
   <si>
-    <t>吉留　貴瑛</t>
+    <t>榎田　晃久</t>
     <rPh sb="0" eb="2">
-      <t>ヨシトメ</t>
+      <t>エノダ</t>
     </rPh>
     <rPh sb="3" eb="4">
-      <t>キ</t>
+      <t>アキラ</t>
     </rPh>
     <rPh sb="4" eb="5">
-      <t>エイ</t>
-    </rPh>
-    <phoneticPr fontId="6"/>
-  </si>
-  <si>
-    <t>変更届（山口　剛志、～令和5年7月31日</t>
+      <t>ヒサ</t>
+    </rPh>
+    <phoneticPr fontId="6"/>
+  </si>
+  <si>
+    <t>変更届（吉留　貴瑛、～令和8年2月28日</t>
     <rPh sb="0" eb="2">
       <t>ヘンコウ</t>
     </rPh>
     <rPh sb="2" eb="3">
       <t>トドケ</t>
-    </rPh>
-    <rPh sb="4" eb="6">
-      <t>ヤマグチ</t>
-    </rPh>
-    <rPh sb="7" eb="9">
-      <t>ツヨシ</t>
     </rPh>
     <rPh sb="11" eb="13">
       <t>レイワ</t>
@@ -9723,6 +9758,13 @@
     <t>2-75</t>
   </si>
   <si>
+    <t>更新</t>
+    <rPh sb="0" eb="2">
+      <t>コウシン</t>
+    </rPh>
+    <phoneticPr fontId="6"/>
+  </si>
+  <si>
     <t>やまだ駅前薬局</t>
     <rPh sb="3" eb="5">
       <t>エキマエ</t>
@@ -9819,25 +9861,7 @@
     <phoneticPr fontId="5"/>
   </si>
   <si>
-    <t>2八福障収第234号</t>
-    <rPh sb="1" eb="2">
-      <t>ハチ</t>
-    </rPh>
-    <rPh sb="2" eb="3">
-      <t>フク</t>
-    </rPh>
-    <rPh sb="3" eb="4">
-      <t>ショウ</t>
-    </rPh>
-    <rPh sb="4" eb="5">
-      <t>シュウ</t>
-    </rPh>
-    <rPh sb="5" eb="6">
-      <t>ダイ</t>
-    </rPh>
-    <rPh sb="9" eb="10">
-      <t>ゴウ</t>
-    </rPh>
+    <t>8八福障第1893号</t>
     <phoneticPr fontId="6"/>
   </si>
   <si>
@@ -9977,28 +10001,6 @@
     <phoneticPr fontId="6"/>
   </si>
   <si>
-    <t>31八福障収第1797号</t>
-    <rPh sb="2" eb="3">
-      <t>ハチ</t>
-    </rPh>
-    <rPh sb="3" eb="4">
-      <t>フク</t>
-    </rPh>
-    <rPh sb="4" eb="5">
-      <t>ショウ</t>
-    </rPh>
-    <rPh sb="5" eb="6">
-      <t>シュウ</t>
-    </rPh>
-    <rPh sb="6" eb="7">
-      <t>ダイ</t>
-    </rPh>
-    <rPh sb="11" eb="12">
-      <t>ゴウ</t>
-    </rPh>
-    <phoneticPr fontId="6"/>
-  </si>
-  <si>
     <t>変更届（開設者住所（東京都八王子市堀之内１４３２－１→、～令和1年8月30日）</t>
     <rPh sb="0" eb="2">
       <t>ヘンコウ</t>
@@ -10121,28 +10123,6 @@
     <phoneticPr fontId="5"/>
   </si>
   <si>
-    <t>2八福障収第252号</t>
-    <rPh sb="1" eb="2">
-      <t>ハチ</t>
-    </rPh>
-    <rPh sb="2" eb="3">
-      <t>フク</t>
-    </rPh>
-    <rPh sb="3" eb="4">
-      <t>ショウ</t>
-    </rPh>
-    <rPh sb="4" eb="5">
-      <t>シュウ</t>
-    </rPh>
-    <rPh sb="5" eb="6">
-      <t>ダイ</t>
-    </rPh>
-    <rPh sb="9" eb="10">
-      <t>ゴウ</t>
-    </rPh>
-    <phoneticPr fontId="6"/>
-  </si>
-  <si>
     <t>変更届（医療機関コード（2945899→）、～平成27年11月1日））</t>
     <rPh sb="4" eb="6">
       <t>イリョウ</t>
@@ -10159,6 +10139,13 @@
     <t>2-78</t>
   </si>
   <si>
+    <t>変更（薬剤師の変更）、更新</t>
+    <rPh sb="11" eb="13">
+      <t>コウシン</t>
+    </rPh>
+    <phoneticPr fontId="6"/>
+  </si>
+  <si>
     <t>スギ薬局　八日町店</t>
     <rPh sb="2" eb="4">
       <t>ヤッキョク</t>
@@ -10219,17 +10206,17 @@
     <phoneticPr fontId="5"/>
   </si>
   <si>
-    <t>栗原　由希</t>
+    <t>今井　裕美</t>
     <rPh sb="0" eb="2">
-      <t>クリハラ</t>
+      <t>イマイ</t>
     </rPh>
     <rPh sb="3" eb="5">
-      <t>ユキ</t>
-    </rPh>
-    <phoneticPr fontId="6"/>
-  </si>
-  <si>
-    <t>変更届（河合　洋介、～平成29年11月30日）</t>
+      <t>ユミ</t>
+    </rPh>
+    <phoneticPr fontId="6"/>
+  </si>
+  <si>
+    <t>変更届（栗原　由希、～令和8年2月28日）</t>
     <rPh sb="0" eb="2">
       <t>ヘンコウ</t>
     </rPh>
@@ -10237,40 +10224,18 @@
       <t>トド</t>
     </rPh>
     <rPh sb="11" eb="13">
-      <t>ヘイセイ</t>
-    </rPh>
-    <rPh sb="15" eb="16">
+      <t>レイワ</t>
+    </rPh>
+    <rPh sb="14" eb="15">
       <t>トシ</t>
     </rPh>
-    <rPh sb="18" eb="19">
+    <rPh sb="16" eb="17">
       <t>ツキ</t>
     </rPh>
-    <rPh sb="21" eb="22">
+    <rPh sb="19" eb="20">
       <t>ヒ</t>
     </rPh>
     <phoneticPr fontId="5"/>
-  </si>
-  <si>
-    <t>2八福障収第271号</t>
-    <rPh sb="1" eb="2">
-      <t>ハチ</t>
-    </rPh>
-    <rPh sb="2" eb="3">
-      <t>フク</t>
-    </rPh>
-    <rPh sb="3" eb="4">
-      <t>ショウ</t>
-    </rPh>
-    <rPh sb="4" eb="5">
-      <t>シュウ</t>
-    </rPh>
-    <rPh sb="5" eb="6">
-      <t>ダイ</t>
-    </rPh>
-    <rPh sb="9" eb="10">
-      <t>ゴウ</t>
-    </rPh>
-    <phoneticPr fontId="6"/>
   </si>
   <si>
     <t>変更届(代表取締役変更：榊原　栄一→杉浦　伸哉、変更日：令和7年5月26日）</t>
@@ -10804,11 +10769,21 @@
     <phoneticPr fontId="6"/>
   </si>
   <si>
-    <t>竹中　亮介</t>
+    <t>浅田　沙織</t>
     <rPh sb="0" eb="2">
+      <t>アサダ</t>
+    </rPh>
+    <rPh sb="3" eb="5">
+      <t>サオリ</t>
+    </rPh>
+    <phoneticPr fontId="6"/>
+  </si>
+  <si>
+    <t>変更届(竹中　亮介、～令和8年1月10日）</t>
+    <rPh sb="4" eb="6">
       <t>タケナカ</t>
     </rPh>
-    <rPh sb="3" eb="5">
+    <rPh sb="7" eb="9">
       <t>リョウスケ</t>
     </rPh>
     <phoneticPr fontId="6"/>
@@ -12077,14 +12052,36 @@
     <phoneticPr fontId="6"/>
   </si>
   <si>
-    <t>竹内　惇</t>
+    <t>山本　大貴</t>
     <rPh sb="0" eb="2">
-      <t>タケウチ</t>
-    </rPh>
-    <rPh sb="3" eb="4">
-      <t>アツシ</t>
-    </rPh>
-    <phoneticPr fontId="6"/>
+      <t>ヤマモト</t>
+    </rPh>
+    <rPh sb="3" eb="5">
+      <t>ダイキ</t>
+    </rPh>
+    <phoneticPr fontId="6"/>
+  </si>
+  <si>
+    <t>変更届（竹内　惇、～令和8年2月28日）</t>
+    <rPh sb="0" eb="2">
+      <t>ヘンコウ</t>
+    </rPh>
+    <rPh sb="2" eb="3">
+      <t>トド</t>
+    </rPh>
+    <rPh sb="10" eb="12">
+      <t>レイワ</t>
+    </rPh>
+    <rPh sb="13" eb="14">
+      <t>トシ</t>
+    </rPh>
+    <rPh sb="15" eb="16">
+      <t>ツキ</t>
+    </rPh>
+    <rPh sb="18" eb="19">
+      <t>ヒ</t>
+    </rPh>
+    <phoneticPr fontId="5"/>
   </si>
   <si>
     <t>２八福障収第187号</t>
@@ -12548,13 +12545,17 @@
     <t>神奈川県横浜市青葉区荏田西２－３－２</t>
   </si>
   <si>
-    <t>守屋　大輔</t>
+    <t>竹中　亮介</t>
     <rPh sb="0" eb="2">
-      <t>モリヤ</t>
+      <t>タケナカ</t>
     </rPh>
     <rPh sb="3" eb="5">
-      <t>ダイスケ</t>
-    </rPh>
+      <t>リョウスケ</t>
+    </rPh>
+    <phoneticPr fontId="6"/>
+  </si>
+  <si>
+    <t>変更届(守屋　大輔、～令和8年1月10日）</t>
     <phoneticPr fontId="6"/>
   </si>
   <si>
@@ -15205,6 +15206,19 @@
     <phoneticPr fontId="6"/>
   </si>
   <si>
+    <t>代表取締役氏名変更</t>
+    <rPh sb="0" eb="5">
+      <t>ダイヒョウトリシマリヤク</t>
+    </rPh>
+    <rPh sb="5" eb="7">
+      <t>シメイ</t>
+    </rPh>
+    <rPh sb="7" eb="9">
+      <t>ヘンコウ</t>
+    </rPh>
+    <phoneticPr fontId="6"/>
+  </si>
+  <si>
     <t>おおるり薬局</t>
     <rPh sb="4" eb="6">
       <t>ヤッキョク</t>
@@ -15286,6 +15300,49 @@
     <phoneticPr fontId="6"/>
   </si>
   <si>
+    <t>変更届(代表取締役氏名：秋山　真衣→奈良　真衣、変更日：令和7年12月19日）</t>
+    <rPh sb="0" eb="2">
+      <t>ヘンコウ</t>
+    </rPh>
+    <rPh sb="2" eb="3">
+      <t>トドケ</t>
+    </rPh>
+    <rPh sb="4" eb="6">
+      <t>ダイヒョウ</t>
+    </rPh>
+    <rPh sb="6" eb="8">
+      <t>トリシマリ</t>
+    </rPh>
+    <rPh sb="9" eb="11">
+      <t>シメイ</t>
+    </rPh>
+    <rPh sb="12" eb="14">
+      <t>アキヤマ</t>
+    </rPh>
+    <rPh sb="15" eb="17">
+      <t>マイ</t>
+    </rPh>
+    <rPh sb="17" eb="18">
+      <t>タキ</t>
+    </rPh>
+    <rPh sb="18" eb="20">
+      <t>ナラ</t>
+    </rPh>
+    <rPh sb="21" eb="23">
+      <t>マイ</t>
+    </rPh>
+    <rPh sb="24" eb="27">
+      <t>ヘンコウビ</t>
+    </rPh>
+    <rPh sb="25" eb="26">
+      <t>ビ</t>
+    </rPh>
+    <rPh sb="27" eb="29">
+      <t>レイワ</t>
+    </rPh>
+    <phoneticPr fontId="6"/>
+  </si>
+  <si>
     <t>2-129</t>
     <phoneticPr fontId="6"/>
   </si>
@@ -15507,16 +15564,17 @@
     <phoneticPr fontId="5"/>
   </si>
   <si>
-    <t>前田　永都</t>
+    <t>根本　舞</t>
     <rPh sb="0" eb="2">
-      <t>マエダ</t>
+      <t>ネモト</t>
     </rPh>
     <rPh sb="3" eb="4">
-      <t>エイ</t>
-    </rPh>
-    <rPh sb="4" eb="5">
-      <t>ト</t>
-    </rPh>
+      <t>マイ</t>
+    </rPh>
+    <phoneticPr fontId="6"/>
+  </si>
+  <si>
+    <t>変更届(前田　永都、～令和8年3月31日）</t>
     <phoneticPr fontId="6"/>
   </si>
   <si>
@@ -15593,7 +15651,7 @@
     <font>
       <sz val="11"/>
       <color theme="1"/>
-      <name val="游ゴシック"/>
+      <name val="ＭＳ Ｐゴシック"/>
       <family val="3"/>
       <charset val="128"/>
       <scheme val="minor"/>
@@ -15601,7 +15659,7 @@
     <font>
       <sz val="11"/>
       <color theme="1"/>
-      <name val="游ゴシック"/>
+      <name val="ＭＳ Ｐゴシック"/>
       <family val="2"/>
       <charset val="128"/>
       <scheme val="minor"/>
@@ -15620,7 +15678,7 @@
     </font>
     <font>
       <sz val="6"/>
-      <name val="游ゴシック"/>
+      <name val="ＭＳ Ｐゴシック"/>
       <family val="2"/>
       <charset val="128"/>
       <scheme val="minor"/>
@@ -15640,7 +15698,7 @@
     <font>
       <sz val="11"/>
       <color theme="1"/>
-      <name val="游ゴシック"/>
+      <name val="ＭＳ Ｐゴシック"/>
       <family val="3"/>
       <charset val="128"/>
       <scheme val="minor"/>
@@ -15666,7 +15724,7 @@
     </font>
     <font>
       <sz val="6"/>
-      <name val="游ゴシック"/>
+      <name val="ＭＳ Ｐゴシック"/>
       <family val="3"/>
       <charset val="128"/>
       <scheme val="minor"/>
@@ -15674,7 +15732,7 @@
     <font>
       <sz val="9"/>
       <color theme="1"/>
-      <name val="游ゴシック"/>
+      <name val="ＭＳ Ｐゴシック"/>
       <family val="2"/>
       <charset val="128"/>
       <scheme val="minor"/>
@@ -15904,7 +15962,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="132">
+  <cellXfs count="133">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -16257,7 +16315,7 @@
       <alignment vertical="center" shrinkToFit="1"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="12" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" shrinkToFit="1"/>
+      <alignment vertical="center" wrapText="1" shrinkToFit="1"/>
     </xf>
     <xf numFmtId="177" fontId="7" fillId="0" borderId="2" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" shrinkToFit="1"/>
@@ -16265,14 +16323,14 @@
     <xf numFmtId="0" fontId="7" fillId="3" borderId="12" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" shrinkToFit="1"/>
     </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="12" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" shrinkToFit="1"/>
+    </xf>
     <xf numFmtId="177" fontId="7" fillId="3" borderId="2" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" shrinkToFit="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="13" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="12" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1" shrinkToFit="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="12" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" shrinkToFit="1"/>
@@ -16285,6 +16343,9 @@
     </xf>
     <xf numFmtId="177" fontId="0" fillId="0" borderId="2" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1" shrinkToFit="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -16304,7 +16365,7 @@
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="標準" xfId="0" builtinId="0"/>
-    <cellStyle name="標準 2" xfId="1" xr:uid="{DAB11290-6572-4745-B6AC-3D17353291DF}"/>
+    <cellStyle name="標準 2" xfId="1" xr:uid="{0C1F6C2C-F3E5-4A5F-BDA4-700D03B90A2C}"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -16320,9 +16381,9 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office テーマ">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme 2007 - 2010">
   <a:themeElements>
-    <a:clrScheme name="Office">
+    <a:clrScheme name="Office 2007 - 2010">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -16330,44 +16391,44 @@
         <a:sysClr val="window" lastClr="FFFFFF"/>
       </a:lt1>
       <a:dk2>
-        <a:srgbClr val="0E2841"/>
+        <a:srgbClr val="1F497D"/>
       </a:dk2>
       <a:lt2>
-        <a:srgbClr val="E8E8E8"/>
+        <a:srgbClr val="EEECE1"/>
       </a:lt2>
       <a:accent1>
-        <a:srgbClr val="156082"/>
+        <a:srgbClr val="4F81BD"/>
       </a:accent1>
       <a:accent2>
-        <a:srgbClr val="E97132"/>
+        <a:srgbClr val="C0504D"/>
       </a:accent2>
       <a:accent3>
-        <a:srgbClr val="196B24"/>
+        <a:srgbClr val="9BBB59"/>
       </a:accent3>
       <a:accent4>
-        <a:srgbClr val="0F9ED5"/>
+        <a:srgbClr val="8064A2"/>
       </a:accent4>
       <a:accent5>
-        <a:srgbClr val="A02B93"/>
+        <a:srgbClr val="4BACC6"/>
       </a:accent5>
       <a:accent6>
-        <a:srgbClr val="4EA72E"/>
+        <a:srgbClr val="F79646"/>
       </a:accent6>
       <a:hlink>
-        <a:srgbClr val="467886"/>
+        <a:srgbClr val="0000FF"/>
       </a:hlink>
       <a:folHlink>
-        <a:srgbClr val="96607D"/>
+        <a:srgbClr val="800080"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office">
+    <a:fontScheme name="Office 2007 - 2010">
       <a:majorFont>
-        <a:latin typeface="Aptos Display" panose="02110004020202020204"/>
+        <a:latin typeface="Cambria"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
-        <a:font script="Jpan" typeface="游ゴシック Light"/>
+        <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
         <a:font script="Hang" typeface="맑은 고딕"/>
-        <a:font script="Hans" typeface="等线 Light"/>
+        <a:font script="Hans" typeface="宋体"/>
         <a:font script="Hant" typeface="新細明體"/>
         <a:font script="Arab" typeface="Times New Roman"/>
         <a:font script="Hebr" typeface="Times New Roman"/>
@@ -16395,31 +16456,14 @@
         <a:font script="Viet" typeface="Times New Roman"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
         <a:font script="Geor" typeface="Sylfaen"/>
-        <a:font script="Armn" typeface="Arial"/>
-        <a:font script="Bugi" typeface="Leelawadee UI"/>
-        <a:font script="Bopo" typeface="Microsoft JhengHei"/>
-        <a:font script="Java" typeface="Javanese Text"/>
-        <a:font script="Lisu" typeface="Segoe UI"/>
-        <a:font script="Mymr" typeface="Myanmar Text"/>
-        <a:font script="Nkoo" typeface="Ebrima"/>
-        <a:font script="Olck" typeface="Nirmala UI"/>
-        <a:font script="Osma" typeface="Ebrima"/>
-        <a:font script="Phag" typeface="Phagspa"/>
-        <a:font script="Syrn" typeface="Estrangelo Edessa"/>
-        <a:font script="Syrj" typeface="Estrangelo Edessa"/>
-        <a:font script="Syre" typeface="Estrangelo Edessa"/>
-        <a:font script="Sora" typeface="Nirmala UI"/>
-        <a:font script="Tale" typeface="Microsoft Tai Le"/>
-        <a:font script="Talu" typeface="Microsoft New Tai Lue"/>
-        <a:font script="Tfng" typeface="Ebrima"/>
       </a:majorFont>
       <a:minorFont>
-        <a:latin typeface="Aptos Narrow" panose="02110004020202020204"/>
+        <a:latin typeface="Calibri"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
-        <a:font script="Jpan" typeface="游ゴシック"/>
+        <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
         <a:font script="Hang" typeface="맑은 고딕"/>
-        <a:font script="Hans" typeface="等线"/>
+        <a:font script="Hans" typeface="宋体"/>
         <a:font script="Hant" typeface="新細明體"/>
         <a:font script="Arab" typeface="Arial"/>
         <a:font script="Hebr" typeface="Arial"/>
@@ -16447,26 +16491,9 @@
         <a:font script="Viet" typeface="Arial"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
         <a:font script="Geor" typeface="Sylfaen"/>
-        <a:font script="Armn" typeface="Arial"/>
-        <a:font script="Bugi" typeface="Leelawadee UI"/>
-        <a:font script="Bopo" typeface="Microsoft JhengHei"/>
-        <a:font script="Java" typeface="Javanese Text"/>
-        <a:font script="Lisu" typeface="Segoe UI"/>
-        <a:font script="Mymr" typeface="Myanmar Text"/>
-        <a:font script="Nkoo" typeface="Ebrima"/>
-        <a:font script="Olck" typeface="Nirmala UI"/>
-        <a:font script="Osma" typeface="Ebrima"/>
-        <a:font script="Phag" typeface="Phagspa"/>
-        <a:font script="Syrn" typeface="Estrangelo Edessa"/>
-        <a:font script="Syrj" typeface="Estrangelo Edessa"/>
-        <a:font script="Syre" typeface="Estrangelo Edessa"/>
-        <a:font script="Sora" typeface="Nirmala UI"/>
-        <a:font script="Tale" typeface="Microsoft Tai Le"/>
-        <a:font script="Talu" typeface="Microsoft New Tai Lue"/>
-        <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office">
+    <a:fmtScheme name="Office 2007 - 2010">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -16475,202 +16502,205 @@
           <a:gsLst>
             <a:gs pos="0">
               <a:schemeClr val="phClr">
-                <a:lumMod val="110000"/>
-                <a:satMod val="105000"/>
-                <a:tint val="67000"/>
+                <a:tint val="50000"/>
+                <a:satMod val="300000"/>
               </a:schemeClr>
             </a:gs>
-            <a:gs pos="50000">
+            <a:gs pos="35000">
               <a:schemeClr val="phClr">
-                <a:lumMod val="105000"/>
-                <a:satMod val="103000"/>
-                <a:tint val="73000"/>
+                <a:tint val="37000"/>
+                <a:satMod val="300000"/>
               </a:schemeClr>
             </a:gs>
             <a:gs pos="100000">
               <a:schemeClr val="phClr">
-                <a:lumMod val="105000"/>
-                <a:satMod val="109000"/>
-                <a:tint val="81000"/>
+                <a:tint val="15000"/>
+                <a:satMod val="350000"/>
               </a:schemeClr>
             </a:gs>
           </a:gsLst>
-          <a:lin ang="5400000" scaled="0"/>
+          <a:lin ang="16200000" scaled="1"/>
         </a:gradFill>
         <a:gradFill rotWithShape="1">
           <a:gsLst>
             <a:gs pos="0">
               <a:schemeClr val="phClr">
-                <a:satMod val="103000"/>
-                <a:lumMod val="102000"/>
-                <a:tint val="94000"/>
+                <a:shade val="51000"/>
+                <a:satMod val="130000"/>
               </a:schemeClr>
             </a:gs>
-            <a:gs pos="50000">
+            <a:gs pos="80000">
               <a:schemeClr val="phClr">
-                <a:satMod val="110000"/>
-                <a:lumMod val="100000"/>
-                <a:shade val="100000"/>
+                <a:shade val="93000"/>
+                <a:satMod val="130000"/>
               </a:schemeClr>
             </a:gs>
             <a:gs pos="100000">
               <a:schemeClr val="phClr">
-                <a:lumMod val="99000"/>
-                <a:satMod val="120000"/>
-                <a:shade val="78000"/>
+                <a:shade val="94000"/>
+                <a:satMod val="135000"/>
               </a:schemeClr>
             </a:gs>
           </a:gsLst>
-          <a:lin ang="5400000" scaled="0"/>
+          <a:lin ang="16200000" scaled="0"/>
         </a:gradFill>
       </a:fillStyleLst>
       <a:lnStyleLst>
-        <a:ln w="12700" cap="flat" cmpd="sng" algn="ctr">
+        <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
           <a:solidFill>
-            <a:schemeClr val="phClr"/>
+            <a:schemeClr val="phClr">
+              <a:shade val="95000"/>
+              <a:satMod val="105000"/>
+            </a:schemeClr>
           </a:solidFill>
           <a:prstDash val="solid"/>
-          <a:miter lim="800000"/>
-        </a:ln>
-        <a:ln w="19050" cap="flat" cmpd="sng" algn="ctr">
-          <a:solidFill>
-            <a:schemeClr val="phClr"/>
-          </a:solidFill>
-          <a:prstDash val="solid"/>
-          <a:miter lim="800000"/>
         </a:ln>
         <a:ln w="25400" cap="flat" cmpd="sng" algn="ctr">
           <a:solidFill>
             <a:schemeClr val="phClr"/>
           </a:solidFill>
           <a:prstDash val="solid"/>
-          <a:miter lim="800000"/>
+        </a:ln>
+        <a:ln w="38100" cap="flat" cmpd="sng" algn="ctr">
+          <a:solidFill>
+            <a:schemeClr val="phClr"/>
+          </a:solidFill>
+          <a:prstDash val="solid"/>
         </a:ln>
       </a:lnStyleLst>
       <a:effectStyleLst>
         <a:effectStyle>
-          <a:effectLst/>
-        </a:effectStyle>
-        <a:effectStyle>
-          <a:effectLst/>
+          <a:effectLst>
+            <a:outerShdw blurRad="40000" dist="20000" dir="5400000" rotWithShape="0">
+              <a:srgbClr val="000000">
+                <a:alpha val="38000"/>
+              </a:srgbClr>
+            </a:outerShdw>
+          </a:effectLst>
         </a:effectStyle>
         <a:effectStyle>
           <a:effectLst>
-            <a:outerShdw blurRad="57150" dist="19050" dir="5400000" algn="ctr" rotWithShape="0">
+            <a:outerShdw blurRad="40000" dist="23000" dir="5400000" rotWithShape="0">
               <a:srgbClr val="000000">
-                <a:alpha val="63000"/>
+                <a:alpha val="35000"/>
               </a:srgbClr>
             </a:outerShdw>
           </a:effectLst>
+        </a:effectStyle>
+        <a:effectStyle>
+          <a:effectLst>
+            <a:outerShdw blurRad="40000" dist="23000" dir="5400000" rotWithShape="0">
+              <a:srgbClr val="000000">
+                <a:alpha val="35000"/>
+              </a:srgbClr>
+            </a:outerShdw>
+          </a:effectLst>
+          <a:scene3d>
+            <a:camera prst="orthographicFront">
+              <a:rot lat="0" lon="0" rev="0"/>
+            </a:camera>
+            <a:lightRig rig="threePt" dir="t">
+              <a:rot lat="0" lon="0" rev="1200000"/>
+            </a:lightRig>
+          </a:scene3d>
+          <a:sp3d>
+            <a:bevelT w="63500" h="25400"/>
+          </a:sp3d>
         </a:effectStyle>
       </a:effectStyleLst>
       <a:bgFillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
         </a:solidFill>
-        <a:solidFill>
-          <a:schemeClr val="phClr">
-            <a:tint val="95000"/>
-            <a:satMod val="170000"/>
-          </a:schemeClr>
-        </a:solidFill>
         <a:gradFill rotWithShape="1">
           <a:gsLst>
             <a:gs pos="0">
               <a:schemeClr val="phClr">
-                <a:tint val="93000"/>
-                <a:satMod val="150000"/>
-                <a:shade val="98000"/>
-                <a:lumMod val="102000"/>
+                <a:tint val="40000"/>
+                <a:satMod val="350000"/>
               </a:schemeClr>
             </a:gs>
-            <a:gs pos="50000">
+            <a:gs pos="40000">
               <a:schemeClr val="phClr">
-                <a:tint val="98000"/>
-                <a:satMod val="130000"/>
-                <a:shade val="90000"/>
-                <a:lumMod val="103000"/>
+                <a:tint val="45000"/>
+                <a:shade val="99000"/>
+                <a:satMod val="350000"/>
               </a:schemeClr>
             </a:gs>
             <a:gs pos="100000">
               <a:schemeClr val="phClr">
-                <a:shade val="63000"/>
-                <a:satMod val="120000"/>
+                <a:shade val="20000"/>
+                <a:satMod val="255000"/>
               </a:schemeClr>
             </a:gs>
           </a:gsLst>
-          <a:lin ang="5400000" scaled="0"/>
+          <a:path path="circle">
+            <a:fillToRect l="50000" t="-80000" r="50000" b="180000"/>
+          </a:path>
+        </a:gradFill>
+        <a:gradFill rotWithShape="1">
+          <a:gsLst>
+            <a:gs pos="0">
+              <a:schemeClr val="phClr">
+                <a:tint val="80000"/>
+                <a:satMod val="300000"/>
+              </a:schemeClr>
+            </a:gs>
+            <a:gs pos="100000">
+              <a:schemeClr val="phClr">
+                <a:shade val="30000"/>
+                <a:satMod val="200000"/>
+              </a:schemeClr>
+            </a:gs>
+          </a:gsLst>
+          <a:path path="circle">
+            <a:fillToRect l="50000" t="50000" r="50000" b="50000"/>
+          </a:path>
         </a:gradFill>
       </a:bgFillStyleLst>
     </a:fmtScheme>
   </a:themeElements>
-  <a:objectDefaults>
-    <a:lnDef>
-      <a:spPr/>
-      <a:bodyPr/>
-      <a:lstStyle/>
-      <a:style>
-        <a:lnRef idx="2">
-          <a:schemeClr val="accent1"/>
-        </a:lnRef>
-        <a:fillRef idx="0">
-          <a:schemeClr val="accent1"/>
-        </a:fillRef>
-        <a:effectRef idx="1">
-          <a:schemeClr val="accent1"/>
-        </a:effectRef>
-        <a:fontRef idx="minor">
-          <a:schemeClr val="tx1"/>
-        </a:fontRef>
-      </a:style>
-    </a:lnDef>
-  </a:objectDefaults>
+  <a:objectDefaults/>
   <a:extraClrSchemeLst/>
-  <a:extLst>
-    <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{2E142A2C-CD16-42D6-873A-C26D2A0506FA}" vid="{1BDDFF52-6CD6-40A5-AB3C-68EB2F1E4D0A}"/>
-    </a:ext>
-  </a:extLst>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{86A80E35-BEA8-4B9F-AE1F-901CB97084DE}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{40895ADD-4DE4-47E7-A06E-ECDFF938A347}">
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:AK142"/>
-  <sheetFormatPr defaultRowHeight="18" outlineLevelCol="1" x14ac:dyDescent="0.55000000000000004"/>
+  <sheetFormatPr defaultRowHeight="13.5" outlineLevelCol="1" x14ac:dyDescent="0.15"/>
   <cols>
-    <col min="2" max="2" width="18.08203125" customWidth="1" outlineLevel="1"/>
-    <col min="3" max="3" width="8.25" style="127" customWidth="1" outlineLevel="1"/>
-    <col min="4" max="4" width="9.25" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="8.25" hidden="1" customWidth="1" outlineLevel="1"/>
-    <col min="6" max="6" width="11" hidden="1" customWidth="1" outlineLevel="1"/>
-    <col min="7" max="7" width="8.25" hidden="1" customWidth="1" outlineLevel="1"/>
-    <col min="8" max="8" width="26.6640625" style="128" customWidth="1" collapsed="1"/>
-    <col min="9" max="9" width="5.75" customWidth="1"/>
-    <col min="10" max="10" width="6.75" customWidth="1"/>
-    <col min="11" max="11" width="32.4140625" customWidth="1"/>
-    <col min="12" max="12" width="8.25" customWidth="1"/>
-    <col min="13" max="13" width="24.6640625" style="130" customWidth="1" outlineLevel="1"/>
-    <col min="14" max="14" width="8.25" customWidth="1" outlineLevel="1"/>
-    <col min="15" max="15" width="32.4140625" customWidth="1" outlineLevel="1"/>
-    <col min="16" max="16" width="12.5" customWidth="1" outlineLevel="1"/>
-    <col min="17" max="17" width="12.75" customWidth="1" outlineLevel="1"/>
-    <col min="18" max="18" width="16.5" style="131" customWidth="1" outlineLevel="1"/>
-    <col min="19" max="19" width="16.5" style="131" customWidth="1"/>
-    <col min="20" max="20" width="16.5" customWidth="1" outlineLevel="1"/>
-    <col min="21" max="21" width="18.75" customWidth="1" outlineLevel="1"/>
-    <col min="22" max="22" width="16.5" customWidth="1" outlineLevel="1"/>
-    <col min="23" max="23" width="18.75" customWidth="1" outlineLevel="1"/>
-    <col min="24" max="24" width="18.75" customWidth="1"/>
-    <col min="25" max="28" width="8.25" customWidth="1" outlineLevel="1"/>
-    <col min="29" max="36" width="24.83203125" customWidth="1" outlineLevel="1"/>
-    <col min="37" max="37" width="24.83203125" customWidth="1"/>
+    <col min="2" max="2" width="19.75" customWidth="1" outlineLevel="1"/>
+    <col min="3" max="3" width="9" style="128" customWidth="1" outlineLevel="1"/>
+    <col min="4" max="4" width="10.125" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="9" hidden="1" customWidth="1" outlineLevel="1"/>
+    <col min="6" max="6" width="12" hidden="1" customWidth="1" outlineLevel="1"/>
+    <col min="7" max="7" width="9" hidden="1" customWidth="1" outlineLevel="1"/>
+    <col min="8" max="8" width="29.125" style="129" customWidth="1" collapsed="1"/>
+    <col min="9" max="9" width="6.25" customWidth="1"/>
+    <col min="10" max="10" width="7.375" customWidth="1"/>
+    <col min="11" max="11" width="35.375" customWidth="1"/>
+    <col min="12" max="12" width="9" customWidth="1"/>
+    <col min="13" max="13" width="26.875" style="131" customWidth="1" outlineLevel="1"/>
+    <col min="14" max="14" width="9" customWidth="1" outlineLevel="1"/>
+    <col min="15" max="15" width="35.375" customWidth="1" outlineLevel="1"/>
+    <col min="16" max="16" width="13.625" customWidth="1" outlineLevel="1"/>
+    <col min="17" max="17" width="13.875" customWidth="1" outlineLevel="1"/>
+    <col min="18" max="18" width="18" style="132" customWidth="1" outlineLevel="1"/>
+    <col min="19" max="19" width="18" style="132" customWidth="1"/>
+    <col min="20" max="20" width="18" customWidth="1" outlineLevel="1"/>
+    <col min="21" max="21" width="20.5" customWidth="1" outlineLevel="1"/>
+    <col min="22" max="22" width="18" customWidth="1" outlineLevel="1"/>
+    <col min="23" max="23" width="20.5" customWidth="1" outlineLevel="1"/>
+    <col min="24" max="24" width="20.5" customWidth="1"/>
+    <col min="25" max="28" width="9" customWidth="1" outlineLevel="1"/>
+    <col min="29" max="37" width="27.125" customWidth="1" outlineLevel="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:37" ht="52" x14ac:dyDescent="0.55000000000000004">
+    <row r="1" spans="1:37" ht="54" x14ac:dyDescent="0.15">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -16717,7 +16747,7 @@
       <c r="AH1" s="14"/>
       <c r="AI1" s="14"/>
     </row>
-    <row r="2" spans="1:37" ht="13.5" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="2" spans="1:37" ht="13.5" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A2" s="15" t="s">
         <v>5</v>
       </c>
@@ -16808,7 +16838,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="3" spans="1:37" ht="42" customHeight="1" thickBot="1" x14ac:dyDescent="0.6">
+    <row r="3" spans="1:37" ht="42" customHeight="1" thickBot="1" x14ac:dyDescent="0.2">
       <c r="A3" s="29"/>
       <c r="B3" s="30"/>
       <c r="C3" s="30"/>
@@ -16873,7 +16903,7 @@
       <c r="AJ3" s="30"/>
       <c r="AK3" s="30"/>
     </row>
-    <row r="4" spans="1:37" ht="41.25" customHeight="1" thickTop="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="4" spans="1:37" ht="41.25" customHeight="1" thickTop="1" x14ac:dyDescent="0.15">
       <c r="A4" s="44" t="s">
         <v>41</v>
       </c>
@@ -16969,7 +16999,7 @@
       <c r="AJ4" s="61"/>
       <c r="AK4" s="61"/>
     </row>
-    <row r="5" spans="1:37" ht="27" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="5" spans="1:37" ht="27" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A5" s="62" t="s">
         <v>57</v>
       </c>
@@ -17057,7 +17087,7 @@
       <c r="AJ5" s="71"/>
       <c r="AK5" s="71"/>
     </row>
-    <row r="6" spans="1:37" ht="40.5" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="6" spans="1:37" ht="40.5" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A6" s="62" t="s">
         <v>67</v>
       </c>
@@ -17149,7 +17179,7 @@
       <c r="AJ6" s="71"/>
       <c r="AK6" s="71"/>
     </row>
-    <row r="7" spans="1:37" ht="27" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="7" spans="1:37" ht="27" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A7" s="62" t="s">
         <v>78</v>
       </c>
@@ -17237,7 +17267,7 @@
       <c r="AJ7" s="71"/>
       <c r="AK7" s="71"/>
     </row>
-    <row r="8" spans="1:37" ht="27" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="8" spans="1:37" ht="27" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A8" s="62" t="s">
         <v>87</v>
       </c>
@@ -17327,7 +17357,7 @@
       <c r="AJ8" s="71"/>
       <c r="AK8" s="71"/>
     </row>
-    <row r="9" spans="1:37" ht="67.5" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="9" spans="1:37" ht="67.5" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A9" s="62" t="s">
         <v>96</v>
       </c>
@@ -17427,7 +17457,7 @@
       <c r="AJ9" s="71"/>
       <c r="AK9" s="71"/>
     </row>
-    <row r="10" spans="1:37" ht="40.5" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="10" spans="1:37" ht="40.5" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A10" s="62" t="s">
         <v>111</v>
       </c>
@@ -17521,7 +17551,7 @@
       <c r="AJ10" s="71"/>
       <c r="AK10" s="71"/>
     </row>
-    <row r="11" spans="1:37" ht="27" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="11" spans="1:37" ht="27" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A11" s="62" t="s">
         <v>123</v>
       </c>
@@ -17611,7 +17641,7 @@
       <c r="AJ11" s="71"/>
       <c r="AK11" s="71"/>
     </row>
-    <row r="12" spans="1:37" ht="67.5" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="12" spans="1:37" ht="67.5" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A12" s="62" t="s">
         <v>132</v>
       </c>
@@ -17711,7 +17741,7 @@
       <c r="AJ12" s="71"/>
       <c r="AK12" s="71"/>
     </row>
-    <row r="13" spans="1:37" ht="48" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="13" spans="1:37" ht="48" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A13" s="62" t="s">
         <v>142</v>
       </c>
@@ -17803,7 +17833,7 @@
       <c r="AJ13" s="71"/>
       <c r="AK13" s="71"/>
     </row>
-    <row r="14" spans="1:37" ht="40.5" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="14" spans="1:37" ht="40.5" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A14" s="62" t="s">
         <v>154</v>
       </c>
@@ -17895,7 +17925,7 @@
       <c r="AJ14" s="71"/>
       <c r="AK14" s="71"/>
     </row>
-    <row r="15" spans="1:37" ht="27" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="15" spans="1:37" ht="27" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A15" s="62" t="s">
         <v>161</v>
       </c>
@@ -17991,7 +18021,7 @@
       <c r="AJ15" s="71"/>
       <c r="AK15" s="71"/>
     </row>
-    <row r="16" spans="1:37" ht="117" x14ac:dyDescent="0.55000000000000004">
+    <row r="16" spans="1:37" ht="121.5" x14ac:dyDescent="0.15">
       <c r="A16" s="62" t="s">
         <v>173</v>
       </c>
@@ -18031,7 +18061,7 @@
         <v>177</v>
       </c>
       <c r="N16" s="73" t="s">
-        <v>80</v>
+        <v>113</v>
       </c>
       <c r="O16" s="73" t="s">
         <v>178</v>
@@ -18089,7 +18119,7 @@
       <c r="AJ16" s="71"/>
       <c r="AK16" s="71"/>
     </row>
-    <row r="17" spans="1:37" ht="27" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="17" spans="1:37" ht="27" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A17" s="62" t="s">
         <v>185</v>
       </c>
@@ -18179,7 +18209,7 @@
       <c r="AJ17" s="71"/>
       <c r="AK17" s="71"/>
     </row>
-    <row r="18" spans="1:37" ht="94.5" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="18" spans="1:37" ht="94.5" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A18" s="62" t="s">
         <v>193</v>
       </c>
@@ -18285,7 +18315,7 @@
       </c>
       <c r="AK18" s="13"/>
     </row>
-    <row r="19" spans="1:37" ht="40.5" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="19" spans="1:37" ht="40.5" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A19" s="62" t="s">
         <v>210</v>
       </c>
@@ -18377,7 +18407,7 @@
       <c r="AJ19" s="71"/>
       <c r="AK19" s="71"/>
     </row>
-    <row r="20" spans="1:37" ht="51.75" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="20" spans="1:37" ht="51.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A20" s="62" t="s">
         <v>218</v>
       </c>
@@ -18469,7 +18499,7 @@
       <c r="AJ20" s="71"/>
       <c r="AK20" s="71"/>
     </row>
-    <row r="21" spans="1:37" ht="32.25" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="21" spans="1:37" ht="32.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A21" s="62" t="s">
         <v>228</v>
       </c>
@@ -18561,7 +18591,7 @@
       <c r="AJ21" s="71"/>
       <c r="AK21" s="71"/>
     </row>
-    <row r="22" spans="1:37" ht="54" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="22" spans="1:37" ht="54" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A22" s="62" t="s">
         <v>238</v>
       </c>
@@ -18659,7 +18689,7 @@
       <c r="AJ22" s="71"/>
       <c r="AK22" s="71"/>
     </row>
-    <row r="23" spans="1:37" ht="27" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="23" spans="1:37" ht="27" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A23" s="62" t="s">
         <v>248</v>
       </c>
@@ -18747,14 +18777,14 @@
       <c r="AJ23" s="71"/>
       <c r="AK23" s="71"/>
     </row>
-    <row r="24" spans="1:37" ht="104" x14ac:dyDescent="0.55000000000000004">
+    <row r="24" spans="1:37" ht="108" x14ac:dyDescent="0.15">
       <c r="A24" s="62" t="s">
         <v>256</v>
       </c>
       <c r="B24" s="13"/>
       <c r="C24" s="77"/>
       <c r="D24" s="65">
-        <v>2955870</v>
+        <v>2956399</v>
       </c>
       <c r="E24" s="48">
         <f t="shared" si="0"/>
@@ -18762,7 +18792,7 @@
       </c>
       <c r="F24" s="49" t="str">
         <f t="shared" si="1"/>
-        <v>1342955870</v>
+        <v>1342956399</v>
       </c>
       <c r="G24" s="50" t="str">
         <f t="shared" si="2"/>
@@ -18845,7 +18875,7 @@
       <c r="AJ24" s="71"/>
       <c r="AK24" s="71"/>
     </row>
-    <row r="25" spans="1:37" ht="27" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="25" spans="1:37" ht="27" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A25" s="62" t="s">
         <v>270</v>
       </c>
@@ -18937,7 +18967,7 @@
       <c r="AJ25" s="71"/>
       <c r="AK25" s="71"/>
     </row>
-    <row r="26" spans="1:37" ht="54" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="26" spans="1:37" ht="54" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A26" s="62" t="s">
         <v>281</v>
       </c>
@@ -19037,7 +19067,7 @@
       <c r="AJ26" s="71"/>
       <c r="AK26" s="71"/>
     </row>
-    <row r="27" spans="1:37" ht="40.5" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="27" spans="1:37" ht="40.5" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A27" s="62" t="s">
         <v>294</v>
       </c>
@@ -19131,7 +19161,7 @@
       <c r="AJ27" s="71"/>
       <c r="AK27" s="71"/>
     </row>
-    <row r="28" spans="1:37" ht="81" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="28" spans="1:37" ht="81" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A28" s="62" t="s">
         <v>306</v>
       </c>
@@ -19227,7 +19257,7 @@
       <c r="AJ28" s="71"/>
       <c r="AK28" s="71"/>
     </row>
-    <row r="29" spans="1:37" ht="40.5" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="29" spans="1:37" ht="40.5" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A29" s="62" t="s">
         <v>319</v>
       </c>
@@ -19319,7 +19349,7 @@
       <c r="AJ29" s="71"/>
       <c r="AK29" s="71"/>
     </row>
-    <row r="30" spans="1:37" ht="54" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="30" spans="1:37" ht="54" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A30" s="62" t="s">
         <v>327</v>
       </c>
@@ -19411,7 +19441,7 @@
       <c r="AJ30" s="71"/>
       <c r="AK30" s="71"/>
     </row>
-    <row r="31" spans="1:37" ht="27" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="31" spans="1:37" ht="27" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A31" s="62" t="s">
         <v>337</v>
       </c>
@@ -19501,7 +19531,7 @@
       <c r="AJ31" s="71"/>
       <c r="AK31" s="71"/>
     </row>
-    <row r="32" spans="1:37" ht="27" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="32" spans="1:37" ht="27" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A32" s="62" t="s">
         <v>344</v>
       </c>
@@ -19591,7 +19621,7 @@
       <c r="AJ32" s="71"/>
       <c r="AK32" s="71"/>
     </row>
-    <row r="33" spans="1:37" ht="27" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="33" spans="1:37" ht="27" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A33" s="62" t="s">
         <v>355</v>
       </c>
@@ -19683,7 +19713,7 @@
       <c r="AJ33" s="71"/>
       <c r="AK33" s="71"/>
     </row>
-    <row r="34" spans="1:37" ht="54" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="34" spans="1:37" ht="54" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A34" s="62" t="s">
         <v>364</v>
       </c>
@@ -19775,7 +19805,7 @@
       <c r="AJ34" s="71"/>
       <c r="AK34" s="71"/>
     </row>
-    <row r="35" spans="1:37" ht="65" x14ac:dyDescent="0.55000000000000004">
+    <row r="35" spans="1:37" ht="67.5" x14ac:dyDescent="0.15">
       <c r="A35" s="62" t="s">
         <v>372</v>
       </c>
@@ -19871,7 +19901,7 @@
       <c r="AJ35" s="71"/>
       <c r="AK35" s="71"/>
     </row>
-    <row r="36" spans="1:37" ht="54" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="36" spans="1:37" ht="54" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A36" s="62" t="s">
         <v>385</v>
       </c>
@@ -19963,7 +19993,7 @@
       <c r="AJ36" s="71"/>
       <c r="AK36" s="71"/>
     </row>
-    <row r="37" spans="1:37" ht="40.5" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="37" spans="1:37" ht="40.5" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A37" s="62" t="s">
         <v>395</v>
       </c>
@@ -20055,7 +20085,7 @@
       <c r="AJ37" s="71"/>
       <c r="AK37" s="71"/>
     </row>
-    <row r="38" spans="1:37" ht="81" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="38" spans="1:37" ht="81" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A38" s="62" t="s">
         <v>402</v>
       </c>
@@ -20151,7 +20181,7 @@
       <c r="AJ38" s="71"/>
       <c r="AK38" s="71"/>
     </row>
-    <row r="39" spans="1:37" ht="54" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="39" spans="1:37" ht="54" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A39" s="62" t="s">
         <v>413</v>
       </c>
@@ -20243,7 +20273,7 @@
       <c r="AJ39" s="71"/>
       <c r="AK39" s="71"/>
     </row>
-    <row r="40" spans="1:37" ht="27" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="40" spans="1:37" ht="27" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A40" s="62" t="s">
         <v>419</v>
       </c>
@@ -20333,7 +20363,7 @@
       <c r="AJ40" s="71"/>
       <c r="AK40" s="71"/>
     </row>
-    <row r="41" spans="1:37" ht="40.5" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="41" spans="1:37" ht="40.5" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A41" s="62" t="s">
         <v>428</v>
       </c>
@@ -20425,7 +20455,7 @@
       <c r="AJ41" s="71"/>
       <c r="AK41" s="71"/>
     </row>
-    <row r="42" spans="1:37" ht="54" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="42" spans="1:37" ht="54" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A42" s="62" t="s">
         <v>437</v>
       </c>
@@ -20525,7 +20555,7 @@
       <c r="AJ42" s="71"/>
       <c r="AK42" s="71"/>
     </row>
-    <row r="43" spans="1:37" ht="40.5" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="43" spans="1:37" ht="40.5" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A43" s="62" t="s">
         <v>449</v>
       </c>
@@ -20619,7 +20649,7 @@
       <c r="AJ43" s="71"/>
       <c r="AK43" s="71"/>
     </row>
-    <row r="44" spans="1:37" ht="54" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="44" spans="1:37" ht="54" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A44" s="62" t="s">
         <v>461</v>
       </c>
@@ -20717,7 +20747,7 @@
       <c r="AJ44" s="71"/>
       <c r="AK44" s="71"/>
     </row>
-    <row r="45" spans="1:37" ht="54" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="45" spans="1:37" ht="54" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A45" s="62" t="s">
         <v>473</v>
       </c>
@@ -20809,7 +20839,7 @@
       <c r="AJ45" s="71"/>
       <c r="AK45" s="71"/>
     </row>
-    <row r="46" spans="1:37" ht="122.25" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="46" spans="1:37" ht="122.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A46" s="62" t="s">
         <v>483</v>
       </c>
@@ -20909,7 +20939,7 @@
       <c r="AJ46" s="71"/>
       <c r="AK46" s="71"/>
     </row>
-    <row r="47" spans="1:37" ht="51" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="47" spans="1:37" ht="51" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A47" s="62" t="s">
         <v>498</v>
       </c>
@@ -21003,7 +21033,7 @@
       <c r="AJ47" s="71"/>
       <c r="AK47" s="71"/>
     </row>
-    <row r="48" spans="1:37" ht="54" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="48" spans="1:37" ht="54" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A48" s="62" t="s">
         <v>509</v>
       </c>
@@ -21095,7 +21125,7 @@
       <c r="AJ48" s="71"/>
       <c r="AK48" s="71"/>
     </row>
-    <row r="49" spans="1:37" ht="81" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="49" spans="1:37" ht="81" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A49" s="62" t="s">
         <v>517</v>
       </c>
@@ -21197,7 +21227,7 @@
       <c r="AJ49" s="71"/>
       <c r="AK49" s="71"/>
     </row>
-    <row r="50" spans="1:37" ht="54" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="50" spans="1:37" ht="54" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A50" s="62" t="s">
         <v>531</v>
       </c>
@@ -21291,7 +21321,7 @@
       <c r="AJ50" s="71"/>
       <c r="AK50" s="71"/>
     </row>
-    <row r="51" spans="1:37" ht="54" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="51" spans="1:37" ht="54" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A51" s="62" t="s">
         <v>541</v>
       </c>
@@ -21385,7 +21415,7 @@
       <c r="AJ51" s="71"/>
       <c r="AK51" s="71"/>
     </row>
-    <row r="52" spans="1:37" ht="54" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="52" spans="1:37" ht="54" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A52" s="62" t="s">
         <v>552</v>
       </c>
@@ -21477,12 +21507,14 @@
       <c r="AJ52" s="71"/>
       <c r="AK52" s="71"/>
     </row>
-    <row r="53" spans="1:37" ht="54" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="53" spans="1:37" ht="54" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A53" s="62" t="s">
         <v>563</v>
       </c>
-      <c r="B53" s="13"/>
-      <c r="C53" s="64"/>
+      <c r="B53" s="13" t="s">
+        <v>564</v>
+      </c>
+      <c r="C53" s="77"/>
       <c r="D53" s="65">
         <v>2954055</v>
       </c>
@@ -21499,7 +21531,7 @@
         <v>　</v>
       </c>
       <c r="H53" s="72" t="s">
-        <v>564</v>
+        <v>565</v>
       </c>
       <c r="I53" s="13" t="s">
         <v>230</v>
@@ -21508,25 +21540,25 @@
         <v>44</v>
       </c>
       <c r="K53" s="13" t="s">
-        <v>565</v>
+        <v>566</v>
       </c>
       <c r="L53" s="13" t="s">
-        <v>566</v>
+        <v>567</v>
       </c>
       <c r="M53" s="13" t="s">
-        <v>567</v>
+        <v>568</v>
       </c>
       <c r="N53" s="73" t="s">
         <v>230</v>
       </c>
       <c r="O53" s="73" t="s">
-        <v>568</v>
+        <v>569</v>
       </c>
       <c r="P53" s="13" t="s">
-        <v>569</v>
+        <v>570</v>
       </c>
       <c r="Q53" s="66" t="s">
-        <v>570</v>
+        <v>571</v>
       </c>
       <c r="R53" s="68">
         <v>39036</v>
@@ -21544,7 +21576,7 @@
         <v>45658</v>
       </c>
       <c r="W53" s="64" t="s">
-        <v>571</v>
+        <v>572</v>
       </c>
       <c r="X53" s="70" t="s">
         <v>54</v>
@@ -21560,9 +21592,11 @@
       </c>
       <c r="AB53" s="63"/>
       <c r="AC53" s="13" t="s">
-        <v>572</v>
-      </c>
-      <c r="AD53" s="13"/>
+        <v>573</v>
+      </c>
+      <c r="AD53" s="13" t="s">
+        <v>574</v>
+      </c>
       <c r="AE53" s="13"/>
       <c r="AF53" s="63"/>
       <c r="AG53" s="63"/>
@@ -21571,9 +21605,9 @@
       <c r="AJ53" s="71"/>
       <c r="AK53" s="71"/>
     </row>
-    <row r="54" spans="1:37" ht="67.5" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="54" spans="1:37" ht="67.5" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A54" s="62" t="s">
-        <v>573</v>
+        <v>575</v>
       </c>
       <c r="B54" s="13"/>
       <c r="C54" s="64" t="s">
@@ -21595,7 +21629,7 @@
         <v>　</v>
       </c>
       <c r="H54" s="13" t="s">
-        <v>574</v>
+        <v>576</v>
       </c>
       <c r="I54" s="13" t="s">
         <v>80</v>
@@ -21604,25 +21638,25 @@
         <v>44</v>
       </c>
       <c r="K54" s="13" t="s">
-        <v>575</v>
+        <v>577</v>
       </c>
       <c r="L54" s="13" t="s">
-        <v>576</v>
+        <v>578</v>
       </c>
       <c r="M54" s="13" t="s">
-        <v>577</v>
+        <v>579</v>
       </c>
       <c r="N54" s="67" t="s">
-        <v>578</v>
+        <v>580</v>
       </c>
       <c r="O54" s="67" t="s">
-        <v>579</v>
+        <v>581</v>
       </c>
       <c r="P54" s="13" t="s">
-        <v>580</v>
+        <v>582</v>
       </c>
       <c r="Q54" s="13" t="s">
-        <v>581</v>
+        <v>583</v>
       </c>
       <c r="R54" s="68">
         <v>39108</v>
@@ -21640,7 +21674,7 @@
         <v>41306</v>
       </c>
       <c r="W54" s="64" t="s">
-        <v>582</v>
+        <v>584</v>
       </c>
       <c r="X54" s="70" t="s">
         <v>54</v>
@@ -21658,10 +21692,10 @@
         <v>43001</v>
       </c>
       <c r="AC54" s="13" t="s">
-        <v>583</v>
+        <v>585</v>
       </c>
       <c r="AD54" s="13" t="s">
-        <v>584</v>
+        <v>586</v>
       </c>
       <c r="AE54" s="13"/>
       <c r="AF54" s="63"/>
@@ -21671,9 +21705,9 @@
       <c r="AJ54" s="71"/>
       <c r="AK54" s="71"/>
     </row>
-    <row r="55" spans="1:37" ht="27" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="55" spans="1:37" ht="27" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A55" s="62" t="s">
-        <v>585</v>
+        <v>587</v>
       </c>
       <c r="B55" s="13"/>
       <c r="C55" s="64"/>
@@ -21693,19 +21727,19 @@
         <v>　</v>
       </c>
       <c r="H55" s="72" t="s">
-        <v>586</v>
+        <v>588</v>
       </c>
       <c r="I55" s="13" t="s">
-        <v>587</v>
+        <v>589</v>
       </c>
       <c r="J55" s="66" t="s">
         <v>44</v>
       </c>
       <c r="K55" s="13" t="s">
-        <v>588</v>
+        <v>590</v>
       </c>
       <c r="L55" s="13" t="s">
-        <v>589</v>
+        <v>591</v>
       </c>
       <c r="M55" s="13" t="s">
         <v>147</v>
@@ -21714,13 +21748,13 @@
         <v>113</v>
       </c>
       <c r="O55" s="73" t="s">
-        <v>590</v>
+        <v>592</v>
       </c>
       <c r="P55" s="13" t="s">
-        <v>591</v>
+        <v>593</v>
       </c>
       <c r="Q55" s="66" t="s">
-        <v>592</v>
+        <v>594</v>
       </c>
       <c r="R55" s="68"/>
       <c r="S55" s="69">
@@ -21730,13 +21764,13 @@
         <v>38899</v>
       </c>
       <c r="U55" s="64" t="s">
-        <v>593</v>
+        <v>595</v>
       </c>
       <c r="V55" s="69">
         <v>45474</v>
       </c>
       <c r="W55" s="64" t="s">
-        <v>594</v>
+        <v>596</v>
       </c>
       <c r="X55" s="70" t="s">
         <v>54</v>
@@ -21752,7 +21786,7 @@
       </c>
       <c r="AB55" s="63"/>
       <c r="AC55" s="13" t="s">
-        <v>595</v>
+        <v>597</v>
       </c>
       <c r="AD55" s="13"/>
       <c r="AE55" s="13"/>
@@ -21763,9 +21797,9 @@
       <c r="AJ55" s="71"/>
       <c r="AK55" s="71"/>
     </row>
-    <row r="56" spans="1:37" ht="40.5" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="56" spans="1:37" ht="40.5" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A56" s="62" t="s">
-        <v>596</v>
+        <v>598</v>
       </c>
       <c r="B56" s="63"/>
       <c r="C56" s="64"/>
@@ -21785,34 +21819,34 @@
         <v>　</v>
       </c>
       <c r="H56" s="72" t="s">
-        <v>597</v>
+        <v>599</v>
       </c>
       <c r="I56" s="82" t="s">
-        <v>598</v>
+        <v>600</v>
       </c>
       <c r="J56" s="66" t="s">
         <v>44</v>
       </c>
       <c r="K56" s="13" t="s">
-        <v>599</v>
+        <v>601</v>
       </c>
       <c r="L56" s="13" t="s">
-        <v>600</v>
+        <v>602</v>
       </c>
       <c r="M56" s="13" t="s">
-        <v>601</v>
+        <v>603</v>
       </c>
       <c r="N56" s="73" t="s">
-        <v>602</v>
+        <v>604</v>
       </c>
       <c r="O56" s="73" t="s">
-        <v>603</v>
+        <v>605</v>
       </c>
       <c r="P56" s="13" t="s">
-        <v>604</v>
+        <v>606</v>
       </c>
       <c r="Q56" s="66" t="s">
-        <v>605</v>
+        <v>607</v>
       </c>
       <c r="R56" s="68">
         <v>40148</v>
@@ -21824,13 +21858,13 @@
         <v>40210</v>
       </c>
       <c r="U56" s="64" t="s">
-        <v>606</v>
+        <v>608</v>
       </c>
       <c r="V56" s="69">
         <v>44593</v>
       </c>
       <c r="W56" s="64" t="s">
-        <v>607</v>
+        <v>609</v>
       </c>
       <c r="X56" s="77" t="s">
         <v>54</v>
@@ -21846,13 +21880,13 @@
       </c>
       <c r="AB56" s="63"/>
       <c r="AC56" s="13" t="s">
-        <v>608</v>
+        <v>610</v>
       </c>
       <c r="AD56" s="13" t="s">
-        <v>609</v>
+        <v>611</v>
       </c>
       <c r="AE56" s="13" t="s">
-        <v>610</v>
+        <v>612</v>
       </c>
       <c r="AF56" s="63"/>
       <c r="AG56" s="63"/>
@@ -21861,9 +21895,9 @@
       <c r="AJ56" s="71"/>
       <c r="AK56" s="71"/>
     </row>
-    <row r="57" spans="1:37" ht="67.5" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="57" spans="1:37" ht="67.5" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A57" s="62" t="s">
-        <v>611</v>
+        <v>613</v>
       </c>
       <c r="B57" s="13"/>
       <c r="C57" s="64"/>
@@ -21883,7 +21917,7 @@
         <v>　</v>
       </c>
       <c r="H57" s="72" t="s">
-        <v>612</v>
+        <v>614</v>
       </c>
       <c r="I57" s="13" t="s">
         <v>98</v>
@@ -21892,25 +21926,25 @@
         <v>44</v>
       </c>
       <c r="K57" s="13" t="s">
-        <v>613</v>
+        <v>615</v>
       </c>
       <c r="L57" s="13" t="s">
-        <v>614</v>
+        <v>616</v>
       </c>
       <c r="M57" s="13" t="s">
-        <v>615</v>
+        <v>617</v>
       </c>
       <c r="N57" s="73" t="s">
-        <v>616</v>
+        <v>618</v>
       </c>
       <c r="O57" s="73" t="s">
-        <v>617</v>
+        <v>619</v>
       </c>
       <c r="P57" s="13" t="s">
-        <v>618</v>
+        <v>620</v>
       </c>
       <c r="Q57" s="66" t="s">
-        <v>619</v>
+        <v>621</v>
       </c>
       <c r="R57" s="74"/>
       <c r="S57" s="69">
@@ -21920,13 +21954,13 @@
         <v>38899</v>
       </c>
       <c r="U57" s="64" t="s">
-        <v>593</v>
+        <v>595</v>
       </c>
       <c r="V57" s="69">
         <v>45474</v>
       </c>
       <c r="W57" s="64" t="s">
-        <v>620</v>
+        <v>622</v>
       </c>
       <c r="X57" s="70" t="s">
         <v>54</v>
@@ -21942,36 +21976,36 @@
       </c>
       <c r="AB57" s="63"/>
       <c r="AC57" s="13" t="s">
-        <v>621</v>
+        <v>623</v>
       </c>
       <c r="AD57" s="13" t="s">
-        <v>622</v>
+        <v>624</v>
       </c>
       <c r="AE57" s="13" t="s">
-        <v>623</v>
+        <v>625</v>
       </c>
       <c r="AF57" s="13" t="s">
-        <v>624</v>
+        <v>626</v>
       </c>
       <c r="AG57" s="13" t="s">
-        <v>625</v>
+        <v>627</v>
       </c>
       <c r="AH57" s="13" t="s">
-        <v>626</v>
+        <v>628</v>
       </c>
       <c r="AI57" s="13" t="s">
-        <v>627</v>
+        <v>629</v>
       </c>
       <c r="AJ57" s="13" t="s">
-        <v>628</v>
+        <v>630</v>
       </c>
       <c r="AK57" s="13" t="s">
-        <v>629</v>
+        <v>631</v>
       </c>
     </row>
-    <row r="58" spans="1:37" ht="54" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="58" spans="1:37" ht="54" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A58" s="62" t="s">
-        <v>630</v>
+        <v>632</v>
       </c>
       <c r="B58" s="13"/>
       <c r="C58" s="64"/>
@@ -21991,19 +22025,19 @@
         <v>　</v>
       </c>
       <c r="H58" s="72" t="s">
-        <v>631</v>
+        <v>633</v>
       </c>
       <c r="I58" s="13" t="s">
         <v>390</v>
       </c>
       <c r="J58" s="66" t="s">
-        <v>632</v>
+        <v>634</v>
       </c>
       <c r="K58" s="13" t="s">
-        <v>633</v>
+        <v>635</v>
       </c>
       <c r="L58" s="13" t="s">
-        <v>634</v>
+        <v>636</v>
       </c>
       <c r="M58" s="13" t="s">
         <v>522</v>
@@ -22015,10 +22049,10 @@
         <v>524</v>
       </c>
       <c r="P58" s="13" t="s">
-        <v>635</v>
+        <v>637</v>
       </c>
       <c r="Q58" s="66" t="s">
-        <v>636</v>
+        <v>638</v>
       </c>
       <c r="R58" s="68">
         <v>39020</v>
@@ -22030,13 +22064,13 @@
         <v>39083</v>
       </c>
       <c r="U58" s="64" t="s">
-        <v>637</v>
+        <v>639</v>
       </c>
       <c r="V58" s="69">
         <v>45658</v>
       </c>
       <c r="W58" s="64" t="s">
-        <v>638</v>
+        <v>640</v>
       </c>
       <c r="X58" s="70" t="s">
         <v>459</v>
@@ -22052,7 +22086,7 @@
       </c>
       <c r="AB58" s="63"/>
       <c r="AC58" s="13" t="s">
-        <v>639</v>
+        <v>641</v>
       </c>
       <c r="AD58" s="13" t="s">
         <v>529</v>
@@ -22065,9 +22099,9 @@
       <c r="AJ58" s="71"/>
       <c r="AK58" s="71"/>
     </row>
-    <row r="59" spans="1:37" ht="54" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="59" spans="1:37" ht="54" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A59" s="62" t="s">
-        <v>640</v>
+        <v>642</v>
       </c>
       <c r="B59" s="13"/>
       <c r="C59" s="64"/>
@@ -22087,7 +22121,7 @@
         <v>　</v>
       </c>
       <c r="H59" s="72" t="s">
-        <v>641</v>
+        <v>643</v>
       </c>
       <c r="I59" s="13" t="s">
         <v>80</v>
@@ -22096,13 +22130,13 @@
         <v>44</v>
       </c>
       <c r="K59" s="13" t="s">
-        <v>642</v>
+        <v>644</v>
       </c>
       <c r="L59" s="13" t="s">
-        <v>643</v>
+        <v>645</v>
       </c>
       <c r="M59" s="13" t="s">
-        <v>644</v>
+        <v>646</v>
       </c>
       <c r="N59" s="73" t="s">
         <v>102</v>
@@ -22111,10 +22145,10 @@
         <v>103</v>
       </c>
       <c r="P59" s="13" t="s">
-        <v>645</v>
+        <v>647</v>
       </c>
       <c r="Q59" s="84" t="s">
-        <v>646</v>
+        <v>648</v>
       </c>
       <c r="R59" s="68">
         <v>39050</v>
@@ -22132,7 +22166,7 @@
         <v>45658</v>
       </c>
       <c r="W59" s="64" t="s">
-        <v>647</v>
+        <v>649</v>
       </c>
       <c r="X59" s="70" t="s">
         <v>54</v>
@@ -22148,16 +22182,16 @@
       </c>
       <c r="AB59" s="63"/>
       <c r="AC59" s="13" t="s">
-        <v>648</v>
+        <v>650</v>
       </c>
       <c r="AD59" s="13" t="s">
-        <v>649</v>
+        <v>651</v>
       </c>
       <c r="AE59" s="13" t="s">
-        <v>650</v>
+        <v>652</v>
       </c>
       <c r="AF59" s="13" t="s">
-        <v>651</v>
+        <v>653</v>
       </c>
       <c r="AG59" s="13" t="s">
         <v>110</v>
@@ -22167,9 +22201,9 @@
       <c r="AJ59" s="71"/>
       <c r="AK59" s="71"/>
     </row>
-    <row r="60" spans="1:37" ht="78" x14ac:dyDescent="0.55000000000000004">
+    <row r="60" spans="1:37" ht="81" x14ac:dyDescent="0.15">
       <c r="A60" s="62" t="s">
-        <v>652</v>
+        <v>654</v>
       </c>
       <c r="B60" s="13"/>
       <c r="C60" s="64"/>
@@ -22189,34 +22223,34 @@
         <v>　</v>
       </c>
       <c r="H60" s="72" t="s">
-        <v>653</v>
+        <v>655</v>
       </c>
       <c r="I60" s="13" t="s">
-        <v>654</v>
+        <v>656</v>
       </c>
       <c r="J60" s="66" t="s">
         <v>44</v>
       </c>
       <c r="K60" s="13" t="s">
-        <v>655</v>
+        <v>657</v>
       </c>
       <c r="L60" s="13" t="s">
-        <v>656</v>
+        <v>658</v>
       </c>
       <c r="M60" s="13" t="s">
-        <v>657</v>
+        <v>659</v>
       </c>
       <c r="N60" s="73" t="s">
-        <v>658</v>
+        <v>660</v>
       </c>
       <c r="O60" s="73" t="s">
-        <v>659</v>
+        <v>661</v>
       </c>
       <c r="P60" s="13" t="s">
-        <v>660</v>
+        <v>662</v>
       </c>
       <c r="Q60" s="66" t="s">
-        <v>661</v>
+        <v>663</v>
       </c>
       <c r="R60" s="68">
         <v>38997</v>
@@ -22234,7 +22268,7 @@
         <v>45658</v>
       </c>
       <c r="W60" s="64" t="s">
-        <v>662</v>
+        <v>664</v>
       </c>
       <c r="X60" s="70" t="s">
         <v>54</v>
@@ -22250,10 +22284,10 @@
       </c>
       <c r="AB60" s="63"/>
       <c r="AC60" s="13" t="s">
-        <v>663</v>
+        <v>665</v>
       </c>
       <c r="AD60" s="13" t="s">
-        <v>664</v>
+        <v>666</v>
       </c>
       <c r="AE60" s="13"/>
       <c r="AF60" s="63"/>
@@ -22263,9 +22297,9 @@
       <c r="AJ60" s="71"/>
       <c r="AK60" s="71"/>
     </row>
-    <row r="61" spans="1:37" ht="27" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="61" spans="1:37" ht="27" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A61" s="62" t="s">
-        <v>665</v>
+        <v>667</v>
       </c>
       <c r="B61" s="63"/>
       <c r="C61" s="64" t="s">
@@ -22287,31 +22321,31 @@
         <v>　</v>
       </c>
       <c r="H61" s="85" t="s">
-        <v>666</v>
+        <v>668</v>
       </c>
       <c r="I61" s="82" t="s">
-        <v>667</v>
+        <v>669</v>
       </c>
       <c r="J61" s="66" t="s">
         <v>44</v>
       </c>
       <c r="K61" s="13" t="s">
-        <v>668</v>
+        <v>670</v>
       </c>
       <c r="L61" s="86" t="s">
-        <v>669</v>
+        <v>671</v>
       </c>
       <c r="M61" s="13" t="s">
-        <v>615</v>
+        <v>617</v>
       </c>
       <c r="N61" s="67" t="s">
-        <v>670</v>
+        <v>672</v>
       </c>
       <c r="O61" s="67" t="s">
-        <v>671</v>
+        <v>673</v>
       </c>
       <c r="P61" s="13" t="s">
-        <v>672</v>
+        <v>674</v>
       </c>
       <c r="Q61" s="66"/>
       <c r="R61" s="68">
@@ -22324,7 +22358,7 @@
         <v>40695</v>
       </c>
       <c r="U61" s="64" t="s">
-        <v>673</v>
+        <v>675</v>
       </c>
       <c r="V61" s="64"/>
       <c r="W61" s="64"/>
@@ -22344,7 +22378,7 @@
         <v>42307</v>
       </c>
       <c r="AC61" s="13" t="s">
-        <v>674</v>
+        <v>676</v>
       </c>
       <c r="AD61" s="13"/>
       <c r="AE61" s="13"/>
@@ -22355,11 +22389,13 @@
       <c r="AJ61" s="71"/>
       <c r="AK61" s="71"/>
     </row>
-    <row r="62" spans="1:37" ht="40.5" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="62" spans="1:37" ht="40.5" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A62" s="62" t="s">
-        <v>665</v>
-      </c>
-      <c r="B62" s="13"/>
+        <v>667</v>
+      </c>
+      <c r="B62" s="13" t="s">
+        <v>677</v>
+      </c>
       <c r="C62" s="64"/>
       <c r="D62" s="65">
         <v>2954394</v>
@@ -22377,7 +22413,7 @@
         <v>二重</v>
       </c>
       <c r="H62" s="72" t="s">
-        <v>675</v>
+        <v>678</v>
       </c>
       <c r="I62" s="82" t="s">
         <v>98</v>
@@ -22386,25 +22422,25 @@
         <v>44</v>
       </c>
       <c r="K62" s="13" t="s">
-        <v>668</v>
+        <v>670</v>
       </c>
       <c r="L62" s="13" t="s">
-        <v>669</v>
+        <v>671</v>
       </c>
       <c r="M62" s="13" t="s">
-        <v>676</v>
+        <v>679</v>
       </c>
       <c r="N62" s="73" t="s">
-        <v>616</v>
+        <v>618</v>
       </c>
       <c r="O62" s="73" t="s">
-        <v>617</v>
+        <v>619</v>
       </c>
       <c r="P62" s="13" t="s">
-        <v>677</v>
+        <v>680</v>
       </c>
       <c r="Q62" s="87" t="s">
-        <v>678</v>
+        <v>681</v>
       </c>
       <c r="R62" s="68">
         <v>40940</v>
@@ -22416,13 +22452,13 @@
         <v>41000</v>
       </c>
       <c r="U62" s="64" t="s">
-        <v>679</v>
+        <v>682</v>
       </c>
       <c r="V62" s="69">
         <v>45383</v>
       </c>
       <c r="W62" s="64" t="s">
-        <v>680</v>
+        <v>683</v>
       </c>
       <c r="X62" s="70" t="s">
         <v>54</v>
@@ -22438,16 +22474,16 @@
       </c>
       <c r="AB62" s="63"/>
       <c r="AC62" s="66" t="s">
-        <v>681</v>
+        <v>684</v>
       </c>
       <c r="AD62" s="13" t="s">
-        <v>627</v>
+        <v>629</v>
       </c>
       <c r="AE62" s="13" t="s">
-        <v>628</v>
+        <v>630</v>
       </c>
       <c r="AF62" s="13" t="s">
-        <v>629</v>
+        <v>631</v>
       </c>
       <c r="AG62" s="63"/>
       <c r="AH62" s="63"/>
@@ -22455,9 +22491,9 @@
       <c r="AJ62" s="71"/>
       <c r="AK62" s="71"/>
     </row>
-    <row r="63" spans="1:37" ht="39" x14ac:dyDescent="0.55000000000000004">
+    <row r="63" spans="1:37" ht="40.5" x14ac:dyDescent="0.15">
       <c r="A63" s="62" t="s">
-        <v>682</v>
+        <v>685</v>
       </c>
       <c r="B63" s="13"/>
       <c r="C63" s="64"/>
@@ -22477,31 +22513,31 @@
         <v>　</v>
       </c>
       <c r="H63" s="72" t="s">
-        <v>683</v>
+        <v>686</v>
       </c>
       <c r="I63" s="88" t="s">
-        <v>684</v>
+        <v>687</v>
       </c>
       <c r="J63" s="66" t="s">
         <v>44</v>
       </c>
       <c r="K63" s="13" t="s">
-        <v>685</v>
+        <v>688</v>
       </c>
       <c r="L63" s="13" t="s">
-        <v>686</v>
+        <v>689</v>
       </c>
       <c r="M63" s="13" t="s">
+        <v>690</v>
+      </c>
+      <c r="N63" s="73" t="s">
         <v>687</v>
       </c>
-      <c r="N63" s="73" t="s">
-        <v>684</v>
-      </c>
       <c r="O63" s="73" t="s">
-        <v>688</v>
+        <v>691</v>
       </c>
       <c r="P63" s="13" t="s">
-        <v>689</v>
+        <v>692</v>
       </c>
       <c r="Q63" s="66"/>
       <c r="R63" s="68">
@@ -22514,13 +22550,13 @@
         <v>40756</v>
       </c>
       <c r="U63" s="64" t="s">
-        <v>690</v>
+        <v>693</v>
       </c>
       <c r="V63" s="69">
         <v>45108</v>
       </c>
       <c r="W63" s="64" t="s">
-        <v>691</v>
+        <v>694</v>
       </c>
       <c r="X63" s="70" t="s">
         <v>54</v>
@@ -22536,7 +22572,7 @@
       </c>
       <c r="AB63" s="63"/>
       <c r="AC63" s="13" t="s">
-        <v>692</v>
+        <v>695</v>
       </c>
       <c r="AD63" s="13"/>
       <c r="AE63" s="13"/>
@@ -22547,9 +22583,9 @@
       <c r="AJ63" s="71"/>
       <c r="AK63" s="71"/>
     </row>
-    <row r="64" spans="1:37" ht="67.5" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="64" spans="1:37" ht="67.5" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A64" s="62" t="s">
-        <v>693</v>
+        <v>696</v>
       </c>
       <c r="B64" s="13"/>
       <c r="C64" s="64"/>
@@ -22569,34 +22605,34 @@
         <v>　</v>
       </c>
       <c r="H64" s="72" t="s">
-        <v>694</v>
+        <v>697</v>
       </c>
       <c r="I64" s="88" t="s">
-        <v>695</v>
+        <v>698</v>
       </c>
       <c r="J64" s="66" t="s">
         <v>44</v>
       </c>
       <c r="K64" s="13" t="s">
-        <v>696</v>
+        <v>699</v>
       </c>
       <c r="L64" s="13" t="s">
-        <v>697</v>
+        <v>700</v>
       </c>
       <c r="M64" s="13" t="s">
-        <v>698</v>
+        <v>701</v>
       </c>
       <c r="N64" s="73" t="s">
-        <v>699</v>
+        <v>702</v>
       </c>
       <c r="O64" s="73" t="s">
-        <v>700</v>
+        <v>703</v>
       </c>
       <c r="P64" s="13" t="s">
-        <v>701</v>
+        <v>704</v>
       </c>
       <c r="Q64" s="66" t="s">
-        <v>702</v>
+        <v>705</v>
       </c>
       <c r="R64" s="68">
         <v>40691</v>
@@ -22608,13 +22644,13 @@
         <v>40756</v>
       </c>
       <c r="U64" s="64" t="s">
-        <v>690</v>
+        <v>693</v>
       </c>
       <c r="V64" s="69">
         <v>45108</v>
       </c>
       <c r="W64" s="89" t="s">
-        <v>703</v>
+        <v>706</v>
       </c>
       <c r="X64" s="70" t="s">
         <v>54</v>
@@ -22630,16 +22666,16 @@
       </c>
       <c r="AB64" s="63"/>
       <c r="AC64" s="13" t="s">
-        <v>704</v>
+        <v>707</v>
       </c>
       <c r="AD64" s="13" t="s">
-        <v>705</v>
+        <v>708</v>
       </c>
       <c r="AE64" s="13" t="s">
-        <v>706</v>
+        <v>709</v>
       </c>
       <c r="AF64" s="13" t="s">
-        <v>707</v>
+        <v>710</v>
       </c>
       <c r="AG64" s="63"/>
       <c r="AH64" s="63"/>
@@ -22647,9 +22683,9 @@
       <c r="AJ64" s="71"/>
       <c r="AK64" s="71"/>
     </row>
-    <row r="65" spans="1:37" ht="54" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="65" spans="1:37" ht="54" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A65" s="62" t="s">
-        <v>708</v>
+        <v>711</v>
       </c>
       <c r="B65" s="63"/>
       <c r="C65" s="64"/>
@@ -22669,7 +22705,7 @@
         <v>　</v>
       </c>
       <c r="H65" s="72" t="s">
-        <v>709</v>
+        <v>712</v>
       </c>
       <c r="I65" s="66" t="s">
         <v>98</v>
@@ -22678,25 +22714,25 @@
         <v>44</v>
       </c>
       <c r="K65" s="13" t="s">
-        <v>710</v>
+        <v>713</v>
       </c>
       <c r="L65" s="13" t="s">
-        <v>711</v>
+        <v>714</v>
       </c>
       <c r="M65" s="13" t="s">
-        <v>601</v>
+        <v>603</v>
       </c>
       <c r="N65" s="73" t="s">
-        <v>602</v>
+        <v>604</v>
       </c>
       <c r="O65" s="73" t="s">
-        <v>712</v>
+        <v>715</v>
       </c>
       <c r="P65" s="13" t="s">
-        <v>713</v>
+        <v>716</v>
       </c>
       <c r="Q65" s="66" t="s">
-        <v>714</v>
+        <v>717</v>
       </c>
       <c r="R65" s="68">
         <v>40759</v>
@@ -22708,13 +22744,13 @@
         <v>40817</v>
       </c>
       <c r="U65" s="64" t="s">
-        <v>715</v>
+        <v>718</v>
       </c>
       <c r="V65" s="69">
         <v>45108</v>
       </c>
       <c r="W65" s="89" t="s">
-        <v>703</v>
+        <v>706</v>
       </c>
       <c r="X65" s="70" t="s">
         <v>54</v>
@@ -22730,16 +22766,16 @@
       </c>
       <c r="AB65" s="63"/>
       <c r="AC65" s="13" t="s">
-        <v>716</v>
+        <v>719</v>
       </c>
       <c r="AD65" s="13" t="s">
-        <v>717</v>
+        <v>720</v>
       </c>
       <c r="AE65" s="13" t="s">
-        <v>718</v>
+        <v>721</v>
       </c>
       <c r="AF65" s="13" t="s">
-        <v>609</v>
+        <v>611</v>
       </c>
       <c r="AG65" s="63"/>
       <c r="AH65" s="63"/>
@@ -22747,9 +22783,9 @@
       <c r="AJ65" s="71"/>
       <c r="AK65" s="71"/>
     </row>
-    <row r="66" spans="1:37" ht="26" x14ac:dyDescent="0.55000000000000004">
+    <row r="66" spans="1:37" ht="27" x14ac:dyDescent="0.15">
       <c r="A66" s="62" t="s">
-        <v>719</v>
+        <v>722</v>
       </c>
       <c r="B66" s="62"/>
       <c r="C66" s="64" t="s">
@@ -22771,27 +22807,27 @@
         <v>　</v>
       </c>
       <c r="H66" s="13" t="s">
-        <v>720</v>
+        <v>723</v>
       </c>
       <c r="I66" s="66" t="s">
-        <v>721</v>
+        <v>724</v>
       </c>
       <c r="J66" s="66" t="s">
         <v>44</v>
       </c>
       <c r="K66" s="13" t="s">
-        <v>722</v>
+        <v>725</v>
       </c>
       <c r="L66" s="13" t="s">
-        <v>723</v>
+        <v>726</v>
       </c>
       <c r="M66" s="13" t="s">
-        <v>724</v>
+        <v>727</v>
       </c>
       <c r="N66" s="73"/>
       <c r="O66" s="67"/>
       <c r="P66" s="13" t="s">
-        <v>725</v>
+        <v>728</v>
       </c>
       <c r="Q66" s="66"/>
       <c r="R66" s="68">
@@ -22804,7 +22840,7 @@
         <v>40817</v>
       </c>
       <c r="U66" s="64" t="s">
-        <v>715</v>
+        <v>718</v>
       </c>
       <c r="V66" s="64"/>
       <c r="W66" s="64"/>
@@ -22824,7 +22860,7 @@
         <v>42408</v>
       </c>
       <c r="AC66" s="13" t="s">
-        <v>726</v>
+        <v>729</v>
       </c>
       <c r="AD66" s="13"/>
       <c r="AE66" s="13"/>
@@ -22835,9 +22871,9 @@
       <c r="AJ66" s="71"/>
       <c r="AK66" s="71"/>
     </row>
-    <row r="67" spans="1:37" ht="61.5" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="67" spans="1:37" ht="61.5" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A67" s="62" t="s">
-        <v>727</v>
+        <v>730</v>
       </c>
       <c r="B67" s="13"/>
       <c r="C67" s="64"/>
@@ -22857,22 +22893,22 @@
         <v>　</v>
       </c>
       <c r="H67" s="72" t="s">
-        <v>728</v>
+        <v>731</v>
       </c>
       <c r="I67" s="82" t="s">
-        <v>729</v>
+        <v>732</v>
       </c>
       <c r="J67" s="66" t="s">
         <v>44</v>
       </c>
       <c r="K67" s="13" t="s">
-        <v>730</v>
+        <v>733</v>
       </c>
       <c r="L67" s="13" t="s">
-        <v>731</v>
+        <v>734</v>
       </c>
       <c r="M67" s="13" t="s">
-        <v>732</v>
+        <v>735</v>
       </c>
       <c r="N67" s="73" t="s">
         <v>557</v>
@@ -22881,10 +22917,10 @@
         <v>558</v>
       </c>
       <c r="P67" s="13" t="s">
-        <v>733</v>
+        <v>736</v>
       </c>
       <c r="Q67" s="66" t="s">
-        <v>734</v>
+        <v>737</v>
       </c>
       <c r="R67" s="68">
         <v>40833</v>
@@ -22902,7 +22938,7 @@
         <v>45292</v>
       </c>
       <c r="W67" s="64" t="s">
-        <v>735</v>
+        <v>738</v>
       </c>
       <c r="X67" s="70" t="s">
         <v>54</v>
@@ -22929,9 +22965,9 @@
       <c r="AJ67" s="71"/>
       <c r="AK67" s="71"/>
     </row>
-    <row r="68" spans="1:37" ht="54" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="68" spans="1:37" ht="54" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A68" s="62" t="s">
-        <v>736</v>
+        <v>739</v>
       </c>
       <c r="B68" s="64"/>
       <c r="C68" s="64"/>
@@ -22951,7 +22987,7 @@
         <v>　</v>
       </c>
       <c r="H68" s="72" t="s">
-        <v>737</v>
+        <v>740</v>
       </c>
       <c r="I68" s="81" t="s">
         <v>60</v>
@@ -22960,22 +22996,22 @@
         <v>44</v>
       </c>
       <c r="K68" s="13" t="s">
-        <v>738</v>
+        <v>741</v>
       </c>
       <c r="L68" s="13" t="s">
-        <v>739</v>
+        <v>742</v>
       </c>
       <c r="M68" s="13" t="s">
-        <v>740</v>
+        <v>743</v>
       </c>
       <c r="N68" s="73" t="s">
         <v>390</v>
       </c>
       <c r="O68" s="73" t="s">
-        <v>741</v>
+        <v>744</v>
       </c>
       <c r="P68" s="13" t="s">
-        <v>740</v>
+        <v>743</v>
       </c>
       <c r="Q68" s="66"/>
       <c r="R68" s="68">
@@ -22988,13 +23024,13 @@
         <v>40391</v>
       </c>
       <c r="U68" s="64" t="s">
-        <v>742</v>
+        <v>745</v>
       </c>
       <c r="V68" s="90">
         <v>44743</v>
       </c>
       <c r="W68" s="89" t="s">
-        <v>743</v>
+        <v>746</v>
       </c>
       <c r="X68" s="77" t="s">
         <v>17</v>
@@ -23008,10 +23044,10 @@
       </c>
       <c r="AB68" s="63"/>
       <c r="AC68" s="13" t="s">
-        <v>744</v>
+        <v>747</v>
       </c>
       <c r="AD68" s="13" t="s">
-        <v>745</v>
+        <v>748</v>
       </c>
       <c r="AE68" s="62"/>
       <c r="AF68" s="63"/>
@@ -23021,9 +23057,9 @@
       <c r="AJ68" s="71"/>
       <c r="AK68" s="71"/>
     </row>
-    <row r="69" spans="1:37" ht="156" x14ac:dyDescent="0.55000000000000004">
+    <row r="69" spans="1:37" ht="162" x14ac:dyDescent="0.15">
       <c r="A69" s="62" t="s">
-        <v>746</v>
+        <v>749</v>
       </c>
       <c r="B69" s="13"/>
       <c r="C69" s="64"/>
@@ -23043,34 +23079,34 @@
         <v>　</v>
       </c>
       <c r="H69" s="72" t="s">
-        <v>747</v>
+        <v>750</v>
       </c>
       <c r="I69" s="82" t="s">
-        <v>748</v>
+        <v>751</v>
       </c>
       <c r="J69" s="66" t="s">
         <v>44</v>
       </c>
       <c r="K69" s="13" t="s">
-        <v>749</v>
+        <v>752</v>
       </c>
       <c r="L69" s="13" t="s">
-        <v>750</v>
+        <v>753</v>
       </c>
       <c r="M69" s="13" t="s">
-        <v>751</v>
+        <v>754</v>
       </c>
       <c r="N69" s="73">
         <v>2220033</v>
       </c>
       <c r="O69" s="73" t="s">
-        <v>752</v>
+        <v>755</v>
       </c>
       <c r="P69" s="13" t="s">
-        <v>753</v>
+        <v>756</v>
       </c>
       <c r="Q69" s="66" t="s">
-        <v>754</v>
+        <v>757</v>
       </c>
       <c r="R69" s="68">
         <v>40940</v>
@@ -23082,13 +23118,13 @@
         <v>41000</v>
       </c>
       <c r="U69" s="64" t="s">
-        <v>679</v>
+        <v>682</v>
       </c>
       <c r="V69" s="69">
         <v>45383</v>
       </c>
       <c r="W69" s="64" t="s">
-        <v>755</v>
+        <v>758</v>
       </c>
       <c r="X69" s="70" t="s">
         <v>54</v>
@@ -23104,16 +23140,16 @@
       </c>
       <c r="AB69" s="63"/>
       <c r="AC69" s="13" t="s">
-        <v>756</v>
+        <v>759</v>
       </c>
       <c r="AD69" s="13" t="s">
-        <v>757</v>
+        <v>760</v>
       </c>
       <c r="AE69" s="13" t="s">
-        <v>758</v>
+        <v>761</v>
       </c>
       <c r="AF69" s="13" t="s">
-        <v>759</v>
+        <v>762</v>
       </c>
       <c r="AG69" s="63"/>
       <c r="AH69" s="63"/>
@@ -23121,9 +23157,9 @@
       <c r="AJ69" s="71"/>
       <c r="AK69" s="71"/>
     </row>
-    <row r="70" spans="1:37" ht="54" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="70" spans="1:37" ht="54" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A70" s="62" t="s">
-        <v>760</v>
+        <v>763</v>
       </c>
       <c r="B70" s="13"/>
       <c r="C70" s="64"/>
@@ -23143,34 +23179,34 @@
         <v>　</v>
       </c>
       <c r="H70" s="72" t="s">
-        <v>761</v>
+        <v>764</v>
       </c>
       <c r="I70" s="82" t="s">
-        <v>729</v>
+        <v>732</v>
       </c>
       <c r="J70" s="66" t="s">
         <v>44</v>
       </c>
       <c r="K70" s="13" t="s">
-        <v>762</v>
+        <v>765</v>
       </c>
       <c r="L70" s="13" t="s">
-        <v>763</v>
+        <v>766</v>
       </c>
       <c r="M70" s="13" t="s">
-        <v>764</v>
+        <v>767</v>
       </c>
       <c r="N70" s="73" t="s">
-        <v>765</v>
+        <v>768</v>
       </c>
       <c r="O70" s="73" t="s">
-        <v>766</v>
+        <v>769</v>
       </c>
       <c r="P70" s="13" t="s">
-        <v>767</v>
+        <v>770</v>
       </c>
       <c r="Q70" s="66" t="s">
-        <v>768</v>
+        <v>771</v>
       </c>
       <c r="R70" s="68">
         <v>40912</v>
@@ -23182,13 +23218,13 @@
         <v>41000</v>
       </c>
       <c r="U70" s="64" t="s">
-        <v>679</v>
+        <v>682</v>
       </c>
       <c r="V70" s="69">
         <v>45383</v>
       </c>
       <c r="W70" s="64" t="s">
-        <v>769</v>
+        <v>772</v>
       </c>
       <c r="X70" s="70" t="s">
         <v>54</v>
@@ -23204,7 +23240,7 @@
       </c>
       <c r="AB70" s="63"/>
       <c r="AC70" s="13" t="s">
-        <v>770</v>
+        <v>773</v>
       </c>
       <c r="AD70" s="13"/>
       <c r="AE70" s="13"/>
@@ -23215,9 +23251,9 @@
       <c r="AJ70" s="71"/>
       <c r="AK70" s="71"/>
     </row>
-    <row r="71" spans="1:37" ht="54" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="71" spans="1:37" ht="54" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A71" s="62" t="s">
-        <v>771</v>
+        <v>774</v>
       </c>
       <c r="B71" s="63"/>
       <c r="C71" s="70"/>
@@ -23237,34 +23273,34 @@
         <v>　</v>
       </c>
       <c r="H71" s="72" t="s">
-        <v>772</v>
+        <v>775</v>
       </c>
       <c r="I71" s="82" t="s">
-        <v>773</v>
+        <v>776</v>
       </c>
       <c r="J71" s="66" t="s">
         <v>44</v>
       </c>
       <c r="K71" s="13" t="s">
-        <v>774</v>
+        <v>777</v>
       </c>
       <c r="L71" s="13" t="s">
-        <v>775</v>
+        <v>778</v>
       </c>
       <c r="M71" s="13" t="s">
-        <v>776</v>
+        <v>779</v>
       </c>
       <c r="N71" s="73" t="s">
-        <v>777</v>
+        <v>780</v>
       </c>
       <c r="O71" s="73" t="s">
-        <v>778</v>
+        <v>781</v>
       </c>
       <c r="P71" s="13" t="s">
-        <v>779</v>
+        <v>782</v>
       </c>
       <c r="Q71" s="66" t="s">
-        <v>780</v>
+        <v>783</v>
       </c>
       <c r="R71" s="68">
         <v>41004</v>
@@ -23276,13 +23312,13 @@
         <v>41061</v>
       </c>
       <c r="U71" s="64" t="s">
-        <v>781</v>
+        <v>784</v>
       </c>
       <c r="V71" s="69">
         <v>45383</v>
       </c>
       <c r="W71" s="64" t="s">
-        <v>782</v>
+        <v>785</v>
       </c>
       <c r="X71" s="70" t="s">
         <v>54</v>
@@ -23307,9 +23343,9 @@
       <c r="AJ71" s="71"/>
       <c r="AK71" s="71"/>
     </row>
-    <row r="72" spans="1:37" ht="108" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="72" spans="1:37" ht="108" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A72" s="62" t="s">
-        <v>783</v>
+        <v>786</v>
       </c>
       <c r="B72" s="63"/>
       <c r="C72" s="64"/>
@@ -23329,7 +23365,7 @@
         <v>　</v>
       </c>
       <c r="H72" s="72" t="s">
-        <v>784</v>
+        <v>787</v>
       </c>
       <c r="I72" s="82" t="s">
         <v>240</v>
@@ -23338,25 +23374,25 @@
         <v>44</v>
       </c>
       <c r="K72" s="13" t="s">
-        <v>785</v>
+        <v>788</v>
       </c>
       <c r="L72" s="13" t="s">
-        <v>786</v>
+        <v>789</v>
       </c>
       <c r="M72" s="13" t="s">
-        <v>787</v>
+        <v>790</v>
       </c>
       <c r="N72" s="73" t="s">
-        <v>788</v>
+        <v>791</v>
       </c>
       <c r="O72" s="73" t="s">
-        <v>789</v>
+        <v>792</v>
       </c>
       <c r="P72" s="13" t="s">
-        <v>790</v>
+        <v>793</v>
       </c>
       <c r="Q72" s="66" t="s">
-        <v>791</v>
+        <v>794</v>
       </c>
       <c r="R72" s="68">
         <v>41060</v>
@@ -23368,13 +23404,13 @@
         <v>41122</v>
       </c>
       <c r="U72" s="64" t="s">
-        <v>792</v>
+        <v>795</v>
       </c>
       <c r="V72" s="69">
         <v>45474</v>
       </c>
       <c r="W72" s="64" t="s">
-        <v>793</v>
+        <v>796</v>
       </c>
       <c r="X72" s="70" t="s">
         <v>54</v>
@@ -23390,7 +23426,7 @@
       </c>
       <c r="AB72" s="63"/>
       <c r="AC72" s="13" t="s">
-        <v>794</v>
+        <v>797</v>
       </c>
       <c r="AD72" s="13"/>
       <c r="AE72" s="13"/>
@@ -23401,9 +23437,9 @@
       <c r="AJ72" s="71"/>
       <c r="AK72" s="71"/>
     </row>
-    <row r="73" spans="1:37" ht="54" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="73" spans="1:37" ht="54" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A73" s="62" t="s">
-        <v>795</v>
+        <v>798</v>
       </c>
       <c r="B73" s="13"/>
       <c r="C73" s="64"/>
@@ -23423,7 +23459,7 @@
         <v>　</v>
       </c>
       <c r="H73" s="72" t="s">
-        <v>796</v>
+        <v>799</v>
       </c>
       <c r="I73" s="82" t="s">
         <v>500</v>
@@ -23432,25 +23468,25 @@
         <v>44</v>
       </c>
       <c r="K73" s="13" t="s">
-        <v>797</v>
+        <v>800</v>
       </c>
       <c r="L73" s="13" t="s">
-        <v>798</v>
+        <v>801</v>
       </c>
       <c r="M73" s="13" t="s">
-        <v>615</v>
+        <v>617</v>
       </c>
       <c r="N73" s="73" t="s">
-        <v>616</v>
+        <v>618</v>
       </c>
       <c r="O73" s="73" t="s">
-        <v>617</v>
+        <v>619</v>
       </c>
       <c r="P73" s="13" t="s">
-        <v>799</v>
+        <v>802</v>
       </c>
       <c r="Q73" s="66" t="s">
-        <v>800</v>
+        <v>803</v>
       </c>
       <c r="R73" s="68">
         <v>41183</v>
@@ -23462,13 +23498,13 @@
         <v>41244</v>
       </c>
       <c r="U73" s="64" t="s">
-        <v>801</v>
+        <v>804</v>
       </c>
       <c r="V73" s="69">
         <v>45566</v>
       </c>
       <c r="W73" s="64" t="s">
-        <v>802</v>
+        <v>805</v>
       </c>
       <c r="X73" s="70" t="s">
         <v>54</v>
@@ -23484,13 +23520,13 @@
       </c>
       <c r="AB73" s="63"/>
       <c r="AC73" s="13" t="s">
-        <v>627</v>
+        <v>629</v>
       </c>
       <c r="AD73" s="13" t="s">
-        <v>628</v>
+        <v>630</v>
       </c>
       <c r="AE73" s="13" t="s">
-        <v>629</v>
+        <v>631</v>
       </c>
       <c r="AF73" s="63"/>
       <c r="AG73" s="63"/>
@@ -23499,9 +23535,9 @@
       <c r="AJ73" s="71"/>
       <c r="AK73" s="71"/>
     </row>
-    <row r="74" spans="1:37" ht="54" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="74" spans="1:37" ht="54" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A74" s="62" t="s">
-        <v>803</v>
+        <v>806</v>
       </c>
       <c r="B74" s="63"/>
       <c r="C74" s="64" t="s">
@@ -23523,32 +23559,32 @@
         <v>　</v>
       </c>
       <c r="H74" s="13" t="s">
-        <v>804</v>
+        <v>807</v>
       </c>
       <c r="I74" s="13" t="s">
-        <v>805</v>
+        <v>808</v>
       </c>
       <c r="J74" s="66" t="s">
         <v>347</v>
       </c>
       <c r="K74" s="13" t="s">
-        <v>806</v>
+        <v>809</v>
       </c>
       <c r="L74" s="13" t="s">
-        <v>807</v>
+        <v>810</v>
       </c>
       <c r="M74" s="13" t="s">
-        <v>808</v>
+        <v>811</v>
       </c>
       <c r="N74" s="67"/>
       <c r="O74" s="67" t="s">
-        <v>809</v>
+        <v>812</v>
       </c>
       <c r="P74" s="13" t="s">
-        <v>810</v>
+        <v>813</v>
       </c>
       <c r="Q74" s="66" t="s">
-        <v>811</v>
+        <v>814</v>
       </c>
       <c r="R74" s="68">
         <v>41325</v>
@@ -23560,7 +23596,7 @@
         <v>41426</v>
       </c>
       <c r="U74" s="70" t="s">
-        <v>812</v>
+        <v>815</v>
       </c>
       <c r="V74" s="64"/>
       <c r="W74" s="64"/>
@@ -23580,7 +23616,7 @@
         <v>42610</v>
       </c>
       <c r="AC74" s="13" t="s">
-        <v>813</v>
+        <v>816</v>
       </c>
       <c r="AD74" s="13"/>
       <c r="AE74" s="13"/>
@@ -23591,9 +23627,9 @@
       <c r="AJ74" s="71"/>
       <c r="AK74" s="71"/>
     </row>
-    <row r="75" spans="1:37" ht="54" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="75" spans="1:37" ht="54" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A75" s="62" t="s">
-        <v>814</v>
+        <v>817</v>
       </c>
       <c r="B75" s="63"/>
       <c r="C75" s="64" t="s">
@@ -23615,7 +23651,7 @@
         <v>　</v>
       </c>
       <c r="H75" s="13" t="s">
-        <v>815</v>
+        <v>818</v>
       </c>
       <c r="I75" s="13" t="s">
         <v>195</v>
@@ -23624,25 +23660,25 @@
         <v>347</v>
       </c>
       <c r="K75" s="13" t="s">
-        <v>816</v>
+        <v>819</v>
       </c>
       <c r="L75" s="13" t="s">
-        <v>817</v>
+        <v>820</v>
       </c>
       <c r="M75" s="13" t="s">
-        <v>818</v>
+        <v>821</v>
       </c>
       <c r="N75" s="91" t="s">
-        <v>819</v>
+        <v>822</v>
       </c>
       <c r="O75" s="67" t="s">
-        <v>820</v>
+        <v>823</v>
       </c>
       <c r="P75" s="13" t="s">
-        <v>821</v>
+        <v>824</v>
       </c>
       <c r="Q75" s="66" t="s">
-        <v>822</v>
+        <v>825</v>
       </c>
       <c r="R75" s="68">
         <v>41366</v>
@@ -23654,7 +23690,7 @@
         <v>41426</v>
       </c>
       <c r="U75" s="70" t="s">
-        <v>812</v>
+        <v>815</v>
       </c>
       <c r="V75" s="64"/>
       <c r="W75" s="64"/>
@@ -23674,13 +23710,13 @@
         <v>43001</v>
       </c>
       <c r="AC75" s="13" t="s">
-        <v>823</v>
+        <v>826</v>
       </c>
       <c r="AD75" s="13" t="s">
-        <v>824</v>
+        <v>827</v>
       </c>
       <c r="AE75" s="13" t="s">
-        <v>825</v>
+        <v>828</v>
       </c>
       <c r="AF75" s="63"/>
       <c r="AG75" s="63"/>
@@ -23689,9 +23725,9 @@
       <c r="AJ75" s="71"/>
       <c r="AK75" s="71"/>
     </row>
-    <row r="76" spans="1:37" ht="40.5" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="76" spans="1:37" ht="40.5" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A76" s="62" t="s">
-        <v>826</v>
+        <v>829</v>
       </c>
       <c r="B76" s="63"/>
       <c r="C76" s="64"/>
@@ -23711,7 +23747,7 @@
         <v>　</v>
       </c>
       <c r="H76" s="72" t="s">
-        <v>827</v>
+        <v>830</v>
       </c>
       <c r="I76" s="66" t="s">
         <v>500</v>
@@ -23720,22 +23756,22 @@
         <v>44</v>
       </c>
       <c r="K76" s="66" t="s">
-        <v>828</v>
+        <v>831</v>
       </c>
       <c r="L76" s="13" t="s">
-        <v>829</v>
+        <v>832</v>
       </c>
       <c r="M76" s="13" t="s">
-        <v>830</v>
+        <v>833</v>
       </c>
       <c r="N76" s="73" t="s">
-        <v>831</v>
+        <v>834</v>
       </c>
       <c r="O76" s="73" t="s">
-        <v>832</v>
+        <v>835</v>
       </c>
       <c r="P76" s="13" t="s">
-        <v>833</v>
+        <v>836</v>
       </c>
       <c r="Q76" s="66"/>
       <c r="R76" s="68">
@@ -23779,9 +23815,9 @@
       <c r="AJ76" s="71"/>
       <c r="AK76" s="71"/>
     </row>
-    <row r="77" spans="1:37" ht="54" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="77" spans="1:37" ht="54" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A77" s="62" t="s">
-        <v>834</v>
+        <v>837</v>
       </c>
       <c r="B77" s="13"/>
       <c r="C77" s="64"/>
@@ -23801,7 +23837,7 @@
         <v>　</v>
       </c>
       <c r="H77" s="72" t="s">
-        <v>835</v>
+        <v>838</v>
       </c>
       <c r="I77" s="13" t="s">
         <v>125</v>
@@ -23810,25 +23846,25 @@
         <v>44</v>
       </c>
       <c r="K77" s="13" t="s">
-        <v>836</v>
+        <v>839</v>
       </c>
       <c r="L77" s="13" t="s">
-        <v>837</v>
+        <v>840</v>
       </c>
       <c r="M77" s="13" t="s">
-        <v>838</v>
+        <v>841</v>
       </c>
       <c r="N77" s="92" t="s">
-        <v>819</v>
+        <v>822</v>
       </c>
       <c r="O77" s="73" t="s">
-        <v>820</v>
+        <v>823</v>
       </c>
       <c r="P77" s="13" t="s">
-        <v>839</v>
+        <v>842</v>
       </c>
       <c r="Q77" s="66" t="s">
-        <v>840</v>
+        <v>843</v>
       </c>
       <c r="R77" s="68">
         <v>41453</v>
@@ -23862,16 +23898,16 @@
       </c>
       <c r="AB77" s="63"/>
       <c r="AC77" s="13" t="s">
-        <v>841</v>
+        <v>844</v>
       </c>
       <c r="AD77" s="13" t="s">
-        <v>842</v>
+        <v>845</v>
       </c>
       <c r="AE77" s="13" t="s">
-        <v>843</v>
+        <v>846</v>
       </c>
       <c r="AF77" s="13" t="s">
-        <v>844</v>
+        <v>847</v>
       </c>
       <c r="AG77" s="63"/>
       <c r="AH77" s="63"/>
@@ -23879,9 +23915,9 @@
       <c r="AJ77" s="71"/>
       <c r="AK77" s="71"/>
     </row>
-    <row r="78" spans="1:37" ht="54" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="78" spans="1:37" ht="54" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A78" s="62" t="s">
-        <v>845</v>
+        <v>848</v>
       </c>
       <c r="B78" s="63"/>
       <c r="C78" s="70"/>
@@ -23901,34 +23937,34 @@
         <v>　</v>
       </c>
       <c r="H78" s="72" t="s">
-        <v>846</v>
+        <v>849</v>
       </c>
       <c r="I78" s="13" t="s">
-        <v>847</v>
+        <v>850</v>
       </c>
       <c r="J78" s="66" t="s">
-        <v>632</v>
+        <v>634</v>
       </c>
       <c r="K78" s="13" t="s">
-        <v>848</v>
+        <v>851</v>
       </c>
       <c r="L78" s="13" t="s">
-        <v>849</v>
+        <v>852</v>
       </c>
       <c r="M78" s="13" t="s">
-        <v>850</v>
+        <v>853</v>
       </c>
       <c r="N78" s="73" t="s">
-        <v>851</v>
+        <v>854</v>
       </c>
       <c r="O78" s="73" t="s">
-        <v>852</v>
+        <v>855</v>
       </c>
       <c r="P78" s="13" t="s">
-        <v>853</v>
+        <v>856</v>
       </c>
       <c r="Q78" s="66" t="s">
-        <v>854</v>
+        <v>857</v>
       </c>
       <c r="R78" s="74">
         <v>39000</v>
@@ -23946,7 +23982,7 @@
         <v>45658</v>
       </c>
       <c r="W78" s="64" t="s">
-        <v>855</v>
+        <v>858</v>
       </c>
       <c r="X78" s="70" t="s">
         <v>54</v>
@@ -23962,7 +23998,7 @@
       </c>
       <c r="AB78" s="63"/>
       <c r="AC78" s="13" t="s">
-        <v>856</v>
+        <v>859</v>
       </c>
       <c r="AD78" s="13"/>
       <c r="AE78" s="13"/>
@@ -23973,11 +24009,13 @@
       <c r="AJ78" s="71"/>
       <c r="AK78" s="71"/>
     </row>
-    <row r="79" spans="1:37" ht="81" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="79" spans="1:37" ht="81" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A79" s="62" t="s">
-        <v>857</v>
-      </c>
-      <c r="B79" s="13"/>
+        <v>860</v>
+      </c>
+      <c r="B79" s="13" t="s">
+        <v>861</v>
+      </c>
       <c r="C79" s="64"/>
       <c r="D79" s="78">
         <v>2955474</v>
@@ -23995,34 +24033,34 @@
         <v>　</v>
       </c>
       <c r="H79" s="72" t="s">
-        <v>858</v>
+        <v>862</v>
       </c>
       <c r="I79" s="13" t="s">
-        <v>859</v>
+        <v>863</v>
       </c>
       <c r="J79" s="66" t="s">
         <v>44</v>
       </c>
       <c r="K79" s="93" t="s">
-        <v>860</v>
+        <v>864</v>
       </c>
       <c r="L79" s="13" t="s">
-        <v>861</v>
+        <v>865</v>
       </c>
       <c r="M79" s="13" t="s">
-        <v>862</v>
+        <v>866</v>
       </c>
       <c r="N79" s="73" t="s">
-        <v>863</v>
+        <v>867</v>
       </c>
       <c r="O79" s="73" t="s">
-        <v>864</v>
+        <v>868</v>
       </c>
       <c r="P79" s="13" t="s">
-        <v>865</v>
+        <v>869</v>
       </c>
       <c r="Q79" s="66" t="s">
-        <v>866</v>
+        <v>870</v>
       </c>
       <c r="R79" s="68">
         <v>41757</v>
@@ -24034,13 +24072,13 @@
         <v>41852</v>
       </c>
       <c r="U79" s="64" t="s">
-        <v>867</v>
+        <v>871</v>
       </c>
       <c r="V79" s="69">
-        <v>44044</v>
+        <v>46204</v>
       </c>
       <c r="W79" s="70" t="s">
-        <v>868</v>
+        <v>872</v>
       </c>
       <c r="X79" s="64" t="s">
         <v>54</v>
@@ -24056,7 +24094,7 @@
       </c>
       <c r="AB79" s="63"/>
       <c r="AC79" s="13" t="s">
-        <v>869</v>
+        <v>873</v>
       </c>
       <c r="AD79" s="62"/>
       <c r="AE79" s="13"/>
@@ -24067,11 +24105,13 @@
       <c r="AJ79" s="71"/>
       <c r="AK79" s="71"/>
     </row>
-    <row r="80" spans="1:37" ht="67.5" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="80" spans="1:37" ht="67.5" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A80" s="62" t="s">
-        <v>870</v>
-      </c>
-      <c r="B80" s="13"/>
+        <v>874</v>
+      </c>
+      <c r="B80" s="13" t="s">
+        <v>861</v>
+      </c>
       <c r="C80" s="64"/>
       <c r="D80" s="78">
         <v>2955649</v>
@@ -24089,34 +24129,34 @@
         <v>　</v>
       </c>
       <c r="H80" s="72" t="s">
-        <v>871</v>
+        <v>875</v>
       </c>
       <c r="I80" s="66" t="s">
-        <v>872</v>
+        <v>876</v>
       </c>
       <c r="J80" s="66" t="s">
         <v>44</v>
       </c>
       <c r="K80" s="93" t="s">
-        <v>873</v>
+        <v>877</v>
       </c>
       <c r="L80" s="94" t="s">
-        <v>874</v>
+        <v>878</v>
       </c>
       <c r="M80" s="13" t="s">
-        <v>875</v>
+        <v>879</v>
       </c>
       <c r="N80" s="73" t="s">
-        <v>876</v>
+        <v>880</v>
       </c>
       <c r="O80" s="73" t="s">
-        <v>877</v>
+        <v>881</v>
       </c>
       <c r="P80" s="13" t="s">
-        <v>878</v>
+        <v>882</v>
       </c>
       <c r="Q80" s="66" t="s">
-        <v>879</v>
+        <v>883</v>
       </c>
       <c r="R80" s="68">
         <v>41796</v>
@@ -24128,13 +24168,13 @@
         <v>41852</v>
       </c>
       <c r="U80" s="64" t="s">
-        <v>867</v>
+        <v>871</v>
       </c>
       <c r="V80" s="69">
-        <v>44044</v>
+        <v>46204</v>
       </c>
       <c r="W80" s="70" t="s">
-        <v>880</v>
+        <v>872</v>
       </c>
       <c r="X80" s="64" t="s">
         <v>54</v>
@@ -24150,10 +24190,10 @@
       </c>
       <c r="AB80" s="63"/>
       <c r="AC80" s="13" t="s">
-        <v>881</v>
+        <v>884</v>
       </c>
       <c r="AD80" s="66" t="s">
-        <v>882</v>
+        <v>885</v>
       </c>
       <c r="AE80" s="13"/>
       <c r="AF80" s="13"/>
@@ -24163,11 +24203,13 @@
       <c r="AJ80" s="71"/>
       <c r="AK80" s="71"/>
     </row>
-    <row r="81" spans="1:37" ht="40.5" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="81" spans="1:37" ht="40.5" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A81" s="62" t="s">
-        <v>883</v>
-      </c>
-      <c r="B81" s="13"/>
+        <v>886</v>
+      </c>
+      <c r="B81" s="13" t="s">
+        <v>861</v>
+      </c>
       <c r="C81" s="64"/>
       <c r="D81" s="78">
         <v>2955094</v>
@@ -24185,34 +24227,34 @@
         <v>　</v>
       </c>
       <c r="H81" s="72" t="s">
-        <v>884</v>
+        <v>887</v>
       </c>
       <c r="I81" s="66" t="s">
-        <v>872</v>
+        <v>876</v>
       </c>
       <c r="J81" s="66" t="s">
         <v>44</v>
       </c>
       <c r="K81" s="93" t="s">
-        <v>885</v>
+        <v>888</v>
       </c>
       <c r="L81" s="94" t="s">
-        <v>886</v>
+        <v>889</v>
       </c>
       <c r="M81" s="13" t="s">
-        <v>818</v>
+        <v>821</v>
       </c>
       <c r="N81" s="73" t="s">
-        <v>819</v>
+        <v>822</v>
       </c>
       <c r="O81" s="73" t="s">
-        <v>820</v>
+        <v>823</v>
       </c>
       <c r="P81" s="13" t="s">
-        <v>887</v>
+        <v>890</v>
       </c>
       <c r="Q81" s="66" t="s">
-        <v>888</v>
+        <v>891</v>
       </c>
       <c r="R81" s="68">
         <v>41795</v>
@@ -24224,13 +24266,13 @@
         <v>41852</v>
       </c>
       <c r="U81" s="64" t="s">
-        <v>867</v>
+        <v>871</v>
       </c>
       <c r="V81" s="69">
-        <v>44044</v>
+        <v>46204</v>
       </c>
       <c r="W81" s="70" t="s">
-        <v>889</v>
+        <v>872</v>
       </c>
       <c r="X81" s="64" t="s">
         <v>54</v>
@@ -24246,13 +24288,13 @@
       </c>
       <c r="AB81" s="63"/>
       <c r="AC81" s="13" t="s">
-        <v>890</v>
+        <v>892</v>
       </c>
       <c r="AD81" s="13" t="s">
-        <v>843</v>
+        <v>846</v>
       </c>
       <c r="AE81" s="13" t="s">
-        <v>844</v>
+        <v>847</v>
       </c>
       <c r="AF81" s="13"/>
       <c r="AG81" s="13"/>
@@ -24261,11 +24303,13 @@
       <c r="AJ81" s="71"/>
       <c r="AK81" s="71"/>
     </row>
-    <row r="82" spans="1:37" ht="54" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="82" spans="1:37" ht="54" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A82" s="62" t="s">
-        <v>891</v>
-      </c>
-      <c r="B82" s="13"/>
+        <v>893</v>
+      </c>
+      <c r="B82" s="13" t="s">
+        <v>894</v>
+      </c>
       <c r="C82" s="64"/>
       <c r="D82" s="78">
         <v>2954915</v>
@@ -24283,34 +24327,34 @@
         <v>　</v>
       </c>
       <c r="H82" s="72" t="s">
-        <v>892</v>
+        <v>895</v>
       </c>
       <c r="I82" s="13" t="s">
-        <v>893</v>
+        <v>896</v>
       </c>
       <c r="J82" s="66" t="s">
         <v>44</v>
       </c>
       <c r="K82" s="93" t="s">
-        <v>894</v>
+        <v>897</v>
       </c>
       <c r="L82" s="13" t="s">
-        <v>895</v>
+        <v>898</v>
       </c>
       <c r="M82" s="13" t="s">
-        <v>896</v>
+        <v>899</v>
       </c>
       <c r="N82" s="73" t="s">
-        <v>897</v>
+        <v>900</v>
       </c>
       <c r="O82" s="73" t="s">
-        <v>898</v>
+        <v>901</v>
       </c>
       <c r="P82" s="13" t="s">
-        <v>899</v>
+        <v>902</v>
       </c>
       <c r="Q82" s="66" t="s">
-        <v>900</v>
+        <v>903</v>
       </c>
       <c r="R82" s="68">
         <v>41794</v>
@@ -24322,13 +24366,13 @@
         <v>41852</v>
       </c>
       <c r="U82" s="64" t="s">
-        <v>867</v>
+        <v>871</v>
       </c>
       <c r="V82" s="69">
-        <v>44044</v>
+        <v>46204</v>
       </c>
       <c r="W82" s="70" t="s">
-        <v>901</v>
+        <v>872</v>
       </c>
       <c r="X82" s="64" t="s">
         <v>54</v>
@@ -24344,7 +24388,7 @@
       </c>
       <c r="AB82" s="63"/>
       <c r="AC82" s="13" t="s">
-        <v>902</v>
+        <v>904</v>
       </c>
       <c r="AD82" s="62"/>
       <c r="AE82" s="13"/>
@@ -24355,9 +24399,9 @@
       <c r="AJ82" s="71"/>
       <c r="AK82" s="71"/>
     </row>
-    <row r="83" spans="1:37" ht="67.5" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="83" spans="1:37" ht="67.5" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A83" s="62" t="s">
-        <v>903</v>
+        <v>905</v>
       </c>
       <c r="B83" s="13"/>
       <c r="C83" s="64"/>
@@ -24377,7 +24421,7 @@
         <v>　</v>
       </c>
       <c r="H83" s="72" t="s">
-        <v>904</v>
+        <v>906</v>
       </c>
       <c r="I83" s="82" t="s">
         <v>283</v>
@@ -24386,13 +24430,13 @@
         <v>44</v>
       </c>
       <c r="K83" s="13" t="s">
-        <v>905</v>
+        <v>907</v>
       </c>
       <c r="L83" s="13" t="s">
-        <v>906</v>
+        <v>908</v>
       </c>
       <c r="M83" s="13" t="s">
-        <v>907</v>
+        <v>909</v>
       </c>
       <c r="N83" s="73" t="s">
         <v>523</v>
@@ -24401,10 +24445,10 @@
         <v>524</v>
       </c>
       <c r="P83" s="13" t="s">
-        <v>908</v>
+        <v>910</v>
       </c>
       <c r="Q83" s="66" t="s">
-        <v>909</v>
+        <v>911</v>
       </c>
       <c r="R83" s="68">
         <v>39904</v>
@@ -24416,13 +24460,13 @@
         <v>39965</v>
       </c>
       <c r="U83" s="64" t="s">
-        <v>910</v>
+        <v>912</v>
       </c>
       <c r="V83" s="69">
         <v>44348</v>
       </c>
       <c r="W83" s="64" t="s">
-        <v>911</v>
+        <v>913</v>
       </c>
       <c r="X83" s="77" t="s">
         <v>54</v>
@@ -24438,7 +24482,7 @@
       </c>
       <c r="AB83" s="63"/>
       <c r="AC83" s="13" t="s">
-        <v>912</v>
+        <v>914</v>
       </c>
       <c r="AD83" s="13" t="s">
         <v>529</v>
@@ -24451,9 +24495,9 @@
       <c r="AJ83" s="71"/>
       <c r="AK83" s="71"/>
     </row>
-    <row r="84" spans="1:37" ht="54" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="84" spans="1:37" ht="54" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A84" s="62" t="s">
-        <v>913</v>
+        <v>915</v>
       </c>
       <c r="B84" s="64"/>
       <c r="C84" s="64"/>
@@ -24473,34 +24517,34 @@
         <v>　</v>
       </c>
       <c r="H84" s="72" t="s">
-        <v>914</v>
+        <v>916</v>
       </c>
       <c r="I84" s="82" t="s">
-        <v>915</v>
+        <v>917</v>
       </c>
       <c r="J84" s="66" t="s">
         <v>44</v>
       </c>
       <c r="K84" s="13" t="s">
-        <v>916</v>
+        <v>918</v>
       </c>
       <c r="L84" s="13" t="s">
-        <v>917</v>
+        <v>919</v>
       </c>
       <c r="M84" s="13" t="s">
-        <v>907</v>
+        <v>909</v>
       </c>
       <c r="N84" s="73" t="s">
-        <v>918</v>
+        <v>920</v>
       </c>
       <c r="O84" s="73" t="s">
         <v>524</v>
       </c>
       <c r="P84" s="13" t="s">
-        <v>919</v>
+        <v>921</v>
       </c>
       <c r="Q84" s="66" t="s">
-        <v>920</v>
+        <v>922</v>
       </c>
       <c r="R84" s="68">
         <v>42501</v>
@@ -24512,13 +24556,13 @@
         <v>42552</v>
       </c>
       <c r="U84" s="64" t="s">
-        <v>921</v>
+        <v>923</v>
       </c>
       <c r="V84" s="90">
         <v>44743</v>
       </c>
       <c r="W84" s="89" t="s">
-        <v>922</v>
+        <v>924</v>
       </c>
       <c r="X84" s="77" t="s">
         <v>54</v>
@@ -24543,9 +24587,9 @@
       <c r="AJ84" s="71"/>
       <c r="AK84" s="71"/>
     </row>
-    <row r="85" spans="1:37" ht="54" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="85" spans="1:37" ht="54" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A85" s="62" t="s">
-        <v>923</v>
+        <v>925</v>
       </c>
       <c r="B85" s="13"/>
       <c r="C85" s="64"/>
@@ -24565,34 +24609,34 @@
         <v>　</v>
       </c>
       <c r="H85" s="72" t="s">
-        <v>924</v>
+        <v>926</v>
       </c>
       <c r="I85" s="82" t="s">
-        <v>654</v>
+        <v>656</v>
       </c>
       <c r="J85" s="66" t="s">
         <v>44</v>
       </c>
       <c r="K85" s="13" t="s">
-        <v>925</v>
+        <v>927</v>
       </c>
       <c r="L85" s="13" t="s">
-        <v>926</v>
+        <v>928</v>
       </c>
       <c r="M85" s="13" t="s">
-        <v>927</v>
+        <v>929</v>
       </c>
       <c r="N85" s="73" t="s">
-        <v>928</v>
+        <v>930</v>
       </c>
       <c r="O85" s="73" t="s">
-        <v>929</v>
+        <v>931</v>
       </c>
       <c r="P85" s="13" t="s">
-        <v>930</v>
+        <v>932</v>
       </c>
       <c r="Q85" s="13" t="s">
-        <v>931</v>
+        <v>933</v>
       </c>
       <c r="R85" s="68">
         <v>42580</v>
@@ -24604,13 +24648,13 @@
         <v>42644</v>
       </c>
       <c r="U85" s="64" t="s">
-        <v>932</v>
+        <v>934</v>
       </c>
       <c r="V85" s="68">
         <v>44835</v>
       </c>
       <c r="W85" s="89" t="s">
-        <v>933</v>
+        <v>935</v>
       </c>
       <c r="X85" s="77" t="s">
         <v>54</v>
@@ -24626,7 +24670,7 @@
       </c>
       <c r="AB85" s="63"/>
       <c r="AC85" s="13" t="s">
-        <v>934</v>
+        <v>936</v>
       </c>
       <c r="AD85" s="13"/>
       <c r="AE85" s="62"/>
@@ -24637,11 +24681,13 @@
       <c r="AJ85" s="71"/>
       <c r="AK85" s="71"/>
     </row>
-    <row r="86" spans="1:37" ht="45" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="86" spans="1:37" ht="45" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A86" s="62" t="s">
-        <v>935</v>
-      </c>
-      <c r="B86" s="13"/>
+        <v>937</v>
+      </c>
+      <c r="B86" s="13" t="s">
+        <v>677</v>
+      </c>
       <c r="C86" s="64"/>
       <c r="D86" s="65">
         <v>2955219</v>
@@ -24659,33 +24705,35 @@
         <v>　</v>
       </c>
       <c r="H86" s="72" t="s">
-        <v>936</v>
+        <v>938</v>
       </c>
       <c r="I86" s="82" t="s">
-        <v>937</v>
+        <v>939</v>
       </c>
       <c r="J86" s="66" t="s">
         <v>44</v>
       </c>
       <c r="K86" s="13" t="s">
-        <v>938</v>
+        <v>940</v>
       </c>
       <c r="L86" s="13" t="s">
-        <v>939</v>
+        <v>941</v>
       </c>
       <c r="M86" s="13" t="s">
-        <v>940</v>
+        <v>942</v>
       </c>
       <c r="N86" s="73" t="s">
-        <v>941</v>
+        <v>943</v>
       </c>
       <c r="O86" s="73" t="s">
         <v>548</v>
       </c>
       <c r="P86" s="13" t="s">
-        <v>942</v>
-      </c>
-      <c r="Q86" s="66"/>
+        <v>944</v>
+      </c>
+      <c r="Q86" s="87" t="s">
+        <v>945</v>
+      </c>
       <c r="R86" s="68">
         <v>42769</v>
       </c>
@@ -24696,13 +24744,13 @@
         <v>42826</v>
       </c>
       <c r="U86" s="64" t="s">
-        <v>943</v>
+        <v>946</v>
       </c>
       <c r="V86" s="69">
         <v>45017</v>
       </c>
       <c r="W86" s="64" t="s">
-        <v>944</v>
+        <v>947</v>
       </c>
       <c r="X86" s="77" t="s">
         <v>54</v>
@@ -24729,9 +24777,9 @@
       <c r="AJ86" s="71"/>
       <c r="AK86" s="71"/>
     </row>
-    <row r="87" spans="1:37" ht="40.5" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="87" spans="1:37" ht="40.5" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A87" s="62" t="s">
-        <v>945</v>
+        <v>948</v>
       </c>
       <c r="B87" s="13"/>
       <c r="C87" s="64"/>
@@ -24751,34 +24799,34 @@
         <v>　</v>
       </c>
       <c r="H87" s="72" t="s">
-        <v>946</v>
+        <v>949</v>
       </c>
       <c r="I87" s="66" t="s">
-        <v>947</v>
+        <v>950</v>
       </c>
       <c r="J87" s="66" t="s">
         <v>44</v>
       </c>
       <c r="K87" s="93" t="s">
-        <v>948</v>
+        <v>951</v>
       </c>
       <c r="L87" s="94" t="s">
-        <v>949</v>
+        <v>952</v>
       </c>
       <c r="M87" s="13" t="s">
-        <v>950</v>
+        <v>953</v>
       </c>
       <c r="N87" s="73" t="s">
-        <v>951</v>
+        <v>954</v>
       </c>
       <c r="O87" s="73" t="s">
-        <v>952</v>
+        <v>955</v>
       </c>
       <c r="P87" s="13" t="s">
-        <v>953</v>
+        <v>956</v>
       </c>
       <c r="Q87" s="66" t="s">
-        <v>954</v>
+        <v>957</v>
       </c>
       <c r="R87" s="69">
         <v>43147</v>
@@ -24790,13 +24838,13 @@
         <v>43191</v>
       </c>
       <c r="U87" s="64" t="s">
-        <v>955</v>
+        <v>958</v>
       </c>
       <c r="V87" s="69">
         <v>45383</v>
       </c>
       <c r="W87" s="70" t="s">
-        <v>956</v>
+        <v>959</v>
       </c>
       <c r="X87" s="77" t="s">
         <v>54</v>
@@ -24812,7 +24860,7 @@
       </c>
       <c r="AB87" s="63"/>
       <c r="AC87" s="66" t="s">
-        <v>957</v>
+        <v>960</v>
       </c>
       <c r="AD87" s="62"/>
       <c r="AE87" s="13"/>
@@ -24823,9 +24871,9 @@
       <c r="AJ87" s="71"/>
       <c r="AK87" s="71"/>
     </row>
-    <row r="88" spans="1:37" ht="54" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="88" spans="1:37" ht="54" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A88" s="62" t="s">
-        <v>958</v>
+        <v>961</v>
       </c>
       <c r="B88" s="13"/>
       <c r="C88" s="64"/>
@@ -24845,7 +24893,7 @@
         <v>　</v>
       </c>
       <c r="H88" s="72" t="s">
-        <v>959</v>
+        <v>962</v>
       </c>
       <c r="I88" s="66" t="s">
         <v>144</v>
@@ -24854,25 +24902,25 @@
         <v>44</v>
       </c>
       <c r="K88" s="93" t="s">
-        <v>960</v>
+        <v>963</v>
       </c>
       <c r="L88" s="94" t="s">
-        <v>961</v>
+        <v>964</v>
       </c>
       <c r="M88" s="13" t="s">
-        <v>962</v>
+        <v>965</v>
       </c>
       <c r="N88" s="73" t="s">
-        <v>963</v>
+        <v>966</v>
       </c>
       <c r="O88" s="73" t="s">
-        <v>964</v>
+        <v>967</v>
       </c>
       <c r="P88" s="13" t="s">
-        <v>965</v>
+        <v>968</v>
       </c>
       <c r="Q88" s="66" t="s">
-        <v>966</v>
+        <v>969</v>
       </c>
       <c r="R88" s="68">
         <v>43117</v>
@@ -24884,13 +24932,13 @@
         <v>43191</v>
       </c>
       <c r="U88" s="64" t="s">
-        <v>967</v>
+        <v>970</v>
       </c>
       <c r="V88" s="69">
         <v>45383</v>
       </c>
       <c r="W88" s="70" t="s">
-        <v>968</v>
+        <v>971</v>
       </c>
       <c r="X88" s="77" t="s">
         <v>54</v>
@@ -24906,7 +24954,7 @@
       </c>
       <c r="AB88" s="63"/>
       <c r="AC88" s="13" t="s">
-        <v>969</v>
+        <v>972</v>
       </c>
       <c r="AD88" s="13"/>
       <c r="AE88" s="13"/>
@@ -24917,9 +24965,9 @@
       <c r="AJ88" s="71"/>
       <c r="AK88" s="71"/>
     </row>
-    <row r="89" spans="1:37" ht="39" x14ac:dyDescent="0.55000000000000004">
+    <row r="89" spans="1:37" ht="40.5" x14ac:dyDescent="0.15">
       <c r="A89" s="62" t="s">
-        <v>970</v>
+        <v>973</v>
       </c>
       <c r="B89" s="13"/>
       <c r="C89" s="64"/>
@@ -24939,34 +24987,34 @@
         <v>　</v>
       </c>
       <c r="H89" s="72" t="s">
-        <v>971</v>
+        <v>974</v>
       </c>
       <c r="I89" s="82" t="s">
-        <v>972</v>
+        <v>975</v>
       </c>
       <c r="J89" s="66" t="s">
         <v>44</v>
       </c>
       <c r="K89" s="13" t="s">
-        <v>973</v>
+        <v>976</v>
       </c>
       <c r="L89" s="13" t="s">
-        <v>974</v>
+        <v>977</v>
       </c>
       <c r="M89" s="13" t="s">
-        <v>975</v>
+        <v>978</v>
       </c>
       <c r="N89" s="73" t="s">
-        <v>976</v>
+        <v>979</v>
       </c>
       <c r="O89" s="73" t="s">
-        <v>977</v>
+        <v>980</v>
       </c>
       <c r="P89" s="13" t="s">
-        <v>978</v>
+        <v>981</v>
       </c>
       <c r="Q89" s="66" t="s">
-        <v>979</v>
+        <v>982</v>
       </c>
       <c r="R89" s="68">
         <v>43363</v>
@@ -24978,13 +25026,13 @@
         <v>43466</v>
       </c>
       <c r="U89" s="64" t="s">
-        <v>980</v>
+        <v>983</v>
       </c>
       <c r="V89" s="69">
         <v>45658</v>
       </c>
       <c r="W89" s="64" t="s">
-        <v>981</v>
+        <v>984</v>
       </c>
       <c r="X89" s="77" t="s">
         <v>54</v>
@@ -25009,9 +25057,9 @@
       <c r="AJ89" s="71"/>
       <c r="AK89" s="71"/>
     </row>
-    <row r="90" spans="1:37" ht="39" x14ac:dyDescent="0.55000000000000004">
+    <row r="90" spans="1:37" ht="40.5" x14ac:dyDescent="0.15">
       <c r="A90" s="62" t="s">
-        <v>982</v>
+        <v>985</v>
       </c>
       <c r="B90" s="13"/>
       <c r="C90" s="64"/>
@@ -25031,34 +25079,34 @@
         <v>　</v>
       </c>
       <c r="H90" s="72" t="s">
-        <v>983</v>
+        <v>986</v>
       </c>
       <c r="I90" s="66" t="s">
-        <v>984</v>
+        <v>987</v>
       </c>
       <c r="J90" s="66" t="s">
         <v>44</v>
       </c>
       <c r="K90" s="93" t="s">
-        <v>985</v>
+        <v>988</v>
       </c>
       <c r="L90" s="94" t="s">
-        <v>986</v>
+        <v>989</v>
       </c>
       <c r="M90" s="13" t="s">
+        <v>990</v>
+      </c>
+      <c r="N90" s="73" t="s">
         <v>987</v>
       </c>
-      <c r="N90" s="73" t="s">
-        <v>984</v>
-      </c>
       <c r="O90" s="73" t="s">
-        <v>988</v>
+        <v>991</v>
       </c>
       <c r="P90" s="13" t="s">
-        <v>989</v>
+        <v>992</v>
       </c>
       <c r="Q90" s="77" t="s">
-        <v>990</v>
+        <v>993</v>
       </c>
       <c r="R90" s="68">
         <v>43388</v>
@@ -25070,13 +25118,13 @@
         <v>43466</v>
       </c>
       <c r="U90" s="64" t="s">
-        <v>991</v>
+        <v>994</v>
       </c>
       <c r="V90" s="69">
         <v>45658</v>
       </c>
       <c r="W90" s="64" t="s">
-        <v>992</v>
+        <v>995</v>
       </c>
       <c r="X90" s="77" t="s">
         <v>54</v>
@@ -25101,9 +25149,9 @@
       <c r="AJ90" s="71"/>
       <c r="AK90" s="71"/>
     </row>
-    <row r="91" spans="1:37" ht="73.5" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="91" spans="1:37" ht="73.5" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A91" s="62" t="s">
-        <v>993</v>
+        <v>996</v>
       </c>
       <c r="B91" s="63"/>
       <c r="C91" s="64"/>
@@ -25123,31 +25171,31 @@
         <v>　</v>
       </c>
       <c r="H91" s="72" t="s">
-        <v>994</v>
+        <v>997</v>
       </c>
       <c r="I91" s="66" t="s">
-        <v>995</v>
+        <v>998</v>
       </c>
       <c r="J91" s="66" t="s">
         <v>44</v>
       </c>
       <c r="K91" s="93" t="s">
-        <v>996</v>
+        <v>999</v>
       </c>
       <c r="L91" s="94" t="s">
-        <v>997</v>
+        <v>1000</v>
       </c>
       <c r="M91" s="13" t="s">
-        <v>998</v>
+        <v>1001</v>
       </c>
       <c r="N91" s="73" t="s">
-        <v>999</v>
+        <v>1002</v>
       </c>
       <c r="O91" s="73" t="s">
-        <v>1000</v>
+        <v>1003</v>
       </c>
       <c r="P91" s="13" t="s">
-        <v>1001</v>
+        <v>1004</v>
       </c>
       <c r="Q91" s="66"/>
       <c r="R91" s="68">
@@ -25160,13 +25208,13 @@
         <v>43466</v>
       </c>
       <c r="U91" s="64" t="s">
-        <v>1002</v>
+        <v>1005</v>
       </c>
       <c r="V91" s="69">
         <v>45658</v>
       </c>
       <c r="W91" s="64" t="s">
-        <v>1003</v>
+        <v>1006</v>
       </c>
       <c r="X91" s="77" t="s">
         <v>54</v>
@@ -25182,10 +25230,10 @@
       </c>
       <c r="AB91" s="63"/>
       <c r="AC91" s="13" t="s">
-        <v>1004</v>
+        <v>1007</v>
       </c>
       <c r="AD91" s="66" t="s">
-        <v>1005</v>
+        <v>1008</v>
       </c>
       <c r="AE91" s="13"/>
       <c r="AF91" s="13"/>
@@ -25195,9 +25243,9 @@
       <c r="AJ91" s="71"/>
       <c r="AK91" s="71"/>
     </row>
-    <row r="92" spans="1:37" ht="54" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="92" spans="1:37" ht="54" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A92" s="62" t="s">
-        <v>1006</v>
+        <v>1009</v>
       </c>
       <c r="B92" s="13"/>
       <c r="C92" s="64"/>
@@ -25217,34 +25265,34 @@
         <v>　</v>
       </c>
       <c r="H92" s="72" t="s">
-        <v>1007</v>
+        <v>1010</v>
       </c>
       <c r="I92" s="66" t="s">
-        <v>1008</v>
+        <v>1011</v>
       </c>
       <c r="J92" s="66" t="s">
         <v>44</v>
       </c>
       <c r="K92" s="93" t="s">
-        <v>1009</v>
+        <v>1012</v>
       </c>
       <c r="L92" s="94" t="s">
-        <v>1010</v>
+        <v>1013</v>
       </c>
       <c r="M92" s="13" t="s">
-        <v>1011</v>
+        <v>1014</v>
       </c>
       <c r="N92" s="73" t="s">
-        <v>1012</v>
+        <v>1015</v>
       </c>
       <c r="O92" s="73" t="s">
-        <v>1013</v>
+        <v>1016</v>
       </c>
       <c r="P92" s="13" t="s">
-        <v>1014</v>
+        <v>1017</v>
       </c>
       <c r="Q92" s="66" t="s">
-        <v>1015</v>
+        <v>1018</v>
       </c>
       <c r="R92" s="68">
         <v>43444</v>
@@ -25256,13 +25304,13 @@
         <v>43556</v>
       </c>
       <c r="U92" s="64" t="s">
-        <v>1016</v>
+        <v>1019</v>
       </c>
       <c r="V92" s="95">
         <v>45748</v>
       </c>
       <c r="W92" s="70" t="s">
-        <v>1017</v>
+        <v>1020</v>
       </c>
       <c r="X92" s="77" t="s">
         <v>54</v>
@@ -25278,7 +25326,7 @@
       </c>
       <c r="AB92" s="63"/>
       <c r="AC92" s="13" t="s">
-        <v>1018</v>
+        <v>1021</v>
       </c>
       <c r="AD92" s="62"/>
       <c r="AE92" s="13"/>
@@ -25289,9 +25337,9 @@
       <c r="AJ92" s="71"/>
       <c r="AK92" s="71"/>
     </row>
-    <row r="93" spans="1:37" ht="54" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="93" spans="1:37" ht="54" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A93" s="62" t="s">
-        <v>1019</v>
+        <v>1022</v>
       </c>
       <c r="B93" s="13"/>
       <c r="C93" s="64"/>
@@ -25311,46 +25359,46 @@
         <v>　</v>
       </c>
       <c r="H93" s="72" t="s">
-        <v>1020</v>
+        <v>1023</v>
       </c>
       <c r="I93" s="66" t="s">
-        <v>1021</v>
+        <v>1024</v>
       </c>
       <c r="J93" s="66" t="s">
         <v>44</v>
       </c>
       <c r="K93" s="93" t="s">
-        <v>1022</v>
+        <v>1025</v>
       </c>
       <c r="L93" s="94" t="s">
-        <v>1023</v>
+        <v>1026</v>
       </c>
       <c r="M93" s="13" t="s">
-        <v>1024</v>
+        <v>1027</v>
       </c>
       <c r="N93" s="73" t="s">
-        <v>941</v>
+        <v>943</v>
       </c>
       <c r="O93" s="73" t="s">
         <v>548</v>
       </c>
       <c r="P93" s="13" t="s">
-        <v>1025</v>
+        <v>1028</v>
       </c>
       <c r="Q93" s="66" t="s">
-        <v>1026</v>
+        <v>1029</v>
       </c>
       <c r="R93" s="68">
         <v>43572</v>
       </c>
       <c r="S93" s="68" t="s">
-        <v>1027</v>
+        <v>1030</v>
       </c>
       <c r="T93" s="64" t="s">
-        <v>1027</v>
+        <v>1030</v>
       </c>
       <c r="U93" s="64" t="s">
-        <v>1028</v>
+        <v>1031</v>
       </c>
       <c r="V93" s="95">
         <v>45839</v>
@@ -25383,9 +25431,9 @@
       <c r="AJ93" s="71"/>
       <c r="AK93" s="71"/>
     </row>
-    <row r="94" spans="1:37" ht="54" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="94" spans="1:37" ht="54" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A94" s="62" t="s">
-        <v>1029</v>
+        <v>1032</v>
       </c>
       <c r="B94" s="13"/>
       <c r="C94" s="64" t="s">
@@ -25407,46 +25455,46 @@
         <v>　</v>
       </c>
       <c r="H94" s="85" t="s">
-        <v>1030</v>
+        <v>1033</v>
       </c>
       <c r="I94" s="66" t="s">
-        <v>598</v>
+        <v>600</v>
       </c>
       <c r="J94" s="66" t="s">
         <v>44</v>
       </c>
       <c r="K94" s="93" t="s">
-        <v>1031</v>
+        <v>1034</v>
       </c>
       <c r="L94" s="94" t="s">
-        <v>1032</v>
+        <v>1035</v>
       </c>
       <c r="M94" s="13" t="s">
-        <v>615</v>
+        <v>617</v>
       </c>
       <c r="N94" s="73" t="s">
-        <v>670</v>
+        <v>672</v>
       </c>
       <c r="O94" s="73" t="s">
-        <v>671</v>
+        <v>673</v>
       </c>
       <c r="P94" s="13" t="s">
-        <v>1033</v>
+        <v>1036</v>
       </c>
       <c r="Q94" s="66" t="s">
-        <v>1034</v>
+        <v>1037</v>
       </c>
       <c r="R94" s="68">
         <v>43578</v>
       </c>
       <c r="S94" s="68" t="s">
-        <v>1035</v>
+        <v>1038</v>
       </c>
       <c r="T94" s="64" t="s">
-        <v>1027</v>
+        <v>1030</v>
       </c>
       <c r="U94" s="64" t="s">
-        <v>1036</v>
+        <v>1039</v>
       </c>
       <c r="V94" s="70"/>
       <c r="W94" s="70"/>
@@ -25466,7 +25514,7 @@
         <v>50112</v>
       </c>
       <c r="AC94" s="13" t="s">
-        <v>1037</v>
+        <v>1040</v>
       </c>
       <c r="AD94" s="62"/>
       <c r="AE94" s="13"/>
@@ -25477,9 +25525,9 @@
       <c r="AJ94" s="71"/>
       <c r="AK94" s="71"/>
     </row>
-    <row r="95" spans="1:37" ht="27" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="95" spans="1:37" ht="27" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A95" s="62" t="s">
-        <v>1038</v>
+        <v>1041</v>
       </c>
       <c r="B95" s="13"/>
       <c r="C95" s="64"/>
@@ -25499,31 +25547,31 @@
         <v>二重</v>
       </c>
       <c r="H95" s="72" t="s">
-        <v>1030</v>
+        <v>1033</v>
       </c>
       <c r="I95" s="66" t="s">
-        <v>598</v>
+        <v>600</v>
       </c>
       <c r="J95" s="66" t="s">
         <v>44</v>
       </c>
       <c r="K95" s="93" t="s">
-        <v>1039</v>
+        <v>1042</v>
       </c>
       <c r="L95" s="94" t="s">
-        <v>1040</v>
+        <v>1043</v>
       </c>
       <c r="M95" s="13" t="s">
-        <v>615</v>
+        <v>617</v>
       </c>
       <c r="N95" s="73" t="s">
-        <v>616</v>
+        <v>618</v>
       </c>
       <c r="O95" s="73" t="s">
-        <v>617</v>
+        <v>619</v>
       </c>
       <c r="P95" s="13" t="s">
-        <v>1041</v>
+        <v>1044</v>
       </c>
       <c r="Q95" s="66"/>
       <c r="R95" s="68">
@@ -25536,7 +25584,7 @@
         <v>44378</v>
       </c>
       <c r="U95" s="64" t="s">
-        <v>1042</v>
+        <v>1045</v>
       </c>
       <c r="V95" s="70"/>
       <c r="W95" s="70"/>
@@ -25554,13 +25602,13 @@
       </c>
       <c r="AB95" s="63"/>
       <c r="AC95" s="13" t="s">
-        <v>627</v>
+        <v>629</v>
       </c>
       <c r="AD95" s="13" t="s">
-        <v>628</v>
+        <v>630</v>
       </c>
       <c r="AE95" s="13" t="s">
-        <v>629</v>
+        <v>631</v>
       </c>
       <c r="AF95" s="13"/>
       <c r="AG95" s="13"/>
@@ -25569,9 +25617,9 @@
       <c r="AJ95" s="71"/>
       <c r="AK95" s="71"/>
     </row>
-    <row r="96" spans="1:37" ht="52" x14ac:dyDescent="0.55000000000000004">
+    <row r="96" spans="1:37" ht="54" x14ac:dyDescent="0.15">
       <c r="A96" s="62" t="s">
-        <v>1043</v>
+        <v>1046</v>
       </c>
       <c r="B96" s="13"/>
       <c r="C96" s="64"/>
@@ -25591,34 +25639,34 @@
         <v>　</v>
       </c>
       <c r="H96" s="72" t="s">
-        <v>1044</v>
+        <v>1047</v>
       </c>
       <c r="I96" s="66" t="s">
-        <v>1045</v>
+        <v>1048</v>
       </c>
       <c r="J96" s="66" t="s">
         <v>44</v>
       </c>
       <c r="K96" s="93" t="s">
-        <v>1046</v>
+        <v>1049</v>
       </c>
       <c r="L96" s="94" t="s">
-        <v>1047</v>
+        <v>1050</v>
       </c>
       <c r="M96" s="13" t="s">
-        <v>940</v>
+        <v>942</v>
       </c>
       <c r="N96" s="73" t="s">
-        <v>941</v>
+        <v>943</v>
       </c>
       <c r="O96" s="73" t="s">
         <v>548</v>
       </c>
       <c r="P96" s="13" t="s">
-        <v>1048</v>
+        <v>1051</v>
       </c>
       <c r="Q96" s="13" t="s">
-        <v>1049</v>
+        <v>1052</v>
       </c>
       <c r="R96" s="68">
         <v>43867</v>
@@ -25630,7 +25678,7 @@
         <v>43922</v>
       </c>
       <c r="U96" s="64" t="s">
-        <v>1050</v>
+        <v>1053</v>
       </c>
       <c r="V96" s="74">
         <v>46113</v>
@@ -25663,11 +25711,13 @@
       <c r="AJ96" s="71"/>
       <c r="AK96" s="71"/>
     </row>
-    <row r="97" spans="1:37" ht="27" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="97" spans="1:37" ht="40.5" x14ac:dyDescent="0.15">
       <c r="A97" s="62" t="s">
-        <v>1051</v>
-      </c>
-      <c r="B97" s="13"/>
+        <v>1054</v>
+      </c>
+      <c r="B97" s="13" t="s">
+        <v>894</v>
+      </c>
       <c r="C97" s="64"/>
       <c r="D97" s="78">
         <v>2955615</v>
@@ -25685,33 +25735,35 @@
         <v>　</v>
       </c>
       <c r="H97" s="72" t="s">
-        <v>1052</v>
+        <v>1055</v>
       </c>
       <c r="I97" s="66" t="s">
-        <v>1053</v>
+        <v>1056</v>
       </c>
       <c r="J97" s="66" t="s">
         <v>44</v>
       </c>
       <c r="K97" s="93" t="s">
-        <v>1054</v>
+        <v>1057</v>
       </c>
       <c r="L97" s="94" t="s">
-        <v>1055</v>
+        <v>1058</v>
       </c>
       <c r="M97" s="13" t="s">
-        <v>1056</v>
+        <v>1059</v>
       </c>
       <c r="N97" s="73" t="s">
-        <v>1057</v>
+        <v>1060</v>
       </c>
       <c r="O97" s="73" t="s">
-        <v>898</v>
+        <v>901</v>
       </c>
       <c r="P97" s="13" t="s">
-        <v>1058</v>
-      </c>
-      <c r="Q97" s="66"/>
+        <v>1061</v>
+      </c>
+      <c r="Q97" s="66" t="s">
+        <v>1062</v>
+      </c>
       <c r="R97" s="68">
         <v>43949</v>
       </c>
@@ -25722,10 +25774,14 @@
         <v>44013</v>
       </c>
       <c r="U97" s="64" t="s">
-        <v>1059</v>
-      </c>
-      <c r="V97" s="70"/>
-      <c r="W97" s="70"/>
+        <v>1063</v>
+      </c>
+      <c r="V97" s="69">
+        <v>46204</v>
+      </c>
+      <c r="W97" s="70" t="s">
+        <v>872</v>
+      </c>
       <c r="X97" s="77" t="s">
         <v>54</v>
       </c>
@@ -25740,7 +25796,7 @@
       </c>
       <c r="AB97" s="63"/>
       <c r="AC97" s="13" t="s">
-        <v>902</v>
+        <v>904</v>
       </c>
       <c r="AD97" s="62"/>
       <c r="AE97" s="13"/>
@@ -25751,9 +25807,9 @@
       <c r="AJ97" s="71"/>
       <c r="AK97" s="71"/>
     </row>
-    <row r="98" spans="1:37" ht="27" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="98" spans="1:37" ht="27" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A98" s="62" t="s">
-        <v>1060</v>
+        <v>1064</v>
       </c>
       <c r="B98" s="96"/>
       <c r="C98" s="97"/>
@@ -25773,31 +25829,31 @@
         <v>　</v>
       </c>
       <c r="H98" s="98" t="s">
-        <v>1061</v>
+        <v>1065</v>
       </c>
       <c r="I98" s="87" t="s">
-        <v>1062</v>
+        <v>1066</v>
       </c>
       <c r="J98" s="66" t="s">
         <v>44</v>
       </c>
       <c r="K98" s="96" t="s">
-        <v>1063</v>
+        <v>1067</v>
       </c>
       <c r="L98" s="87" t="s">
-        <v>1064</v>
+        <v>1068</v>
       </c>
       <c r="M98" s="96" t="s">
-        <v>1065</v>
+        <v>1069</v>
       </c>
       <c r="N98" s="73" t="s">
-        <v>1066</v>
+        <v>1070</v>
       </c>
       <c r="O98" s="73" t="s">
-        <v>1067</v>
+        <v>1071</v>
       </c>
       <c r="P98" s="96" t="s">
-        <v>1068</v>
+        <v>1072</v>
       </c>
       <c r="Q98" s="96"/>
       <c r="R98" s="68">
@@ -25810,7 +25866,7 @@
         <v>44105</v>
       </c>
       <c r="U98" s="97" t="s">
-        <v>1069</v>
+        <v>1073</v>
       </c>
       <c r="V98" s="96"/>
       <c r="W98" s="96"/>
@@ -25837,9 +25893,9 @@
       <c r="AJ98" s="71"/>
       <c r="AK98" s="71"/>
     </row>
-    <row r="99" spans="1:37" ht="27" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="99" spans="1:37" ht="27" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A99" s="62" t="s">
-        <v>1070</v>
+        <v>1074</v>
       </c>
       <c r="B99" s="96"/>
       <c r="C99" s="97"/>
@@ -25859,31 +25915,31 @@
         <v>　</v>
       </c>
       <c r="H99" s="98" t="s">
-        <v>1071</v>
+        <v>1075</v>
       </c>
       <c r="I99" s="87" t="s">
-        <v>1072</v>
+        <v>1076</v>
       </c>
       <c r="J99" s="66" t="s">
         <v>44</v>
       </c>
       <c r="K99" s="96" t="s">
-        <v>1073</v>
+        <v>1077</v>
       </c>
       <c r="L99" s="87" t="s">
-        <v>1074</v>
+        <v>1078</v>
       </c>
       <c r="M99" s="96" t="s">
-        <v>1075</v>
+        <v>1079</v>
       </c>
       <c r="N99" s="73" t="s">
-        <v>1076</v>
+        <v>1080</v>
       </c>
       <c r="O99" s="73" t="s">
-        <v>1077</v>
+        <v>1081</v>
       </c>
       <c r="P99" s="96" t="s">
-        <v>1078</v>
+        <v>1082</v>
       </c>
       <c r="Q99" s="96"/>
       <c r="R99" s="100">
@@ -25896,7 +25952,7 @@
         <v>44105</v>
       </c>
       <c r="U99" s="97" t="s">
-        <v>1079</v>
+        <v>1083</v>
       </c>
       <c r="V99" s="96"/>
       <c r="W99" s="96"/>
@@ -25923,9 +25979,9 @@
       <c r="AJ99" s="71"/>
       <c r="AK99" s="71"/>
     </row>
-    <row r="100" spans="1:37" ht="40.5" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="100" spans="1:37" ht="40.5" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A100" s="62" t="s">
-        <v>1080</v>
+        <v>1084</v>
       </c>
       <c r="B100" s="13"/>
       <c r="C100" s="97"/>
@@ -25945,34 +26001,34 @@
         <v>　</v>
       </c>
       <c r="H100" s="98" t="s">
-        <v>1081</v>
+        <v>1085</v>
       </c>
       <c r="I100" s="87" t="s">
-        <v>667</v>
+        <v>669</v>
       </c>
       <c r="J100" s="66" t="s">
         <v>44</v>
       </c>
       <c r="K100" s="96" t="s">
-        <v>1082</v>
+        <v>1086</v>
       </c>
       <c r="L100" s="87" t="s">
-        <v>1083</v>
+        <v>1087</v>
       </c>
       <c r="M100" s="96" t="s">
-        <v>1084</v>
+        <v>1088</v>
       </c>
       <c r="N100" s="73" t="s">
-        <v>616</v>
+        <v>618</v>
       </c>
       <c r="O100" s="73" t="s">
-        <v>617</v>
+        <v>619</v>
       </c>
       <c r="P100" s="96" t="s">
-        <v>1085</v>
+        <v>1089</v>
       </c>
       <c r="Q100" s="87" t="s">
-        <v>1086</v>
+        <v>1090</v>
       </c>
       <c r="R100" s="99">
         <v>43987</v>
@@ -25984,7 +26040,7 @@
         <v>44105</v>
       </c>
       <c r="U100" s="97" t="s">
-        <v>1087</v>
+        <v>1091</v>
       </c>
       <c r="V100" s="96"/>
       <c r="W100" s="96"/>
@@ -26002,13 +26058,13 @@
       </c>
       <c r="AB100" s="96"/>
       <c r="AC100" s="13" t="s">
-        <v>627</v>
+        <v>629</v>
       </c>
       <c r="AD100" s="13" t="s">
-        <v>628</v>
+        <v>630</v>
       </c>
       <c r="AE100" s="87" t="s">
-        <v>1088</v>
+        <v>1092</v>
       </c>
       <c r="AF100" s="96"/>
       <c r="AG100" s="96"/>
@@ -26017,9 +26073,9 @@
       <c r="AJ100" s="71"/>
       <c r="AK100" s="71"/>
     </row>
-    <row r="101" spans="1:37" ht="27" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="101" spans="1:37" ht="27" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A101" s="62" t="s">
-        <v>1089</v>
+        <v>1093</v>
       </c>
       <c r="B101" s="13"/>
       <c r="C101" s="97"/>
@@ -26039,31 +26095,31 @@
         <v>　</v>
       </c>
       <c r="H101" s="98" t="s">
-        <v>1090</v>
+        <v>1094</v>
       </c>
       <c r="I101" s="87" t="s">
-        <v>1091</v>
+        <v>1095</v>
       </c>
       <c r="J101" s="66" t="s">
         <v>44</v>
       </c>
       <c r="K101" s="96" t="s">
-        <v>1092</v>
+        <v>1096</v>
       </c>
       <c r="L101" s="87" t="s">
-        <v>1093</v>
+        <v>1097</v>
       </c>
       <c r="M101" s="96" t="s">
-        <v>1094</v>
+        <v>1098</v>
       </c>
       <c r="N101" s="73" t="s">
-        <v>897</v>
+        <v>900</v>
       </c>
       <c r="O101" s="73" t="s">
-        <v>898</v>
+        <v>901</v>
       </c>
       <c r="P101" s="96" t="s">
-        <v>1095</v>
+        <v>1099</v>
       </c>
       <c r="Q101" s="96"/>
       <c r="R101" s="99">
@@ -26076,7 +26132,7 @@
         <v>44197</v>
       </c>
       <c r="U101" s="97" t="s">
-        <v>1096</v>
+        <v>1100</v>
       </c>
       <c r="V101" s="96"/>
       <c r="W101" s="96"/>
@@ -26094,7 +26150,7 @@
       </c>
       <c r="AB101" s="96"/>
       <c r="AC101" s="13" t="s">
-        <v>902</v>
+        <v>904</v>
       </c>
       <c r="AD101" s="96"/>
       <c r="AE101" s="96"/>
@@ -26105,11 +26161,13 @@
       <c r="AJ101" s="71"/>
       <c r="AK101" s="71"/>
     </row>
-    <row r="102" spans="1:37" ht="42" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="102" spans="1:37" ht="42" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A102" s="62" t="s">
-        <v>1097</v>
-      </c>
-      <c r="B102" s="13"/>
+        <v>1101</v>
+      </c>
+      <c r="B102" s="13" t="s">
+        <v>677</v>
+      </c>
       <c r="C102" s="97"/>
       <c r="D102" s="96">
         <v>2955755</v>
@@ -26127,33 +26185,35 @@
         <v>　</v>
       </c>
       <c r="H102" s="98" t="s">
-        <v>1098</v>
+        <v>1102</v>
       </c>
       <c r="I102" s="87" t="s">
-        <v>1099</v>
+        <v>1103</v>
       </c>
       <c r="J102" s="66" t="s">
         <v>44</v>
       </c>
       <c r="K102" s="96" t="s">
-        <v>1100</v>
+        <v>1104</v>
       </c>
       <c r="L102" s="87" t="s">
-        <v>1101</v>
+        <v>1105</v>
       </c>
       <c r="M102" s="87" t="s">
-        <v>1102</v>
+        <v>1106</v>
       </c>
       <c r="N102" s="73" t="s">
         <v>547</v>
       </c>
       <c r="O102" s="73" t="s">
-        <v>1103</v>
+        <v>1107</v>
       </c>
       <c r="P102" s="96" t="s">
-        <v>1104</v>
-      </c>
-      <c r="Q102" s="96"/>
+        <v>1108</v>
+      </c>
+      <c r="Q102" s="87" t="s">
+        <v>1109</v>
+      </c>
       <c r="R102" s="99">
         <v>44235</v>
       </c>
@@ -26164,7 +26224,7 @@
         <v>44287</v>
       </c>
       <c r="U102" s="97" t="s">
-        <v>1105</v>
+        <v>1110</v>
       </c>
       <c r="V102" s="96"/>
       <c r="W102" s="96"/>
@@ -26193,9 +26253,9 @@
       <c r="AJ102" s="71"/>
       <c r="AK102" s="71"/>
     </row>
-    <row r="103" spans="1:37" ht="27" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="103" spans="1:37" ht="27" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A103" s="62" t="s">
-        <v>1106</v>
+        <v>1111</v>
       </c>
       <c r="B103" s="96"/>
       <c r="C103" s="97"/>
@@ -26215,7 +26275,7 @@
         <v>　</v>
       </c>
       <c r="H103" s="98" t="s">
-        <v>1107</v>
+        <v>1112</v>
       </c>
       <c r="I103" s="87" t="s">
         <v>144</v>
@@ -26224,22 +26284,22 @@
         <v>44</v>
       </c>
       <c r="K103" s="96" t="s">
-        <v>1108</v>
+        <v>1113</v>
       </c>
       <c r="L103" s="87" t="s">
-        <v>1109</v>
+        <v>1114</v>
       </c>
       <c r="M103" s="96" t="s">
-        <v>1110</v>
+        <v>1115</v>
       </c>
       <c r="N103" s="73" t="s">
-        <v>1111</v>
+        <v>1116</v>
       </c>
       <c r="O103" s="73" t="s">
-        <v>1112</v>
+        <v>1117</v>
       </c>
       <c r="P103" s="96" t="s">
-        <v>1113</v>
+        <v>1118</v>
       </c>
       <c r="Q103" s="96"/>
       <c r="R103" s="99">
@@ -26252,7 +26312,7 @@
         <v>44287</v>
       </c>
       <c r="U103" s="97" t="s">
-        <v>1114</v>
+        <v>1119</v>
       </c>
       <c r="V103" s="96"/>
       <c r="W103" s="96"/>
@@ -26279,9 +26339,9 @@
       <c r="AJ103" s="71"/>
       <c r="AK103" s="71"/>
     </row>
-    <row r="104" spans="1:37" ht="45.75" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="104" spans="1:37" ht="45.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A104" s="62" t="s">
-        <v>1115</v>
+        <v>1120</v>
       </c>
       <c r="B104" s="13"/>
       <c r="C104" s="77"/>
@@ -26301,19 +26361,19 @@
         <v>　</v>
       </c>
       <c r="H104" s="98" t="s">
-        <v>1116</v>
+        <v>1121</v>
       </c>
       <c r="I104" s="87" t="s">
-        <v>1117</v>
+        <v>1122</v>
       </c>
       <c r="J104" s="66" t="s">
         <v>44</v>
       </c>
       <c r="K104" s="13" t="s">
-        <v>1118</v>
+        <v>1123</v>
       </c>
       <c r="L104" s="13" t="s">
-        <v>1119</v>
+        <v>1124</v>
       </c>
       <c r="M104" s="13" t="s">
         <v>546</v>
@@ -26325,10 +26385,10 @@
         <v>548</v>
       </c>
       <c r="P104" s="13" t="s">
-        <v>1120</v>
+        <v>1125</v>
       </c>
       <c r="Q104" s="13" t="s">
-        <v>1121</v>
+        <v>1126</v>
       </c>
       <c r="R104" s="74">
         <v>44403</v>
@@ -26340,7 +26400,7 @@
         <v>44470</v>
       </c>
       <c r="U104" s="97" t="s">
-        <v>1122</v>
+        <v>1127</v>
       </c>
       <c r="V104" s="101"/>
       <c r="W104" s="77"/>
@@ -26369,9 +26429,9 @@
       <c r="AJ104" s="71"/>
       <c r="AK104" s="71"/>
     </row>
-    <row r="105" spans="1:37" ht="48.75" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="105" spans="1:37" ht="48.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A105" s="62" t="s">
-        <v>1123</v>
+        <v>1128</v>
       </c>
       <c r="B105" s="87"/>
       <c r="C105" s="64" t="s">
@@ -26393,34 +26453,34 @@
         <v>　</v>
       </c>
       <c r="H105" s="98" t="s">
-        <v>1124</v>
+        <v>1129</v>
       </c>
       <c r="I105" s="87" t="s">
-        <v>972</v>
+        <v>975</v>
       </c>
       <c r="J105" s="66" t="s">
         <v>44</v>
       </c>
       <c r="K105" s="96" t="s">
-        <v>1125</v>
+        <v>1130</v>
       </c>
       <c r="L105" s="87" t="s">
-        <v>1126</v>
+        <v>1131</v>
       </c>
       <c r="M105" s="96" t="s">
-        <v>1127</v>
+        <v>1132</v>
       </c>
       <c r="N105" s="73" t="s">
-        <v>1128</v>
+        <v>1133</v>
       </c>
       <c r="O105" s="73" t="s">
-        <v>1129</v>
+        <v>1134</v>
       </c>
       <c r="P105" s="96" t="s">
-        <v>1130</v>
+        <v>1135</v>
       </c>
       <c r="Q105" s="87" t="s">
-        <v>1131</v>
+        <v>1136</v>
       </c>
       <c r="R105" s="99">
         <v>44466</v>
@@ -26432,7 +26492,7 @@
         <v>44562</v>
       </c>
       <c r="U105" s="97" t="s">
-        <v>1132</v>
+        <v>1137</v>
       </c>
       <c r="V105" s="96"/>
       <c r="W105" s="96"/>
@@ -26452,10 +26512,10 @@
         <v>50802</v>
       </c>
       <c r="AC105" s="13" t="s">
-        <v>1133</v>
+        <v>1138</v>
       </c>
       <c r="AD105" s="87" t="s">
-        <v>1134</v>
+        <v>1139</v>
       </c>
       <c r="AE105" s="96"/>
       <c r="AF105" s="96"/>
@@ -26465,9 +26525,9 @@
       <c r="AJ105" s="71"/>
       <c r="AK105" s="71"/>
     </row>
-    <row r="106" spans="1:37" ht="45" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="106" spans="1:37" ht="45" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A106" s="62" t="s">
-        <v>1135</v>
+        <v>1140</v>
       </c>
       <c r="B106" s="13"/>
       <c r="C106" s="97"/>
@@ -26487,34 +26547,34 @@
         <v>　</v>
       </c>
       <c r="H106" s="98" t="s">
-        <v>1136</v>
+        <v>1141</v>
       </c>
       <c r="I106" s="87" t="s">
-        <v>1045</v>
+        <v>1048</v>
       </c>
       <c r="J106" s="66" t="s">
         <v>44</v>
       </c>
       <c r="K106" s="96" t="s">
-        <v>1137</v>
+        <v>1142</v>
       </c>
       <c r="L106" s="87" t="s">
-        <v>1138</v>
+        <v>1143</v>
       </c>
       <c r="M106" s="96" t="s">
-        <v>1139</v>
+        <v>1144</v>
       </c>
       <c r="N106" s="73" t="s">
-        <v>897</v>
+        <v>900</v>
       </c>
       <c r="O106" s="73" t="s">
-        <v>898</v>
+        <v>901</v>
       </c>
       <c r="P106" s="96" t="s">
-        <v>1140</v>
+        <v>1145</v>
       </c>
       <c r="Q106" s="87" t="s">
-        <v>1141</v>
+        <v>1146</v>
       </c>
       <c r="R106" s="99">
         <v>44505</v>
@@ -26526,7 +26586,7 @@
         <v>44562</v>
       </c>
       <c r="U106" s="97" t="s">
-        <v>1142</v>
+        <v>1147</v>
       </c>
       <c r="V106" s="96"/>
       <c r="W106" s="96"/>
@@ -26544,7 +26604,7 @@
       </c>
       <c r="AB106" s="96"/>
       <c r="AC106" s="13" t="s">
-        <v>902</v>
+        <v>904</v>
       </c>
       <c r="AD106" s="96"/>
       <c r="AE106" s="96"/>
@@ -26555,9 +26615,9 @@
       <c r="AJ106" s="71"/>
       <c r="AK106" s="71"/>
     </row>
-    <row r="107" spans="1:37" ht="46.5" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="107" spans="1:37" ht="46.5" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A107" s="62" t="s">
-        <v>1143</v>
+        <v>1148</v>
       </c>
       <c r="B107" s="13"/>
       <c r="C107" s="97"/>
@@ -26577,19 +26637,19 @@
         <v>　</v>
       </c>
       <c r="H107" s="98" t="s">
-        <v>1144</v>
+        <v>1149</v>
       </c>
       <c r="I107" s="87" t="s">
-        <v>918</v>
+        <v>920</v>
       </c>
       <c r="J107" s="66" t="s">
         <v>44</v>
       </c>
       <c r="K107" s="96" t="s">
-        <v>1145</v>
+        <v>1150</v>
       </c>
       <c r="L107" s="87" t="s">
-        <v>1146</v>
+        <v>1151</v>
       </c>
       <c r="M107" s="13" t="s">
         <v>546</v>
@@ -26601,10 +26661,10 @@
         <v>548</v>
       </c>
       <c r="P107" s="96" t="s">
-        <v>1147</v>
+        <v>1152</v>
       </c>
       <c r="Q107" s="87" t="s">
-        <v>1148</v>
+        <v>1153</v>
       </c>
       <c r="R107" s="99">
         <v>44511</v>
@@ -26616,7 +26676,7 @@
         <v>44562</v>
       </c>
       <c r="U107" s="97" t="s">
-        <v>1149</v>
+        <v>1154</v>
       </c>
       <c r="V107" s="96"/>
       <c r="W107" s="96"/>
@@ -26645,9 +26705,9 @@
       <c r="AJ107" s="71"/>
       <c r="AK107" s="71"/>
     </row>
-    <row r="108" spans="1:37" ht="45.75" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="108" spans="1:37" ht="45.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A108" s="62" t="s">
-        <v>1150</v>
+        <v>1155</v>
       </c>
       <c r="B108" s="96"/>
       <c r="C108" s="97"/>
@@ -26667,34 +26727,34 @@
         <v>　</v>
       </c>
       <c r="H108" s="98" t="s">
-        <v>1151</v>
+        <v>1156</v>
       </c>
       <c r="I108" s="87" t="s">
-        <v>947</v>
+        <v>950</v>
       </c>
       <c r="J108" s="66" t="s">
         <v>44</v>
       </c>
       <c r="K108" s="96" t="s">
-        <v>1152</v>
+        <v>1157</v>
       </c>
       <c r="L108" s="87" t="s">
-        <v>1153</v>
+        <v>1158</v>
       </c>
       <c r="M108" s="96" t="s">
-        <v>1154</v>
+        <v>1159</v>
       </c>
       <c r="N108" s="73" t="s">
-        <v>1155</v>
+        <v>1160</v>
       </c>
       <c r="O108" s="73" t="s">
-        <v>1156</v>
+        <v>1161</v>
       </c>
       <c r="P108" s="96" t="s">
-        <v>1157</v>
+        <v>1162</v>
       </c>
       <c r="Q108" s="87" t="s">
-        <v>1158</v>
+        <v>1163</v>
       </c>
       <c r="R108" s="99">
         <v>44599</v>
@@ -26706,7 +26766,7 @@
         <v>44652</v>
       </c>
       <c r="U108" s="97" t="s">
-        <v>1159</v>
+        <v>1164</v>
       </c>
       <c r="V108" s="96"/>
       <c r="W108" s="96"/>
@@ -26733,9 +26793,9 @@
       <c r="AJ108" s="71"/>
       <c r="AK108" s="71"/>
     </row>
-    <row r="109" spans="1:37" ht="76.5" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="109" spans="1:37" ht="76.5" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A109" s="62" t="s">
-        <v>1160</v>
+        <v>1165</v>
       </c>
       <c r="B109" s="87"/>
       <c r="C109" s="97"/>
@@ -26755,31 +26815,31 @@
         <v>　</v>
       </c>
       <c r="H109" s="98" t="s">
-        <v>1161</v>
+        <v>1166</v>
       </c>
       <c r="I109" s="87" t="s">
-        <v>1162</v>
+        <v>1167</v>
       </c>
       <c r="J109" s="66" t="s">
         <v>44</v>
       </c>
       <c r="K109" s="96" t="s">
-        <v>1163</v>
+        <v>1168</v>
       </c>
       <c r="L109" s="87" t="s">
-        <v>1164</v>
+        <v>1169</v>
       </c>
       <c r="M109" s="96" t="s">
-        <v>1165</v>
+        <v>1170</v>
       </c>
       <c r="N109" s="73" t="s">
-        <v>1166</v>
+        <v>1171</v>
       </c>
       <c r="O109" s="73" t="s">
-        <v>1167</v>
+        <v>1172</v>
       </c>
       <c r="P109" s="96" t="s">
-        <v>1168</v>
+        <v>1173</v>
       </c>
       <c r="Q109" s="96"/>
       <c r="R109" s="99">
@@ -26792,7 +26852,7 @@
         <v>44652</v>
       </c>
       <c r="U109" s="97" t="s">
-        <v>1169</v>
+        <v>1174</v>
       </c>
       <c r="V109" s="96"/>
       <c r="W109" s="96"/>
@@ -26810,7 +26870,7 @@
       </c>
       <c r="AB109" s="96"/>
       <c r="AC109" s="13" t="s">
-        <v>1170</v>
+        <v>1175</v>
       </c>
       <c r="AD109" s="96"/>
       <c r="AE109" s="96"/>
@@ -26821,9 +26881,9 @@
       <c r="AJ109" s="71"/>
       <c r="AK109" s="71"/>
     </row>
-    <row r="110" spans="1:37" ht="45.75" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="110" spans="1:37" ht="45.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A110" s="62" t="s">
-        <v>1171</v>
+        <v>1176</v>
       </c>
       <c r="B110" s="96"/>
       <c r="C110" s="97"/>
@@ -26843,34 +26903,34 @@
         <v>　</v>
       </c>
       <c r="H110" s="98" t="s">
-        <v>1172</v>
+        <v>1177</v>
       </c>
       <c r="I110" s="87" t="s">
-        <v>1173</v>
+        <v>1178</v>
       </c>
       <c r="J110" s="66" t="s">
         <v>44</v>
       </c>
       <c r="K110" s="96" t="s">
-        <v>1174</v>
+        <v>1179</v>
       </c>
       <c r="L110" s="87" t="s">
-        <v>1175</v>
+        <v>1180</v>
       </c>
       <c r="M110" s="13" t="s">
-        <v>1176</v>
+        <v>1181</v>
       </c>
       <c r="N110" s="73" t="s">
-        <v>1177</v>
+        <v>1182</v>
       </c>
       <c r="O110" s="73" t="s">
-        <v>1178</v>
+        <v>1183</v>
       </c>
       <c r="P110" s="96" t="s">
-        <v>1179</v>
+        <v>1184</v>
       </c>
       <c r="Q110" s="87" t="s">
-        <v>1180</v>
+        <v>1185</v>
       </c>
       <c r="R110" s="99">
         <v>44581</v>
@@ -26882,7 +26942,7 @@
         <v>44652</v>
       </c>
       <c r="U110" s="97" t="s">
-        <v>1181</v>
+        <v>1186</v>
       </c>
       <c r="V110" s="96"/>
       <c r="W110" s="96"/>
@@ -26900,7 +26960,7 @@
       </c>
       <c r="AB110" s="96"/>
       <c r="AC110" s="87" t="s">
-        <v>1182</v>
+        <v>1187</v>
       </c>
       <c r="AD110" s="87"/>
       <c r="AE110" s="96"/>
@@ -26911,9 +26971,9 @@
       <c r="AJ110" s="71"/>
       <c r="AK110" s="71"/>
     </row>
-    <row r="111" spans="1:37" ht="39" x14ac:dyDescent="0.55000000000000004">
+    <row r="111" spans="1:37" ht="40.5" x14ac:dyDescent="0.15">
       <c r="A111" s="62" t="s">
-        <v>1183</v>
+        <v>1188</v>
       </c>
       <c r="B111" s="102"/>
       <c r="C111" s="97"/>
@@ -26933,7 +26993,7 @@
         <v>　</v>
       </c>
       <c r="H111" s="98" t="s">
-        <v>1184</v>
+        <v>1189</v>
       </c>
       <c r="I111" s="87" t="s">
         <v>323</v>
@@ -26942,22 +27002,22 @@
         <v>44</v>
       </c>
       <c r="K111" s="96" t="s">
-        <v>1185</v>
+        <v>1190</v>
       </c>
       <c r="L111" s="87" t="s">
-        <v>1186</v>
+        <v>1191</v>
       </c>
       <c r="M111" s="96" t="s">
-        <v>950</v>
+        <v>953</v>
       </c>
       <c r="N111" s="73" t="s">
-        <v>951</v>
+        <v>954</v>
       </c>
       <c r="O111" s="73" t="s">
-        <v>1187</v>
+        <v>1192</v>
       </c>
       <c r="P111" s="96" t="s">
-        <v>1188</v>
+        <v>1193</v>
       </c>
       <c r="Q111" s="96"/>
       <c r="R111" s="99">
@@ -26970,7 +27030,7 @@
         <v>44743</v>
       </c>
       <c r="U111" s="97" t="s">
-        <v>1189</v>
+        <v>1194</v>
       </c>
       <c r="V111" s="96"/>
       <c r="W111" s="96"/>
@@ -26988,10 +27048,10 @@
       </c>
       <c r="AB111" s="96"/>
       <c r="AC111" s="66" t="s">
-        <v>1190</v>
+        <v>1195</v>
       </c>
       <c r="AD111" s="96" t="s">
-        <v>1191</v>
+        <v>1196</v>
       </c>
       <c r="AE111" s="96"/>
       <c r="AF111" s="96"/>
@@ -27001,9 +27061,9 @@
       <c r="AJ111" s="71"/>
       <c r="AK111" s="71"/>
     </row>
-    <row r="112" spans="1:37" ht="49.5" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="112" spans="1:37" ht="49.5" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A112" s="62" t="s">
-        <v>1192</v>
+        <v>1197</v>
       </c>
       <c r="B112" s="102"/>
       <c r="C112" s="97"/>
@@ -27023,34 +27083,34 @@
         <v>　</v>
       </c>
       <c r="H112" s="98" t="s">
-        <v>1193</v>
+        <v>1198</v>
       </c>
       <c r="I112" s="87" t="s">
-        <v>1053</v>
+        <v>1056</v>
       </c>
       <c r="J112" s="66" t="s">
         <v>44</v>
       </c>
       <c r="K112" s="96" t="s">
-        <v>1194</v>
+        <v>1199</v>
       </c>
       <c r="L112" s="87" t="s">
-        <v>1195</v>
+        <v>1200</v>
       </c>
       <c r="M112" s="96" t="s">
-        <v>1196</v>
+        <v>1201</v>
       </c>
       <c r="N112" s="73" t="s">
-        <v>1197</v>
+        <v>1202</v>
       </c>
       <c r="O112" s="73" t="s">
-        <v>1198</v>
+        <v>1203</v>
       </c>
       <c r="P112" s="96" t="s">
-        <v>1199</v>
+        <v>1204</v>
       </c>
       <c r="Q112" s="87" t="s">
-        <v>1200</v>
+        <v>1205</v>
       </c>
       <c r="R112" s="99">
         <v>44687</v>
@@ -27062,7 +27122,7 @@
         <v>44743</v>
       </c>
       <c r="U112" s="97" t="s">
-        <v>1201</v>
+        <v>1206</v>
       </c>
       <c r="V112" s="96"/>
       <c r="W112" s="96"/>
@@ -27089,9 +27149,9 @@
       <c r="AJ112" s="71"/>
       <c r="AK112" s="71"/>
     </row>
-    <row r="113" spans="1:37" ht="40.5" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="113" spans="1:37" ht="40.5" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A113" s="96" t="s">
-        <v>1202</v>
+        <v>1207</v>
       </c>
       <c r="B113" s="13"/>
       <c r="C113" s="97"/>
@@ -27111,34 +27171,34 @@
         <v>　</v>
       </c>
       <c r="H113" s="98" t="s">
-        <v>1203</v>
+        <v>1208</v>
       </c>
       <c r="I113" s="87" t="s">
-        <v>1204</v>
+        <v>1209</v>
       </c>
       <c r="J113" s="66" t="s">
         <v>44</v>
       </c>
       <c r="K113" s="96" t="s">
-        <v>1205</v>
+        <v>1210</v>
       </c>
       <c r="L113" s="87" t="s">
-        <v>1206</v>
+        <v>1211</v>
       </c>
       <c r="M113" s="87" t="s">
-        <v>950</v>
+        <v>953</v>
       </c>
       <c r="N113" s="73" t="s">
-        <v>951</v>
+        <v>954</v>
       </c>
       <c r="O113" s="73" t="s">
-        <v>1187</v>
+        <v>1192</v>
       </c>
       <c r="P113" s="87" t="s">
-        <v>1207</v>
+        <v>1212</v>
       </c>
       <c r="Q113" s="87" t="s">
-        <v>1208</v>
+        <v>1213</v>
       </c>
       <c r="R113" s="99">
         <v>44608</v>
@@ -27150,7 +27210,7 @@
         <v>44743</v>
       </c>
       <c r="U113" s="97" t="s">
-        <v>1209</v>
+        <v>1214</v>
       </c>
       <c r="V113" s="87"/>
       <c r="W113" s="87"/>
@@ -27168,7 +27228,7 @@
       </c>
       <c r="AB113" s="87"/>
       <c r="AC113" s="66" t="s">
-        <v>1190</v>
+        <v>1195</v>
       </c>
       <c r="AD113" s="87"/>
       <c r="AE113" s="87"/>
@@ -27179,9 +27239,9 @@
       <c r="AJ113" s="71"/>
       <c r="AK113" s="71"/>
     </row>
-    <row r="114" spans="1:37" ht="39" x14ac:dyDescent="0.55000000000000004">
+    <row r="114" spans="1:37" ht="40.5" x14ac:dyDescent="0.15">
       <c r="A114" s="96" t="s">
-        <v>1210</v>
+        <v>1215</v>
       </c>
       <c r="B114" s="13"/>
       <c r="C114" s="97"/>
@@ -27198,7 +27258,7 @@
       </c>
       <c r="G114" s="50"/>
       <c r="H114" s="98" t="s">
-        <v>1211</v>
+        <v>1216</v>
       </c>
       <c r="I114" s="87" t="s">
         <v>339</v>
@@ -27207,25 +27267,25 @@
         <v>44</v>
       </c>
       <c r="K114" s="96" t="s">
-        <v>1212</v>
+        <v>1217</v>
       </c>
       <c r="L114" s="87" t="s">
-        <v>1213</v>
+        <v>1218</v>
       </c>
       <c r="M114" s="87" t="s">
-        <v>1139</v>
+        <v>1144</v>
       </c>
       <c r="N114" s="73" t="s">
-        <v>897</v>
+        <v>900</v>
       </c>
       <c r="O114" s="73" t="s">
-        <v>898</v>
+        <v>901</v>
       </c>
       <c r="P114" s="87" t="s">
-        <v>1214</v>
+        <v>1219</v>
       </c>
       <c r="Q114" s="87" t="s">
-        <v>1215</v>
+        <v>1220</v>
       </c>
       <c r="R114" s="99">
         <v>44866</v>
@@ -27237,7 +27297,7 @@
         <v>44927</v>
       </c>
       <c r="U114" s="97" t="s">
-        <v>1216</v>
+        <v>1221</v>
       </c>
       <c r="V114" s="87"/>
       <c r="W114" s="87"/>
@@ -27255,7 +27315,7 @@
       </c>
       <c r="AB114" s="87"/>
       <c r="AC114" s="13" t="s">
-        <v>902</v>
+        <v>904</v>
       </c>
       <c r="AD114" s="87"/>
       <c r="AE114" s="87"/>
@@ -27266,9 +27326,9 @@
       <c r="AJ114" s="71"/>
       <c r="AK114" s="71"/>
     </row>
-    <row r="115" spans="1:37" ht="40.5" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="115" spans="1:37" ht="40.5" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A115" s="96" t="s">
-        <v>1217</v>
+        <v>1222</v>
       </c>
       <c r="B115" s="102"/>
       <c r="C115" s="97"/>
@@ -27285,31 +27345,31 @@
       </c>
       <c r="G115" s="50"/>
       <c r="H115" s="98" t="s">
-        <v>1218</v>
+        <v>1223</v>
       </c>
       <c r="I115" s="87" t="s">
-        <v>1219</v>
+        <v>1224</v>
       </c>
       <c r="J115" s="66" t="s">
         <v>44</v>
       </c>
       <c r="K115" s="96" t="s">
-        <v>1220</v>
+        <v>1225</v>
       </c>
       <c r="L115" s="87" t="s">
-        <v>1221</v>
+        <v>1226</v>
       </c>
       <c r="M115" s="87" t="s">
-        <v>1222</v>
+        <v>1227</v>
       </c>
       <c r="N115" s="73" t="s">
-        <v>1223</v>
+        <v>1228</v>
       </c>
       <c r="O115" s="73" t="s">
-        <v>1224</v>
+        <v>1229</v>
       </c>
       <c r="P115" s="87" t="s">
-        <v>1225</v>
+        <v>1230</v>
       </c>
       <c r="Q115" s="87"/>
       <c r="R115" s="99">
@@ -27322,7 +27382,7 @@
         <v>44927</v>
       </c>
       <c r="U115" s="97" t="s">
-        <v>1226</v>
+        <v>1231</v>
       </c>
       <c r="V115" s="87"/>
       <c r="W115" s="87"/>
@@ -27349,9 +27409,9 @@
       <c r="AJ115" s="71"/>
       <c r="AK115" s="71"/>
     </row>
-    <row r="116" spans="1:37" ht="40.5" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="116" spans="1:37" ht="40.5" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A116" s="96" t="s">
-        <v>1227</v>
+        <v>1232</v>
       </c>
       <c r="B116" s="102"/>
       <c r="C116" s="97"/>
@@ -27368,7 +27428,7 @@
       </c>
       <c r="G116" s="50"/>
       <c r="H116" s="98" t="s">
-        <v>1228</v>
+        <v>1233</v>
       </c>
       <c r="I116" s="87" t="s">
         <v>212</v>
@@ -27377,22 +27437,22 @@
         <v>44</v>
       </c>
       <c r="K116" s="87" t="s">
-        <v>1229</v>
+        <v>1234</v>
       </c>
       <c r="L116" s="87" t="s">
-        <v>1230</v>
+        <v>1235</v>
       </c>
       <c r="M116" s="87" t="s">
-        <v>1065</v>
+        <v>1069</v>
       </c>
       <c r="N116" s="73" t="s">
-        <v>831</v>
+        <v>834</v>
       </c>
       <c r="O116" s="73" t="s">
-        <v>1231</v>
+        <v>1236</v>
       </c>
       <c r="P116" s="87" t="s">
-        <v>1232</v>
+        <v>1237</v>
       </c>
       <c r="Q116" s="87"/>
       <c r="R116" s="99">
@@ -27405,7 +27465,7 @@
         <v>44927</v>
       </c>
       <c r="U116" s="97" t="s">
-        <v>1233</v>
+        <v>1238</v>
       </c>
       <c r="V116" s="87"/>
       <c r="W116" s="87"/>
@@ -27432,9 +27492,9 @@
       <c r="AJ116" s="71"/>
       <c r="AK116" s="71"/>
     </row>
-    <row r="117" spans="1:37" ht="40.5" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="117" spans="1:37" ht="40.5" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A117" s="96" t="s">
-        <v>1234</v>
+        <v>1239</v>
       </c>
       <c r="B117" s="102"/>
       <c r="C117" s="97"/>
@@ -27451,31 +27511,31 @@
       </c>
       <c r="G117" s="50"/>
       <c r="H117" s="98" t="s">
-        <v>1235</v>
+        <v>1240</v>
       </c>
       <c r="I117" s="87" t="s">
-        <v>1236</v>
+        <v>1241</v>
       </c>
       <c r="J117" s="66" t="s">
         <v>44</v>
       </c>
       <c r="K117" s="96" t="s">
-        <v>1237</v>
+        <v>1242</v>
       </c>
       <c r="L117" s="87" t="s">
-        <v>1238</v>
+        <v>1243</v>
       </c>
       <c r="M117" s="87" t="s">
-        <v>1239</v>
+        <v>1244</v>
       </c>
       <c r="N117" s="73" t="s">
-        <v>1240</v>
+        <v>1245</v>
       </c>
       <c r="O117" s="73" t="s">
-        <v>1241</v>
+        <v>1246</v>
       </c>
       <c r="P117" s="87" t="s">
-        <v>1242</v>
+        <v>1247</v>
       </c>
       <c r="Q117" s="87"/>
       <c r="R117" s="99">
@@ -27488,7 +27548,7 @@
         <v>44927</v>
       </c>
       <c r="U117" s="97" t="s">
-        <v>1243</v>
+        <v>1248</v>
       </c>
       <c r="V117" s="87"/>
       <c r="W117" s="87"/>
@@ -27515,9 +27575,9 @@
       <c r="AJ117" s="71"/>
       <c r="AK117" s="71"/>
     </row>
-    <row r="118" spans="1:37" ht="52" x14ac:dyDescent="0.55000000000000004">
+    <row r="118" spans="1:37" ht="54" x14ac:dyDescent="0.15">
       <c r="A118" s="96" t="s">
-        <v>1244</v>
+        <v>1249</v>
       </c>
       <c r="B118" s="103"/>
       <c r="C118" s="97"/>
@@ -27537,34 +27597,34 @@
         <v>　</v>
       </c>
       <c r="H118" s="98" t="s">
-        <v>1245</v>
+        <v>1250</v>
       </c>
       <c r="I118" s="87" t="s">
-        <v>1246</v>
+        <v>1251</v>
       </c>
       <c r="J118" s="66" t="s">
-        <v>1247</v>
+        <v>1252</v>
       </c>
       <c r="K118" s="87" t="s">
-        <v>1248</v>
+        <v>1253</v>
       </c>
       <c r="L118" s="87" t="s">
-        <v>1249</v>
+        <v>1254</v>
       </c>
       <c r="M118" s="13" t="s">
-        <v>601</v>
+        <v>603</v>
       </c>
       <c r="N118" s="73" t="s">
-        <v>602</v>
+        <v>604</v>
       </c>
       <c r="O118" s="73" t="s">
-        <v>712</v>
+        <v>715</v>
       </c>
       <c r="P118" s="96" t="s">
-        <v>1250</v>
+        <v>1255</v>
       </c>
       <c r="Q118" s="87" t="s">
-        <v>1251</v>
+        <v>1256</v>
       </c>
       <c r="R118" s="99">
         <v>44942</v>
@@ -27576,7 +27636,7 @@
         <v>45017</v>
       </c>
       <c r="U118" s="97" t="s">
-        <v>1252</v>
+        <v>1257</v>
       </c>
       <c r="V118" s="96"/>
       <c r="W118" s="96"/>
@@ -27603,9 +27663,9 @@
       <c r="AJ118" s="71"/>
       <c r="AK118" s="71"/>
     </row>
-    <row r="119" spans="1:37" ht="40.5" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="119" spans="1:37" ht="40.5" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A119" s="96" t="s">
-        <v>1253</v>
+        <v>1258</v>
       </c>
       <c r="B119" s="13"/>
       <c r="C119" s="97"/>
@@ -27625,34 +27685,34 @@
         <v>　</v>
       </c>
       <c r="H119" s="98" t="s">
-        <v>1254</v>
+        <v>1259</v>
       </c>
       <c r="I119" s="87" t="s">
-        <v>1255</v>
+        <v>1260</v>
       </c>
       <c r="J119" s="66" t="s">
-        <v>1247</v>
+        <v>1252</v>
       </c>
       <c r="K119" s="96" t="s">
-        <v>1256</v>
+        <v>1261</v>
       </c>
       <c r="L119" s="87" t="s">
-        <v>1257</v>
+        <v>1262</v>
       </c>
       <c r="M119" s="96" t="s">
-        <v>1139</v>
+        <v>1144</v>
       </c>
       <c r="N119" s="73" t="s">
-        <v>897</v>
+        <v>900</v>
       </c>
       <c r="O119" s="73" t="s">
-        <v>898</v>
+        <v>901</v>
       </c>
       <c r="P119" s="87" t="s">
-        <v>1258</v>
+        <v>1263</v>
       </c>
       <c r="Q119" s="87" t="s">
-        <v>1259</v>
+        <v>1264</v>
       </c>
       <c r="R119" s="99">
         <v>44959</v>
@@ -27664,7 +27724,7 @@
         <v>45017</v>
       </c>
       <c r="U119" s="97" t="s">
-        <v>1260</v>
+        <v>1265</v>
       </c>
       <c r="V119" s="87"/>
       <c r="W119" s="87"/>
@@ -27682,7 +27742,7 @@
       </c>
       <c r="AB119" s="87"/>
       <c r="AC119" s="13" t="s">
-        <v>902</v>
+        <v>904</v>
       </c>
       <c r="AD119" s="87"/>
       <c r="AE119" s="87"/>
@@ -27693,9 +27753,9 @@
       <c r="AJ119" s="71"/>
       <c r="AK119" s="71"/>
     </row>
-    <row r="120" spans="1:37" ht="42" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="120" spans="1:37" ht="42" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A120" s="96" t="s">
-        <v>1261</v>
+        <v>1266</v>
       </c>
       <c r="B120" s="71"/>
       <c r="C120" s="104"/>
@@ -27712,31 +27772,31 @@
       </c>
       <c r="G120" s="71"/>
       <c r="H120" s="106" t="s">
-        <v>1262</v>
+        <v>1267</v>
       </c>
       <c r="I120" s="106" t="s">
-        <v>972</v>
+        <v>975</v>
       </c>
       <c r="J120" s="66" t="s">
-        <v>1247</v>
+        <v>1252</v>
       </c>
       <c r="K120" s="71" t="s">
-        <v>1263</v>
+        <v>1268</v>
       </c>
       <c r="L120" s="107" t="s">
-        <v>1264</v>
+        <v>1269</v>
       </c>
       <c r="M120" s="71" t="s">
-        <v>1265</v>
+        <v>1270</v>
       </c>
       <c r="N120" s="108" t="s">
-        <v>1266</v>
+        <v>1271</v>
       </c>
       <c r="O120" s="109" t="s">
-        <v>1267</v>
+        <v>1272</v>
       </c>
       <c r="P120" s="71" t="s">
-        <v>1268</v>
+        <v>1273</v>
       </c>
       <c r="Q120" s="71"/>
       <c r="R120" s="99">
@@ -27749,7 +27809,7 @@
         <v>45108</v>
       </c>
       <c r="U120" s="97" t="s">
-        <v>1269</v>
+        <v>1274</v>
       </c>
       <c r="V120" s="71"/>
       <c r="W120" s="71"/>
@@ -27776,9 +27836,9 @@
       <c r="AJ120" s="71"/>
       <c r="AK120" s="71"/>
     </row>
-    <row r="121" spans="1:37" ht="26" x14ac:dyDescent="0.55000000000000004">
+    <row r="121" spans="1:37" ht="27" x14ac:dyDescent="0.15">
       <c r="A121" s="62" t="s">
-        <v>1270</v>
+        <v>1275</v>
       </c>
       <c r="B121" s="96"/>
       <c r="C121" s="97"/>
@@ -27798,31 +27858,31 @@
         <v>　</v>
       </c>
       <c r="H121" s="98" t="s">
-        <v>1271</v>
+        <v>1276</v>
       </c>
       <c r="I121" s="87" t="s">
-        <v>915</v>
+        <v>917</v>
       </c>
       <c r="J121" s="66" t="s">
         <v>44</v>
       </c>
       <c r="K121" s="96" t="s">
-        <v>1272</v>
+        <v>1277</v>
       </c>
       <c r="L121" s="87" t="s">
-        <v>1273</v>
+        <v>1278</v>
       </c>
       <c r="M121" s="96" t="s">
-        <v>1110</v>
+        <v>1115</v>
       </c>
       <c r="N121" s="73" t="s">
-        <v>1111</v>
+        <v>1116</v>
       </c>
       <c r="O121" s="73" t="s">
-        <v>1112</v>
+        <v>1117</v>
       </c>
       <c r="P121" s="96" t="s">
-        <v>1274</v>
+        <v>1279</v>
       </c>
       <c r="Q121" s="96"/>
       <c r="R121" s="99">
@@ -27835,7 +27895,7 @@
         <v>45200</v>
       </c>
       <c r="U121" s="97" t="s">
-        <v>1275</v>
+        <v>1280</v>
       </c>
       <c r="V121" s="96"/>
       <c r="W121" s="96"/>
@@ -27862,9 +27922,9 @@
       <c r="AJ121" s="71"/>
       <c r="AK121" s="71"/>
     </row>
-    <row r="122" spans="1:37" ht="27" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="122" spans="1:37" ht="27" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A122" s="62" t="s">
-        <v>1276</v>
+        <v>1281</v>
       </c>
       <c r="B122" s="13"/>
       <c r="C122" s="97"/>
@@ -27884,31 +27944,31 @@
         <v>　</v>
       </c>
       <c r="H122" s="98" t="s">
-        <v>1277</v>
+        <v>1282</v>
       </c>
       <c r="I122" s="87" t="s">
-        <v>1045</v>
+        <v>1048</v>
       </c>
       <c r="J122" s="66" t="s">
         <v>44</v>
       </c>
       <c r="K122" s="96" t="s">
-        <v>1278</v>
+        <v>1283</v>
       </c>
       <c r="L122" s="87" t="s">
-        <v>1279</v>
+        <v>1284</v>
       </c>
       <c r="M122" s="96" t="s">
-        <v>1139</v>
+        <v>1144</v>
       </c>
       <c r="N122" s="73" t="s">
-        <v>897</v>
+        <v>900</v>
       </c>
       <c r="O122" s="73" t="s">
-        <v>898</v>
+        <v>901</v>
       </c>
       <c r="P122" s="96" t="s">
-        <v>1280</v>
+        <v>1285</v>
       </c>
       <c r="Q122" s="96"/>
       <c r="R122" s="99">
@@ -27921,7 +27981,7 @@
         <v>45200</v>
       </c>
       <c r="U122" s="97" t="s">
-        <v>1281</v>
+        <v>1286</v>
       </c>
       <c r="V122" s="96"/>
       <c r="W122" s="96"/>
@@ -27939,7 +27999,7 @@
       </c>
       <c r="AB122" s="96"/>
       <c r="AC122" s="13" t="s">
-        <v>902</v>
+        <v>904</v>
       </c>
       <c r="AD122" s="96"/>
       <c r="AE122" s="96"/>
@@ -27950,9 +28010,9 @@
       <c r="AJ122" s="71"/>
       <c r="AK122" s="71"/>
     </row>
-    <row r="123" spans="1:37" ht="35.25" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="123" spans="1:37" ht="35.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A123" s="71" t="s">
-        <v>1282</v>
+        <v>1287</v>
       </c>
       <c r="B123" s="71"/>
       <c r="C123" s="104"/>
@@ -27969,31 +28029,31 @@
       </c>
       <c r="G123" s="71"/>
       <c r="H123" s="106" t="s">
-        <v>1283</v>
+        <v>1288</v>
       </c>
       <c r="I123" s="107" t="s">
-        <v>1284</v>
+        <v>1289</v>
       </c>
       <c r="J123" s="66" t="s">
         <v>44</v>
       </c>
       <c r="K123" s="71" t="s">
-        <v>1285</v>
+        <v>1290</v>
       </c>
       <c r="L123" s="107" t="s">
-        <v>1286</v>
+        <v>1291</v>
       </c>
       <c r="M123" s="107" t="s">
-        <v>1287</v>
+        <v>1292</v>
       </c>
       <c r="N123" s="108" t="s">
-        <v>1288</v>
+        <v>1293</v>
       </c>
       <c r="O123" s="108" t="s">
-        <v>1289</v>
+        <v>1294</v>
       </c>
       <c r="P123" s="71" t="s">
-        <v>1290</v>
+        <v>1295</v>
       </c>
       <c r="Q123" s="71"/>
       <c r="R123" s="99">
@@ -28006,7 +28066,7 @@
         <v>45292</v>
       </c>
       <c r="U123" s="97" t="s">
-        <v>1291</v>
+        <v>1296</v>
       </c>
       <c r="V123" s="71"/>
       <c r="W123" s="71"/>
@@ -28033,9 +28093,9 @@
       <c r="AJ123" s="71"/>
       <c r="AK123" s="71"/>
     </row>
-    <row r="124" spans="1:37" ht="114.75" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="124" spans="1:37" ht="114.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A124" s="71" t="s">
-        <v>1292</v>
+        <v>1297</v>
       </c>
       <c r="B124" s="107"/>
       <c r="C124" s="104"/>
@@ -28051,19 +28111,19 @@
       </c>
       <c r="G124" s="71"/>
       <c r="H124" s="106" t="s">
-        <v>1293</v>
+        <v>1298</v>
       </c>
       <c r="I124" s="107" t="s">
-        <v>1294</v>
+        <v>1299</v>
       </c>
       <c r="J124" s="66" t="s">
         <v>44</v>
       </c>
       <c r="K124" s="71" t="s">
-        <v>1295</v>
+        <v>1300</v>
       </c>
       <c r="L124" s="107" t="s">
-        <v>1296</v>
+        <v>1301</v>
       </c>
       <c r="M124" s="107" t="s">
         <v>487</v>
@@ -28072,10 +28132,10 @@
         <v>488</v>
       </c>
       <c r="O124" s="108" t="s">
-        <v>1297</v>
+        <v>1302</v>
       </c>
       <c r="P124" s="71" t="s">
-        <v>1298</v>
+        <v>1303</v>
       </c>
       <c r="Q124" s="71"/>
       <c r="R124" s="99">
@@ -28088,7 +28148,7 @@
         <v>45383</v>
       </c>
       <c r="U124" s="97" t="s">
-        <v>1299</v>
+        <v>1304</v>
       </c>
       <c r="V124" s="71"/>
       <c r="W124" s="71"/>
@@ -28106,7 +28166,7 @@
       </c>
       <c r="AB124" s="71"/>
       <c r="AC124" s="107" t="s">
-        <v>1300</v>
+        <v>1305</v>
       </c>
       <c r="AD124" s="71"/>
       <c r="AE124" s="71"/>
@@ -28117,9 +28177,9 @@
       <c r="AJ124" s="71"/>
       <c r="AK124" s="71"/>
     </row>
-    <row r="125" spans="1:37" ht="35.25" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="125" spans="1:37" ht="35.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A125" s="71" t="s">
-        <v>1301</v>
+        <v>1306</v>
       </c>
       <c r="B125" s="71"/>
       <c r="C125" s="104"/>
@@ -28136,31 +28196,31 @@
       </c>
       <c r="G125" s="71"/>
       <c r="H125" s="106" t="s">
-        <v>1302</v>
+        <v>1307</v>
       </c>
       <c r="I125" s="107" t="s">
-        <v>1303</v>
+        <v>1308</v>
       </c>
       <c r="J125" s="66" t="s">
         <v>44</v>
       </c>
       <c r="K125" s="71" t="s">
-        <v>1304</v>
+        <v>1309</v>
       </c>
       <c r="L125" s="107" t="s">
-        <v>1305</v>
+        <v>1310</v>
       </c>
       <c r="M125" s="107" t="s">
-        <v>1306</v>
+        <v>1311</v>
       </c>
       <c r="N125" s="108" t="s">
-        <v>1177</v>
+        <v>1182</v>
       </c>
       <c r="O125" s="108" t="s">
-        <v>1307</v>
+        <v>1312</v>
       </c>
       <c r="P125" s="71" t="s">
-        <v>1308</v>
+        <v>1313</v>
       </c>
       <c r="Q125" s="71"/>
       <c r="R125" s="99">
@@ -28173,7 +28233,7 @@
         <v>45566</v>
       </c>
       <c r="U125" s="97" t="s">
-        <v>1309</v>
+        <v>1314</v>
       </c>
       <c r="V125" s="71"/>
       <c r="W125" s="71"/>
@@ -28200,9 +28260,9 @@
       <c r="AJ125" s="71"/>
       <c r="AK125" s="71"/>
     </row>
-    <row r="126" spans="1:37" ht="35.25" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="126" spans="1:37" ht="35.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A126" s="71" t="s">
-        <v>1310</v>
+        <v>1315</v>
       </c>
       <c r="B126" s="13"/>
       <c r="C126" s="104"/>
@@ -28219,31 +28279,31 @@
       </c>
       <c r="G126" s="71"/>
       <c r="H126" s="106" t="s">
-        <v>1311</v>
+        <v>1316</v>
       </c>
       <c r="I126" s="107" t="s">
-        <v>947</v>
+        <v>950</v>
       </c>
       <c r="J126" s="66" t="s">
         <v>44</v>
       </c>
       <c r="K126" s="71" t="s">
-        <v>1312</v>
+        <v>1317</v>
       </c>
       <c r="L126" s="107" t="s">
-        <v>1313</v>
+        <v>1318</v>
       </c>
       <c r="M126" s="107" t="s">
-        <v>1094</v>
+        <v>1098</v>
       </c>
       <c r="N126" s="108" t="s">
-        <v>1057</v>
+        <v>1060</v>
       </c>
       <c r="O126" s="108" t="s">
-        <v>898</v>
+        <v>901</v>
       </c>
       <c r="P126" s="71" t="s">
-        <v>1314</v>
+        <v>1319</v>
       </c>
       <c r="Q126" s="71"/>
       <c r="R126" s="99">
@@ -28256,7 +28316,7 @@
         <v>45566</v>
       </c>
       <c r="U126" s="97" t="s">
-        <v>1309</v>
+        <v>1314</v>
       </c>
       <c r="V126" s="71"/>
       <c r="W126" s="71"/>
@@ -28274,7 +28334,7 @@
       </c>
       <c r="AB126" s="71"/>
       <c r="AC126" s="13" t="s">
-        <v>902</v>
+        <v>904</v>
       </c>
       <c r="AD126" s="71"/>
       <c r="AE126" s="71"/>
@@ -28285,9 +28345,9 @@
       <c r="AJ126" s="71"/>
       <c r="AK126" s="71"/>
     </row>
-    <row r="127" spans="1:37" ht="35.25" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="127" spans="1:37" ht="35.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A127" s="71" t="s">
-        <v>1315</v>
+        <v>1320</v>
       </c>
       <c r="B127" s="96"/>
       <c r="C127" s="104"/>
@@ -28304,31 +28364,31 @@
       </c>
       <c r="G127" s="71"/>
       <c r="H127" s="111" t="s">
-        <v>1316</v>
+        <v>1321</v>
       </c>
       <c r="I127" s="107" t="s">
-        <v>915</v>
+        <v>917</v>
       </c>
       <c r="J127" s="66" t="s">
         <v>44</v>
       </c>
       <c r="K127" s="112" t="s">
-        <v>1317</v>
+        <v>1322</v>
       </c>
       <c r="L127" s="106" t="s">
-        <v>1318</v>
+        <v>1323</v>
       </c>
       <c r="M127" s="113" t="s">
-        <v>1319</v>
+        <v>1324</v>
       </c>
       <c r="N127" s="108" t="s">
-        <v>915</v>
+        <v>917</v>
       </c>
       <c r="O127" s="114" t="s">
-        <v>1317</v>
+        <v>1322</v>
       </c>
       <c r="P127" s="105" t="s">
-        <v>1320</v>
+        <v>1325</v>
       </c>
       <c r="Q127" s="71"/>
       <c r="R127" s="99">
@@ -28341,7 +28401,7 @@
         <v>45658</v>
       </c>
       <c r="U127" s="115" t="s">
-        <v>1321</v>
+        <v>1326</v>
       </c>
       <c r="V127" s="71"/>
       <c r="W127" s="71"/>
@@ -28368,9 +28428,9 @@
       <c r="AJ127" s="71"/>
       <c r="AK127" s="71"/>
     </row>
-    <row r="128" spans="1:37" ht="35.25" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="128" spans="1:37" ht="35.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A128" s="71" t="s">
-        <v>1322</v>
+        <v>1327</v>
       </c>
       <c r="B128" s="96"/>
       <c r="C128" s="104"/>
@@ -28387,31 +28447,31 @@
       </c>
       <c r="G128" s="71"/>
       <c r="H128" s="116" t="s">
-        <v>1323</v>
+        <v>1328</v>
       </c>
       <c r="I128" s="106" t="s">
-        <v>1324</v>
+        <v>1329</v>
       </c>
       <c r="J128" s="66" t="s">
         <v>44</v>
       </c>
       <c r="K128" s="117" t="s">
-        <v>1325</v>
+        <v>1330</v>
       </c>
       <c r="L128" s="106" t="s">
-        <v>1326</v>
+        <v>1331</v>
       </c>
       <c r="M128" s="118" t="s">
-        <v>1327</v>
+        <v>1332</v>
       </c>
       <c r="N128" s="108" t="s">
         <v>311</v>
       </c>
       <c r="O128" s="119" t="s">
-        <v>1328</v>
+        <v>1333</v>
       </c>
       <c r="P128" s="105" t="s">
-        <v>1329</v>
+        <v>1334</v>
       </c>
       <c r="Q128" s="71"/>
       <c r="R128" s="99">
@@ -28424,7 +28484,7 @@
         <v>45658</v>
       </c>
       <c r="U128" s="115" t="s">
-        <v>1321</v>
+        <v>1326</v>
       </c>
       <c r="V128" s="71"/>
       <c r="W128" s="71"/>
@@ -28451,9 +28511,9 @@
       <c r="AJ128" s="71"/>
       <c r="AK128" s="71"/>
     </row>
-    <row r="129" spans="1:37" ht="43.5" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="129" spans="1:37" ht="43.5" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A129" s="71" t="s">
-        <v>1330</v>
+        <v>1335</v>
       </c>
       <c r="B129" s="13"/>
       <c r="C129" s="104"/>
@@ -28470,34 +28530,34 @@
       </c>
       <c r="G129" s="71"/>
       <c r="H129" s="116" t="s">
-        <v>1331</v>
+        <v>1336</v>
       </c>
       <c r="I129" s="106" t="s">
-        <v>1332</v>
+        <v>1337</v>
       </c>
       <c r="J129" s="66" t="s">
         <v>44</v>
       </c>
-      <c r="K129" s="117" t="s">
-        <v>1333</v>
+      <c r="K129" s="120" t="s">
+        <v>1338</v>
       </c>
       <c r="L129" s="106" t="s">
-        <v>1334</v>
+        <v>1339</v>
       </c>
       <c r="M129" s="118" t="s">
-        <v>1335</v>
+        <v>1340</v>
       </c>
       <c r="N129" s="108" t="s">
-        <v>941</v>
-      </c>
-      <c r="O129" s="120" t="s">
-        <v>1336</v>
+        <v>943</v>
+      </c>
+      <c r="O129" s="121" t="s">
+        <v>1341</v>
       </c>
       <c r="P129" s="105" t="s">
-        <v>1337</v>
+        <v>1342</v>
       </c>
       <c r="Q129" s="87" t="s">
-        <v>1338</v>
+        <v>1343</v>
       </c>
       <c r="R129" s="99">
         <v>45603</v>
@@ -28509,7 +28569,7 @@
         <v>45658</v>
       </c>
       <c r="U129" s="115" t="s">
-        <v>1321</v>
+        <v>1326</v>
       </c>
       <c r="V129" s="71"/>
       <c r="W129" s="71"/>
@@ -28536,9 +28596,9 @@
       <c r="AJ129" s="71"/>
       <c r="AK129" s="71"/>
     </row>
-    <row r="130" spans="1:37" ht="35.25" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="130" spans="1:37" ht="35.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A130" s="71" t="s">
-        <v>1339</v>
+        <v>1344</v>
       </c>
       <c r="B130" s="96"/>
       <c r="C130" s="104"/>
@@ -28554,8 +28614,8 @@
         <v>1342956191</v>
       </c>
       <c r="G130" s="71"/>
-      <c r="H130" s="121" t="s">
-        <v>1340</v>
+      <c r="H130" s="122" t="s">
+        <v>1345</v>
       </c>
       <c r="I130" s="106" t="s">
         <v>144</v>
@@ -28563,23 +28623,23 @@
       <c r="J130" s="66" t="s">
         <v>44</v>
       </c>
-      <c r="K130" s="122" t="s">
-        <v>1341</v>
+      <c r="K130" s="117" t="s">
+        <v>1346</v>
       </c>
       <c r="L130" s="106" t="s">
-        <v>1342</v>
+        <v>1347</v>
       </c>
       <c r="M130" s="118" t="s">
-        <v>1343</v>
+        <v>1348</v>
       </c>
       <c r="N130" s="108" t="s">
-        <v>1344</v>
+        <v>1349</v>
       </c>
       <c r="O130" s="123" t="s">
-        <v>1345</v>
+        <v>1350</v>
       </c>
       <c r="P130" s="105" t="s">
-        <v>1346</v>
+        <v>1351</v>
       </c>
       <c r="Q130" s="71"/>
       <c r="R130" s="99">
@@ -28592,7 +28652,7 @@
         <v>45748</v>
       </c>
       <c r="U130" s="115" t="s">
-        <v>1347</v>
+        <v>1352</v>
       </c>
       <c r="V130" s="71"/>
       <c r="W130" s="71"/>
@@ -28619,9 +28679,9 @@
       <c r="AJ130" s="71"/>
       <c r="AK130" s="71"/>
     </row>
-    <row r="131" spans="1:37" ht="35.25" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="131" spans="1:37" ht="35.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A131" s="71" t="s">
-        <v>1348</v>
+        <v>1353</v>
       </c>
       <c r="B131" s="96"/>
       <c r="C131" s="104"/>
@@ -28637,32 +28697,32 @@
         <v>1342956126</v>
       </c>
       <c r="G131" s="71"/>
-      <c r="H131" s="121" t="s">
-        <v>1349</v>
+      <c r="H131" s="122" t="s">
+        <v>1354</v>
       </c>
       <c r="I131" s="106" t="s">
-        <v>915</v>
+        <v>917</v>
       </c>
       <c r="J131" s="66" t="s">
         <v>44</v>
       </c>
-      <c r="K131" s="117" t="s">
-        <v>1350</v>
+      <c r="K131" s="120" t="s">
+        <v>1355</v>
       </c>
       <c r="L131" s="106" t="s">
-        <v>1351</v>
+        <v>1356</v>
       </c>
       <c r="M131" s="118" t="s">
-        <v>1352</v>
+        <v>1357</v>
       </c>
       <c r="N131" s="108" t="s">
-        <v>1353</v>
+        <v>1358</v>
       </c>
       <c r="O131" s="124" t="s">
-        <v>1354</v>
+        <v>1359</v>
       </c>
       <c r="P131" s="105" t="s">
-        <v>1355</v>
+        <v>1360</v>
       </c>
       <c r="Q131" s="71"/>
       <c r="R131" s="99">
@@ -28675,7 +28735,7 @@
         <v>45748</v>
       </c>
       <c r="U131" s="115" t="s">
-        <v>1347</v>
+        <v>1352</v>
       </c>
       <c r="V131" s="71"/>
       <c r="W131" s="71"/>
@@ -28702,9 +28762,9 @@
       <c r="AJ131" s="71"/>
       <c r="AK131" s="71"/>
     </row>
-    <row r="132" spans="1:37" ht="35.25" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="132" spans="1:37" ht="35.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A132" s="71" t="s">
-        <v>1356</v>
+        <v>1361</v>
       </c>
       <c r="B132" s="96"/>
       <c r="C132" s="104"/>
@@ -28720,32 +28780,32 @@
         <v>1342956209</v>
       </c>
       <c r="G132" s="71"/>
-      <c r="H132" s="121" t="s">
-        <v>1357</v>
+      <c r="H132" s="122" t="s">
+        <v>1362</v>
       </c>
       <c r="I132" s="106" t="s">
-        <v>972</v>
+        <v>975</v>
       </c>
       <c r="J132" s="66" t="s">
         <v>44</v>
       </c>
       <c r="K132" s="125" t="s">
-        <v>1358</v>
+        <v>1363</v>
       </c>
       <c r="L132" s="106" t="s">
-        <v>1359</v>
+        <v>1364</v>
       </c>
       <c r="M132" s="126" t="s">
-        <v>1360</v>
+        <v>1365</v>
       </c>
       <c r="N132" s="108" t="s">
-        <v>667</v>
+        <v>669</v>
       </c>
       <c r="O132" s="124" t="s">
-        <v>1361</v>
+        <v>1366</v>
       </c>
       <c r="P132" s="105" t="s">
-        <v>1362</v>
+        <v>1367</v>
       </c>
       <c r="Q132" s="71"/>
       <c r="R132" s="99">
@@ -28758,7 +28818,7 @@
         <v>45839</v>
       </c>
       <c r="U132" s="115" t="s">
-        <v>1363</v>
+        <v>1368</v>
       </c>
       <c r="V132" s="71"/>
       <c r="W132" s="71"/>
@@ -28785,11 +28845,13 @@
       <c r="AJ132" s="71"/>
       <c r="AK132" s="71"/>
     </row>
-    <row r="133" spans="1:37" ht="40.5" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="133" spans="1:37" ht="40.5" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A133" s="71" t="s">
-        <v>1364</v>
-      </c>
-      <c r="B133" s="13"/>
+        <v>1369</v>
+      </c>
+      <c r="B133" s="13" t="s">
+        <v>1370</v>
+      </c>
       <c r="C133" s="104"/>
       <c r="D133" s="105">
         <v>2956274</v>
@@ -28803,8 +28865,8 @@
         <v>1342956274</v>
       </c>
       <c r="G133" s="71"/>
-      <c r="H133" s="121" t="s">
-        <v>1365</v>
+      <c r="H133" s="122" t="s">
+        <v>1371</v>
       </c>
       <c r="I133" s="106" t="s">
         <v>148</v>
@@ -28813,25 +28875,25 @@
         <v>44</v>
       </c>
       <c r="K133" s="125" t="s">
-        <v>1366</v>
+        <v>1372</v>
       </c>
       <c r="L133" s="106" t="s">
-        <v>1367</v>
+        <v>1373</v>
       </c>
       <c r="M133" s="126" t="s">
-        <v>1368</v>
+        <v>1374</v>
       </c>
       <c r="N133" s="108" t="s">
-        <v>1369</v>
+        <v>1375</v>
       </c>
       <c r="O133" s="124" t="s">
-        <v>1370</v>
+        <v>1376</v>
       </c>
       <c r="P133" s="105" t="s">
-        <v>1371</v>
+        <v>1377</v>
       </c>
       <c r="Q133" s="87" t="s">
-        <v>1372</v>
+        <v>1378</v>
       </c>
       <c r="R133" s="99">
         <v>45965</v>
@@ -28843,7 +28905,7 @@
         <v>46023</v>
       </c>
       <c r="U133" s="115" t="s">
-        <v>1373</v>
+        <v>1379</v>
       </c>
       <c r="V133" s="71"/>
       <c r="W133" s="71"/>
@@ -28860,7 +28922,9 @@
         <v>50801</v>
       </c>
       <c r="AB133" s="71"/>
-      <c r="AC133" s="71"/>
+      <c r="AC133" s="13" t="s">
+        <v>1380</v>
+      </c>
       <c r="AD133" s="71"/>
       <c r="AE133" s="71"/>
       <c r="AF133" s="71"/>
@@ -28870,9 +28934,9 @@
       <c r="AJ133" s="71"/>
       <c r="AK133" s="71"/>
     </row>
-    <row r="134" spans="1:37" ht="40.5" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="134" spans="1:37" ht="40.5" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A134" s="71" t="s">
-        <v>1374</v>
+        <v>1381</v>
       </c>
       <c r="B134" s="13"/>
       <c r="C134" s="104"/>
@@ -28888,32 +28952,32 @@
         <v>1342956258</v>
       </c>
       <c r="G134" s="71"/>
-      <c r="H134" s="121" t="s">
-        <v>1375</v>
+      <c r="H134" s="122" t="s">
+        <v>1382</v>
       </c>
       <c r="I134" s="106" t="s">
-        <v>1162</v>
+        <v>1167</v>
       </c>
       <c r="J134" s="66" t="s">
         <v>44</v>
       </c>
-      <c r="K134" s="125" t="s">
-        <v>1376</v>
+      <c r="K134" s="127" t="s">
+        <v>1383</v>
       </c>
       <c r="L134" s="106" t="s">
-        <v>1377</v>
+        <v>1384</v>
       </c>
       <c r="M134" s="126" t="s">
-        <v>1378</v>
+        <v>1385</v>
       </c>
       <c r="N134" s="108" t="s">
-        <v>616</v>
+        <v>618</v>
       </c>
       <c r="O134" s="124" t="s">
-        <v>1379</v>
+        <v>1386</v>
       </c>
       <c r="P134" s="105" t="s">
-        <v>1380</v>
+        <v>1387</v>
       </c>
       <c r="Q134" s="87"/>
       <c r="R134" s="99">
@@ -28926,7 +28990,7 @@
         <v>46113</v>
       </c>
       <c r="U134" s="115" t="s">
-        <v>1381</v>
+        <v>1388</v>
       </c>
       <c r="V134" s="71"/>
       <c r="W134" s="71"/>
@@ -28953,9 +29017,9 @@
       <c r="AJ134" s="71"/>
       <c r="AK134" s="71"/>
     </row>
-    <row r="135" spans="1:37" ht="40.5" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="135" spans="1:37" ht="40.5" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A135" s="71" t="s">
-        <v>1382</v>
+        <v>1389</v>
       </c>
       <c r="B135" s="13"/>
       <c r="C135" s="104"/>
@@ -28971,32 +29035,32 @@
         <v>1342956308</v>
       </c>
       <c r="G135" s="71"/>
-      <c r="H135" s="121" t="s">
-        <v>1383</v>
+      <c r="H135" s="122" t="s">
+        <v>1390</v>
       </c>
       <c r="I135" s="106" t="s">
-        <v>667</v>
+        <v>669</v>
       </c>
       <c r="J135" s="66" t="s">
         <v>44</v>
       </c>
-      <c r="K135" s="125" t="s">
-        <v>1384</v>
+      <c r="K135" s="127" t="s">
+        <v>1391</v>
       </c>
       <c r="L135" s="106" t="s">
-        <v>1385</v>
+        <v>1392</v>
       </c>
       <c r="M135" s="126" t="s">
-        <v>1386</v>
+        <v>1393</v>
       </c>
       <c r="N135" s="108" t="s">
-        <v>1387</v>
+        <v>1394</v>
       </c>
       <c r="O135" s="124" t="s">
-        <v>1388</v>
+        <v>1395</v>
       </c>
       <c r="P135" s="105" t="s">
-        <v>1389</v>
+        <v>1396</v>
       </c>
       <c r="Q135" s="87"/>
       <c r="R135" s="99">
@@ -29009,7 +29073,7 @@
         <v>46113</v>
       </c>
       <c r="U135" s="115" t="s">
-        <v>1381</v>
+        <v>1388</v>
       </c>
       <c r="V135" s="71"/>
       <c r="W135" s="71"/>
@@ -29036,11 +29100,13 @@
       <c r="AJ135" s="71"/>
       <c r="AK135" s="71"/>
     </row>
-    <row r="136" spans="1:37" ht="40.5" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="136" spans="1:37" ht="40.5" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A136" s="71" t="s">
-        <v>1390</v>
-      </c>
-      <c r="B136" s="13"/>
+        <v>1397</v>
+      </c>
+      <c r="B136" s="13" t="s">
+        <v>677</v>
+      </c>
       <c r="C136" s="104"/>
       <c r="D136" s="105">
         <v>2956316</v>
@@ -29054,34 +29120,36 @@
         <v>1342956316</v>
       </c>
       <c r="G136" s="71"/>
-      <c r="H136" s="121" t="s">
-        <v>1391</v>
+      <c r="H136" s="122" t="s">
+        <v>1398</v>
       </c>
       <c r="I136" s="106" t="s">
-        <v>684</v>
+        <v>687</v>
       </c>
       <c r="J136" s="66" t="s">
         <v>44</v>
       </c>
-      <c r="K136" s="125" t="s">
-        <v>1392</v>
+      <c r="K136" s="127" t="s">
+        <v>1399</v>
       </c>
       <c r="L136" s="106" t="s">
-        <v>1393</v>
+        <v>1400</v>
       </c>
       <c r="M136" s="126" t="s">
-        <v>1394</v>
+        <v>1401</v>
       </c>
       <c r="N136" s="108" t="s">
-        <v>1395</v>
+        <v>1402</v>
       </c>
       <c r="O136" s="124" t="s">
-        <v>1396</v>
+        <v>1403</v>
       </c>
       <c r="P136" s="105" t="s">
-        <v>1397</v>
-      </c>
-      <c r="Q136" s="87"/>
+        <v>1404</v>
+      </c>
+      <c r="Q136" s="87" t="s">
+        <v>1405</v>
+      </c>
       <c r="R136" s="99">
         <v>46059</v>
       </c>
@@ -29092,7 +29160,7 @@
         <v>46113</v>
       </c>
       <c r="U136" s="115" t="s">
-        <v>1381</v>
+        <v>1388</v>
       </c>
       <c r="V136" s="71"/>
       <c r="W136" s="71"/>
@@ -29119,9 +29187,9 @@
       <c r="AJ136" s="71"/>
       <c r="AK136" s="71"/>
     </row>
-    <row r="137" spans="1:37" ht="40.5" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="137" spans="1:37" ht="40.5" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A137" s="71" t="s">
-        <v>1398</v>
+        <v>1406</v>
       </c>
       <c r="B137" s="13"/>
       <c r="C137" s="104"/>
@@ -29137,32 +29205,32 @@
         <v>1342956324</v>
       </c>
       <c r="G137" s="71"/>
-      <c r="H137" s="121" t="s">
-        <v>1399</v>
+      <c r="H137" s="122" t="s">
+        <v>1407</v>
       </c>
       <c r="I137" s="106" t="s">
-        <v>947</v>
+        <v>950</v>
       </c>
       <c r="J137" s="66" t="s">
         <v>44</v>
       </c>
       <c r="K137" s="125" t="s">
-        <v>1400</v>
+        <v>1408</v>
       </c>
       <c r="L137" s="106" t="s">
-        <v>1401</v>
+        <v>1409</v>
       </c>
       <c r="M137" s="126" t="s">
-        <v>1402</v>
+        <v>1410</v>
       </c>
       <c r="N137" s="108" t="s">
-        <v>1403</v>
+        <v>1411</v>
       </c>
       <c r="O137" s="124" t="s">
-        <v>1404</v>
+        <v>1412</v>
       </c>
       <c r="P137" s="105" t="s">
-        <v>1405</v>
+        <v>1413</v>
       </c>
       <c r="Q137" s="87"/>
       <c r="R137" s="99">
@@ -29175,7 +29243,7 @@
         <v>46113</v>
       </c>
       <c r="U137" s="115" t="s">
-        <v>1381</v>
+        <v>1388</v>
       </c>
       <c r="V137" s="71"/>
       <c r="W137" s="71"/>
@@ -29202,14 +29270,14 @@
       <c r="AJ137" s="71"/>
       <c r="AK137" s="71"/>
     </row>
-    <row r="140" spans="1:37" x14ac:dyDescent="0.55000000000000004">
-      <c r="I140" s="129"/>
+    <row r="140" spans="1:37" x14ac:dyDescent="0.15">
+      <c r="I140" s="130"/>
     </row>
-    <row r="141" spans="1:37" x14ac:dyDescent="0.55000000000000004">
-      <c r="I141" s="129"/>
+    <row r="141" spans="1:37" x14ac:dyDescent="0.15">
+      <c r="I141" s="130"/>
     </row>
-    <row r="142" spans="1:37" x14ac:dyDescent="0.55000000000000004">
-      <c r="I142" s="129"/>
+    <row r="142" spans="1:37" x14ac:dyDescent="0.15">
+      <c r="I142" s="130"/>
     </row>
   </sheetData>
   <autoFilter ref="A3:AK137" xr:uid="{00000000-0001-0000-0100-000000000000}"/>
@@ -29244,17 +29312,13 @@
   </mergeCells>
   <phoneticPr fontId="4"/>
   <dataValidations count="1">
-    <dataValidation imeMode="halfAlpha" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="E121:G122 E120:F120 E4:G119" xr:uid="{26D226A7-D063-415E-AD4E-D503C49EA81A}"/>
+    <dataValidation imeMode="halfAlpha" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="E121:G122 E120:F120 E4:G119" xr:uid="{6322E221-FAAE-4936-BC01-0D19C3CC7D8F}"/>
   </dataValidations>
   <printOptions horizontalCentered="1"/>
   <pageMargins left="0.23622047244094491" right="0.23622047244094491" top="0.15748031496062992" bottom="0.15748031496062992" header="0" footer="0"/>
-  <pageSetup paperSize="9" scale="31" fitToHeight="0" orientation="landscape" horizontalDpi="4294967293" r:id="rId1"/>
+  <pageSetup paperSize="9" scale="13" orientation="portrait" horizontalDpi="4294967293" r:id="rId1"/>
   <headerFooter>
     <oddFooter>&amp;P / &amp;N ページ</oddFooter>
   </headerFooter>
-  <rowBreaks count="2" manualBreakCount="2">
-    <brk id="52" max="16383" man="1"/>
-    <brk id="96" max="16383" man="1"/>
-  </rowBreaks>
 </worksheet>
 </file>